--- a/data/ILP.MI.xlsx
+++ b/data/ILP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="457">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">ILP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99759578704834</t>
+    <t xml:space="preserve">1.99759566783905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93599545955658</t>
+    <t xml:space="preserve">1.93599569797516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96195566654205</t>
+    <t xml:space="preserve">1.96195578575134</t>
   </si>
   <si>
     <t xml:space="preserve">2.02839541435242</t>
@@ -59,247 +59,247 @@
     <t xml:space="preserve">2.00111556053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95359551906586</t>
+    <t xml:space="preserve">1.95359575748444</t>
   </si>
   <si>
     <t xml:space="preserve">1.97955560684204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94171571731567</t>
+    <t xml:space="preserve">1.94171595573425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96283566951752</t>
+    <t xml:space="preserve">1.96283555030823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97515535354614</t>
+    <t xml:space="preserve">1.97515559196472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95139539241791</t>
+    <t xml:space="preserve">1.95139575004578</t>
   </si>
   <si>
     <t xml:space="preserve">1.90959572792053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88803565502167</t>
+    <t xml:space="preserve">1.88803613185883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9109160900116</t>
+    <t xml:space="preserve">1.91091549396515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9403954744339</t>
+    <t xml:space="preserve">1.94039559364319</t>
   </si>
   <si>
     <t xml:space="preserve">1.96239566802979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95887565612793</t>
+    <t xml:space="preserve">1.95887553691864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93775570392609</t>
+    <t xml:space="preserve">1.9377555847168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99671566486359</t>
+    <t xml:space="preserve">1.99671578407288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95535588264465</t>
+    <t xml:space="preserve">1.95535564422607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98879563808441</t>
+    <t xml:space="preserve">1.98879539966583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04951524734497</t>
+    <t xml:space="preserve">2.04951548576355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03719568252563</t>
+    <t xml:space="preserve">2.03719544410706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0239953994751</t>
+    <t xml:space="preserve">2.02399563789368</t>
   </si>
   <si>
     <t xml:space="preserve">2.04159545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91839575767517</t>
+    <t xml:space="preserve">1.91839587688446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0063955783844</t>
+    <t xml:space="preserve">2.00639533996582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90079569816589</t>
+    <t xml:space="preserve">1.90079593658447</t>
   </si>
   <si>
     <t xml:space="preserve">1.86559581756592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8831958770752</t>
+    <t xml:space="preserve">1.88319599628448</t>
   </si>
   <si>
     <t xml:space="preserve">1.91022717952728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92824852466583</t>
+    <t xml:space="preserve">1.92824840545654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8922061920166</t>
+    <t xml:space="preserve">1.89220654964447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94626927375793</t>
+    <t xml:space="preserve">1.94626951217651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96429038047791</t>
+    <t xml:space="preserve">1.96429049968719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98231112957001</t>
+    <t xml:space="preserve">1.9823112487793</t>
   </si>
   <si>
     <t xml:space="preserve">2.00033235549927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85616433620453</t>
+    <t xml:space="preserve">1.85616421699524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83814322948456</t>
+    <t xml:space="preserve">1.83814346790314</t>
   </si>
   <si>
     <t xml:space="preserve">1.78408026695251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87418532371521</t>
+    <t xml:space="preserve">1.87418508529663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82012224197388</t>
+    <t xml:space="preserve">1.82012212276459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80210137367249</t>
+    <t xml:space="preserve">1.8021012544632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95527970790863</t>
+    <t xml:space="preserve">1.95527982711792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97330093383789</t>
+    <t xml:space="preserve">1.97330105304718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90121686458588</t>
+    <t xml:space="preserve">1.90121650695801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91923797130585</t>
+    <t xml:space="preserve">1.91923785209656</t>
   </si>
   <si>
     <t xml:space="preserve">1.84715378284454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86517477035522</t>
+    <t xml:space="preserve">1.86517465114594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88319563865662</t>
+    <t xml:space="preserve">1.8831958770752</t>
   </si>
   <si>
     <t xml:space="preserve">1.74803829193115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79309093952179</t>
+    <t xml:space="preserve">1.79309070110321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78858554363251</t>
+    <t xml:space="preserve">1.78858542442322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81111168861389</t>
+    <t xml:space="preserve">1.81111180782318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82913279533386</t>
+    <t xml:space="preserve">1.82913303375244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7975959777832</t>
+    <t xml:space="preserve">1.79759609699249</t>
   </si>
   <si>
     <t xml:space="preserve">1.7255117893219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74353289604187</t>
+    <t xml:space="preserve">1.74353313446045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76605939865112</t>
+    <t xml:space="preserve">1.76605916023254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75704884529114</t>
+    <t xml:space="preserve">1.75704872608185</t>
   </si>
   <si>
     <t xml:space="preserve">1.77506983280182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73001718521118</t>
+    <t xml:space="preserve">1.73001730442047</t>
   </si>
   <si>
     <t xml:space="preserve">1.73902750015259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7119961977005</t>
+    <t xml:space="preserve">1.71199607849121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65793299674988</t>
+    <t xml:space="preserve">1.65793311595917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66694355010986</t>
+    <t xml:space="preserve">1.66694366931915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69397509098053</t>
+    <t xml:space="preserve">1.69397521018982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58584904670715</t>
+    <t xml:space="preserve">1.58584916591644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68496465682983</t>
+    <t xml:space="preserve">1.68496477603912</t>
   </si>
   <si>
     <t xml:space="preserve">1.64892268180847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67595422267914</t>
+    <t xml:space="preserve">1.67595410346985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70298564434052</t>
+    <t xml:space="preserve">1.7029857635498</t>
   </si>
   <si>
     <t xml:space="preserve">1.72100675106049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63090169429779</t>
+    <t xml:space="preserve">1.6309015750885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05439567565918</t>
+    <t xml:space="preserve">2.0543954372406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2165846824646</t>
+    <t xml:space="preserve">2.21658420562744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16252160072327</t>
+    <t xml:space="preserve">2.16252136230469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41481614112854</t>
+    <t xml:space="preserve">2.41481566429138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36075258255005</t>
+    <t xml:space="preserve">2.36075282096863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5770046710968</t>
+    <t xml:space="preserve">2.57700443267822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61304664611816</t>
+    <t xml:space="preserve">2.61304688453674</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06357192993164</t>
+    <t xml:space="preserve">3.06357216835022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46003437042236</t>
+    <t xml:space="preserve">3.46003460884094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26180338859558</t>
+    <t xml:space="preserve">3.261803150177</t>
   </si>
   <si>
     <t xml:space="preserve">3.22576117515564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17169809341431</t>
+    <t xml:space="preserve">3.17169833183289</t>
   </si>
   <si>
     <t xml:space="preserve">3.04555130004883</t>
@@ -311,79 +311,79 @@
     <t xml:space="preserve">3.00950884819031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11763548851013</t>
+    <t xml:space="preserve">3.11763525009155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91940426826477</t>
+    <t xml:space="preserve">2.91940402984619</t>
   </si>
   <si>
     <t xml:space="preserve">2.73919367790222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72117280960083</t>
+    <t xml:space="preserve">2.72117304801941</t>
   </si>
   <si>
     <t xml:space="preserve">2.70315170288086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8292989730835</t>
+    <t xml:space="preserve">2.82929921150208</t>
   </si>
   <si>
     <t xml:space="preserve">2.86534094810486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93742489814758</t>
+    <t xml:space="preserve">2.93742561340332</t>
   </si>
   <si>
     <t xml:space="preserve">2.8112781047821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9013831615448</t>
+    <t xml:space="preserve">2.90138292312622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03781151771545</t>
+    <t xml:space="preserve">3.03781127929688</t>
   </si>
   <si>
     <t xml:space="preserve">3.11057353019714</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01962089538574</t>
+    <t xml:space="preserve">3.0196213722229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09238290786743</t>
+    <t xml:space="preserve">3.09238314628601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18333554267883</t>
+    <t xml:space="preserve">3.18333578109741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23790717124939</t>
+    <t xml:space="preserve">3.23790693283081</t>
   </si>
   <si>
     <t xml:space="preserve">3.36524033546448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41981172561646</t>
+    <t xml:space="preserve">3.41981196403503</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40162134170532</t>
+    <t xml:space="preserve">3.4016215801239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38343095779419</t>
+    <t xml:space="preserve">3.38343071937561</t>
   </si>
   <si>
     <t xml:space="preserve">3.31066918373108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34704971313477</t>
+    <t xml:space="preserve">3.34704995155334</t>
   </si>
   <si>
     <t xml:space="preserve">3.32885956764221</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45619297027588</t>
+    <t xml:space="preserve">3.4561927318573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29247856140137</t>
+    <t xml:space="preserve">3.29247832298279</t>
   </si>
   <si>
     <t xml:space="preserve">3.27428793907166</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">3.25609731674194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43800210952759</t>
+    <t xml:space="preserve">3.43800258636475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47438359260559</t>
+    <t xml:space="preserve">3.47438335418701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6926691532135</t>
+    <t xml:space="preserve">3.69266963005066</t>
   </si>
   <si>
     <t xml:space="preserve">3.60171675682068</t>
@@ -407,43 +407,43 @@
     <t xml:space="preserve">3.67447853088379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91095566749573</t>
+    <t xml:space="preserve">3.91095519065857</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03828811645508</t>
+    <t xml:space="preserve">4.03828859329224</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05647897720337</t>
+    <t xml:space="preserve">4.05647850036621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98371696472168</t>
+    <t xml:space="preserve">3.98371744155884</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80181193351746</t>
+    <t xml:space="preserve">3.80181217193604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96552658081055</t>
+    <t xml:space="preserve">3.96552681922913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0200982093811</t>
+    <t xml:space="preserve">4.02009868621826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92914533615112</t>
+    <t xml:space="preserve">3.92914581298828</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89276504516602</t>
+    <t xml:space="preserve">3.89276480674744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94733572006226</t>
+    <t xml:space="preserve">3.94733595848083</t>
   </si>
   <si>
     <t xml:space="preserve">4.22019338607788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20200300216675</t>
+    <t xml:space="preserve">4.20200252532959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29295492172241</t>
+    <t xml:space="preserve">4.29295539855957</t>
   </si>
   <si>
     <t xml:space="preserve">4.40209865570068</t>
@@ -452,13 +452,13 @@
     <t xml:space="preserve">4.43847990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36571788787842</t>
+    <t xml:space="preserve">4.3657169342041</t>
   </si>
   <si>
     <t xml:space="preserve">4.34752655029297</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37498474121094</t>
+    <t xml:space="preserve">4.3749852180481</t>
   </si>
   <si>
     <t xml:space="preserve">4.39329051971436</t>
@@ -467,13 +467,13 @@
     <t xml:space="preserve">4.28345775604248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24684715270996</t>
+    <t xml:space="preserve">4.2468466758728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26515245437622</t>
+    <t xml:space="preserve">4.26515197753906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17362594604492</t>
+    <t xml:space="preserve">4.17362546920776</t>
   </si>
   <si>
     <t xml:space="preserve">4.10040426254272</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">4.13701486587524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48481702804565</t>
+    <t xml:space="preserve">4.48481750488281</t>
   </si>
   <si>
     <t xml:space="preserve">4.33837366104126</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">4.15532064437866</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30176210403442</t>
+    <t xml:space="preserve">4.30176258087158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46651220321655</t>
+    <t xml:space="preserve">4.46651172637939</t>
   </si>
   <si>
     <t xml:space="preserve">4.19193124771118</t>
@@ -506,64 +506,64 @@
     <t xml:space="preserve">4.11870956420898</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06379318237305</t>
+    <t xml:space="preserve">4.06379365921021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99057197570801</t>
+    <t xml:space="preserve">3.99057245254517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97226619720459</t>
+    <t xml:space="preserve">3.97226667404175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93565630912781</t>
+    <t xml:space="preserve">3.93565607070923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02718210220337</t>
+    <t xml:space="preserve">4.02718305587769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08209896087646</t>
+    <t xml:space="preserve">4.08209848403931</t>
   </si>
   <si>
     <t xml:space="preserve">3.95396089553833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91735076904297</t>
+    <t xml:space="preserve">3.91735053062439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78921270370483</t>
+    <t xml:space="preserve">3.78921246528625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86243414878845</t>
+    <t xml:space="preserve">3.86243367195129</t>
   </si>
   <si>
     <t xml:space="preserve">3.88073945045471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66107535362244</t>
+    <t xml:space="preserve">3.66107511520386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77090764045715</t>
+    <t xml:space="preserve">3.77090740203857</t>
   </si>
   <si>
     <t xml:space="preserve">3.69768571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82582330703735</t>
+    <t xml:space="preserve">3.82582378387451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04548835754395</t>
+    <t xml:space="preserve">4.04548788070679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2285418510437</t>
+    <t xml:space="preserve">4.22854232788086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35667943954468</t>
+    <t xml:space="preserve">4.35667991638184</t>
   </si>
   <si>
     <t xml:space="preserve">4.00887727737427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84412860870361</t>
+    <t xml:space="preserve">3.84412884712219</t>
   </si>
   <si>
     <t xml:space="preserve">3.75260186195374</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">3.56954836845398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53293704986572</t>
+    <t xml:space="preserve">3.5329372882843</t>
   </si>
   <si>
     <t xml:space="preserve">3.42310523986816</t>
@@ -584,37 +584,37 @@
     <t xml:space="preserve">3.18513536453247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76411175727844</t>
+    <t xml:space="preserve">2.76411151885986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83733344078064</t>
+    <t xml:space="preserve">2.83733320236206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72750067710876</t>
+    <t xml:space="preserve">2.72750115394592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61766862869263</t>
+    <t xml:space="preserve">2.61766839027405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80072236061096</t>
+    <t xml:space="preserve">2.80072259902954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92886018753052</t>
+    <t xml:space="preserve">2.9288604259491</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13021922111511</t>
+    <t xml:space="preserve">3.13021945953369</t>
   </si>
   <si>
     <t xml:space="preserve">3.16683030128479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36818885803223</t>
+    <t xml:space="preserve">3.36818909645081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4047999382019</t>
+    <t xml:space="preserve">3.40479969978333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44141054153442</t>
+    <t xml:space="preserve">3.441410779953</t>
   </si>
   <si>
     <t xml:space="preserve">3.34988379478455</t>
@@ -629,31 +629,31 @@
     <t xml:space="preserve">3.60615921020508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58785390853882</t>
+    <t xml:space="preserve">3.58785367012024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59700632095337</t>
+    <t xml:space="preserve">3.59700655937195</t>
   </si>
   <si>
     <t xml:space="preserve">3.55124306678772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48717403411865</t>
+    <t xml:space="preserve">3.48717379570007</t>
   </si>
   <si>
     <t xml:space="preserve">3.45971584320068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38649439811707</t>
+    <t xml:space="preserve">3.38649463653564</t>
   </si>
   <si>
     <t xml:space="preserve">3.45056343078613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37734198570251</t>
+    <t xml:space="preserve">3.37734174728394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28581500053406</t>
+    <t xml:space="preserve">3.28581476211548</t>
   </si>
   <si>
     <t xml:space="preserve">3.35903644561768</t>
@@ -662,16 +662,16 @@
     <t xml:space="preserve">3.36844539642334</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38726353645325</t>
+    <t xml:space="preserve">3.38726329803467</t>
   </si>
   <si>
     <t xml:space="preserve">3.45312714576721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52839970588684</t>
+    <t xml:space="preserve">3.52839946746826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40608191490173</t>
+    <t xml:space="preserve">3.40608143806458</t>
   </si>
   <si>
     <t xml:space="preserve">3.57544493675232</t>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">3.63189911842346</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78244423866272</t>
+    <t xml:space="preserve">3.7824444770813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88594436645508</t>
+    <t xml:space="preserve">3.8859441280365</t>
   </si>
   <si>
     <t xml:space="preserve">3.89535307884216</t>
@@ -695,7 +695,7 @@
     <t xml:space="preserve">3.83889865875244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82008099555969</t>
+    <t xml:space="preserve">3.82008075714111</t>
   </si>
   <si>
     <t xml:space="preserve">3.79185366630554</t>
@@ -704,58 +704,55 @@
     <t xml:space="preserve">3.71658110618591</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70717191696167</t>
+    <t xml:space="preserve">3.70717215538025</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69776272773743</t>
+    <t xml:space="preserve">3.69776320457458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41549110412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3590362071991</t>
+    <t xml:space="preserve">3.41549062728882</t>
   </si>
   <si>
     <t xml:space="preserve">3.48135423660278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24612760543823</t>
+    <t xml:space="preserve">3.24612784385681</t>
   </si>
   <si>
     <t xml:space="preserve">3.15203714370728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21790027618408</t>
+    <t xml:space="preserve">3.21790051460266</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37785458564758</t>
+    <t xml:space="preserve">3.377854347229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4719455242157</t>
+    <t xml:space="preserve">3.47194504737854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50017261505127</t>
+    <t xml:space="preserve">3.50017237663269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64130830764771</t>
+    <t xml:space="preserve">3.64130854606628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50958180427551</t>
+    <t xml:space="preserve">3.50958156585693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66012644767761</t>
+    <t xml:space="preserve">3.66012668609619</t>
   </si>
   <si>
     <t xml:space="preserve">3.56603598594666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51899027824402</t>
+    <t xml:space="preserve">3.5189905166626</t>
   </si>
   <si>
     <t xml:space="preserve">3.46253609657288</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68835401535034</t>
+    <t xml:space="preserve">3.68835377693176</t>
   </si>
   <si>
     <t xml:space="preserve">3.76362657546997</t>
@@ -773,13 +770,13 @@
     <t xml:space="preserve">3.74480843544006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72599005699158</t>
+    <t xml:space="preserve">3.72599029541016</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84830808639526</t>
+    <t xml:space="preserve">3.84830832481384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33080959320068</t>
+    <t xml:space="preserve">3.33080911636353</t>
   </si>
   <si>
     <t xml:space="preserve">3.60367202758789</t>
@@ -788,16 +785,16 @@
     <t xml:space="preserve">4.04589891433716</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97062563896179</t>
+    <t xml:space="preserve">3.97062587738037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82948994636536</t>
+    <t xml:space="preserve">3.82948970794678</t>
   </si>
   <si>
     <t xml:space="preserve">4.02708053588867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90476250648499</t>
+    <t xml:space="preserve">3.90476274490356</t>
   </si>
   <si>
     <t xml:space="preserve">3.85771679878235</t>
@@ -809,16 +806,16 @@
     <t xml:space="preserve">4.20585203170776</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27171611785889</t>
+    <t xml:space="preserve">4.27171564102173</t>
   </si>
   <si>
     <t xml:space="preserve">4.43167066574097</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53516960144043</t>
+    <t xml:space="preserve">4.53517007827759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40344285964966</t>
+    <t xml:space="preserve">4.4034423828125</t>
   </si>
   <si>
     <t xml:space="preserve">4.55398797988892</t>
@@ -830,10 +827,10 @@
     <t xml:space="preserve">4.54457855224609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51635217666626</t>
+    <t xml:space="preserve">4.51635122299194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32816982269287</t>
+    <t xml:space="preserve">4.32817029953003</t>
   </si>
   <si>
     <t xml:space="preserve">4.25289726257324</t>
@@ -845,7 +842,7 @@
     <t xml:space="preserve">4.61044216156006</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61985158920288</t>
+    <t xml:space="preserve">4.61985111236572</t>
   </si>
   <si>
     <t xml:space="preserve">4.50694227218628</t>
@@ -854,25 +851,25 @@
     <t xml:space="preserve">4.57280588150024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63866901397705</t>
+    <t xml:space="preserve">4.63866949081421</t>
   </si>
   <si>
     <t xml:space="preserve">4.64807891845703</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48812437057495</t>
+    <t xml:space="preserve">4.48812389373779</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42225980758667</t>
+    <t xml:space="preserve">4.42226028442383</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4598970413208</t>
+    <t xml:space="preserve">4.45989656448364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33757925033569</t>
+    <t xml:space="preserve">4.33757972717285</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37521553039551</t>
+    <t xml:space="preserve">4.37521600723267</t>
   </si>
   <si>
     <t xml:space="preserve">4.28112506866455</t>
@@ -881,7 +878,7 @@
     <t xml:space="preserve">4.38462448120117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19644355773926</t>
+    <t xml:space="preserve">4.1964430809021</t>
   </si>
   <si>
     <t xml:space="preserve">4.17762517929077</t>
@@ -896,7 +893,7 @@
     <t xml:space="preserve">4.24348926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36580657958984</t>
+    <t xml:space="preserve">4.36580610275269</t>
   </si>
   <si>
     <t xml:space="preserve">4.31876134872437</t>
@@ -905,10 +902,10 @@
     <t xml:space="preserve">4.56339693069458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44107866287231</t>
+    <t xml:space="preserve">4.44107913970947</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46930599212646</t>
+    <t xml:space="preserve">4.46930646896362</t>
   </si>
   <si>
     <t xml:space="preserve">4.9303503036499</t>
@@ -917,13 +914,13 @@
     <t xml:space="preserve">4.76098775863647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65748691558838</t>
+    <t xml:space="preserve">4.65748739242554</t>
   </si>
   <si>
     <t xml:space="preserve">4.66689682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3093523979187</t>
+    <t xml:space="preserve">4.30935144424438</t>
   </si>
   <si>
     <t xml:space="preserve">4.15880727767944</t>
@@ -935,25 +932,25 @@
     <t xml:space="preserve">4.22466993331909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12117099761963</t>
+    <t xml:space="preserve">4.12117052078247</t>
   </si>
   <si>
     <t xml:space="preserve">3.99885296821594</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95180749893188</t>
+    <t xml:space="preserve">3.95180773735046</t>
   </si>
   <si>
     <t xml:space="preserve">4.08353424072266</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29994297027588</t>
+    <t xml:space="preserve">4.29994344711304</t>
   </si>
   <si>
     <t xml:space="preserve">4.70453310012817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75157833099365</t>
+    <t xml:space="preserve">4.75157880783081</t>
   </si>
   <si>
     <t xml:space="preserve">4.59162425994873</t>
@@ -962,10 +959,10 @@
     <t xml:space="preserve">4.34698820114136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49753379821777</t>
+    <t xml:space="preserve">4.49753332138062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62926054000854</t>
+    <t xml:space="preserve">4.62926006317139</t>
   </si>
   <si>
     <t xml:space="preserve">4.84566879272461</t>
@@ -974,16 +971,16 @@
     <t xml:space="preserve">4.93975925445557</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66643905639648</t>
+    <t xml:space="preserve">4.66643953323364</t>
   </si>
   <si>
     <t xml:space="preserve">4.64739322662354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57120656967163</t>
+    <t xml:space="preserve">4.57120609283447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62834644317627</t>
+    <t xml:space="preserve">4.62834596633911</t>
   </si>
   <si>
     <t xml:space="preserve">4.609299659729</t>
@@ -995,19 +992,19 @@
     <t xml:space="preserve">4.72357988357544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74262666702271</t>
+    <t xml:space="preserve">4.74262619018555</t>
   </si>
   <si>
     <t xml:space="preserve">4.85690641403198</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95213985443115</t>
+    <t xml:space="preserve">4.95213937759399</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90452289581299</t>
+    <t xml:space="preserve">4.90452337265015</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04737329483032</t>
+    <t xml:space="preserve">5.04737377166748</t>
   </si>
   <si>
     <t xml:space="preserve">4.99975681304932</t>
@@ -1016,10 +1013,10 @@
     <t xml:space="preserve">5.09499025344849</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28545761108398</t>
+    <t xml:space="preserve">5.28545713424683</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66639089584351</t>
+    <t xml:space="preserve">5.66639041900635</t>
   </si>
   <si>
     <t xml:space="preserve">5.57115745544434</t>
@@ -1028,28 +1025,28 @@
     <t xml:space="preserve">5.76162433624268</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71400737762451</t>
+    <t xml:space="preserve">5.71400785446167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.380690574646</t>
+    <t xml:space="preserve">5.38069009780884</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42830657958984</t>
+    <t xml:space="preserve">5.428307056427</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23784017562866</t>
+    <t xml:space="preserve">5.23784065246582</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1902232170105</t>
+    <t xml:space="preserve">5.19022369384766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14260721206665</t>
+    <t xml:space="preserve">5.14260673522949</t>
   </si>
   <si>
     <t xml:space="preserve">4.80929040908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76167297363281</t>
+    <t xml:space="preserve">4.76167345046997</t>
   </si>
   <si>
     <t xml:space="preserve">4.81835985183716</t>
@@ -23738,7 +23735,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G847" t="s">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -23764,7 +23761,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G848" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -23790,7 +23787,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G849" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -23842,7 +23839,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G851" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -23868,7 +23865,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G852" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -23894,7 +23891,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G853" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -23920,7 +23917,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G854" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -23946,7 +23943,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G855" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -23972,7 +23969,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G856" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -23998,7 +23995,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G857" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -24024,7 +24021,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G858" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -24050,7 +24047,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G859" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -24076,7 +24073,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G860" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -24102,7 +24099,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G861" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -24154,7 +24151,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G863" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -24206,7 +24203,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G865" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -24232,7 +24229,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G866" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -24284,7 +24281,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G868" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -24310,7 +24307,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G869" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -24336,7 +24333,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G870" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -24362,7 +24359,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G871" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -24388,7 +24385,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G872" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -24414,7 +24411,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G873" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -24466,7 +24463,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G875" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -24570,7 +24567,7 @@
         <v>4</v>
       </c>
       <c r="G879" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -24596,7 +24593,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G880" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -24674,7 +24671,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G883" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -24778,7 +24775,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G887" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -24804,7 +24801,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G888" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -24908,7 +24905,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G892" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -24960,7 +24957,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G894" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -24986,7 +24983,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G895" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -25012,7 +25009,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G896" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -25038,7 +25035,7 @@
         <v>4</v>
       </c>
       <c r="G897" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -25116,7 +25113,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G900" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -25142,7 +25139,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G901" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -25168,7 +25165,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G902" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -25220,7 +25217,7 @@
         <v>4</v>
       </c>
       <c r="G904" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -25246,7 +25243,7 @@
         <v>4</v>
       </c>
       <c r="G905" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -25298,7 +25295,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G907" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -25324,7 +25321,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G908" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -25350,7 +25347,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G909" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -25376,7 +25373,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G910" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -25402,7 +25399,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G911" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -25454,7 +25451,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G913" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -25480,7 +25477,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G914" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -25610,7 +25607,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G919" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -25688,7 +25685,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G922" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -25714,7 +25711,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G923" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -25740,7 +25737,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G924" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -25766,7 +25763,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G925" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -25792,7 +25789,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G926" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -25818,7 +25815,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G927" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -25844,7 +25841,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G928" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -25870,7 +25867,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G929" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -25896,7 +25893,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G930" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -25922,7 +25919,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G931" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -25948,7 +25945,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G932" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -25974,7 +25971,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G933" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26000,7 +25997,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G934" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26026,7 +26023,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G935" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26052,7 +26049,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G936" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26078,7 +26075,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G937" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -26130,7 +26127,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G939" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26156,7 +26153,7 @@
         <v>4</v>
       </c>
       <c r="G940" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -26182,7 +26179,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G941" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -26208,7 +26205,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G942" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -26234,7 +26231,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G943" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -26260,7 +26257,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G944" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -26286,7 +26283,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G945" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -26312,7 +26309,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G946" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -26338,7 +26335,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G947" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -26416,7 +26413,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G950" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26468,7 +26465,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G952" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26494,7 +26491,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G953" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26520,7 +26517,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G954" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26546,7 +26543,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G955" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26572,7 +26569,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G956" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26598,7 +26595,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G957" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26624,7 +26621,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G958" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -26650,7 +26647,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G959" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -26676,7 +26673,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G960" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -26702,7 +26699,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G961" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -26728,7 +26725,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G962" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -26754,7 +26751,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G963" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -26780,7 +26777,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G964" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -26806,7 +26803,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G965" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -26832,7 +26829,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G966" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -26858,7 +26855,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G967" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -26884,7 +26881,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G968" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -26910,7 +26907,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G969" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -26936,7 +26933,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G970" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -26962,7 +26959,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G971" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -26988,7 +26985,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G972" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27014,7 +27011,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G973" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27040,7 +27037,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G974" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27066,7 +27063,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G975" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -27092,7 +27089,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G976" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27118,7 +27115,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G977" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27144,7 +27141,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G978" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -27170,7 +27167,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G979" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27196,7 +27193,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G980" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27222,7 +27219,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G981" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27248,7 +27245,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G982" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -27274,7 +27271,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G983" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -27300,7 +27297,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G984" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27326,7 +27323,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G985" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -27352,7 +27349,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G986" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -27378,7 +27375,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G987" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -27404,7 +27401,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G988" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -27430,7 +27427,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G989" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -27456,7 +27453,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G990" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -27482,7 +27479,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G991" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -27508,7 +27505,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G992" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -27534,7 +27531,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G993" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -27560,7 +27557,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G994" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -27586,7 +27583,7 @@
         <v>4.5</v>
       </c>
       <c r="G995" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -27612,7 +27609,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G996" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -27638,7 +27635,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G997" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -27664,7 +27661,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G998" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -27690,7 +27687,7 @@
         <v>4.5</v>
       </c>
       <c r="G999" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -27716,7 +27713,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1000" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -27742,7 +27739,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1001" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -27768,7 +27765,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1002" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -27794,7 +27791,7 @@
         <v>4.5</v>
       </c>
       <c r="G1003" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -27820,7 +27817,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1004" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -27846,7 +27843,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1005" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -27872,7 +27869,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1006" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -27898,7 +27895,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1007" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -27924,7 +27921,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1008" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -27950,7 +27947,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1009" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -27976,7 +27973,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1010" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -28002,7 +27999,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1011" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28028,7 +28025,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1012" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28054,7 +28051,7 @@
         <v>4.75</v>
       </c>
       <c r="G1013" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28080,7 +28077,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1014" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28106,7 +28103,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1015" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28132,7 +28129,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1016" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28158,7 +28155,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1017" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -28184,7 +28181,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1018" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -28210,7 +28207,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1019" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -28236,7 +28233,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1020" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28262,7 +28259,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1021" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28288,7 +28285,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1022" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -28314,7 +28311,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1023" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -28340,7 +28337,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1024" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28366,7 +28363,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1025" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28392,7 +28389,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1026" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28418,7 +28415,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1027" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28444,7 +28441,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1028" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28470,7 +28467,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1029" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28496,7 +28493,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1030" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28522,7 +28519,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1031" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28548,7 +28545,7 @@
         <v>4.5</v>
       </c>
       <c r="G1032" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28574,7 +28571,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1033" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28600,7 +28597,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1034" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28626,7 +28623,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1035" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -28652,7 +28649,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1036" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -28678,7 +28675,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1037" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -28704,7 +28701,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1038" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -28730,7 +28727,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1039" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -28756,7 +28753,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1040" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -28782,7 +28779,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1041" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -28808,7 +28805,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1042" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -28834,7 +28831,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1043" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -28860,7 +28857,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1044" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -28886,7 +28883,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1045" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -28912,7 +28909,7 @@
         <v>4.25</v>
       </c>
       <c r="G1046" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -28938,7 +28935,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1047" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -28964,7 +28961,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1048" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -28990,7 +28987,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1049" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29016,7 +29013,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1050" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29042,7 +29039,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1051" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29068,7 +29065,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1052" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -29094,7 +29091,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1053" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29120,7 +29117,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1054" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29146,7 +29143,7 @@
         <v>5</v>
       </c>
       <c r="G1055" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29172,7 +29169,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1056" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29198,7 +29195,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29224,7 +29221,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1058" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29250,7 +29247,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1059" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29276,7 +29273,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1060" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29302,7 +29299,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1061" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29328,7 +29325,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1062" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29354,7 +29351,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1063" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29380,7 +29377,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1064" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29406,7 +29403,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1065" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29432,7 +29429,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1066" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29458,7 +29455,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1067" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29484,7 +29481,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1068" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29510,7 +29507,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1069" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29536,7 +29533,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1070" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29562,7 +29559,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1071" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -29588,7 +29585,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1072" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -29614,7 +29611,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1073" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -29640,7 +29637,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1074" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -29666,7 +29663,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1075" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -29692,7 +29689,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1076" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -29718,7 +29715,7 @@
         <v>5.25</v>
       </c>
       <c r="G1077" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -29744,7 +29741,7 @@
         <v>5.25</v>
       </c>
       <c r="G1078" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -29770,7 +29767,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1079" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -29796,7 +29793,7 @@
         <v>5</v>
       </c>
       <c r="G1080" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -29822,7 +29819,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1081" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -29848,7 +29845,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1082" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -29874,7 +29871,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1083" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -29900,7 +29897,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1084" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -29926,7 +29923,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1085" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -29952,7 +29949,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1086" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -29978,7 +29975,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1087" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30004,7 +30001,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1088" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30030,7 +30027,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1089" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -30056,7 +30053,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1090" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30082,7 +30079,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1091" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30108,7 +30105,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1092" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30134,7 +30131,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1093" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30160,7 +30157,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1094" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -30186,7 +30183,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1095" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -30212,7 +30209,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1096" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -30238,7 +30235,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1097" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -30264,7 +30261,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1098" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -30290,7 +30287,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1099" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -30316,7 +30313,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1100" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -30342,7 +30339,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1101" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -30368,7 +30365,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1102" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -30394,7 +30391,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1103" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -30420,7 +30417,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1104" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -30446,7 +30443,7 @@
         <v>5.25</v>
       </c>
       <c r="G1105" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -30472,7 +30469,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1106" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30498,7 +30495,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1107" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30524,7 +30521,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1108" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -30550,7 +30547,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1109" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -30576,7 +30573,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1110" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -30602,7 +30599,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1111" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -30628,7 +30625,7 @@
         <v>6</v>
       </c>
       <c r="G1112" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -30654,7 +30651,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1113" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -30680,7 +30677,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1114" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -30706,7 +30703,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -30732,7 +30729,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1116" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -30758,7 +30755,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1117" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -30784,7 +30781,7 @@
         <v>5.5</v>
       </c>
       <c r="G1118" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -30810,7 +30807,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1119" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -30836,7 +30833,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1120" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -30862,7 +30859,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1121" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -30888,7 +30885,7 @@
         <v>5.5</v>
       </c>
       <c r="G1122" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -30914,7 +30911,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1123" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -30940,7 +30937,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1124" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -30966,7 +30963,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1125" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -30992,7 +30989,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1126" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31018,7 +31015,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1127" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31044,7 +31041,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1128" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31070,7 +31067,7 @@
         <v>5.5</v>
       </c>
       <c r="G1129" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31096,7 +31093,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1130" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31122,7 +31119,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1131" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31148,7 +31145,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1132" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31174,7 +31171,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1133" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31200,7 +31197,7 @@
         <v>5.5</v>
       </c>
       <c r="G1134" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31226,7 +31223,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1135" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31252,7 +31249,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1136" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31278,7 +31275,7 @@
         <v>5.5</v>
       </c>
       <c r="G1137" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31304,7 +31301,7 @@
         <v>5.5</v>
       </c>
       <c r="G1138" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31330,7 +31327,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1139" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31356,7 +31353,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1140" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31382,7 +31379,7 @@
         <v>5.25</v>
       </c>
       <c r="G1141" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31408,7 +31405,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1142" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31434,7 +31431,7 @@
         <v>5.25</v>
       </c>
       <c r="G1143" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31460,7 +31457,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1144" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31486,7 +31483,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1145" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31512,7 +31509,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1146" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31538,7 +31535,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1147" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31564,7 +31561,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1148" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31590,7 +31587,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1149" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -31616,7 +31613,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1150" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -31642,7 +31639,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1151" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -31668,7 +31665,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1152" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -31694,7 +31691,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1153" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -31720,7 +31717,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1154" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -31746,7 +31743,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1155" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -31772,7 +31769,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1156" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -31798,7 +31795,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1157" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -31824,7 +31821,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1158" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -31850,7 +31847,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1159" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -31876,7 +31873,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1160" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -31902,7 +31899,7 @@
         <v>5.25</v>
       </c>
       <c r="G1161" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -31928,7 +31925,7 @@
         <v>5.25</v>
       </c>
       <c r="G1162" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -31954,7 +31951,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1163" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -31980,7 +31977,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1164" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32006,7 +32003,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1165" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32032,7 +32029,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1166" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -32058,7 +32055,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1167" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -32084,7 +32081,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1168" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -32110,7 +32107,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1169" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -32136,7 +32133,7 @@
         <v>5</v>
       </c>
       <c r="G1170" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -32162,7 +32159,7 @@
         <v>5</v>
       </c>
       <c r="G1171" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -32188,7 +32185,7 @@
         <v>5</v>
       </c>
       <c r="G1172" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -32214,7 +32211,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1173" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -32240,7 +32237,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1174" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -32266,7 +32263,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1175" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -32292,7 +32289,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1176" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -32318,7 +32315,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1177" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -32344,7 +32341,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1178" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -32370,7 +32367,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1179" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -32396,7 +32393,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1180" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -32422,7 +32419,7 @@
         <v>5.25</v>
       </c>
       <c r="G1181" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -32448,7 +32445,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1182" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -32474,7 +32471,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1183" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -32500,7 +32497,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1184" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -32526,7 +32523,7 @@
         <v>5.25</v>
       </c>
       <c r="G1185" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -32552,7 +32549,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1186" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -32578,7 +32575,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1187" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -32604,7 +32601,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1188" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -32630,7 +32627,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1189" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -32656,7 +32653,7 @@
         <v>5</v>
       </c>
       <c r="G1190" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -32682,7 +32679,7 @@
         <v>5</v>
       </c>
       <c r="G1191" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -32708,7 +32705,7 @@
         <v>5</v>
       </c>
       <c r="G1192" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -32734,7 +32731,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1193" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -32760,7 +32757,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1194" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -32786,7 +32783,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1195" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -32812,7 +32809,7 @@
         <v>5</v>
       </c>
       <c r="G1196" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -32838,7 +32835,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1197" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -32864,7 +32861,7 @@
         <v>5</v>
       </c>
       <c r="G1198" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -32890,7 +32887,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1199" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -32916,7 +32913,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1200" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -32942,7 +32939,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1201" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -32968,7 +32965,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1202" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -32994,7 +32991,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1203" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33020,7 +33017,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1204" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -33046,7 +33043,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1205" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -33072,7 +33069,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1206" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -33098,7 +33095,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1207" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -33124,7 +33121,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1208" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -33150,7 +33147,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1209" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -33176,7 +33173,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1210" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -33202,7 +33199,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1211" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -33228,7 +33225,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1212" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -33254,7 +33251,7 @@
         <v>5</v>
       </c>
       <c r="G1213" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -33280,7 +33277,7 @@
         <v>5</v>
       </c>
       <c r="G1214" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -33306,7 +33303,7 @@
         <v>5</v>
       </c>
       <c r="G1215" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -33332,7 +33329,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1216" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -33358,7 +33355,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1217" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -33384,7 +33381,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1218" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -33410,7 +33407,7 @@
         <v>5</v>
       </c>
       <c r="G1219" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -33436,7 +33433,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1220" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -33462,7 +33459,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1221" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -33488,7 +33485,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1222" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -33514,7 +33511,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1223" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -33540,7 +33537,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1224" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -33566,7 +33563,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1225" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -33592,7 +33589,7 @@
         <v>5</v>
       </c>
       <c r="G1226" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -33618,7 +33615,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1227" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -33644,7 +33641,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1228" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -33670,7 +33667,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1229" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -33696,7 +33693,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1230" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -33722,7 +33719,7 @@
         <v>5</v>
       </c>
       <c r="G1231" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -33748,7 +33745,7 @@
         <v>5</v>
       </c>
       <c r="G1232" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -33774,7 +33771,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1233" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -33800,7 +33797,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1234" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -33826,7 +33823,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1235" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -33852,7 +33849,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1236" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -33878,7 +33875,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1237" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -33904,7 +33901,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1238" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -33930,7 +33927,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1239" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -33956,7 +33953,7 @@
         <v>5</v>
       </c>
       <c r="G1240" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -33982,7 +33979,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1241" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34008,7 +34005,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1242" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -34034,7 +34031,7 @@
         <v>5</v>
       </c>
       <c r="G1243" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -34060,7 +34057,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1244" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -34086,7 +34083,7 @@
         <v>5</v>
       </c>
       <c r="G1245" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34112,7 +34109,7 @@
         <v>5</v>
       </c>
       <c r="G1246" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34138,7 +34135,7 @@
         <v>5</v>
       </c>
       <c r="G1247" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -34164,7 +34161,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1248" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -34190,7 +34187,7 @@
         <v>5</v>
       </c>
       <c r="G1249" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -34216,7 +34213,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1250" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -34242,7 +34239,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1251" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -34268,7 +34265,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1252" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -34294,7 +34291,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1253" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -34320,7 +34317,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1254" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -34346,7 +34343,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1255" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -34372,7 +34369,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1256" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -34398,7 +34395,7 @@
         <v>5</v>
       </c>
       <c r="G1257" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -34424,7 +34421,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1258" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -34450,7 +34447,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1259" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -34476,7 +34473,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1260" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -34502,7 +34499,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1261" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -34528,7 +34525,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1262" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -34554,7 +34551,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1263" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -34580,7 +34577,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1264" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -34606,7 +34603,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1265" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -34632,7 +34629,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1266" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -34658,7 +34655,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1267" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -34684,7 +34681,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1268" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -34710,7 +34707,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1269" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -34736,7 +34733,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1270" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -34762,7 +34759,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1271" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -34788,7 +34785,7 @@
         <v>5</v>
       </c>
       <c r="G1272" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -34814,7 +34811,7 @@
         <v>5</v>
       </c>
       <c r="G1273" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -34840,7 +34837,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1274" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -34866,7 +34863,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1275" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -34892,7 +34889,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1276" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -34918,7 +34915,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1277" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -34944,7 +34941,7 @@
         <v>5</v>
       </c>
       <c r="G1278" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -34970,7 +34967,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1279" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -34996,7 +34993,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1280" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -35022,7 +35019,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1281" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -35048,7 +35045,7 @@
         <v>5</v>
       </c>
       <c r="G1282" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -35074,7 +35071,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1283" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -35100,7 +35097,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1284" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -35126,7 +35123,7 @@
         <v>5</v>
       </c>
       <c r="G1285" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -35152,7 +35149,7 @@
         <v>5</v>
       </c>
       <c r="G1286" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -35178,7 +35175,7 @@
         <v>5</v>
       </c>
       <c r="G1287" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -35204,7 +35201,7 @@
         <v>5</v>
       </c>
       <c r="G1288" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -35230,7 +35227,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1289" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -35256,7 +35253,7 @@
         <v>5</v>
       </c>
       <c r="G1290" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35282,7 +35279,7 @@
         <v>5</v>
       </c>
       <c r="G1291" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35308,7 +35305,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1292" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35334,7 +35331,7 @@
         <v>5</v>
       </c>
       <c r="G1293" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35360,7 +35357,7 @@
         <v>5</v>
       </c>
       <c r="G1294" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35386,7 +35383,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1295" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35412,7 +35409,7 @@
         <v>5</v>
       </c>
       <c r="G1296" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35438,7 +35435,7 @@
         <v>5</v>
       </c>
       <c r="G1297" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -35464,7 +35461,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1298" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35490,7 +35487,7 @@
         <v>5</v>
       </c>
       <c r="G1299" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35516,7 +35513,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1300" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35542,7 +35539,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1301" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -35568,7 +35565,7 @@
         <v>5</v>
       </c>
       <c r="G1302" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35594,7 +35591,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1303" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35620,7 +35617,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1304" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -35646,7 +35643,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1305" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -35672,7 +35669,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1306" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -35698,7 +35695,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1307" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -35724,7 +35721,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1308" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -35750,7 +35747,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1309" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -35776,7 +35773,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1310" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -35802,7 +35799,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1311" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -35828,7 +35825,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1312" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -35854,7 +35851,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1313" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -35880,7 +35877,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1314" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -35906,7 +35903,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1315" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -35932,7 +35929,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1316" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -35958,7 +35955,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1317" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -35984,7 +35981,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1318" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36010,7 +36007,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1319" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -36036,7 +36033,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1320" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36062,7 +36059,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1321" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -36088,7 +36085,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1322" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -36114,7 +36111,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1323" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -36140,7 +36137,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1324" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -36166,7 +36163,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1325" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -36192,7 +36189,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1326" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -36218,7 +36215,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1327" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -36244,7 +36241,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1328" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -36270,7 +36267,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1329" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -36296,7 +36293,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1330" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -36322,7 +36319,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1331" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -36348,7 +36345,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1332" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -36374,7 +36371,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1333" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -36400,7 +36397,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1334" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -36426,7 +36423,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1335" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -36452,7 +36449,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1336" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -36478,7 +36475,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1337" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -36504,7 +36501,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1338" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -36530,7 +36527,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1339" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -36556,7 +36553,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1340" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -36582,7 +36579,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1341" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -36608,7 +36605,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1342" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -36634,7 +36631,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1343" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -36660,7 +36657,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1344" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -36686,7 +36683,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1345" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -36712,7 +36709,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1346" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -36738,7 +36735,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1347" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -36764,7 +36761,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1348" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -36790,7 +36787,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1349" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -36816,7 +36813,7 @@
         <v>5.5</v>
       </c>
       <c r="G1350" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -36842,7 +36839,7 @@
         <v>5.5</v>
       </c>
       <c r="G1351" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -36868,7 +36865,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1352" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -36894,7 +36891,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1353" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -36920,7 +36917,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1354" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -36946,7 +36943,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1355" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -36972,7 +36969,7 @@
         <v>5.5</v>
       </c>
       <c r="G1356" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -36998,7 +36995,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1357" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37024,7 +37021,7 @@
         <v>5.5</v>
       </c>
       <c r="G1358" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -37050,7 +37047,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1359" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37076,7 +37073,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1360" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37102,7 +37099,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1361" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -37128,7 +37125,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1362" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37154,7 +37151,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1363" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -37180,7 +37177,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1364" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -37206,7 +37203,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1365" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -37232,7 +37229,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1366" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -37258,7 +37255,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1367" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -37284,7 +37281,7 @@
         <v>5.75</v>
       </c>
       <c r="G1368" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -37310,7 +37307,7 @@
         <v>5.75</v>
       </c>
       <c r="G1369" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -37336,7 +37333,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1370" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -37362,7 +37359,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1371" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -37388,7 +37385,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1372" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -37414,7 +37411,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1373" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -37440,7 +37437,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1374" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -37466,7 +37463,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1375" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -37492,7 +37489,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1376" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -37518,7 +37515,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1377" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -37544,7 +37541,7 @@
         <v>5.5</v>
       </c>
       <c r="G1378" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -37570,7 +37567,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1379" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -37596,7 +37593,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1380" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -37622,7 +37619,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1381" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -37648,7 +37645,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1382" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -37674,7 +37671,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1383" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -37700,7 +37697,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1384" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -37726,7 +37723,7 @@
         <v>5.5</v>
       </c>
       <c r="G1385" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -37752,7 +37749,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1386" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -37778,7 +37775,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1387" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -37804,7 +37801,7 @@
         <v>5.25</v>
       </c>
       <c r="G1388" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -37830,7 +37827,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1389" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -37856,7 +37853,7 @@
         <v>5.25</v>
       </c>
       <c r="G1390" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -37882,7 +37879,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1391" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -37908,7 +37905,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1392" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -37934,7 +37931,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1393" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -37960,7 +37957,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1394" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -37986,7 +37983,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1395" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38012,7 +38009,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1396" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38038,7 +38035,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1397" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38064,7 +38061,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1398" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -38090,7 +38087,7 @@
         <v>5</v>
       </c>
       <c r="G1399" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -38116,7 +38113,7 @@
         <v>5</v>
       </c>
       <c r="G1400" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -38142,7 +38139,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1401" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -38168,7 +38165,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1402" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -38194,7 +38191,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1403" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -38220,7 +38217,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1404" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -38246,7 +38243,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1405" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -38272,7 +38269,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1406" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -38298,7 +38295,7 @@
         <v>5.25</v>
       </c>
       <c r="G1407" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -38324,7 +38321,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1408" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -38350,7 +38347,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1409" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -38376,7 +38373,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1410" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -38402,7 +38399,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1411" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38428,7 +38425,7 @@
         <v>5.25</v>
       </c>
       <c r="G1412" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -38454,7 +38451,7 @@
         <v>5.25</v>
       </c>
       <c r="G1413" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -38480,7 +38477,7 @@
         <v>5.25</v>
       </c>
       <c r="G1414" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -38506,7 +38503,7 @@
         <v>5.25</v>
       </c>
       <c r="G1415" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -38532,7 +38529,7 @@
         <v>5.25</v>
       </c>
       <c r="G1416" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -38558,7 +38555,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1417" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -38584,7 +38581,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1418" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -38610,7 +38607,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1419" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -38636,7 +38633,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1420" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -38662,7 +38659,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1421" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -38688,7 +38685,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1422" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -38714,7 +38711,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1423" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -38740,7 +38737,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1424" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -38766,7 +38763,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1425" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -38792,7 +38789,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1426" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -38818,7 +38815,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1427" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -38844,7 +38841,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1428" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -38870,7 +38867,7 @@
         <v>5.25</v>
       </c>
       <c r="G1429" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -38896,7 +38893,7 @@
         <v>5.25</v>
       </c>
       <c r="G1430" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -38922,7 +38919,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1431" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -38948,7 +38945,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1432" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -38974,7 +38971,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1433" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39000,7 +38997,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1434" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39026,7 +39023,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1435" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -39052,7 +39049,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1436" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -39078,7 +39075,7 @@
         <v>5</v>
       </c>
       <c r="G1437" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39104,7 +39101,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1438" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39130,7 +39127,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1439" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39156,7 +39153,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1440" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -39182,7 +39179,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1441" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -39208,7 +39205,7 @@
         <v>5</v>
       </c>
       <c r="G1442" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39234,7 +39231,7 @@
         <v>5</v>
       </c>
       <c r="G1443" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -39260,7 +39257,7 @@
         <v>5</v>
       </c>
       <c r="G1444" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -39286,7 +39283,7 @@
         <v>5</v>
       </c>
       <c r="G1445" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -39312,7 +39309,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1446" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -39338,7 +39335,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1447" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -39364,7 +39361,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1448" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -39390,7 +39387,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1449" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39416,7 +39413,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1450" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39442,7 +39439,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1451" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39468,7 +39465,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1452" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39494,7 +39491,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1453" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39520,7 +39517,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1454" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39546,7 +39543,7 @@
         <v>5</v>
       </c>
       <c r="G1455" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39572,7 +39569,7 @@
         <v>5</v>
       </c>
       <c r="G1456" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39598,7 +39595,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1457" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39624,7 +39621,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1458" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39650,7 +39647,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1459" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39676,7 +39673,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1460" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -39702,7 +39699,7 @@
         <v>5</v>
       </c>
       <c r="G1461" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -39728,7 +39725,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1462" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -39754,7 +39751,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1463" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -39780,7 +39777,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1464" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -39806,7 +39803,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1465" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -39832,7 +39829,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1466" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -39858,7 +39855,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1467" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -39884,7 +39881,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1468" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -39910,7 +39907,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1469" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -39936,7 +39933,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1470" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -39962,7 +39959,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1471" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -39988,7 +39985,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1472" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40014,7 +40011,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1473" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40040,7 +40037,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1474" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40066,7 +40063,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1475" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -40092,7 +40089,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1476" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -40118,7 +40115,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1477" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -40144,7 +40141,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1478" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -40170,7 +40167,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1479" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -40196,7 +40193,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1480" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -40222,7 +40219,7 @@
         <v>4.5</v>
       </c>
       <c r="G1481" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -40248,7 +40245,7 @@
         <v>4.5</v>
       </c>
       <c r="G1482" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -40274,7 +40271,7 @@
         <v>4.5</v>
       </c>
       <c r="G1483" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -40300,7 +40297,7 @@
         <v>4.5</v>
       </c>
       <c r="G1484" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -40326,7 +40323,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1485" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -40352,7 +40349,7 @@
         <v>4.5</v>
       </c>
       <c r="G1486" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -40378,7 +40375,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1487" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -40404,7 +40401,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1488" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40430,7 +40427,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1489" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40456,7 +40453,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1490" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40482,7 +40479,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1491" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40508,7 +40505,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1492" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -40534,7 +40531,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1493" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40560,7 +40557,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1494" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -40586,7 +40583,7 @@
         <v>4.5</v>
       </c>
       <c r="G1495" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -40612,7 +40609,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1496" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -40638,7 +40635,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1497" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -40664,7 +40661,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1498" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -40690,7 +40687,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1499" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -40716,7 +40713,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1500" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -40742,7 +40739,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1501" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -40768,7 +40765,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1502" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -40794,7 +40791,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1503" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -40820,7 +40817,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1504" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -40846,7 +40843,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1505" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -40872,7 +40869,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1506" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -40898,7 +40895,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1507" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -40924,7 +40921,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1508" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -40950,7 +40947,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1509" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -40976,7 +40973,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1510" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41002,7 +40999,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1511" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41028,7 +41025,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1512" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41054,7 +41051,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1513" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41080,7 +41077,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1514" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41106,7 +41103,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1515" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41132,7 +41129,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1516" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41158,7 +41155,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1517" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -41184,7 +41181,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1518" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -41210,7 +41207,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1519" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41236,7 +41233,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1520" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -41262,7 +41259,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1521" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -41288,7 +41285,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1522" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -41314,7 +41311,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1523" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -41340,7 +41337,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1524" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -41366,7 +41363,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1525" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -41392,7 +41389,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1526" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41418,7 +41415,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1527" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41444,7 +41441,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1528" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41470,7 +41467,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1529" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41496,7 +41493,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1530" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41522,7 +41519,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1531" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41548,7 +41545,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1532" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41574,7 +41571,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1533" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41600,7 +41597,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1534" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41626,7 +41623,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1535" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41652,7 +41649,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1536" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41678,7 +41675,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1537" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -41704,7 +41701,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1538" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -41730,7 +41727,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1539" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -41756,7 +41753,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1540" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -41782,7 +41779,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1541" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -41808,7 +41805,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1542" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -41834,7 +41831,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1543" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -41860,7 +41857,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1544" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -41886,7 +41883,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1545" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -41912,7 +41909,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1546" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -41938,7 +41935,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1547" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -41964,7 +41961,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1548" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -41990,7 +41987,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1549" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42016,7 +42013,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1550" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42042,7 +42039,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1551" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42068,7 +42065,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1552" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42094,7 +42091,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1553" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42120,7 +42117,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1554" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42146,7 +42143,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1555" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42172,7 +42169,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1556" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42198,7 +42195,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1557" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -42224,7 +42221,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1558" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -42250,7 +42247,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1559" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -42276,7 +42273,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1560" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -42302,7 +42299,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1561" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -42328,7 +42325,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1562" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -42354,7 +42351,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1563" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -42380,7 +42377,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1564" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -42406,7 +42403,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1565" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42432,7 +42429,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1566" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42458,7 +42455,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1567" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42484,7 +42481,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1568" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42510,7 +42507,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1569" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42536,7 +42533,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1570" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42562,7 +42559,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1571" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42588,7 +42585,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1572" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42614,7 +42611,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1573" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42640,7 +42637,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1574" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42666,7 +42663,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1575" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -42692,7 +42689,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1576" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -42718,7 +42715,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1577" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -42744,7 +42741,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1578" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -42770,7 +42767,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1579" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -42796,7 +42793,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1580" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -42822,7 +42819,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1581" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -42848,7 +42845,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1582" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -42874,7 +42871,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1583" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -42900,7 +42897,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1584" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -42926,7 +42923,7 @@
         <v>4.5</v>
       </c>
       <c r="G1585" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -42952,7 +42949,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -42978,7 +42975,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1587" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43004,7 +43001,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1588" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43030,7 +43027,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1589" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43056,7 +43053,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1590" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43082,7 +43079,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1591" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43108,7 +43105,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1592" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43134,7 +43131,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1593" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43160,7 +43157,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1594" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43186,7 +43183,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1595" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -43212,7 +43209,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1596" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43238,7 +43235,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1597" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -43264,7 +43261,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1598" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -43290,7 +43287,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1599" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -43316,7 +43313,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1600" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -43342,7 +43339,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1601" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -43368,7 +43365,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1602" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -43394,7 +43391,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1603" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43420,7 +43417,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1604" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43446,7 +43443,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1605" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43472,7 +43469,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1606" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43498,7 +43495,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1607" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43524,7 +43521,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1608" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43550,7 +43547,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1609" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43576,7 +43573,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1610" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43602,7 +43599,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1611" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43628,7 +43625,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1612" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43654,7 +43651,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1613" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43680,7 +43677,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1614" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43706,7 +43703,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1615" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -43732,7 +43729,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1616" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43758,7 +43755,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1617" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43784,7 +43781,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1618" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43810,7 +43807,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1619" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43836,7 +43833,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1620" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -43862,7 +43859,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1621" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -43888,7 +43885,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1622" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -43914,7 +43911,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1623" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -43940,7 +43937,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1624" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -43966,7 +43963,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1625" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -43992,7 +43989,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1626" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44018,7 +44015,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1627" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44044,7 +44041,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1628" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44070,7 +44067,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1629" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44096,7 +44093,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1630" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44122,7 +44119,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1631" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44148,7 +44145,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1632" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44174,7 +44171,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1633" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44200,7 +44197,7 @@
         <v>5.75</v>
       </c>
       <c r="G1634" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44226,7 +44223,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1635" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44252,7 +44249,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1636" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44278,7 +44275,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1637" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44304,7 +44301,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1638" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44330,7 +44327,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1639" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44356,7 +44353,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1640" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44382,7 +44379,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1641" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44408,7 +44405,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1642" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44434,7 +44431,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1643" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44460,7 +44457,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1644" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44486,7 +44483,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1645" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44512,7 +44509,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1646" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44538,7 +44535,7 @@
         <v>5.75</v>
       </c>
       <c r="G1647" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44564,7 +44561,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1648" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44590,7 +44587,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1649" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44616,7 +44613,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1650" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44642,7 +44639,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1651" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44668,7 +44665,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1652" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44694,7 +44691,7 @@
         <v>5.25</v>
       </c>
       <c r="G1653" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44720,7 +44717,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1654" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44746,7 +44743,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1655" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44772,7 +44769,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1656" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44798,7 +44795,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1657" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44824,7 +44821,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1658" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44850,7 +44847,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1659" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -44876,7 +44873,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1660" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44902,7 +44899,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1661" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44928,7 +44925,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1662" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44954,7 +44951,7 @@
         <v>5.5</v>
       </c>
       <c r="G1663" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44980,7 +44977,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1664" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45006,7 +45003,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1665" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45032,7 +45029,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1666" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45058,7 +45055,7 @@
         <v>5.5</v>
       </c>
       <c r="G1667" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45084,7 +45081,7 @@
         <v>5.5</v>
       </c>
       <c r="G1668" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45110,7 +45107,7 @@
         <v>5.5</v>
       </c>
       <c r="G1669" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45136,7 +45133,7 @@
         <v>5.5</v>
       </c>
       <c r="G1670" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45162,7 +45159,7 @@
         <v>5.5</v>
       </c>
       <c r="G1671" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45188,7 +45185,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1672" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45214,7 +45211,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1673" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45240,7 +45237,7 @@
         <v>5.75</v>
       </c>
       <c r="G1674" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45266,7 +45263,7 @@
         <v>5.75</v>
       </c>
       <c r="G1675" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45292,7 +45289,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1676" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45318,7 +45315,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1677" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45344,7 +45341,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1678" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45370,7 +45367,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1679" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45396,7 +45393,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1680" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45422,7 +45419,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1681" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45448,7 +45445,7 @@
         <v>5.75</v>
       </c>
       <c r="G1682" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45474,7 +45471,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1683" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45500,7 +45497,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1684" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45526,7 +45523,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1685" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45552,7 +45549,7 @@
         <v>5.5</v>
       </c>
       <c r="G1686" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45578,7 +45575,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1687" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45604,7 +45601,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1688" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45630,7 +45627,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1689" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45656,7 +45653,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1690" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45682,7 +45679,7 @@
         <v>5.75</v>
       </c>
       <c r="G1691" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45708,7 +45705,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1692" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45716,7 +45713,7 @@
     </row>
     <row r="1693">
       <c r="A1693" s="1" t="n">
-        <v>45940.6088310185</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B1693" t="n">
         <v>6000</v>
@@ -45734,9 +45731,35 @@
         <v>5.75</v>
       </c>
       <c r="G1693" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1693" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" s="1" t="n">
+        <v>45943.6450925926</v>
+      </c>
+      <c r="B1694" t="n">
+        <v>18600</v>
+      </c>
+      <c r="C1694" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="D1694" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="E1694" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="F1694" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="G1694" t="s">
+        <v>444</v>
+      </c>
+      <c r="H1694" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ILP.MI.xlsx
+++ b/data/ILP.MI.xlsx
@@ -38,64 +38,64 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97119569778442</t>
+    <t xml:space="preserve">1.971195936203</t>
   </si>
   <si>
     <t xml:space="preserve">ILP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99759566783905</t>
+    <t xml:space="preserve">1.99759590625763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93599569797516</t>
+    <t xml:space="preserve">1.93599593639374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96195578575134</t>
+    <t xml:space="preserve">1.96195566654205</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02839541435242</t>
+    <t xml:space="preserve">2.028395652771</t>
   </si>
   <si>
     <t xml:space="preserve">2.00111556053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95359575748444</t>
+    <t xml:space="preserve">1.95359551906586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97955560684204</t>
+    <t xml:space="preserve">1.97955584526062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94171595573425</t>
+    <t xml:space="preserve">1.94171607494354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96283555030823</t>
+    <t xml:space="preserve">1.96283566951752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97515559196472</t>
+    <t xml:space="preserve">1.97515547275543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95139575004578</t>
+    <t xml:space="preserve">1.95139563083649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90959572792053</t>
+    <t xml:space="preserve">1.90959584712982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88803613185883</t>
+    <t xml:space="preserve">1.88803589344025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91091549396515</t>
+    <t xml:space="preserve">1.91091561317444</t>
   </si>
   <si>
     <t xml:space="preserve">1.94039559364319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96239566802979</t>
+    <t xml:space="preserve">1.9623955488205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95887553691864</t>
+    <t xml:space="preserve">1.95887565612793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9377555847168</t>
+    <t xml:space="preserve">1.93775570392609</t>
   </si>
   <si>
     <t xml:space="preserve">1.99671578407288</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">1.95535564422607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98879539966583</t>
+    <t xml:space="preserve">1.98879563808441</t>
   </si>
   <si>
     <t xml:space="preserve">2.04951548576355</t>
@@ -113,88 +113,88 @@
     <t xml:space="preserve">2.03719544410706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02399563789368</t>
+    <t xml:space="preserve">2.0239953994751</t>
   </si>
   <si>
     <t xml:space="preserve">2.04159545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91839587688446</t>
+    <t xml:space="preserve">1.91839575767517</t>
   </si>
   <si>
     <t xml:space="preserve">2.00639533996582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90079593658447</t>
+    <t xml:space="preserve">1.90079581737518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86559581756592</t>
+    <t xml:space="preserve">1.86559569835663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88319599628448</t>
+    <t xml:space="preserve">1.8831958770752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91022717952728</t>
+    <t xml:space="preserve">1.91022729873657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92824840545654</t>
+    <t xml:space="preserve">1.92824828624725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89220654964447</t>
+    <t xml:space="preserve">1.89220607280731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94626951217651</t>
+    <t xml:space="preserve">1.94626939296722</t>
   </si>
   <si>
     <t xml:space="preserve">1.96429049968719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9823112487793</t>
+    <t xml:space="preserve">1.98231148719788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00033235549927</t>
+    <t xml:space="preserve">2.00033211708069</t>
   </si>
   <si>
     <t xml:space="preserve">1.85616421699524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83814346790314</t>
+    <t xml:space="preserve">1.83814311027527</t>
   </si>
   <si>
     <t xml:space="preserve">1.78408026695251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87418508529663</t>
+    <t xml:space="preserve">1.8741854429245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82012212276459</t>
+    <t xml:space="preserve">1.82012224197388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8021012544632</t>
+    <t xml:space="preserve">1.80210137367249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95527982711792</t>
+    <t xml:space="preserve">1.95528018474579</t>
   </si>
   <si>
     <t xml:space="preserve">1.97330105304718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90121650695801</t>
+    <t xml:space="preserve">1.9012166261673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91923785209656</t>
+    <t xml:space="preserve">1.91923797130585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84715378284454</t>
+    <t xml:space="preserve">1.84715390205383</t>
   </si>
   <si>
     <t xml:space="preserve">1.86517465114594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8831958770752</t>
+    <t xml:space="preserve">1.88319563865662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74803829193115</t>
+    <t xml:space="preserve">1.74803817272186</t>
   </si>
   <si>
     <t xml:space="preserve">1.79309070110321</t>
@@ -206,49 +206,49 @@
     <t xml:space="preserve">1.81111180782318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82913303375244</t>
+    <t xml:space="preserve">1.82913267612457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79759609699249</t>
+    <t xml:space="preserve">1.79759573936462</t>
   </si>
   <si>
     <t xml:space="preserve">1.7255117893219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74353313446045</t>
+    <t xml:space="preserve">1.74353277683258</t>
   </si>
   <si>
     <t xml:space="preserve">1.76605916023254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75704872608185</t>
+    <t xml:space="preserve">1.75704884529114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77506983280182</t>
+    <t xml:space="preserve">1.77506971359253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73001730442047</t>
+    <t xml:space="preserve">1.73001718521118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73902750015259</t>
+    <t xml:space="preserve">1.73902761936188</t>
   </si>
   <si>
     <t xml:space="preserve">1.71199607849121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65793311595917</t>
+    <t xml:space="preserve">1.65793323516846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66694366931915</t>
+    <t xml:space="preserve">1.66694378852844</t>
   </si>
   <si>
     <t xml:space="preserve">1.69397521018982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58584916591644</t>
+    <t xml:space="preserve">1.58584928512573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68496477603912</t>
+    <t xml:space="preserve">1.68496465682983</t>
   </si>
   <si>
     <t xml:space="preserve">1.64892268180847</t>
@@ -257,49 +257,49 @@
     <t xml:space="preserve">1.67595410346985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7029857635498</t>
+    <t xml:space="preserve">1.70298564434052</t>
   </si>
   <si>
     <t xml:space="preserve">1.72100675106049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6309015750885</t>
+    <t xml:space="preserve">1.63090169429779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0543954372406</t>
+    <t xml:space="preserve">2.05439519882202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21658420562744</t>
+    <t xml:space="preserve">2.21658444404602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16252136230469</t>
+    <t xml:space="preserve">2.16252160072327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41481566429138</t>
+    <t xml:space="preserve">2.41481590270996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36075282096863</t>
+    <t xml:space="preserve">2.36075258255005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57700443267822</t>
+    <t xml:space="preserve">2.57700490951538</t>
   </si>
   <si>
     <t xml:space="preserve">2.61304688453674</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06357216835022</t>
+    <t xml:space="preserve">3.0635724067688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46003460884094</t>
+    <t xml:space="preserve">3.46003437042236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.261803150177</t>
+    <t xml:space="preserve">3.26180338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22576117515564</t>
+    <t xml:space="preserve">3.22576141357422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17169833183289</t>
+    <t xml:space="preserve">3.17169857025146</t>
   </si>
   <si>
     <t xml:space="preserve">3.04555130004883</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">3.02753019332886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00950884819031</t>
+    <t xml:space="preserve">3.00950932502747</t>
   </si>
   <si>
     <t xml:space="preserve">3.11763525009155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91940402984619</t>
+    <t xml:space="preserve">2.91940379142761</t>
   </si>
   <si>
     <t xml:space="preserve">2.73919367790222</t>
@@ -323,55 +323,55 @@
     <t xml:space="preserve">2.72117304801941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70315170288086</t>
+    <t xml:space="preserve">2.70315194129944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82929921150208</t>
+    <t xml:space="preserve">2.8292989730835</t>
   </si>
   <si>
     <t xml:space="preserve">2.86534094810486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93742561340332</t>
+    <t xml:space="preserve">2.93742513656616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8112781047821</t>
+    <t xml:space="preserve">2.81127762794495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90138292312622</t>
+    <t xml:space="preserve">2.9013831615448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03781127929688</t>
+    <t xml:space="preserve">3.03781151771545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11057353019714</t>
+    <t xml:space="preserve">3.11057376861572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0196213722229</t>
+    <t xml:space="preserve">3.01962113380432</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09238314628601</t>
+    <t xml:space="preserve">3.09238338470459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18333578109741</t>
+    <t xml:space="preserve">3.18333530426025</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23790693283081</t>
+    <t xml:space="preserve">3.23790717124939</t>
   </si>
   <si>
     <t xml:space="preserve">3.36524033546448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41981196403503</t>
+    <t xml:space="preserve">3.41981172561646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4016215801239</t>
+    <t xml:space="preserve">3.40162134170532</t>
   </si>
   <si>
     <t xml:space="preserve">3.38343071937561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31066918373108</t>
+    <t xml:space="preserve">3.3106689453125</t>
   </si>
   <si>
     <t xml:space="preserve">3.34704995155334</t>
@@ -380,25 +380,25 @@
     <t xml:space="preserve">3.32885956764221</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4561927318573</t>
+    <t xml:space="preserve">3.45619249343872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29247832298279</t>
+    <t xml:space="preserve">3.29247856140137</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27428793907166</t>
+    <t xml:space="preserve">3.27428770065308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25609731674194</t>
+    <t xml:space="preserve">3.25609755516052</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43800258636475</t>
+    <t xml:space="preserve">3.43800210952759</t>
   </si>
   <si>
     <t xml:space="preserve">3.47438335418701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69266963005066</t>
+    <t xml:space="preserve">3.69266891479492</t>
   </si>
   <si>
     <t xml:space="preserve">3.60171675682068</t>
@@ -407,58 +407,58 @@
     <t xml:space="preserve">3.67447853088379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91095519065857</t>
+    <t xml:space="preserve">3.91095495223999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03828859329224</t>
+    <t xml:space="preserve">4.03828811645508</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05647850036621</t>
+    <t xml:space="preserve">4.05647897720337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98371744155884</t>
+    <t xml:space="preserve">3.98371696472168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80181217193604</t>
+    <t xml:space="preserve">3.80181193351746</t>
   </si>
   <si>
     <t xml:space="preserve">3.96552681922913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02009868621826</t>
+    <t xml:space="preserve">4.0200982093811</t>
   </si>
   <si>
     <t xml:space="preserve">3.92914581298828</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89276480674744</t>
+    <t xml:space="preserve">3.89276456832886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94733595848083</t>
+    <t xml:space="preserve">3.94733643531799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22019338607788</t>
+    <t xml:space="preserve">4.22019290924072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20200252532959</t>
+    <t xml:space="preserve">4.20200300216675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29295539855957</t>
+    <t xml:space="preserve">4.29295492172241</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40209865570068</t>
+    <t xml:space="preserve">4.40209817886353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43847990036011</t>
+    <t xml:space="preserve">4.43847942352295</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3657169342041</t>
+    <t xml:space="preserve">4.36571788787842</t>
   </si>
   <si>
     <t xml:space="preserve">4.34752655029297</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3749852180481</t>
+    <t xml:space="preserve">4.37498474121094</t>
   </si>
   <si>
     <t xml:space="preserve">4.39329051971436</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">4.28345775604248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2468466758728</t>
+    <t xml:space="preserve">4.24684715270996</t>
   </si>
   <si>
     <t xml:space="preserve">4.26515197753906</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">4.17362546920776</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10040426254272</t>
+    <t xml:space="preserve">4.10040378570557</t>
   </si>
   <si>
     <t xml:space="preserve">4.21023607254028</t>
@@ -485,31 +485,31 @@
     <t xml:space="preserve">4.13701486587524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48481750488281</t>
+    <t xml:space="preserve">4.4848165512085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33837366104126</t>
+    <t xml:space="preserve">4.33837413787842</t>
   </si>
   <si>
     <t xml:space="preserve">4.15532064437866</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30176258087158</t>
+    <t xml:space="preserve">4.3017635345459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46651172637939</t>
+    <t xml:space="preserve">4.46651124954224</t>
   </si>
   <si>
     <t xml:space="preserve">4.19193124771118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11870956420898</t>
+    <t xml:space="preserve">4.11870908737183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06379365921021</t>
+    <t xml:space="preserve">4.06379270553589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99057245254517</t>
+    <t xml:space="preserve">3.99057269096375</t>
   </si>
   <si>
     <t xml:space="preserve">3.97226667404175</t>
@@ -518,73 +518,73 @@
     <t xml:space="preserve">3.93565607070923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02718305587769</t>
+    <t xml:space="preserve">4.02718210220337</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08209848403931</t>
+    <t xml:space="preserve">4.08209896087646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95396089553833</t>
+    <t xml:space="preserve">3.95396113395691</t>
   </si>
   <si>
     <t xml:space="preserve">3.91735053062439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78921246528625</t>
+    <t xml:space="preserve">3.78921270370483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86243367195129</t>
+    <t xml:space="preserve">3.86243343353271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88073945045471</t>
+    <t xml:space="preserve">3.88073897361755</t>
   </si>
   <si>
     <t xml:space="preserve">3.66107511520386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77090740203857</t>
+    <t xml:space="preserve">3.77090716362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69768571853638</t>
+    <t xml:space="preserve">3.69768595695496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82582378387451</t>
+    <t xml:space="preserve">3.82582306861877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04548788070679</t>
+    <t xml:space="preserve">4.04548835754395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22854232788086</t>
+    <t xml:space="preserve">4.2285418510437</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35667991638184</t>
+    <t xml:space="preserve">4.35668039321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00887727737427</t>
+    <t xml:space="preserve">4.00887775421143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84412884712219</t>
+    <t xml:space="preserve">3.84412860870361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75260186195374</t>
+    <t xml:space="preserve">3.75260210037231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47802138328552</t>
+    <t xml:space="preserve">3.47802114486694</t>
   </si>
   <si>
     <t xml:space="preserve">3.56954836845398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5329372882843</t>
+    <t xml:space="preserve">3.53293752670288</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42310523986816</t>
+    <t xml:space="preserve">3.42310571670532</t>
   </si>
   <si>
     <t xml:space="preserve">3.18513536453247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76411151885986</t>
+    <t xml:space="preserve">2.76411175727844</t>
   </si>
   <si>
     <t xml:space="preserve">2.83733320236206</t>
@@ -593,37 +593,37 @@
     <t xml:space="preserve">2.72750115394592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61766839027405</t>
+    <t xml:space="preserve">2.61766886711121</t>
   </si>
   <si>
     <t xml:space="preserve">2.80072259902954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9288604259491</t>
+    <t xml:space="preserve">2.92886018753052</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13021945953369</t>
+    <t xml:space="preserve">3.13021898269653</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16683030128479</t>
+    <t xml:space="preserve">3.16683006286621</t>
   </si>
   <si>
     <t xml:space="preserve">3.36818909645081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40479969978333</t>
+    <t xml:space="preserve">3.4047999382019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.441410779953</t>
+    <t xml:space="preserve">3.44141054153442</t>
   </si>
   <si>
     <t xml:space="preserve">3.34988379478455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22174596786499</t>
+    <t xml:space="preserve">3.22174620628357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25835704803467</t>
+    <t xml:space="preserve">3.25835680961609</t>
   </si>
   <si>
     <t xml:space="preserve">3.60615921020508</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">3.59700655937195</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55124306678772</t>
+    <t xml:space="preserve">3.55124258995056</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48717379570007</t>
+    <t xml:space="preserve">3.48717403411865</t>
   </si>
   <si>
     <t xml:space="preserve">3.45971584320068</t>
@@ -647,34 +647,34 @@
     <t xml:space="preserve">3.38649463653564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45056343078613</t>
+    <t xml:space="preserve">3.45056319236755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37734174728394</t>
+    <t xml:space="preserve">3.37734198570251</t>
   </si>
   <si>
     <t xml:space="preserve">3.28581476211548</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35903644561768</t>
+    <t xml:space="preserve">3.3590362071991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36844539642334</t>
+    <t xml:space="preserve">3.36844515800476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38726329803467</t>
+    <t xml:space="preserve">3.38726353645325</t>
   </si>
   <si>
     <t xml:space="preserve">3.45312714576721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52839946746826</t>
+    <t xml:space="preserve">3.52839970588684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40608143806458</t>
+    <t xml:space="preserve">3.40608167648315</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57544493675232</t>
+    <t xml:space="preserve">3.5754451751709</t>
   </si>
   <si>
     <t xml:space="preserve">3.66953587532043</t>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">3.63189911842346</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7824444770813</t>
+    <t xml:space="preserve">3.78244423866272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8859441280365</t>
+    <t xml:space="preserve">3.88594436645508</t>
   </si>
   <si>
     <t xml:space="preserve">3.89535307884216</t>
@@ -695,7 +695,7 @@
     <t xml:space="preserve">3.83889865875244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82008075714111</t>
+    <t xml:space="preserve">3.82008028030396</t>
   </si>
   <si>
     <t xml:space="preserve">3.79185366630554</t>
@@ -704,16 +704,16 @@
     <t xml:space="preserve">3.71658110618591</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70717215538025</t>
+    <t xml:space="preserve">3.70717191696167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69776320457458</t>
+    <t xml:space="preserve">3.69776296615601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41549062728882</t>
+    <t xml:space="preserve">3.41549110412598</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48135423660278</t>
+    <t xml:space="preserve">3.48135447502136</t>
   </si>
   <si>
     <t xml:space="preserve">3.24612784385681</t>
@@ -722,19 +722,19 @@
     <t xml:space="preserve">3.15203714370728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21790051460266</t>
+    <t xml:space="preserve">3.21790027618408</t>
   </si>
   <si>
     <t xml:space="preserve">3.377854347229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47194504737854</t>
+    <t xml:space="preserve">3.47194528579712</t>
   </si>
   <si>
     <t xml:space="preserve">3.50017237663269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64130854606628</t>
+    <t xml:space="preserve">3.64130830764771</t>
   </si>
   <si>
     <t xml:space="preserve">3.50958156585693</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">3.56603598594666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5189905166626</t>
+    <t xml:space="preserve">3.51899075508118</t>
   </si>
   <si>
     <t xml:space="preserve">3.46253609657288</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">3.68835377693176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76362657546997</t>
+    <t xml:space="preserve">3.76362633705139</t>
   </si>
   <si>
     <t xml:space="preserve">3.55662679672241</t>
@@ -764,16 +764,16 @@
     <t xml:space="preserve">3.81067180633545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6224901676178</t>
+    <t xml:space="preserve">3.62249040603638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74480843544006</t>
+    <t xml:space="preserve">3.74480819702148</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72599029541016</t>
+    <t xml:space="preserve">3.725989818573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84830832481384</t>
+    <t xml:space="preserve">3.84830808639526</t>
   </si>
   <si>
     <t xml:space="preserve">3.33080911636353</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">4.04589891433716</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97062587738037</t>
+    <t xml:space="preserve">3.97062516212463</t>
   </si>
   <si>
     <t xml:space="preserve">3.82948970794678</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">3.90476274490356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85771679878235</t>
+    <t xml:space="preserve">3.85771703720093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13057994842529</t>
+    <t xml:space="preserve">4.13057947158813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20585203170776</t>
+    <t xml:space="preserve">4.20585298538208</t>
   </si>
   <si>
     <t xml:space="preserve">4.27171564102173</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43167066574097</t>
+    <t xml:space="preserve">4.43166971206665</t>
   </si>
   <si>
     <t xml:space="preserve">4.53517007827759</t>
@@ -821,25 +821,25 @@
     <t xml:space="preserve">4.55398797988892</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68571472167969</t>
+    <t xml:space="preserve">4.68571424484253</t>
   </si>
   <si>
     <t xml:space="preserve">4.54457855224609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51635122299194</t>
+    <t xml:space="preserve">4.51635217666626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32817029953003</t>
+    <t xml:space="preserve">4.32816982269287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25289726257324</t>
+    <t xml:space="preserve">4.2528977394104</t>
   </si>
   <si>
     <t xml:space="preserve">4.47871541976929</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61044216156006</t>
+    <t xml:space="preserve">4.61044263839722</t>
   </si>
   <si>
     <t xml:space="preserve">4.61985111236572</t>
@@ -848,25 +848,25 @@
     <t xml:space="preserve">4.50694227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57280588150024</t>
+    <t xml:space="preserve">4.5728063583374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63866949081421</t>
+    <t xml:space="preserve">4.63866901397705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64807891845703</t>
+    <t xml:space="preserve">4.64807844161987</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48812389373779</t>
+    <t xml:space="preserve">4.48812437057495</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42226028442383</t>
+    <t xml:space="preserve">4.42226076126099</t>
   </si>
   <si>
     <t xml:space="preserve">4.45989656448364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33757972717285</t>
+    <t xml:space="preserve">4.33757925033569</t>
   </si>
   <si>
     <t xml:space="preserve">4.37521600723267</t>
@@ -875,25 +875,25 @@
     <t xml:space="preserve">4.28112506866455</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38462448120117</t>
+    <t xml:space="preserve">4.38462400436401</t>
   </si>
   <si>
     <t xml:space="preserve">4.1964430809021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17762517929077</t>
+    <t xml:space="preserve">4.17762470245361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23407983779907</t>
+    <t xml:space="preserve">4.23407936096191</t>
   </si>
   <si>
     <t xml:space="preserve">4.39403390884399</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24348926544189</t>
+    <t xml:space="preserve">4.24348878860474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36580610275269</t>
+    <t xml:space="preserve">4.36580657958984</t>
   </si>
   <si>
     <t xml:space="preserve">4.31876134872437</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">4.56339693069458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44107913970947</t>
+    <t xml:space="preserve">4.44107866287231</t>
   </si>
   <si>
     <t xml:space="preserve">4.46930646896362</t>
@@ -911,16 +911,16 @@
     <t xml:space="preserve">4.9303503036499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76098775863647</t>
+    <t xml:space="preserve">4.76098728179932</t>
   </si>
   <si>
     <t xml:space="preserve">4.65748739242554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66689682006836</t>
+    <t xml:space="preserve">4.6668963432312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30935144424438</t>
+    <t xml:space="preserve">4.30935192108154</t>
   </si>
   <si>
     <t xml:space="preserve">4.15880727767944</t>
@@ -929,19 +929,19 @@
     <t xml:space="preserve">4.14939785003662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22466993331909</t>
+    <t xml:space="preserve">4.22467088699341</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12117052078247</t>
+    <t xml:space="preserve">4.12117099761963</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99885296821594</t>
+    <t xml:space="preserve">3.99885272979736</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95180773735046</t>
+    <t xml:space="preserve">3.95180749893188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08353424072266</t>
+    <t xml:space="preserve">4.08353471755981</t>
   </si>
   <si>
     <t xml:space="preserve">4.29994344711304</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">4.70453310012817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75157880783081</t>
+    <t xml:space="preserve">4.75157833099365</t>
   </si>
   <si>
     <t xml:space="preserve">4.59162425994873</t>
@@ -959,55 +959,55 @@
     <t xml:space="preserve">4.34698820114136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49753332138062</t>
+    <t xml:space="preserve">4.49753379821777</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62926006317139</t>
+    <t xml:space="preserve">4.6292610168457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84566879272461</t>
+    <t xml:space="preserve">4.84566831588745</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93975925445557</t>
+    <t xml:space="preserve">4.93976020812988</t>
   </si>
   <si>
     <t xml:space="preserve">4.66643953323364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64739322662354</t>
+    <t xml:space="preserve">4.64739274978638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57120609283447</t>
+    <t xml:space="preserve">4.57120656967163</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62834596633911</t>
+    <t xml:space="preserve">4.62834644317627</t>
   </si>
   <si>
     <t xml:space="preserve">4.609299659729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49501943588257</t>
+    <t xml:space="preserve">4.49501895904541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72357988357544</t>
+    <t xml:space="preserve">4.72357940673828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74262619018555</t>
+    <t xml:space="preserve">4.74262571334839</t>
   </si>
   <si>
     <t xml:space="preserve">4.85690641403198</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95213937759399</t>
+    <t xml:space="preserve">4.95213985443115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90452337265015</t>
+    <t xml:space="preserve">4.90452289581299</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04737377166748</t>
+    <t xml:space="preserve">5.04737329483032</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99975681304932</t>
+    <t xml:space="preserve">4.99975728988647</t>
   </si>
   <si>
     <t xml:space="preserve">5.09499025344849</t>
@@ -1016,52 +1016,52 @@
     <t xml:space="preserve">5.28545713424683</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66639041900635</t>
+    <t xml:space="preserve">5.66639137268066</t>
   </si>
   <si>
     <t xml:space="preserve">5.57115745544434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76162433624268</t>
+    <t xml:space="preserve">5.76162481307983</t>
   </si>
   <si>
     <t xml:space="preserve">5.71400785446167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38069009780884</t>
+    <t xml:space="preserve">5.38069105148315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.428307056427</t>
+    <t xml:space="preserve">5.42830657958984</t>
   </si>
   <si>
     <t xml:space="preserve">5.23784065246582</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19022369384766</t>
+    <t xml:space="preserve">5.1902232170105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14260673522949</t>
+    <t xml:space="preserve">5.14260721206665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80929040908813</t>
+    <t xml:space="preserve">4.80928993225098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76167345046997</t>
+    <t xml:space="preserve">4.76167297363281</t>
   </si>
   <si>
     <t xml:space="preserve">4.81835985183716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74126577377319</t>
+    <t xml:space="preserve">4.74126625061035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76053953170776</t>
+    <t xml:space="preserve">4.76053905487061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86654376983643</t>
+    <t xml:space="preserve">4.86654329299927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79908609390259</t>
+    <t xml:space="preserve">4.79908561706543</t>
   </si>
   <si>
     <t xml:space="preserve">4.72199249267578</t>
@@ -1082,16 +1082,16 @@
     <t xml:space="preserve">4.91472673416138</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96291065216064</t>
+    <t xml:space="preserve">4.96291017532349</t>
   </si>
   <si>
     <t xml:space="preserve">5.0110936164856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6834454536438</t>
+    <t xml:space="preserve">4.68344593048096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66417217254639</t>
+    <t xml:space="preserve">4.66417264938354</t>
   </si>
   <si>
     <t xml:space="preserve">4.64489889144897</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">4.60635185241699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79979991912842</t>
+    <t xml:space="preserve">4.79980039596558</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76077747344971</t>
+    <t xml:space="preserve">4.76077699661255</t>
   </si>
   <si>
     <t xml:space="preserve">4.83882284164429</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">5.31685161590576</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56074380874634</t>
+    <t xml:space="preserve">5.56074333190918</t>
   </si>
   <si>
     <t xml:space="preserve">5.80463600158691</t>
@@ -1145,10 +1145,10 @@
     <t xml:space="preserve">5.60952234268188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26807308197021</t>
+    <t xml:space="preserve">5.26807355880737</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12173748016357</t>
+    <t xml:space="preserve">5.12173795700073</t>
   </si>
   <si>
     <t xml:space="preserve">4.97540235519409</t>
@@ -1157,10 +1157,10 @@
     <t xml:space="preserve">5.17051649093628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9266242980957</t>
+    <t xml:space="preserve">4.92662382125854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87784576416016</t>
+    <t xml:space="preserve">4.877845287323</t>
   </si>
   <si>
     <t xml:space="preserve">5.02418088912964</t>
@@ -45739,7 +45739,7 @@
     </row>
     <row r="1694">
       <c r="A1694" s="1" t="n">
-        <v>45943.6450925926</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B1694" t="n">
         <v>18600</v>
@@ -45760,6 +45760,32 @@
         <v>444</v>
       </c>
       <c r="H1694" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" s="1" t="n">
+        <v>45944.357025463</v>
+      </c>
+      <c r="B1695" t="n">
+        <v>4800</v>
+      </c>
+      <c r="C1695" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="D1695" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="E1695" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="F1695" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="G1695" t="s">
+        <v>448</v>
+      </c>
+      <c r="H1695" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ILP.MI.xlsx
+++ b/data/ILP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="458">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,193 +38,193 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.971195936203</t>
+    <t xml:space="preserve">1.97119557857513</t>
   </si>
   <si>
     <t xml:space="preserve">ILP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99759590625763</t>
+    <t xml:space="preserve">1.99759566783905</t>
   </si>
   <si>
     <t xml:space="preserve">1.93599593639374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96195566654205</t>
+    <t xml:space="preserve">1.96195578575134</t>
   </si>
   <si>
     <t xml:space="preserve">2.028395652771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00111556053162</t>
+    <t xml:space="preserve">2.00111532211304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95359551906586</t>
+    <t xml:space="preserve">1.95359563827515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97955584526062</t>
+    <t xml:space="preserve">1.9795560836792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94171607494354</t>
+    <t xml:space="preserve">1.94171571731567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96283566951752</t>
+    <t xml:space="preserve">1.96283578872681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97515547275543</t>
+    <t xml:space="preserve">1.97515523433685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95139563083649</t>
+    <t xml:space="preserve">1.9513955116272</t>
   </si>
   <si>
     <t xml:space="preserve">1.90959584712982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88803589344025</t>
+    <t xml:space="preserve">1.88803577423096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91091561317444</t>
+    <t xml:space="preserve">1.91091585159302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94039559364319</t>
+    <t xml:space="preserve">1.9403954744339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9623955488205</t>
+    <t xml:space="preserve">1.96239542961121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95887565612793</t>
+    <t xml:space="preserve">1.95887577533722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93775570392609</t>
+    <t xml:space="preserve">1.93775582313538</t>
   </si>
   <si>
     <t xml:space="preserve">1.99671578407288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95535564422607</t>
+    <t xml:space="preserve">1.95535552501678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98879563808441</t>
+    <t xml:space="preserve">1.98879551887512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04951548576355</t>
+    <t xml:space="preserve">2.04951572418213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03719544410706</t>
+    <t xml:space="preserve">2.03719592094421</t>
   </si>
   <si>
     <t xml:space="preserve">2.0239953994751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04159545898438</t>
+    <t xml:space="preserve">2.0415952205658</t>
   </si>
   <si>
     <t xml:space="preserve">1.91839575767517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00639533996582</t>
+    <t xml:space="preserve">2.00639581680298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90079581737518</t>
+    <t xml:space="preserve">1.90079593658447</t>
   </si>
   <si>
     <t xml:space="preserve">1.86559569835663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8831958770752</t>
+    <t xml:space="preserve">1.88319599628448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91022729873657</t>
+    <t xml:space="preserve">1.91022717952728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92824828624725</t>
+    <t xml:space="preserve">1.92824840545654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89220607280731</t>
+    <t xml:space="preserve">1.89220643043518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94626939296722</t>
+    <t xml:space="preserve">1.94626951217651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96429049968719</t>
+    <t xml:space="preserve">1.96429073810577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98231148719788</t>
+    <t xml:space="preserve">1.98231136798859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00033211708069</t>
+    <t xml:space="preserve">2.00033259391785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85616421699524</t>
+    <t xml:space="preserve">1.85616445541382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83814311027527</t>
+    <t xml:space="preserve">1.83814322948456</t>
   </si>
   <si>
     <t xml:space="preserve">1.78408026695251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8741854429245</t>
+    <t xml:space="preserve">1.87418532371521</t>
   </si>
   <si>
     <t xml:space="preserve">1.82012224197388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80210137367249</t>
+    <t xml:space="preserve">1.8021012544632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95528018474579</t>
+    <t xml:space="preserve">1.95527982711792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97330105304718</t>
+    <t xml:space="preserve">1.9733008146286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9012166261673</t>
+    <t xml:space="preserve">1.90121650695801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91923797130585</t>
+    <t xml:space="preserve">1.91923785209656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84715390205383</t>
+    <t xml:space="preserve">1.84715378284454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86517465114594</t>
+    <t xml:space="preserve">1.86517453193665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88319563865662</t>
+    <t xml:space="preserve">1.88319575786591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74803817272186</t>
+    <t xml:space="preserve">1.74803829193115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79309070110321</t>
+    <t xml:space="preserve">1.79309058189392</t>
   </si>
   <si>
     <t xml:space="preserve">1.78858542442322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81111180782318</t>
+    <t xml:space="preserve">1.81111192703247</t>
   </si>
   <si>
     <t xml:space="preserve">1.82913267612457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79759573936462</t>
+    <t xml:space="preserve">1.79759609699249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7255117893219</t>
+    <t xml:space="preserve">1.72551190853119</t>
   </si>
   <si>
     <t xml:space="preserve">1.74353277683258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76605916023254</t>
+    <t xml:space="preserve">1.76605927944183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75704884529114</t>
+    <t xml:space="preserve">1.75704872608185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77506971359253</t>
+    <t xml:space="preserve">1.77506983280182</t>
   </si>
   <si>
     <t xml:space="preserve">1.73001718521118</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">1.73902761936188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71199607849121</t>
+    <t xml:space="preserve">1.7119961977005</t>
   </si>
   <si>
     <t xml:space="preserve">1.65793323516846</t>
@@ -245,10 +245,10 @@
     <t xml:space="preserve">1.69397521018982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58584928512573</t>
+    <t xml:space="preserve">1.58584916591644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68496465682983</t>
+    <t xml:space="preserve">1.68496477603912</t>
   </si>
   <si>
     <t xml:space="preserve">1.64892268180847</t>
@@ -257,145 +257,145 @@
     <t xml:space="preserve">1.67595410346985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70298564434052</t>
+    <t xml:space="preserve">1.70298552513123</t>
   </si>
   <si>
     <t xml:space="preserve">1.72100675106049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63090169429779</t>
+    <t xml:space="preserve">1.6309015750885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05439519882202</t>
+    <t xml:space="preserve">2.05439567565918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21658444404602</t>
+    <t xml:space="preserve">2.2165846824646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16252160072327</t>
+    <t xml:space="preserve">2.16252136230469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41481590270996</t>
+    <t xml:space="preserve">2.41481566429138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36075258255005</t>
+    <t xml:space="preserve">2.36075234413147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57700490951538</t>
+    <t xml:space="preserve">2.5770046710968</t>
   </si>
   <si>
     <t xml:space="preserve">2.61304688453674</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0635724067688</t>
+    <t xml:space="preserve">3.06357192993164</t>
   </si>
   <si>
     <t xml:space="preserve">3.46003437042236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26180338859558</t>
+    <t xml:space="preserve">3.261803150177</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22576141357422</t>
+    <t xml:space="preserve">3.22576117515564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17169857025146</t>
+    <t xml:space="preserve">3.17169833183289</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04555130004883</t>
+    <t xml:space="preserve">3.04555153846741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02753019332886</t>
+    <t xml:space="preserve">3.0275297164917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00950932502747</t>
+    <t xml:space="preserve">3.00950908660889</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11763525009155</t>
+    <t xml:space="preserve">3.11763501167297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91940379142761</t>
+    <t xml:space="preserve">2.91940402984619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73919367790222</t>
+    <t xml:space="preserve">2.7391939163208</t>
   </si>
   <si>
     <t xml:space="preserve">2.72117304801941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70315194129944</t>
+    <t xml:space="preserve">2.70315170288086</t>
   </si>
   <si>
     <t xml:space="preserve">2.8292989730835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86534094810486</t>
+    <t xml:space="preserve">2.86534118652344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93742513656616</t>
+    <t xml:space="preserve">2.93742489814758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81127762794495</t>
+    <t xml:space="preserve">2.81127786636353</t>
   </si>
   <si>
     <t xml:space="preserve">2.9013831615448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03781151771545</t>
+    <t xml:space="preserve">3.03781175613403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11057376861572</t>
+    <t xml:space="preserve">3.11057353019714</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01962113380432</t>
+    <t xml:space="preserve">3.01962089538574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09238338470459</t>
+    <t xml:space="preserve">3.09238314628601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18333530426025</t>
+    <t xml:space="preserve">3.18333554267883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23790717124939</t>
+    <t xml:space="preserve">3.23790693283081</t>
   </si>
   <si>
     <t xml:space="preserve">3.36524033546448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41981172561646</t>
+    <t xml:space="preserve">3.41981196403503</t>
   </si>
   <si>
     <t xml:space="preserve">3.40162134170532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38343071937561</t>
+    <t xml:space="preserve">3.38343095779419</t>
   </si>
   <si>
     <t xml:space="preserve">3.3106689453125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34704995155334</t>
+    <t xml:space="preserve">3.34705018997192</t>
   </si>
   <si>
     <t xml:space="preserve">3.32885956764221</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45619249343872</t>
+    <t xml:space="preserve">3.4561927318573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29247856140137</t>
+    <t xml:space="preserve">3.29247832298279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27428770065308</t>
+    <t xml:space="preserve">3.27428817749023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25609755516052</t>
+    <t xml:space="preserve">3.25609707832336</t>
   </si>
   <si>
     <t xml:space="preserve">3.43800210952759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47438335418701</t>
+    <t xml:space="preserve">3.47438359260559</t>
   </si>
   <si>
     <t xml:space="preserve">3.69266891479492</t>
@@ -404,22 +404,22 @@
     <t xml:space="preserve">3.60171675682068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67447853088379</t>
+    <t xml:space="preserve">3.67447900772095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91095495223999</t>
+    <t xml:space="preserve">3.91095566749573</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03828811645508</t>
+    <t xml:space="preserve">4.03828907012939</t>
   </si>
   <si>
     <t xml:space="preserve">4.05647897720337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98371696472168</t>
+    <t xml:space="preserve">3.98371648788452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80181193351746</t>
+    <t xml:space="preserve">3.80181217193604</t>
   </si>
   <si>
     <t xml:space="preserve">3.96552681922913</t>
@@ -428,22 +428,22 @@
     <t xml:space="preserve">4.0200982093811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92914581298828</t>
+    <t xml:space="preserve">3.9291455745697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89276456832886</t>
+    <t xml:space="preserve">3.89276480674744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94733643531799</t>
+    <t xml:space="preserve">3.94733619689941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22019290924072</t>
+    <t xml:space="preserve">4.22019338607788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20200300216675</t>
+    <t xml:space="preserve">4.20200347900391</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29295492172241</t>
+    <t xml:space="preserve">4.29295539855957</t>
   </si>
   <si>
     <t xml:space="preserve">4.40209817886353</t>
@@ -452,88 +452,88 @@
     <t xml:space="preserve">4.43847942352295</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36571788787842</t>
+    <t xml:space="preserve">4.3657169342041</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34752655029297</t>
+    <t xml:space="preserve">4.34752702713013</t>
   </si>
   <si>
     <t xml:space="preserve">4.37498474121094</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39329051971436</t>
+    <t xml:space="preserve">4.3932900428772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28345775604248</t>
+    <t xml:space="preserve">4.28345823287964</t>
   </si>
   <si>
     <t xml:space="preserve">4.24684715270996</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26515197753906</t>
+    <t xml:space="preserve">4.26515293121338</t>
   </si>
   <si>
     <t xml:space="preserve">4.17362546920776</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10040378570557</t>
+    <t xml:space="preserve">4.10040426254272</t>
   </si>
   <si>
     <t xml:space="preserve">4.21023607254028</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13701486587524</t>
+    <t xml:space="preserve">4.1370153427124</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4848165512085</t>
+    <t xml:space="preserve">4.48481750488281</t>
   </si>
   <si>
     <t xml:space="preserve">4.33837413787842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15532064437866</t>
+    <t xml:space="preserve">4.1553201675415</t>
   </si>
   <si>
     <t xml:space="preserve">4.3017635345459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46651124954224</t>
+    <t xml:space="preserve">4.46651220321655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19193124771118</t>
+    <t xml:space="preserve">4.19193077087402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11870908737183</t>
+    <t xml:space="preserve">4.11870956420898</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06379270553589</t>
+    <t xml:space="preserve">4.06379365921021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99057269096375</t>
+    <t xml:space="preserve">3.99057221412659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97226667404175</t>
+    <t xml:space="preserve">3.97226691246033</t>
   </si>
   <si>
     <t xml:space="preserve">3.93565607070923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02718210220337</t>
+    <t xml:space="preserve">4.02718305587769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08209896087646</t>
+    <t xml:space="preserve">4.08209943771362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95396113395691</t>
+    <t xml:space="preserve">3.95396161079407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91735053062439</t>
+    <t xml:space="preserve">3.91735076904297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78921270370483</t>
+    <t xml:space="preserve">3.78921246528625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86243343353271</t>
+    <t xml:space="preserve">3.86243414878845</t>
   </si>
   <si>
     <t xml:space="preserve">3.88073897361755</t>
@@ -542,28 +542,28 @@
     <t xml:space="preserve">3.66107511520386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77090716362</t>
+    <t xml:space="preserve">3.77090740203857</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69768595695496</t>
+    <t xml:space="preserve">3.69768619537354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82582306861877</t>
+    <t xml:space="preserve">3.82582330703735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04548835754395</t>
+    <t xml:space="preserve">4.04548788070679</t>
   </si>
   <si>
     <t xml:space="preserve">4.2285418510437</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35668039321899</t>
+    <t xml:space="preserve">4.35667943954468</t>
   </si>
   <si>
     <t xml:space="preserve">4.00887775421143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84412860870361</t>
+    <t xml:space="preserve">3.84412884712219</t>
   </si>
   <si>
     <t xml:space="preserve">3.75260210037231</t>
@@ -578,46 +578,46 @@
     <t xml:space="preserve">3.53293752670288</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42310571670532</t>
+    <t xml:space="preserve">3.42310547828674</t>
   </si>
   <si>
     <t xml:space="preserve">3.18513536453247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76411175727844</t>
+    <t xml:space="preserve">2.76411199569702</t>
   </si>
   <si>
     <t xml:space="preserve">2.83733320236206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72750115394592</t>
+    <t xml:space="preserve">2.72750091552734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61766886711121</t>
+    <t xml:space="preserve">2.61766862869263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80072259902954</t>
+    <t xml:space="preserve">2.80072236061096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92886018753052</t>
+    <t xml:space="preserve">2.92885994911194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13021898269653</t>
+    <t xml:space="preserve">3.13021945953369</t>
   </si>
   <si>
     <t xml:space="preserve">3.16683006286621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36818909645081</t>
+    <t xml:space="preserve">3.36818933486938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4047999382019</t>
+    <t xml:space="preserve">3.40480017662048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44141054153442</t>
+    <t xml:space="preserve">3.441410779953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34988379478455</t>
+    <t xml:space="preserve">3.34988403320312</t>
   </si>
   <si>
     <t xml:space="preserve">3.22174620628357</t>
@@ -626,28 +626,28 @@
     <t xml:space="preserve">3.25835680961609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60615921020508</t>
+    <t xml:space="preserve">3.6061589717865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58785367012024</t>
+    <t xml:space="preserve">3.58785390853882</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59700655937195</t>
+    <t xml:space="preserve">3.59700632095337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55124258995056</t>
+    <t xml:space="preserve">3.55124306678772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48717403411865</t>
+    <t xml:space="preserve">3.48717379570007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45971584320068</t>
+    <t xml:space="preserve">3.45971608161926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38649463653564</t>
+    <t xml:space="preserve">3.38649439811707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45056319236755</t>
+    <t xml:space="preserve">3.45056343078613</t>
   </si>
   <si>
     <t xml:space="preserve">3.37734198570251</t>
@@ -656,37 +656,37 @@
     <t xml:space="preserve">3.28581476211548</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3590362071991</t>
+    <t xml:space="preserve">3.35903644561768</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36844515800476</t>
+    <t xml:space="preserve">3.36844563484192</t>
   </si>
   <si>
     <t xml:space="preserve">3.38726353645325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45312714576721</t>
+    <t xml:space="preserve">3.45312738418579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52839970588684</t>
+    <t xml:space="preserve">3.52839946746826</t>
   </si>
   <si>
     <t xml:space="preserve">3.40608167648315</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5754451751709</t>
+    <t xml:space="preserve">3.57544493675232</t>
   </si>
   <si>
     <t xml:space="preserve">3.66953587532043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63189911842346</t>
+    <t xml:space="preserve">3.63189935684204</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78244423866272</t>
+    <t xml:space="preserve">3.7824444770813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88594436645508</t>
+    <t xml:space="preserve">3.8859441280365</t>
   </si>
   <si>
     <t xml:space="preserve">3.89535307884216</t>
@@ -695,7 +695,7 @@
     <t xml:space="preserve">3.83889865875244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82008028030396</t>
+    <t xml:space="preserve">3.82008075714111</t>
   </si>
   <si>
     <t xml:space="preserve">3.79185366630554</t>
@@ -707,25 +707,25 @@
     <t xml:space="preserve">3.70717191696167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69776296615601</t>
+    <t xml:space="preserve">3.69776320457458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41549110412598</t>
+    <t xml:space="preserve">3.4154908657074</t>
   </si>
   <si>
     <t xml:space="preserve">3.48135447502136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24612784385681</t>
+    <t xml:space="preserve">3.24612760543823</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15203714370728</t>
+    <t xml:space="preserve">3.1520369052887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21790027618408</t>
+    <t xml:space="preserve">3.21790051460266</t>
   </si>
   <si>
-    <t xml:space="preserve">3.377854347229</t>
+    <t xml:space="preserve">3.37785458564758</t>
   </si>
   <si>
     <t xml:space="preserve">3.47194528579712</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">3.50958156585693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66012668609619</t>
+    <t xml:space="preserve">3.66012692451477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56603598594666</t>
+    <t xml:space="preserve">3.56603574752808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51899075508118</t>
+    <t xml:space="preserve">3.5189905166626</t>
   </si>
   <si>
     <t xml:space="preserve">3.46253609657288</t>
@@ -764,13 +764,13 @@
     <t xml:space="preserve">3.81067180633545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62249040603638</t>
+    <t xml:space="preserve">3.6224901676178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74480819702148</t>
+    <t xml:space="preserve">3.74480795860291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.725989818573</t>
+    <t xml:space="preserve">3.72599005699158</t>
   </si>
   <si>
     <t xml:space="preserve">3.84830808639526</t>
@@ -779,10 +779,10 @@
     <t xml:space="preserve">3.33080911636353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60367202758789</t>
+    <t xml:space="preserve">3.60367178916931</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04589891433716</t>
+    <t xml:space="preserve">4.04589796066284</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062516212463</t>
@@ -791,25 +791,25 @@
     <t xml:space="preserve">3.82948970794678</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02708053588867</t>
+    <t xml:space="preserve">4.02708005905151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90476274490356</t>
+    <t xml:space="preserve">3.90476226806641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85771703720093</t>
+    <t xml:space="preserve">3.85771679878235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13057947158813</t>
+    <t xml:space="preserve">4.13057994842529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20585298538208</t>
+    <t xml:space="preserve">4.20585250854492</t>
   </si>
   <si>
     <t xml:space="preserve">4.27171564102173</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43166971206665</t>
+    <t xml:space="preserve">4.43167018890381</t>
   </si>
   <si>
     <t xml:space="preserve">4.53517007827759</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">4.4034423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55398797988892</t>
+    <t xml:space="preserve">4.55398750305176</t>
   </si>
   <si>
     <t xml:space="preserve">4.68571424484253</t>
@@ -827,61 +827,61 @@
     <t xml:space="preserve">4.54457855224609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51635217666626</t>
+    <t xml:space="preserve">4.51635122299194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32816982269287</t>
+    <t xml:space="preserve">4.32817029953003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2528977394104</t>
+    <t xml:space="preserve">4.25289726257324</t>
   </si>
   <si>
     <t xml:space="preserve">4.47871541976929</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61044263839722</t>
+    <t xml:space="preserve">4.61044216156006</t>
   </si>
   <si>
     <t xml:space="preserve">4.61985111236572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50694227218628</t>
+    <t xml:space="preserve">4.50694274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5728063583374</t>
+    <t xml:space="preserve">4.57280588150024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63866901397705</t>
+    <t xml:space="preserve">4.63866949081421</t>
   </si>
   <si>
     <t xml:space="preserve">4.64807844161987</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48812437057495</t>
+    <t xml:space="preserve">4.48812389373779</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42226076126099</t>
+    <t xml:space="preserve">4.42226028442383</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45989656448364</t>
+    <t xml:space="preserve">4.4598970413208</t>
   </si>
   <si>
     <t xml:space="preserve">4.33757925033569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37521600723267</t>
+    <t xml:space="preserve">4.37521553039551</t>
   </si>
   <si>
     <t xml:space="preserve">4.28112506866455</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38462400436401</t>
+    <t xml:space="preserve">4.38462448120117</t>
   </si>
   <si>
     <t xml:space="preserve">4.1964430809021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17762470245361</t>
+    <t xml:space="preserve">4.17762517929077</t>
   </si>
   <si>
     <t xml:space="preserve">4.23407936096191</t>
@@ -890,16 +890,16 @@
     <t xml:space="preserve">4.39403390884399</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24348878860474</t>
+    <t xml:space="preserve">4.24348926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36580657958984</t>
+    <t xml:space="preserve">4.36580610275269</t>
   </si>
   <si>
     <t xml:space="preserve">4.31876134872437</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56339693069458</t>
+    <t xml:space="preserve">4.56339645385742</t>
   </si>
   <si>
     <t xml:space="preserve">4.44107866287231</t>
@@ -914,13 +914,13 @@
     <t xml:space="preserve">4.76098728179932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65748739242554</t>
+    <t xml:space="preserve">4.65748691558838</t>
   </si>
   <si>
     <t xml:space="preserve">4.6668963432312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30935192108154</t>
+    <t xml:space="preserve">4.30935144424438</t>
   </si>
   <si>
     <t xml:space="preserve">4.15880727767944</t>
@@ -929,7 +929,7 @@
     <t xml:space="preserve">4.14939785003662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22467088699341</t>
+    <t xml:space="preserve">4.22467041015625</t>
   </si>
   <si>
     <t xml:space="preserve">4.12117099761963</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">3.99885272979736</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95180749893188</t>
+    <t xml:space="preserve">3.95180726051331</t>
   </si>
   <si>
     <t xml:space="preserve">4.08353471755981</t>
@@ -947,40 +947,40 @@
     <t xml:space="preserve">4.29994344711304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70453310012817</t>
+    <t xml:space="preserve">4.70453262329102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75157833099365</t>
+    <t xml:space="preserve">4.75157880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59162425994873</t>
+    <t xml:space="preserve">4.59162378311157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34698820114136</t>
+    <t xml:space="preserve">4.3469877243042</t>
   </si>
   <si>
     <t xml:space="preserve">4.49753379821777</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6292610168457</t>
+    <t xml:space="preserve">4.62925958633423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84566831588745</t>
+    <t xml:space="preserve">4.84566926956177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93976020812988</t>
+    <t xml:space="preserve">4.93975925445557</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66643953323364</t>
+    <t xml:space="preserve">4.6664400100708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64739274978638</t>
+    <t xml:space="preserve">4.64739322662354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57120656967163</t>
+    <t xml:space="preserve">4.57120609283447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62834644317627</t>
+    <t xml:space="preserve">4.62834596633911</t>
   </si>
   <si>
     <t xml:space="preserve">4.609299659729</t>
@@ -989,25 +989,25 @@
     <t xml:space="preserve">4.49501895904541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72357940673828</t>
+    <t xml:space="preserve">4.72357988357544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74262571334839</t>
+    <t xml:space="preserve">4.74262619018555</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85690641403198</t>
+    <t xml:space="preserve">4.85690593719482</t>
   </si>
   <si>
     <t xml:space="preserve">4.95213985443115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90452289581299</t>
+    <t xml:space="preserve">4.90452337265015</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04737329483032</t>
+    <t xml:space="preserve">5.04737377166748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99975728988647</t>
+    <t xml:space="preserve">4.99975633621216</t>
   </si>
   <si>
     <t xml:space="preserve">5.09499025344849</t>
@@ -1016,55 +1016,55 @@
     <t xml:space="preserve">5.28545713424683</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66639137268066</t>
+    <t xml:space="preserve">5.66639089584351</t>
   </si>
   <si>
     <t xml:space="preserve">5.57115745544434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76162481307983</t>
+    <t xml:space="preserve">5.76162433624268</t>
   </si>
   <si>
     <t xml:space="preserve">5.71400785446167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38069105148315</t>
+    <t xml:space="preserve">5.380690574646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42830657958984</t>
+    <t xml:space="preserve">5.42830753326416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23784065246582</t>
+    <t xml:space="preserve">5.2378396987915</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1902232170105</t>
+    <t xml:space="preserve">5.19022369384766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14260721206665</t>
+    <t xml:space="preserve">5.14260673522949</t>
   </si>
   <si>
     <t xml:space="preserve">4.80928993225098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76167297363281</t>
+    <t xml:space="preserve">4.76167345046997</t>
   </si>
   <si>
     <t xml:space="preserve">4.81835985183716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74126625061035</t>
+    <t xml:space="preserve">4.74126577377319</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76053905487061</t>
+    <t xml:space="preserve">4.76053953170776</t>
   </si>
   <si>
     <t xml:space="preserve">4.86654329299927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79908561706543</t>
+    <t xml:space="preserve">4.79908609390259</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72199249267578</t>
+    <t xml:space="preserve">4.72199296951294</t>
   </si>
   <si>
     <t xml:space="preserve">4.58707857131958</t>
@@ -1082,7 +1082,7 @@
     <t xml:space="preserve">4.91472673416138</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96291017532349</t>
+    <t xml:space="preserve">4.96291065216064</t>
   </si>
   <si>
     <t xml:space="preserve">5.0110936164856</t>
@@ -1091,19 +1091,19 @@
     <t xml:space="preserve">4.68344593048096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66417264938354</t>
+    <t xml:space="preserve">4.66417217254639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64489889144897</t>
+    <t xml:space="preserve">4.64489936828613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60635185241699</t>
+    <t xml:space="preserve">4.60635232925415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79980039596558</t>
+    <t xml:space="preserve">4.79979991912842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76077699661255</t>
+    <t xml:space="preserve">4.76077747344971</t>
   </si>
   <si>
     <t xml:space="preserve">4.83882284164429</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">5.31685161590576</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56074333190918</t>
+    <t xml:space="preserve">5.56074380874634</t>
   </si>
   <si>
     <t xml:space="preserve">5.80463600158691</t>
@@ -1145,10 +1145,10 @@
     <t xml:space="preserve">5.60952234268188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26807355880737</t>
+    <t xml:space="preserve">5.26807308197021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12173795700073</t>
+    <t xml:space="preserve">5.12173748016357</t>
   </si>
   <si>
     <t xml:space="preserve">4.97540235519409</t>
@@ -1157,10 +1157,10 @@
     <t xml:space="preserve">5.17051649093628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92662382125854</t>
+    <t xml:space="preserve">4.9266242980957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.877845287323</t>
+    <t xml:space="preserve">4.87784576416016</t>
   </si>
   <si>
     <t xml:space="preserve">5.02418088912964</t>
@@ -1383,6 +1383,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
   </si>
 </sst>
 </file>
@@ -45765,7 +45768,7 @@
     </row>
     <row r="1695">
       <c r="A1695" s="1" t="n">
-        <v>45944.357025463</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B1695" t="n">
         <v>4800</v>
@@ -45786,6 +45789,32 @@
         <v>448</v>
       </c>
       <c r="H1695" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" s="1" t="n">
+        <v>45945.5984027778</v>
+      </c>
+      <c r="B1696" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C1696" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="D1696" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="E1696" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="F1696" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1696" t="s">
+        <v>457</v>
+      </c>
+      <c r="H1696" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ILP.MI.xlsx
+++ b/data/ILP.MI.xlsx
@@ -38,172 +38,172 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97119557857513</t>
+    <t xml:space="preserve">1.97119569778442</t>
   </si>
   <si>
     <t xml:space="preserve">ILP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99759566783905</t>
+    <t xml:space="preserve">1.99759542942047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93599593639374</t>
+    <t xml:space="preserve">1.93599569797516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96195578575134</t>
+    <t xml:space="preserve">1.96195590496063</t>
   </si>
   <si>
     <t xml:space="preserve">2.028395652771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00111532211304</t>
+    <t xml:space="preserve">2.00111556053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95359563827515</t>
+    <t xml:space="preserve">1.95359551906586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9795560836792</t>
+    <t xml:space="preserve">1.97955596446991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94171571731567</t>
+    <t xml:space="preserve">1.94171607494354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96283578872681</t>
+    <t xml:space="preserve">1.96283555030823</t>
   </si>
   <si>
     <t xml:space="preserve">1.97515523433685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9513955116272</t>
+    <t xml:space="preserve">1.95139575004578</t>
   </si>
   <si>
     <t xml:space="preserve">1.90959584712982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88803577423096</t>
+    <t xml:space="preserve">1.88803589344025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91091585159302</t>
+    <t xml:space="preserve">1.91091561317444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9403954744339</t>
+    <t xml:space="preserve">1.94039595127106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96239542961121</t>
+    <t xml:space="preserve">1.96239590644836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95887577533722</t>
+    <t xml:space="preserve">1.95887565612793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93775582313538</t>
+    <t xml:space="preserve">1.93775522708893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99671578407288</t>
+    <t xml:space="preserve">1.99671542644501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95535552501678</t>
+    <t xml:space="preserve">1.95535576343536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98879551887512</t>
+    <t xml:space="preserve">1.9887957572937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04951572418213</t>
+    <t xml:space="preserve">2.04951500892639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03719592094421</t>
+    <t xml:space="preserve">2.03719568252563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0239953994751</t>
+    <t xml:space="preserve">2.02399516105652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0415952205658</t>
+    <t xml:space="preserve">2.04159545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91839575767517</t>
+    <t xml:space="preserve">1.91839599609375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00639581680298</t>
+    <t xml:space="preserve">2.00639533996582</t>
   </si>
   <si>
     <t xml:space="preserve">1.90079593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86559569835663</t>
+    <t xml:space="preserve">1.86559581756592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88319599628448</t>
+    <t xml:space="preserve">1.8831958770752</t>
   </si>
   <si>
     <t xml:space="preserve">1.91022717952728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92824840545654</t>
+    <t xml:space="preserve">1.92824828624725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89220643043518</t>
+    <t xml:space="preserve">1.89220654964447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94626951217651</t>
+    <t xml:space="preserve">1.94626927375793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96429073810577</t>
+    <t xml:space="preserve">1.96429038047791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98231136798859</t>
+    <t xml:space="preserve">1.98231148719788</t>
   </si>
   <si>
     <t xml:space="preserve">2.00033259391785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85616445541382</t>
+    <t xml:space="preserve">1.85616433620453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83814322948456</t>
+    <t xml:space="preserve">1.83814311027527</t>
   </si>
   <si>
     <t xml:space="preserve">1.78408026695251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87418532371521</t>
+    <t xml:space="preserve">1.87418520450592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82012224197388</t>
+    <t xml:space="preserve">1.82012236118317</t>
   </si>
   <si>
     <t xml:space="preserve">1.8021012544632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95527982711792</t>
+    <t xml:space="preserve">1.95527994632721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9733008146286</t>
+    <t xml:space="preserve">1.97330117225647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90121650695801</t>
+    <t xml:space="preserve">1.9012166261673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91923785209656</t>
+    <t xml:space="preserve">1.91923773288727</t>
   </si>
   <si>
     <t xml:space="preserve">1.84715378284454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86517453193665</t>
+    <t xml:space="preserve">1.86517465114594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88319575786591</t>
+    <t xml:space="preserve">1.88319563865662</t>
   </si>
   <si>
     <t xml:space="preserve">1.74803829193115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79309058189392</t>
+    <t xml:space="preserve">1.7930908203125</t>
   </si>
   <si>
     <t xml:space="preserve">1.78858542442322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81111192703247</t>
+    <t xml:space="preserve">1.8111115694046</t>
   </si>
   <si>
     <t xml:space="preserve">1.82913267612457</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">1.72551190853119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74353277683258</t>
+    <t xml:space="preserve">1.74353289604187</t>
   </si>
   <si>
     <t xml:space="preserve">1.76605927944183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75704872608185</t>
+    <t xml:space="preserve">1.75704884529114</t>
   </si>
   <si>
     <t xml:space="preserve">1.77506983280182</t>
@@ -230,64 +230,64 @@
     <t xml:space="preserve">1.73001718521118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73902761936188</t>
+    <t xml:space="preserve">1.73902773857117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7119961977005</t>
+    <t xml:space="preserve">1.71199607849121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65793323516846</t>
+    <t xml:space="preserve">1.65793335437775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66694378852844</t>
+    <t xml:space="preserve">1.66694390773773</t>
   </si>
   <si>
     <t xml:space="preserve">1.69397521018982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58584916591644</t>
+    <t xml:space="preserve">1.58584904670715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68496477603912</t>
+    <t xml:space="preserve">1.68496465682983</t>
   </si>
   <si>
     <t xml:space="preserve">1.64892268180847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67595410346985</t>
+    <t xml:space="preserve">1.67595434188843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70298552513123</t>
+    <t xml:space="preserve">1.70298564434052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72100675106049</t>
+    <t xml:space="preserve">1.7210066318512</t>
   </si>
   <si>
     <t xml:space="preserve">1.6309015750885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05439567565918</t>
+    <t xml:space="preserve">2.0543954372406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2165846824646</t>
+    <t xml:space="preserve">2.21658444404602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16252136230469</t>
+    <t xml:space="preserve">2.16252183914185</t>
   </si>
   <si>
     <t xml:space="preserve">2.41481566429138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36075234413147</t>
+    <t xml:space="preserve">2.36075258255005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5770046710968</t>
+    <t xml:space="preserve">2.57700514793396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61304688453674</t>
+    <t xml:space="preserve">2.61304712295532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06357192993164</t>
+    <t xml:space="preserve">3.06357216835022</t>
   </si>
   <si>
     <t xml:space="preserve">3.46003437042236</t>
@@ -296,22 +296,22 @@
     <t xml:space="preserve">3.261803150177</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22576117515564</t>
+    <t xml:space="preserve">3.22576141357422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17169833183289</t>
+    <t xml:space="preserve">3.17169809341431</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04555153846741</t>
+    <t xml:space="preserve">3.04555106163025</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0275297164917</t>
+    <t xml:space="preserve">3.02752995491028</t>
   </si>
   <si>
     <t xml:space="preserve">3.00950908660889</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11763501167297</t>
+    <t xml:space="preserve">3.11763525009155</t>
   </si>
   <si>
     <t xml:space="preserve">2.91940402984619</t>
@@ -323,10 +323,10 @@
     <t xml:space="preserve">2.72117304801941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70315170288086</t>
+    <t xml:space="preserve">2.70315194129944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8292989730835</t>
+    <t xml:space="preserve">2.82929921150208</t>
   </si>
   <si>
     <t xml:space="preserve">2.86534118652344</t>
@@ -338,10 +338,10 @@
     <t xml:space="preserve">2.81127786636353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9013831615448</t>
+    <t xml:space="preserve">2.90138292312622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03781175613403</t>
+    <t xml:space="preserve">3.03781127929688</t>
   </si>
   <si>
     <t xml:space="preserve">3.11057353019714</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">3.09238314628601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18333554267883</t>
+    <t xml:space="preserve">3.18333578109741</t>
   </si>
   <si>
     <t xml:space="preserve">3.23790693283081</t>
@@ -362,52 +362,52 @@
     <t xml:space="preserve">3.36524033546448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41981196403503</t>
+    <t xml:space="preserve">3.41981172561646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40162134170532</t>
+    <t xml:space="preserve">3.4016215801239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38343095779419</t>
+    <t xml:space="preserve">3.38343119621277</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3106689453125</t>
+    <t xml:space="preserve">3.31066942214966</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34705018997192</t>
+    <t xml:space="preserve">3.34704971313477</t>
   </si>
   <si>
     <t xml:space="preserve">3.32885956764221</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4561927318573</t>
+    <t xml:space="preserve">3.45619297027588</t>
   </si>
   <si>
     <t xml:space="preserve">3.29247832298279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27428817749023</t>
+    <t xml:space="preserve">3.27428793907166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25609707832336</t>
+    <t xml:space="preserve">3.25609731674194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43800210952759</t>
+    <t xml:space="preserve">3.43800234794617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47438359260559</t>
+    <t xml:space="preserve">3.47438311576843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69266891479492</t>
+    <t xml:space="preserve">3.6926691532135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60171675682068</t>
+    <t xml:space="preserve">3.6017165184021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67447900772095</t>
+    <t xml:space="preserve">3.67447876930237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91095566749573</t>
+    <t xml:space="preserve">3.91095519065857</t>
   </si>
   <si>
     <t xml:space="preserve">4.03828907012939</t>
@@ -416,10 +416,10 @@
     <t xml:space="preserve">4.05647897720337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98371648788452</t>
+    <t xml:space="preserve">3.98371696472168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80181217193604</t>
+    <t xml:space="preserve">3.80181169509888</t>
   </si>
   <si>
     <t xml:space="preserve">3.96552681922913</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">4.22019338607788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20200347900391</t>
+    <t xml:space="preserve">4.20200252532959</t>
   </si>
   <si>
     <t xml:space="preserve">4.29295539855957</t>
@@ -455,16 +455,16 @@
     <t xml:space="preserve">4.3657169342041</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34752702713013</t>
+    <t xml:space="preserve">4.34752750396729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37498474121094</t>
+    <t xml:space="preserve">4.3749852180481</t>
   </si>
   <si>
     <t xml:space="preserve">4.3932900428772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28345823287964</t>
+    <t xml:space="preserve">4.28345775604248</t>
   </si>
   <si>
     <t xml:space="preserve">4.24684715270996</t>
@@ -479,19 +479,19 @@
     <t xml:space="preserve">4.10040426254272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21023607254028</t>
+    <t xml:space="preserve">4.21023654937744</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1370153427124</t>
+    <t xml:space="preserve">4.13701486587524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48481750488281</t>
+    <t xml:space="preserve">4.48481702804565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33837413787842</t>
+    <t xml:space="preserve">4.33837366104126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1553201675415</t>
+    <t xml:space="preserve">4.15532064437866</t>
   </si>
   <si>
     <t xml:space="preserve">4.3017635345459</t>
@@ -503,52 +503,52 @@
     <t xml:space="preserve">4.19193077087402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11870956420898</t>
+    <t xml:space="preserve">4.11870908737183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06379365921021</t>
+    <t xml:space="preserve">4.06379413604736</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99057221412659</t>
+    <t xml:space="preserve">3.99057197570801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97226691246033</t>
+    <t xml:space="preserve">3.97226667404175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93565607070923</t>
+    <t xml:space="preserve">3.93565583229065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02718305587769</t>
+    <t xml:space="preserve">4.02718257904053</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08209943771362</t>
+    <t xml:space="preserve">4.08209848403931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95396161079407</t>
+    <t xml:space="preserve">3.95396137237549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91735076904297</t>
+    <t xml:space="preserve">3.91735029220581</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78921246528625</t>
+    <t xml:space="preserve">3.78921270370483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86243414878845</t>
+    <t xml:space="preserve">3.86243438720703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88073897361755</t>
+    <t xml:space="preserve">3.88073921203613</t>
   </si>
   <si>
     <t xml:space="preserve">3.66107511520386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77090740203857</t>
+    <t xml:space="preserve">3.77090716362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69768619537354</t>
+    <t xml:space="preserve">3.69768595695496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82582330703735</t>
+    <t xml:space="preserve">3.82582402229309</t>
   </si>
   <si>
     <t xml:space="preserve">4.04548788070679</t>
@@ -557,19 +557,19 @@
     <t xml:space="preserve">4.2285418510437</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35667943954468</t>
+    <t xml:space="preserve">4.35667991638184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00887775421143</t>
+    <t xml:space="preserve">4.00887727737427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84412884712219</t>
+    <t xml:space="preserve">3.84412860870361</t>
   </si>
   <si>
     <t xml:space="preserve">3.75260210037231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47802114486694</t>
+    <t xml:space="preserve">3.4780216217041</t>
   </si>
   <si>
     <t xml:space="preserve">3.56954836845398</t>
@@ -578,52 +578,52 @@
     <t xml:space="preserve">3.53293752670288</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42310547828674</t>
+    <t xml:space="preserve">3.42310523986816</t>
   </si>
   <si>
     <t xml:space="preserve">3.18513536453247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76411199569702</t>
+    <t xml:space="preserve">2.76411175727844</t>
   </si>
   <si>
     <t xml:space="preserve">2.83733320236206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72750091552734</t>
+    <t xml:space="preserve">2.72750115394592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61766862869263</t>
+    <t xml:space="preserve">2.61766839027405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80072236061096</t>
+    <t xml:space="preserve">2.80072259902954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92885994911194</t>
+    <t xml:space="preserve">2.9288604259491</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13021945953369</t>
+    <t xml:space="preserve">3.13021922111511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16683006286621</t>
+    <t xml:space="preserve">3.16682982444763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36818933486938</t>
+    <t xml:space="preserve">3.36818909645081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40480017662048</t>
+    <t xml:space="preserve">3.4047999382019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.441410779953</t>
+    <t xml:space="preserve">3.44141054153442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34988403320312</t>
+    <t xml:space="preserve">3.34988379478455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22174620628357</t>
+    <t xml:space="preserve">3.22174596786499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25835680961609</t>
+    <t xml:space="preserve">3.25835657119751</t>
   </si>
   <si>
     <t xml:space="preserve">3.6061589717865</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">3.58785390853882</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59700632095337</t>
+    <t xml:space="preserve">3.59700655937195</t>
   </si>
   <si>
     <t xml:space="preserve">3.55124306678772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48717379570007</t>
+    <t xml:space="preserve">3.48717427253723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45971608161926</t>
+    <t xml:space="preserve">3.45971584320068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38649439811707</t>
+    <t xml:space="preserve">3.38649463653564</t>
   </si>
   <si>
     <t xml:space="preserve">3.45056343078613</t>
@@ -653,22 +653,22 @@
     <t xml:space="preserve">3.37734198570251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28581476211548</t>
+    <t xml:space="preserve">3.28581500053406</t>
   </si>
   <si>
     <t xml:space="preserve">3.35903644561768</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36844563484192</t>
+    <t xml:space="preserve">3.36844539642334</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38726353645325</t>
+    <t xml:space="preserve">3.38726377487183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45312738418579</t>
+    <t xml:space="preserve">3.45312714576721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52839946746826</t>
+    <t xml:space="preserve">3.52839994430542</t>
   </si>
   <si>
     <t xml:space="preserve">3.40608167648315</t>
@@ -677,49 +677,49 @@
     <t xml:space="preserve">3.57544493675232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66953587532043</t>
+    <t xml:space="preserve">3.66953563690186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63189935684204</t>
+    <t xml:space="preserve">3.63189911842346</t>
   </si>
   <si>
     <t xml:space="preserve">3.7824444770813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8859441280365</t>
+    <t xml:space="preserve">3.88594388961792</t>
   </si>
   <si>
     <t xml:space="preserve">3.89535307884216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83889865875244</t>
+    <t xml:space="preserve">3.83889889717102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82008075714111</t>
+    <t xml:space="preserve">3.82008099555969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79185366630554</t>
+    <t xml:space="preserve">3.79185342788696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71658110618591</t>
+    <t xml:space="preserve">3.71658086776733</t>
   </si>
   <si>
     <t xml:space="preserve">3.70717191696167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69776320457458</t>
+    <t xml:space="preserve">3.69776296615601</t>
   </si>
   <si>
     <t xml:space="preserve">3.4154908657074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48135447502136</t>
+    <t xml:space="preserve">3.48135423660278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24612760543823</t>
+    <t xml:space="preserve">3.24612784385681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1520369052887</t>
+    <t xml:space="preserve">3.15203714370728</t>
   </si>
   <si>
     <t xml:space="preserve">3.21790051460266</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">3.47194528579712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50017237663269</t>
+    <t xml:space="preserve">3.50017261505127</t>
   </si>
   <si>
     <t xml:space="preserve">3.64130830764771</t>
@@ -740,16 +740,16 @@
     <t xml:space="preserve">3.50958156585693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66012692451477</t>
+    <t xml:space="preserve">3.66012644767761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56603574752808</t>
+    <t xml:space="preserve">3.56603622436523</t>
   </si>
   <si>
     <t xml:space="preserve">3.5189905166626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46253609657288</t>
+    <t xml:space="preserve">3.46253633499146</t>
   </si>
   <si>
     <t xml:space="preserve">3.68835377693176</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">3.6224901676178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74480795860291</t>
+    <t xml:space="preserve">3.74480819702148</t>
   </si>
   <si>
     <t xml:space="preserve">3.72599005699158</t>
@@ -776,55 +776,55 @@
     <t xml:space="preserve">3.84830808639526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33080911636353</t>
+    <t xml:space="preserve">3.33080887794495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60367178916931</t>
+    <t xml:space="preserve">3.60367202758789</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04589796066284</t>
+    <t xml:space="preserve">4.0458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97062516212463</t>
+    <t xml:space="preserve">3.97062587738037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82948970794678</t>
+    <t xml:space="preserve">3.82948994636536</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02708005905151</t>
+    <t xml:space="preserve">4.02708053588867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90476226806641</t>
+    <t xml:space="preserve">3.90476250648499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85771679878235</t>
+    <t xml:space="preserve">3.85771703720093</t>
   </si>
   <si>
     <t xml:space="preserve">4.13057994842529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20585250854492</t>
+    <t xml:space="preserve">4.20585203170776</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27171564102173</t>
+    <t xml:space="preserve">4.27171611785889</t>
   </si>
   <si>
     <t xml:space="preserve">4.43167018890381</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53517007827759</t>
+    <t xml:space="preserve">4.53516960144043</t>
   </si>
   <si>
     <t xml:space="preserve">4.4034423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55398750305176</t>
+    <t xml:space="preserve">4.55398845672607</t>
   </si>
   <si>
     <t xml:space="preserve">4.68571424484253</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54457855224609</t>
+    <t xml:space="preserve">4.54457950592041</t>
   </si>
   <si>
     <t xml:space="preserve">4.51635122299194</t>
@@ -833,13 +833,13 @@
     <t xml:space="preserve">4.32817029953003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25289726257324</t>
+    <t xml:space="preserve">4.25289821624756</t>
   </si>
   <si>
     <t xml:space="preserve">4.47871541976929</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61044216156006</t>
+    <t xml:space="preserve">4.6104416847229</t>
   </si>
   <si>
     <t xml:space="preserve">4.61985111236572</t>
@@ -851,22 +851,22 @@
     <t xml:space="preserve">4.57280588150024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63866949081421</t>
+    <t xml:space="preserve">4.63866901397705</t>
   </si>
   <si>
     <t xml:space="preserve">4.64807844161987</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48812389373779</t>
+    <t xml:space="preserve">4.48812437057495</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42226028442383</t>
+    <t xml:space="preserve">4.42226076126099</t>
   </si>
   <si>
     <t xml:space="preserve">4.4598970413208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33757925033569</t>
+    <t xml:space="preserve">4.33757972717285</t>
   </si>
   <si>
     <t xml:space="preserve">4.37521553039551</t>
@@ -881,10 +881,10 @@
     <t xml:space="preserve">4.1964430809021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17762517929077</t>
+    <t xml:space="preserve">4.17762565612793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23407936096191</t>
+    <t xml:space="preserve">4.23407983779907</t>
   </si>
   <si>
     <t xml:space="preserve">4.39403390884399</t>
@@ -899,25 +899,25 @@
     <t xml:space="preserve">4.31876134872437</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56339645385742</t>
+    <t xml:space="preserve">4.56339693069458</t>
   </si>
   <si>
     <t xml:space="preserve">4.44107866287231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46930646896362</t>
+    <t xml:space="preserve">4.46930694580078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9303503036499</t>
+    <t xml:space="preserve">4.93034982681274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76098728179932</t>
+    <t xml:space="preserve">4.76098775863647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65748691558838</t>
+    <t xml:space="preserve">4.65748739242554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6668963432312</t>
+    <t xml:space="preserve">4.66689682006836</t>
   </si>
   <si>
     <t xml:space="preserve">4.30935144424438</t>
@@ -926,52 +926,52 @@
     <t xml:space="preserve">4.15880727767944</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14939785003662</t>
+    <t xml:space="preserve">4.14939737319946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22467041015625</t>
+    <t xml:space="preserve">4.22466993331909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12117099761963</t>
+    <t xml:space="preserve">4.12117052078247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99885272979736</t>
+    <t xml:space="preserve">3.99885296821594</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95180726051331</t>
+    <t xml:space="preserve">3.95180749893188</t>
   </si>
   <si>
     <t xml:space="preserve">4.08353471755981</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29994344711304</t>
+    <t xml:space="preserve">4.29994297027588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70453262329102</t>
+    <t xml:space="preserve">4.70453310012817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75157880783081</t>
+    <t xml:space="preserve">4.75157833099365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59162378311157</t>
+    <t xml:space="preserve">4.59162425994873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3469877243042</t>
+    <t xml:space="preserve">4.34698867797852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49753379821777</t>
+    <t xml:space="preserve">4.49753332138062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62925958633423</t>
+    <t xml:space="preserve">4.62926054000854</t>
   </si>
   <si>
     <t xml:space="preserve">4.84566926956177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93975925445557</t>
+    <t xml:space="preserve">4.93975973129272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6664400100708</t>
+    <t xml:space="preserve">4.66643905639648</t>
   </si>
   <si>
     <t xml:space="preserve">4.64739322662354</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">4.62834596633911</t>
   </si>
   <si>
-    <t xml:space="preserve">4.609299659729</t>
+    <t xml:space="preserve">4.60930013656616</t>
   </si>
   <si>
     <t xml:space="preserve">4.49501895904541</t>
@@ -992,22 +992,22 @@
     <t xml:space="preserve">4.72357988357544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74262619018555</t>
+    <t xml:space="preserve">4.74262571334839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85690593719482</t>
+    <t xml:space="preserve">4.85690689086914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95213985443115</t>
+    <t xml:space="preserve">4.95213937759399</t>
   </si>
   <si>
     <t xml:space="preserve">4.90452337265015</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04737377166748</t>
+    <t xml:space="preserve">5.04737329483032</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99975633621216</t>
+    <t xml:space="preserve">4.99975681304932</t>
   </si>
   <si>
     <t xml:space="preserve">5.09499025344849</t>
@@ -1016,13 +1016,13 @@
     <t xml:space="preserve">5.28545713424683</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66639089584351</t>
+    <t xml:space="preserve">5.66639041900635</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57115745544434</t>
+    <t xml:space="preserve">5.57115697860718</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76162433624268</t>
+    <t xml:space="preserve">5.76162481307983</t>
   </si>
   <si>
     <t xml:space="preserve">5.71400785446167</t>
@@ -1031,16 +1031,16 @@
     <t xml:space="preserve">5.380690574646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42830753326416</t>
+    <t xml:space="preserve">5.428307056427</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2378396987915</t>
+    <t xml:space="preserve">5.23784065246582</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19022369384766</t>
+    <t xml:space="preserve">5.1902232170105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14260673522949</t>
+    <t xml:space="preserve">5.14260721206665</t>
   </si>
   <si>
     <t xml:space="preserve">4.80928993225098</t>
@@ -1052,19 +1052,19 @@
     <t xml:space="preserve">4.81835985183716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74126577377319</t>
+    <t xml:space="preserve">4.74126625061035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76053953170776</t>
+    <t xml:space="preserve">4.76053905487061</t>
   </si>
   <si>
     <t xml:space="preserve">4.86654329299927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79908609390259</t>
+    <t xml:space="preserve">4.79908561706543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72199296951294</t>
+    <t xml:space="preserve">4.72199201583862</t>
   </si>
   <si>
     <t xml:space="preserve">4.58707857131958</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">4.77981281280518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91472673416138</t>
+    <t xml:space="preserve">4.91472721099854</t>
   </si>
   <si>
     <t xml:space="preserve">4.96291065216064</t>
@@ -1088,22 +1088,22 @@
     <t xml:space="preserve">5.0110936164856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68344593048096</t>
+    <t xml:space="preserve">4.6834454536438</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66417217254639</t>
+    <t xml:space="preserve">4.66417264938354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64489936828613</t>
+    <t xml:space="preserve">4.64489841461182</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60635232925415</t>
+    <t xml:space="preserve">4.60635185241699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79979991912842</t>
+    <t xml:space="preserve">4.79980039596558</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76077747344971</t>
+    <t xml:space="preserve">4.76077699661255</t>
   </si>
   <si>
     <t xml:space="preserve">4.83882284164429</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">5.31685161590576</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56074380874634</t>
+    <t xml:space="preserve">5.56074333190918</t>
   </si>
   <si>
     <t xml:space="preserve">5.80463600158691</t>
@@ -1145,10 +1145,10 @@
     <t xml:space="preserve">5.60952234268188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26807308197021</t>
+    <t xml:space="preserve">5.26807355880737</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12173748016357</t>
+    <t xml:space="preserve">5.12173795700073</t>
   </si>
   <si>
     <t xml:space="preserve">4.97540235519409</t>
@@ -1157,10 +1157,10 @@
     <t xml:space="preserve">5.17051649093628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9266242980957</t>
+    <t xml:space="preserve">4.92662382125854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87784576416016</t>
+    <t xml:space="preserve">4.877845287323</t>
   </si>
   <si>
     <t xml:space="preserve">5.02418088912964</t>
@@ -45794,7 +45794,7 @@
     </row>
     <row r="1696">
       <c r="A1696" s="1" t="n">
-        <v>45945.5984027778</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B1696" t="n">
         <v>18000</v>
@@ -45815,6 +45815,32 @@
         <v>457</v>
       </c>
       <c r="H1696" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" s="1" t="n">
+        <v>45946.6494907407</v>
+      </c>
+      <c r="B1697" t="n">
+        <v>4200</v>
+      </c>
+      <c r="C1697" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="D1697" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1697" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="F1697" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1697" t="s">
+        <v>457</v>
+      </c>
+      <c r="H1697" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ILP.MI.xlsx
+++ b/data/ILP.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">ILP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99759542942047</t>
+    <t xml:space="preserve">1.99759519100189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93599569797516</t>
+    <t xml:space="preserve">1.93599545955658</t>
   </si>
   <si>
     <t xml:space="preserve">1.96195590496063</t>
@@ -59,22 +59,22 @@
     <t xml:space="preserve">2.00111556053162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95359551906586</t>
+    <t xml:space="preserve">1.95359587669373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97955596446991</t>
+    <t xml:space="preserve">1.97955548763275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94171607494354</t>
+    <t xml:space="preserve">1.94171547889709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96283555030823</t>
+    <t xml:space="preserve">1.96283566951752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97515523433685</t>
+    <t xml:space="preserve">1.97515559196472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95139575004578</t>
+    <t xml:space="preserve">1.95139539241791</t>
   </si>
   <si>
     <t xml:space="preserve">1.90959584712982</t>
@@ -83,43 +83,43 @@
     <t xml:space="preserve">1.88803589344025</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91091561317444</t>
+    <t xml:space="preserve">1.91091549396515</t>
   </si>
   <si>
     <t xml:space="preserve">1.94039595127106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96239590644836</t>
+    <t xml:space="preserve">1.96239578723907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95887565612793</t>
+    <t xml:space="preserve">1.95887553691864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93775522708893</t>
+    <t xml:space="preserve">1.9377555847168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99671542644501</t>
+    <t xml:space="preserve">1.99671566486359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95535576343536</t>
+    <t xml:space="preserve">1.9553554058075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9887957572937</t>
+    <t xml:space="preserve">1.98879599571228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04951500892639</t>
+    <t xml:space="preserve">2.04951548576355</t>
   </si>
   <si>
     <t xml:space="preserve">2.03719568252563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02399516105652</t>
+    <t xml:space="preserve">2.02399563789368</t>
   </si>
   <si>
     <t xml:space="preserve">2.04159545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91839599609375</t>
+    <t xml:space="preserve">1.91839587688446</t>
   </si>
   <si>
     <t xml:space="preserve">2.00639533996582</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">1.86559581756592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8831958770752</t>
+    <t xml:space="preserve">1.88319599628448</t>
   </si>
   <si>
     <t xml:space="preserve">1.91022717952728</t>
@@ -140,25 +140,25 @@
     <t xml:space="preserve">1.92824828624725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89220654964447</t>
+    <t xml:space="preserve">1.89220631122589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94626927375793</t>
+    <t xml:space="preserve">1.94626951217651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96429038047791</t>
+    <t xml:space="preserve">1.96429026126862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98231148719788</t>
+    <t xml:space="preserve">1.9823112487793</t>
   </si>
   <si>
     <t xml:space="preserve">2.00033259391785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85616433620453</t>
+    <t xml:space="preserve">1.85616409778595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83814311027527</t>
+    <t xml:space="preserve">1.83814334869385</t>
   </si>
   <si>
     <t xml:space="preserve">1.78408026695251</t>
@@ -170,82 +170,79 @@
     <t xml:space="preserve">1.82012236118317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8021012544632</t>
+    <t xml:space="preserve">1.80210137367249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95527994632721</t>
+    <t xml:space="preserve">1.95527970790863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97330117225647</t>
+    <t xml:space="preserve">1.97330105304718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9012166261673</t>
+    <t xml:space="preserve">1.90121674537659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91923773288727</t>
+    <t xml:space="preserve">1.91923797130585</t>
   </si>
   <si>
     <t xml:space="preserve">1.84715378284454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86517465114594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88319563865662</t>
+    <t xml:space="preserve">1.86517477035522</t>
   </si>
   <si>
     <t xml:space="preserve">1.74803829193115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7930908203125</t>
+    <t xml:space="preserve">1.79309070110321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78858542442322</t>
+    <t xml:space="preserve">1.78858554363251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8111115694046</t>
+    <t xml:space="preserve">1.81111168861389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82913267612457</t>
+    <t xml:space="preserve">1.82913291454315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79759609699249</t>
+    <t xml:space="preserve">1.79759585857391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72551190853119</t>
+    <t xml:space="preserve">1.72551202774048</t>
   </si>
   <si>
     <t xml:space="preserve">1.74353289604187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76605927944183</t>
+    <t xml:space="preserve">1.76605939865112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75704884529114</t>
+    <t xml:space="preserve">1.75704860687256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77506983280182</t>
+    <t xml:space="preserve">1.77506971359253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73001718521118</t>
+    <t xml:space="preserve">1.73001730442047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73902773857117</t>
+    <t xml:space="preserve">1.73902761936188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71199607849121</t>
+    <t xml:space="preserve">1.71199631690979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65793335437775</t>
+    <t xml:space="preserve">1.65793323516846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66694390773773</t>
+    <t xml:space="preserve">1.66694366931915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69397521018982</t>
+    <t xml:space="preserve">1.69397509098053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58584904670715</t>
+    <t xml:space="preserve">1.58584916591644</t>
   </si>
   <si>
     <t xml:space="preserve">1.68496465682983</t>
@@ -254,10 +251,10 @@
     <t xml:space="preserve">1.64892268180847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67595434188843</t>
+    <t xml:space="preserve">1.67595422267914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70298564434052</t>
+    <t xml:space="preserve">1.70298540592194</t>
   </si>
   <si>
     <t xml:space="preserve">1.7210066318512</t>
@@ -269,7 +266,7 @@
     <t xml:space="preserve">2.0543954372406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21658444404602</t>
+    <t xml:space="preserve">2.2165846824646</t>
   </si>
   <si>
     <t xml:space="preserve">2.16252183914185</t>
@@ -278,28 +275,28 @@
     <t xml:space="preserve">2.41481566429138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36075258255005</t>
+    <t xml:space="preserve">2.36075234413147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57700514793396</t>
+    <t xml:space="preserve">2.57700490951538</t>
   </si>
   <si>
     <t xml:space="preserve">2.61304712295532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06357216835022</t>
+    <t xml:space="preserve">3.0635724067688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46003437042236</t>
+    <t xml:space="preserve">3.46003460884094</t>
   </si>
   <si>
     <t xml:space="preserve">3.261803150177</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22576141357422</t>
+    <t xml:space="preserve">3.22576117515564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17169809341431</t>
+    <t xml:space="preserve">3.17169833183289</t>
   </si>
   <si>
     <t xml:space="preserve">3.04555106163025</t>
@@ -314,28 +311,28 @@
     <t xml:space="preserve">3.11763525009155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91940402984619</t>
+    <t xml:space="preserve">2.91940426826477</t>
   </si>
   <si>
     <t xml:space="preserve">2.7391939163208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72117304801941</t>
+    <t xml:space="preserve">2.72117280960083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70315194129944</t>
+    <t xml:space="preserve">2.70315217971802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82929921150208</t>
+    <t xml:space="preserve">2.82929873466492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86534118652344</t>
+    <t xml:space="preserve">2.86534070968628</t>
   </si>
   <si>
     <t xml:space="preserve">2.93742489814758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81127786636353</t>
+    <t xml:space="preserve">2.8112781047821</t>
   </si>
   <si>
     <t xml:space="preserve">2.90138292312622</t>
@@ -347,34 +344,34 @@
     <t xml:space="preserve">3.11057353019714</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01962089538574</t>
+    <t xml:space="preserve">3.0196213722229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09238314628601</t>
+    <t xml:space="preserve">3.09238338470459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18333578109741</t>
+    <t xml:space="preserve">3.18333530426025</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23790693283081</t>
+    <t xml:space="preserve">3.23790717124939</t>
   </si>
   <si>
     <t xml:space="preserve">3.36524033546448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41981172561646</t>
+    <t xml:space="preserve">3.41981196403503</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4016215801239</t>
+    <t xml:space="preserve">3.40162134170532</t>
   </si>
   <si>
     <t xml:space="preserve">3.38343119621277</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31066942214966</t>
+    <t xml:space="preserve">3.31066918373108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34704971313477</t>
+    <t xml:space="preserve">3.34704995155334</t>
   </si>
   <si>
     <t xml:space="preserve">3.32885956764221</t>
@@ -389,7 +386,7 @@
     <t xml:space="preserve">3.27428793907166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25609731674194</t>
+    <t xml:space="preserve">3.25609707832336</t>
   </si>
   <si>
     <t xml:space="preserve">3.43800234794617</t>
@@ -398,16 +395,16 @@
     <t xml:space="preserve">3.47438311576843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6926691532135</t>
+    <t xml:space="preserve">3.69266939163208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6017165184021</t>
+    <t xml:space="preserve">3.60171675682068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67447876930237</t>
+    <t xml:space="preserve">3.67447853088379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91095519065857</t>
+    <t xml:space="preserve">3.91095495223999</t>
   </si>
   <si>
     <t xml:space="preserve">4.03828907012939</t>
@@ -419,7 +416,7 @@
     <t xml:space="preserve">3.98371696472168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80181169509888</t>
+    <t xml:space="preserve">3.80181217193604</t>
   </si>
   <si>
     <t xml:space="preserve">3.96552681922913</t>
@@ -428,40 +425,40 @@
     <t xml:space="preserve">4.0200982093811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9291455745697</t>
+    <t xml:space="preserve">3.92914533615112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89276480674744</t>
+    <t xml:space="preserve">3.89276504516602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94733619689941</t>
+    <t xml:space="preserve">3.94733643531799</t>
   </si>
   <si>
     <t xml:space="preserve">4.22019338607788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20200252532959</t>
+    <t xml:space="preserve">4.20200300216675</t>
   </si>
   <si>
     <t xml:space="preserve">4.29295539855957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40209817886353</t>
+    <t xml:space="preserve">4.40209865570068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43847942352295</t>
+    <t xml:space="preserve">4.43847990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3657169342041</t>
+    <t xml:space="preserve">4.36571741104126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34752750396729</t>
+    <t xml:space="preserve">4.34752702713013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3749852180481</t>
+    <t xml:space="preserve">4.37498474121094</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3932900428772</t>
+    <t xml:space="preserve">4.39329051971436</t>
   </si>
   <si>
     <t xml:space="preserve">4.28345775604248</t>
@@ -470,16 +467,16 @@
     <t xml:space="preserve">4.24684715270996</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26515293121338</t>
+    <t xml:space="preserve">4.26515245437622</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17362546920776</t>
+    <t xml:space="preserve">4.17362594604492</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10040426254272</t>
+    <t xml:space="preserve">4.10040378570557</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21023654937744</t>
+    <t xml:space="preserve">4.21023607254028</t>
   </si>
   <si>
     <t xml:space="preserve">4.13701486587524</t>
@@ -488,7 +485,7 @@
     <t xml:space="preserve">4.48481702804565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33837366104126</t>
+    <t xml:space="preserve">4.33837413787842</t>
   </si>
   <si>
     <t xml:space="preserve">4.15532064437866</t>
@@ -500,13 +497,13 @@
     <t xml:space="preserve">4.46651220321655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19193077087402</t>
+    <t xml:space="preserve">4.19193124771118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11870908737183</t>
+    <t xml:space="preserve">4.11870956420898</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06379413604736</t>
+    <t xml:space="preserve">4.06379365921021</t>
   </si>
   <si>
     <t xml:space="preserve">3.99057197570801</t>
@@ -524,10 +521,10 @@
     <t xml:space="preserve">4.08209848403931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95396137237549</t>
+    <t xml:space="preserve">3.95396089553833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91735029220581</t>
+    <t xml:space="preserve">3.91735053062439</t>
   </si>
   <si>
     <t xml:space="preserve">3.78921270370483</t>
@@ -539,25 +536,25 @@
     <t xml:space="preserve">3.88073921203613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66107511520386</t>
+    <t xml:space="preserve">3.66107535362244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77090716362</t>
+    <t xml:space="preserve">3.77090740203857</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69768595695496</t>
+    <t xml:space="preserve">3.69768571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82582402229309</t>
+    <t xml:space="preserve">3.82582354545593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04548788070679</t>
+    <t xml:space="preserve">4.04548835754395</t>
   </si>
   <si>
     <t xml:space="preserve">4.2285418510437</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35667991638184</t>
+    <t xml:space="preserve">4.35667943954468</t>
   </si>
   <si>
     <t xml:space="preserve">4.00887727737427</t>
@@ -566,16 +563,16 @@
     <t xml:space="preserve">3.84412860870361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75260210037231</t>
+    <t xml:space="preserve">3.75260186195374</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4780216217041</t>
+    <t xml:space="preserve">3.47802138328552</t>
   </si>
   <si>
     <t xml:space="preserve">3.56954836845398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53293752670288</t>
+    <t xml:space="preserve">3.5329372882843</t>
   </si>
   <si>
     <t xml:space="preserve">3.42310523986816</t>
@@ -587,13 +584,13 @@
     <t xml:space="preserve">2.76411175727844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83733320236206</t>
+    <t xml:space="preserve">2.83733296394348</t>
   </si>
   <si>
     <t xml:space="preserve">2.72750115394592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61766839027405</t>
+    <t xml:space="preserve">2.61766862869263</t>
   </si>
   <si>
     <t xml:space="preserve">2.80072259902954</t>
@@ -602,28 +599,28 @@
     <t xml:space="preserve">2.9288604259491</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13021922111511</t>
+    <t xml:space="preserve">3.13021898269653</t>
   </si>
   <si>
     <t xml:space="preserve">3.16682982444763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36818909645081</t>
+    <t xml:space="preserve">3.36818933486938</t>
   </si>
   <si>
     <t xml:space="preserve">3.4047999382019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44141054153442</t>
+    <t xml:space="preserve">3.441410779953</t>
   </si>
   <si>
     <t xml:space="preserve">3.34988379478455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22174596786499</t>
+    <t xml:space="preserve">3.22174620628357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25835657119751</t>
+    <t xml:space="preserve">3.25835680961609</t>
   </si>
   <si>
     <t xml:space="preserve">3.6061589717865</t>
@@ -638,7 +635,7 @@
     <t xml:space="preserve">3.55124306678772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48717427253723</t>
+    <t xml:space="preserve">3.48717403411865</t>
   </si>
   <si>
     <t xml:space="preserve">3.45971584320068</t>
@@ -650,22 +647,22 @@
     <t xml:space="preserve">3.45056343078613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37734198570251</t>
+    <t xml:space="preserve">3.37734174728394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28581500053406</t>
+    <t xml:space="preserve">3.28581523895264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35903644561768</t>
+    <t xml:space="preserve">3.35903668403625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36844539642334</t>
+    <t xml:space="preserve">3.36844515800476</t>
   </si>
   <si>
     <t xml:space="preserve">3.38726377487183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45312714576721</t>
+    <t xml:space="preserve">3.45312738418579</t>
   </si>
   <si>
     <t xml:space="preserve">3.52839994430542</t>
@@ -683,19 +680,19 @@
     <t xml:space="preserve">3.63189911842346</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7824444770813</t>
+    <t xml:space="preserve">3.78244423866272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88594388961792</t>
+    <t xml:space="preserve">3.8859441280365</t>
   </si>
   <si>
     <t xml:space="preserve">3.89535307884216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83889889717102</t>
+    <t xml:space="preserve">3.83889865875244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82008099555969</t>
+    <t xml:space="preserve">3.82008075714111</t>
   </si>
   <si>
     <t xml:space="preserve">3.79185342788696</t>
@@ -710,37 +707,40 @@
     <t xml:space="preserve">3.69776296615601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4154908657074</t>
+    <t xml:space="preserve">3.41549110412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35903644561768</t>
   </si>
   <si>
     <t xml:space="preserve">3.48135423660278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24612784385681</t>
+    <t xml:space="preserve">3.24612760543823</t>
   </si>
   <si>
     <t xml:space="preserve">3.15203714370728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21790051460266</t>
+    <t xml:space="preserve">3.21790027618408</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37785458564758</t>
+    <t xml:space="preserve">3.37785482406616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47194528579712</t>
+    <t xml:space="preserve">3.47194504737854</t>
   </si>
   <si>
     <t xml:space="preserve">3.50017261505127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64130830764771</t>
+    <t xml:space="preserve">3.64130854606628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50958156585693</t>
+    <t xml:space="preserve">3.50958132743835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66012644767761</t>
+    <t xml:space="preserve">3.66012668609619</t>
   </si>
   <si>
     <t xml:space="preserve">3.56603622436523</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">3.33080887794495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60367202758789</t>
+    <t xml:space="preserve">3.60367226600647</t>
   </si>
   <si>
     <t xml:space="preserve">4.0458984375</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">4.4034423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55398845672607</t>
+    <t xml:space="preserve">4.55398797988892</t>
   </si>
   <si>
     <t xml:space="preserve">4.68571424484253</t>
@@ -827,13 +827,13 @@
     <t xml:space="preserve">4.54457950592041</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51635122299194</t>
+    <t xml:space="preserve">4.5163516998291</t>
   </si>
   <si>
     <t xml:space="preserve">4.32817029953003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25289821624756</t>
+    <t xml:space="preserve">4.2528977394104</t>
   </si>
   <si>
     <t xml:space="preserve">4.47871541976929</t>
@@ -842,16 +842,16 @@
     <t xml:space="preserve">4.6104416847229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61985111236572</t>
+    <t xml:space="preserve">4.61985158920288</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50694274902344</t>
+    <t xml:space="preserve">4.50694227218628</t>
   </si>
   <si>
     <t xml:space="preserve">4.57280588150024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63866901397705</t>
+    <t xml:space="preserve">4.63866949081421</t>
   </si>
   <si>
     <t xml:space="preserve">4.64807844161987</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">4.1964430809021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17762565612793</t>
+    <t xml:space="preserve">4.17762517929077</t>
   </si>
   <si>
     <t xml:space="preserve">4.23407983779907</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">4.24348926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36580610275269</t>
+    <t xml:space="preserve">4.36580657958984</t>
   </si>
   <si>
     <t xml:space="preserve">4.31876134872437</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">4.56339693069458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44107866287231</t>
+    <t xml:space="preserve">4.44107913970947</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46930694580078</t>
+    <t xml:space="preserve">4.46930646896362</t>
   </si>
   <si>
     <t xml:space="preserve">4.93034982681274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76098775863647</t>
+    <t xml:space="preserve">4.76098728179932</t>
   </si>
   <si>
     <t xml:space="preserve">4.65748739242554</t>
@@ -920,13 +920,13 @@
     <t xml:space="preserve">4.66689682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30935144424438</t>
+    <t xml:space="preserve">4.30935192108154</t>
   </si>
   <si>
     <t xml:space="preserve">4.15880727767944</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14939737319946</t>
+    <t xml:space="preserve">4.14939785003662</t>
   </si>
   <si>
     <t xml:space="preserve">4.22466993331909</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">4.29994297027588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70453310012817</t>
+    <t xml:space="preserve">4.70453262329102</t>
   </si>
   <si>
     <t xml:space="preserve">4.75157833099365</t>
@@ -962,10 +962,10 @@
     <t xml:space="preserve">4.49753332138062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62926054000854</t>
+    <t xml:space="preserve">4.62926006317139</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84566926956177</t>
+    <t xml:space="preserve">4.84566974639893</t>
   </si>
   <si>
     <t xml:space="preserve">4.93975973129272</t>
@@ -8190,7 +8190,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G249" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -8216,7 +8216,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G250" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -8658,7 +8658,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G267" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -8684,7 +8684,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G268" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -8736,7 +8736,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G270" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -8762,7 +8762,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G271" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -8788,7 +8788,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G272" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -8814,7 +8814,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G273" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -8840,7 +8840,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G274" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -8970,7 +8970,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G279" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -8996,7 +8996,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G280" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -9022,7 +9022,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G281" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -9048,7 +9048,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G282" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -9074,7 +9074,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G283" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -9100,7 +9100,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G284" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -9178,7 +9178,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G287" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -9204,7 +9204,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G288" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -10426,7 +10426,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G335" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -10556,7 +10556,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G340" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -10582,7 +10582,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G341" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -10634,7 +10634,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G343" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -10686,7 +10686,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G345" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -10712,7 +10712,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G346" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -10738,7 +10738,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G347" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -10764,7 +10764,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G348" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -10790,7 +10790,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G349" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -10816,7 +10816,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G350" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -10842,7 +10842,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G351" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -10868,7 +10868,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G352" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -11076,7 +11076,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G360" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -11102,7 +11102,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G361" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -11128,7 +11128,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G362" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -11154,7 +11154,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G363" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -11180,7 +11180,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G364" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -11206,7 +11206,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G365" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -11232,7 +11232,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G366" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -11258,7 +11258,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G367" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -11284,7 +11284,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G368" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -11310,7 +11310,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G369" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -11336,7 +11336,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G370" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -11362,7 +11362,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G371" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -11388,7 +11388,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G372" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -11414,7 +11414,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G373" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -11440,7 +11440,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G374" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -11466,7 +11466,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G375" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -11492,7 +11492,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G376" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -11518,7 +11518,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G377" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -11544,7 +11544,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G378" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -11570,7 +11570,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G379" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -11596,7 +11596,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G380" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -11622,7 +11622,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G381" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -11648,7 +11648,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G382" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -11674,7 +11674,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G383" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -11700,7 +11700,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G384" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -11726,7 +11726,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G385" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -11752,7 +11752,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G386" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -11778,7 +11778,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G387" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -11804,7 +11804,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G388" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -11830,7 +11830,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G389" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -11856,7 +11856,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G390" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -11882,7 +11882,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G391" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -11908,7 +11908,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G392" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -11934,7 +11934,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G393" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -11960,7 +11960,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G394" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -11986,7 +11986,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G395" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -12012,7 +12012,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G396" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -12038,7 +12038,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G397" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -12064,7 +12064,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G398" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -12090,7 +12090,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G399" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -12116,7 +12116,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G400" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -12142,7 +12142,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G401" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -12168,7 +12168,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G402" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -12194,7 +12194,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G403" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -12220,7 +12220,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G404" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -12246,7 +12246,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G405" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -12272,7 +12272,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G406" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -12298,7 +12298,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G407" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -12324,7 +12324,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G408" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -12350,7 +12350,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G409" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -12376,7 +12376,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G410" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -12402,7 +12402,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G411" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -12428,7 +12428,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G412" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -12454,7 +12454,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G413" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -12480,7 +12480,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G414" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -12506,7 +12506,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G415" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -12532,7 +12532,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G416" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -12558,7 +12558,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G417" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -12584,7 +12584,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G418" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -12610,7 +12610,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G419" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -12636,7 +12636,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G420" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -12662,7 +12662,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G421" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -12688,7 +12688,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G422" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -12714,7 +12714,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G423" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -12740,7 +12740,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G424" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -12766,7 +12766,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G425" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -12792,7 +12792,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G426" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -12818,7 +12818,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G427" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -12844,7 +12844,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G428" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -12870,7 +12870,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G429" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -12896,7 +12896,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G430" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -12922,7 +12922,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G431" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -12948,7 +12948,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G432" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -12974,7 +12974,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G433" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -13000,7 +13000,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G434" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -13026,7 +13026,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G435" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -13052,7 +13052,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G436" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -13078,7 +13078,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G437" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -13104,7 +13104,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G438" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -13130,7 +13130,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G439" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -13156,7 +13156,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G440" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -13182,7 +13182,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G441" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -13208,7 +13208,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G442" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -13234,7 +13234,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G443" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -13260,7 +13260,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G444" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -13286,7 +13286,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G445" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -13312,7 +13312,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G446" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -13338,7 +13338,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G447" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -13364,7 +13364,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G448" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -13390,7 +13390,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G449" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -13416,7 +13416,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G450" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -13442,7 +13442,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G451" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -13468,7 +13468,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G452" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -13494,7 +13494,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G453" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -13520,7 +13520,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G454" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -13546,7 +13546,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G455" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -13572,7 +13572,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G456" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -13598,7 +13598,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G457" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -13624,7 +13624,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G458" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -13650,7 +13650,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G459" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -13676,7 +13676,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G460" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -13702,7 +13702,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G461" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -13728,7 +13728,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G462" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -13754,7 +13754,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G463" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -13780,7 +13780,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G464" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -13806,7 +13806,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G465" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -13832,7 +13832,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G466" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -13858,7 +13858,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G467" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -13884,7 +13884,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G468" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -13910,7 +13910,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G469" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -13936,7 +13936,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G470" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -13962,7 +13962,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G471" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -13988,7 +13988,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G472" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -14014,7 +14014,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G473" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -14482,7 +14482,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G491" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -14508,7 +14508,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G492" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -14586,7 +14586,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G495" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -14612,7 +14612,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G496" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -14716,7 +14716,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G500" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15652,7 +15652,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G536" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -15678,7 +15678,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G537" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -15704,7 +15704,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G538" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -15730,7 +15730,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G539" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -15756,7 +15756,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G540" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -15782,7 +15782,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G541" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -15808,7 +15808,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G542" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -15834,7 +15834,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G543" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -15860,7 +15860,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G544" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -15886,7 +15886,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G545" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -15912,7 +15912,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G546" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -15938,7 +15938,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G547" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -15964,7 +15964,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G548" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -15990,7 +15990,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G549" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -16016,7 +16016,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G550" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -16042,7 +16042,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G551" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -16068,7 +16068,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G552" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -16094,7 +16094,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G553" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -16120,7 +16120,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G554" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -16146,7 +16146,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G555" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -16172,7 +16172,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G556" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -16198,7 +16198,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G557" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -16224,7 +16224,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G558" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -16250,7 +16250,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G559" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -16276,7 +16276,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G560" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -16302,7 +16302,7 @@
         <v>3</v>
       </c>
       <c r="G561" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -16328,7 +16328,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G562" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -16354,7 +16354,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G563" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -16380,7 +16380,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G564" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -16406,7 +16406,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G565" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -16432,7 +16432,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G566" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -16458,7 +16458,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G567" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -16484,7 +16484,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G568" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -16510,7 +16510,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G569" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -16536,7 +16536,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G570" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -16562,7 +16562,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G571" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -16588,7 +16588,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G572" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -16614,7 +16614,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G573" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -16640,7 +16640,7 @@
         <v>3.5</v>
       </c>
       <c r="G574" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -16666,7 +16666,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G575" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -16692,7 +16692,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G576" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -16718,7 +16718,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G577" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -16744,7 +16744,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G578" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -16770,7 +16770,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G579" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -16796,7 +16796,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G580" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -16822,7 +16822,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G581" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -16848,7 +16848,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G582" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -16874,7 +16874,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G583" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -16900,7 +16900,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G584" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -16926,7 +16926,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G585" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -16952,7 +16952,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G586" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -16978,7 +16978,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G587" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -17004,7 +17004,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G588" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -17030,7 +17030,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G589" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -17056,7 +17056,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G590" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -17082,7 +17082,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G591" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -17108,7 +17108,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G592" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -17134,7 +17134,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G593" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -17160,7 +17160,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G594" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -17186,7 +17186,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G595" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -17212,7 +17212,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G596" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -17238,7 +17238,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G597" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -17264,7 +17264,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G598" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -17290,7 +17290,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G599" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -17316,7 +17316,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G600" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -17342,7 +17342,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G601" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -17368,7 +17368,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G602" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -17394,7 +17394,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G603" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -17420,7 +17420,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G604" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -17446,7 +17446,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G605" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -17472,7 +17472,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G606" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -17498,7 +17498,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G607" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -17524,7 +17524,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G608" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -17550,7 +17550,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G609" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -17576,7 +17576,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G610" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -17602,7 +17602,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G611" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -17628,7 +17628,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G612" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -17654,7 +17654,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G613" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -17680,7 +17680,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G614" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -17706,7 +17706,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G615" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -17732,7 +17732,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G616" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -17758,7 +17758,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G617" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -17784,7 +17784,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G618" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -17810,7 +17810,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G619" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -17836,7 +17836,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G620" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -17862,7 +17862,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G621" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -17888,7 +17888,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G622" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -17914,7 +17914,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G623" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -17940,7 +17940,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G624" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -17966,7 +17966,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G625" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -17992,7 +17992,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G626" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -18018,7 +18018,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G627" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -18044,7 +18044,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G628" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -18070,7 +18070,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G629" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -18096,7 +18096,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G630" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -18122,7 +18122,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G631" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -18148,7 +18148,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G632" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -18174,7 +18174,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G633" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -18200,7 +18200,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G634" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -18226,7 +18226,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G635" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -18252,7 +18252,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G636" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -18278,7 +18278,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G637" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -18304,7 +18304,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G638" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -18330,7 +18330,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G639" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -18356,7 +18356,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G640" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -18382,7 +18382,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G641" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -18408,7 +18408,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G642" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -18434,7 +18434,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G643" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -18460,7 +18460,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G644" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -18486,7 +18486,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G645" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -18512,7 +18512,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G646" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -18538,7 +18538,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G647" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -18564,7 +18564,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G648" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -18590,7 +18590,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G649" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -18616,7 +18616,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G650" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -18642,7 +18642,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G651" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -18668,7 +18668,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G652" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -18694,7 +18694,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G653" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -18720,7 +18720,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G654" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -18746,7 +18746,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G655" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -18772,7 +18772,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G656" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -18798,7 +18798,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G657" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -18824,7 +18824,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G658" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -18850,7 +18850,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G659" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -18876,7 +18876,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G660" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -18902,7 +18902,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G661" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -18928,7 +18928,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G662" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -18954,7 +18954,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G663" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -18980,7 +18980,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G664" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -19006,7 +19006,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G665" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -19032,7 +19032,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G666" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -19058,7 +19058,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G667" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -19084,7 +19084,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G668" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -19110,7 +19110,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G669" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -19136,7 +19136,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G670" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -19162,7 +19162,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G671" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -19188,7 +19188,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G672" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -19214,7 +19214,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G673" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -19240,7 +19240,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G674" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -19266,7 +19266,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G675" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -19292,7 +19292,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G676" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -19318,7 +19318,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G677" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -19344,7 +19344,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G678" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -19370,7 +19370,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G679" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -19396,7 +19396,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G680" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -19422,7 +19422,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G681" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -19448,7 +19448,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G682" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -19474,7 +19474,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G683" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -19500,7 +19500,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G684" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -19526,7 +19526,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G685" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -19552,7 +19552,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G686" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -19578,7 +19578,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G687" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -19604,7 +19604,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G688" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -19630,7 +19630,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G689" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -19656,7 +19656,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G690" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -19682,7 +19682,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G691" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -19708,7 +19708,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G692" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -19734,7 +19734,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G693" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -19760,7 +19760,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G694" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -19786,7 +19786,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G695" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -19812,7 +19812,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G696" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -19838,7 +19838,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G697" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -19864,7 +19864,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G698" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -19890,7 +19890,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G699" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -19916,7 +19916,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G700" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -19942,7 +19942,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G701" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -19968,7 +19968,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G702" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -19994,7 +19994,7 @@
         <v>4.5</v>
       </c>
       <c r="G703" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -20020,7 +20020,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G704" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -20046,7 +20046,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G705" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -20072,7 +20072,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G706" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -20098,7 +20098,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G707" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -20124,7 +20124,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G708" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -20150,7 +20150,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G709" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -20176,7 +20176,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G710" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -20202,7 +20202,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G711" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -20228,7 +20228,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G712" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -20254,7 +20254,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G713" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -20280,7 +20280,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G714" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -20306,7 +20306,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G715" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -20332,7 +20332,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G716" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -20358,7 +20358,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G717" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -20384,7 +20384,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G718" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -20410,7 +20410,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G719" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -20436,7 +20436,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G720" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -20462,7 +20462,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G721" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -20488,7 +20488,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G722" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -20514,7 +20514,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G723" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -20540,7 +20540,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G724" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -20566,7 +20566,7 @@
         <v>4</v>
       </c>
       <c r="G725" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -20592,7 +20592,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G726" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -20618,7 +20618,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G727" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -20644,7 +20644,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G728" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -20670,7 +20670,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G729" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -20696,7 +20696,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G730" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -20722,7 +20722,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G731" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -20748,7 +20748,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G732" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -20774,7 +20774,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G733" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -20800,7 +20800,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G734" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -20826,7 +20826,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G735" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -20852,7 +20852,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G736" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -20878,7 +20878,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G737" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -20904,7 +20904,7 @@
         <v>4.5</v>
       </c>
       <c r="G738" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -20930,7 +20930,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G739" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -20956,7 +20956,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G740" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -20982,7 +20982,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G741" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -21008,7 +21008,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G742" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -21034,7 +21034,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G743" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -21060,7 +21060,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G744" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -21086,7 +21086,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G745" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -21112,7 +21112,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G746" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -21138,7 +21138,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G747" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -21164,7 +21164,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G748" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -21190,7 +21190,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G749" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -21216,7 +21216,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G750" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -21242,7 +21242,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G751" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -21268,7 +21268,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G752" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -21294,7 +21294,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G753" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -21320,7 +21320,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G754" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -21346,7 +21346,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G755" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -21372,7 +21372,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G756" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -21398,7 +21398,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G757" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -21424,7 +21424,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G758" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -21450,7 +21450,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G759" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -21476,7 +21476,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G760" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -21502,7 +21502,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G761" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -21528,7 +21528,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G762" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -21554,7 +21554,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G763" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -21580,7 +21580,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G764" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -21606,7 +21606,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G765" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -21632,7 +21632,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G766" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -21658,7 +21658,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G767" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -21684,7 +21684,7 @@
         <v>4</v>
       </c>
       <c r="G768" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -21710,7 +21710,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G769" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -21736,7 +21736,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G770" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -21762,7 +21762,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G771" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -21788,7 +21788,7 @@
         <v>4</v>
       </c>
       <c r="G772" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -21814,7 +21814,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G773" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -21840,7 +21840,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G774" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -21866,7 +21866,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G775" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -21892,7 +21892,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G776" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -21918,7 +21918,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G777" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -21944,7 +21944,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G778" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -21970,7 +21970,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G779" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -21996,7 +21996,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G780" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -22022,7 +22022,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G781" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -22048,7 +22048,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G782" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -22074,7 +22074,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G783" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -22100,7 +22100,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G784" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -22126,7 +22126,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G785" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -22152,7 +22152,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G786" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -22178,7 +22178,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G787" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -22204,7 +22204,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G788" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -22230,7 +22230,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G789" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -22256,7 +22256,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G790" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -22282,7 +22282,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G791" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -22308,7 +22308,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G792" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -22334,7 +22334,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G793" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -22360,7 +22360,7 @@
         <v>4</v>
       </c>
       <c r="G794" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -22386,7 +22386,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G795" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -22412,7 +22412,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G796" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -22438,7 +22438,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G797" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -22464,7 +22464,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G798" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -22490,7 +22490,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G799" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -22516,7 +22516,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G800" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -22542,7 +22542,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G801" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -22568,7 +22568,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G802" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -22594,7 +22594,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G803" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -22620,7 +22620,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G804" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -22646,7 +22646,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G805" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -22672,7 +22672,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G806" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -22698,7 +22698,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G807" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -22724,7 +22724,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G808" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -22750,7 +22750,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G809" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -22776,7 +22776,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G810" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -22802,7 +22802,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G811" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -22828,7 +22828,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G812" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -22854,7 +22854,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G813" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -22880,7 +22880,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G814" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -22906,7 +22906,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G815" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -22932,7 +22932,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G816" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -22958,7 +22958,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G817" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -22984,7 +22984,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G818" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -23010,7 +23010,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G819" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -23036,7 +23036,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G820" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -23062,7 +23062,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G821" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -23088,7 +23088,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G822" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -23114,7 +23114,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G823" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -23140,7 +23140,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G824" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -23166,7 +23166,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G825" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -23192,7 +23192,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G826" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -23218,7 +23218,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G827" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -23244,7 +23244,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G828" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -23270,7 +23270,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G829" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -23296,7 +23296,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G830" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -23322,7 +23322,7 @@
         <v>3.75</v>
       </c>
       <c r="G831" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -23348,7 +23348,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G832" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -23374,7 +23374,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G833" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -23400,7 +23400,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G834" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -23426,7 +23426,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G835" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -23452,7 +23452,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G836" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -23478,7 +23478,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G837" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -23504,7 +23504,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G838" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -23530,7 +23530,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G839" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -23556,7 +23556,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G840" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -23582,7 +23582,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G841" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -23608,7 +23608,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G842" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -23634,7 +23634,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G843" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -23660,7 +23660,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G844" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -23686,7 +23686,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G845" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -23712,7 +23712,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G846" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -23738,7 +23738,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G847" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -23816,7 +23816,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G850" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24128,7 +24128,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G862" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -24180,7 +24180,7 @@
         <v>3.75</v>
       </c>
       <c r="G864" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -24258,7 +24258,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G867" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -24440,7 +24440,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G874" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -24492,7 +24492,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G876" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -24518,7 +24518,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G877" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -24544,7 +24544,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G878" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -24622,7 +24622,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G881" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -24648,7 +24648,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G882" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -24700,7 +24700,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G884" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -24726,7 +24726,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G885" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -24752,7 +24752,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G886" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -24830,7 +24830,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G889" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -24856,7 +24856,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G890" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -24882,7 +24882,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G891" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -24934,7 +24934,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G893" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -25064,7 +25064,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G898" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -25090,7 +25090,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G899" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -25194,7 +25194,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G903" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -25272,7 +25272,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G906" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -25428,7 +25428,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G912" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -25506,7 +25506,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G915" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -25532,7 +25532,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G916" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -25558,7 +25558,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G917" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -25584,7 +25584,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G918" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -25636,7 +25636,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G920" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -25662,7 +25662,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G921" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26104,7 +26104,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G938" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26364,7 +26364,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G948" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -26390,7 +26390,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G949" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26442,7 +26442,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G951" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -45820,7 +45820,7 @@
     </row>
     <row r="1697">
       <c r="A1697" s="1" t="n">
-        <v>45946.6494907407</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B1697" t="n">
         <v>4200</v>
@@ -45841,6 +45841,32 @@
         <v>457</v>
       </c>
       <c r="H1697" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" s="1" t="n">
+        <v>45947.6494444444</v>
+      </c>
+      <c r="B1698" t="n">
+        <v>13800</v>
+      </c>
+      <c r="C1698" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="D1698" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="E1698" t="n">
+        <v>5.84999990463257</v>
+      </c>
+      <c r="F1698" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="G1698" t="s">
+        <v>447</v>
+      </c>
+      <c r="H1698" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ILP.MI.xlsx
+++ b/data/ILP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="459">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,1354 +38,1357 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97119569778442</t>
+    <t xml:space="preserve">1.9502626657486</t>
   </si>
   <si>
     <t xml:space="preserve">ILP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99759519100189</t>
+    <t xml:space="preserve">1.97638237476349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93599545955658</t>
+    <t xml:space="preserve">1.91543638706207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96195590496063</t>
+    <t xml:space="preserve">1.94112062454224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.028395652771</t>
+    <t xml:space="preserve">2.00685524940491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00111556053162</t>
+    <t xml:space="preserve">1.97986459732056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95359587669373</t>
+    <t xml:space="preserve">1.93284952640533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97955548763275</t>
+    <t xml:space="preserve">1.95853364467621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94171547889709</t>
+    <t xml:space="preserve">1.92109608650208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96283566951752</t>
+    <t xml:space="preserve">1.94199156761169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97515559196472</t>
+    <t xml:space="preserve">1.95418083667755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95139539241791</t>
+    <t xml:space="preserve">1.93067288398743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90959584712982</t>
+    <t xml:space="preserve">1.88931703567505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88803589344025</t>
+    <t xml:space="preserve">1.86798620223999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91091549396515</t>
+    <t xml:space="preserve">1.8906227350235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94039595127106</t>
+    <t xml:space="preserve">1.91978991031647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96239578723907</t>
+    <t xml:space="preserve">1.94155621528625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95887553691864</t>
+    <t xml:space="preserve">1.93807339668274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9377555847168</t>
+    <t xml:space="preserve">1.91717755794525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99671566486359</t>
+    <t xml:space="preserve">1.97551167011261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9553554058075</t>
+    <t xml:space="preserve">1.93459069728851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98879599571228</t>
+    <t xml:space="preserve">1.96767520904541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04951548576355</t>
+    <t xml:space="preserve">2.02775073051453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03719568252563</t>
+    <t xml:space="preserve">2.01556181907654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02399563789368</t>
+    <t xml:space="preserve">2.00250148773193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04159545898438</t>
+    <t xml:space="preserve">2.0199146270752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91839587688446</t>
+    <t xml:space="preserve">1.8980233669281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00639533996582</t>
+    <t xml:space="preserve">1.98508858680725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90079593658447</t>
+    <t xml:space="preserve">1.88061046600342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86559581756592</t>
+    <t xml:space="preserve">1.8457840681076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88319599628448</t>
+    <t xml:space="preserve">1.86319720745087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91022717952728</t>
+    <t xml:space="preserve">1.88994169235229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92824828624725</t>
+    <t xml:space="preserve">1.90777134895325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89220631122589</t>
+    <t xml:space="preserve">1.87211203575134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94626951217651</t>
+    <t xml:space="preserve">1.9256010055542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96429026126862</t>
+    <t xml:space="preserve">1.94343078136444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9823112487793</t>
+    <t xml:space="preserve">1.9612603187561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00033259391785</t>
+    <t xml:space="preserve">1.97908985614777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85616409778595</t>
+    <t xml:space="preserve">1.83645308017731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83814334869385</t>
+    <t xml:space="preserve">1.81862306594849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78408026695251</t>
+    <t xml:space="preserve">1.76513433456421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87418520450592</t>
+    <t xml:space="preserve">1.8542822599411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82012236118317</t>
+    <t xml:space="preserve">1.80079352855682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80210137367249</t>
+    <t xml:space="preserve">1.78296399116516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95527970790863</t>
+    <t xml:space="preserve">1.93451595306396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97330105304718</t>
+    <t xml:space="preserve">1.95234537124634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90121674537659</t>
+    <t xml:space="preserve">1.88102698326111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91923797130585</t>
+    <t xml:space="preserve">1.89885652065277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84715378284454</t>
+    <t xml:space="preserve">1.82753789424896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86517477035522</t>
+    <t xml:space="preserve">1.8453676700592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74803829193115</t>
+    <t xml:space="preserve">1.72947514057159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79309070110321</t>
+    <t xml:space="preserve">1.7740490436554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78858554363251</t>
+    <t xml:space="preserve">1.76959180831909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81111168861389</t>
+    <t xml:space="preserve">1.79187881946564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82913291454315</t>
+    <t xml:space="preserve">1.80970859527588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79759585857391</t>
+    <t xml:space="preserve">1.77850663661957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72551202774048</t>
+    <t xml:space="preserve">1.70718801021576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74353289604187</t>
+    <t xml:space="preserve">1.72501742839813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76605939865112</t>
+    <t xml:space="preserve">1.74730467796326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75704860687256</t>
+    <t xml:space="preserve">1.73838996887207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77506971359253</t>
+    <t xml:space="preserve">1.75621950626373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73001730442047</t>
+    <t xml:space="preserve">1.71164548397064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73902761936188</t>
+    <t xml:space="preserve">1.72055995464325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71199631690979</t>
+    <t xml:space="preserve">1.69381558895111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65793323516846</t>
+    <t xml:space="preserve">1.64032685756683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66694366931915</t>
+    <t xml:space="preserve">1.6492418050766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69397509098053</t>
+    <t xml:space="preserve">1.67598605155945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58584916591644</t>
+    <t xml:space="preserve">1.56900823116302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68496465682983</t>
+    <t xml:space="preserve">1.66707122325897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64892268180847</t>
+    <t xml:space="preserve">1.63141191005707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67595422267914</t>
+    <t xml:space="preserve">1.65815627574921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70298540592194</t>
+    <t xml:space="preserve">1.68490076065063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7210066318512</t>
+    <t xml:space="preserve">1.70273053646088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6309015750885</t>
+    <t xml:space="preserve">1.61358225345612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0543954372406</t>
+    <t xml:space="preserve">2.03257870674133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2165846824646</t>
+    <t xml:space="preserve">2.19304537773132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16252183914185</t>
+    <t xml:space="preserve">2.13955640792847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41481566429138</t>
+    <t xml:space="preserve">2.3891716003418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36075234413147</t>
+    <t xml:space="preserve">2.33568263053894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57700490951538</t>
+    <t xml:space="preserve">2.54963803291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61304712295532</t>
+    <t xml:space="preserve">2.58529758453369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0635724067688</t>
+    <t xml:space="preserve">3.03103852272034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46003460884094</t>
+    <t xml:space="preserve">3.42329096794128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.261803150177</t>
+    <t xml:space="preserve">3.22716450691223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22576117515564</t>
+    <t xml:space="preserve">3.19150519371033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17169833183289</t>
+    <t xml:space="preserve">3.13801646232605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04555106163025</t>
+    <t xml:space="preserve">3.01320934295654</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02752995491028</t>
+    <t xml:space="preserve">2.99537944793701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00950908660889</t>
+    <t xml:space="preserve">2.97754979133606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11763525009155</t>
+    <t xml:space="preserve">3.08452773094177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91940426826477</t>
+    <t xml:space="preserve">2.88840198516846</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7391939163208</t>
+    <t xml:space="preserve">2.71010518074036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72117280960083</t>
+    <t xml:space="preserve">2.6922755241394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70315217971802</t>
+    <t xml:space="preserve">2.67444610595703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82929873466492</t>
+    <t xml:space="preserve">2.79925346374512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86534070968628</t>
+    <t xml:space="preserve">2.8349130153656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93742489814758</t>
+    <t xml:space="preserve">2.90623140335083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8112781047821</t>
+    <t xml:space="preserve">2.78142356872559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90138292312622</t>
+    <t xml:space="preserve">2.87057185173035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03781127929688</t>
+    <t xml:space="preserve">3.0055513381958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11057353019714</t>
+    <t xml:space="preserve">3.07754111289978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0196213722229</t>
+    <t xml:space="preserve">2.98755431175232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09238338470459</t>
+    <t xml:space="preserve">3.05954337120056</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18333530426025</t>
+    <t xml:space="preserve">3.14953017234802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23790717124939</t>
+    <t xml:space="preserve">3.2035219669342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36524033546448</t>
+    <t xml:space="preserve">3.32950377464294</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41981196403503</t>
+    <t xml:space="preserve">3.38349556922913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40162134170532</t>
+    <t xml:space="preserve">3.36549806594849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38343119621277</t>
+    <t xml:space="preserve">3.34750080108643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31066918373108</t>
+    <t xml:space="preserve">3.27551174163818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34704995155334</t>
+    <t xml:space="preserve">3.31150603294373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32885956764221</t>
+    <t xml:space="preserve">3.29350876808167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45619297027588</t>
+    <t xml:space="preserve">3.41948986053467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29247832298279</t>
+    <t xml:space="preserve">3.25751399993896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27428793907166</t>
+    <t xml:space="preserve">3.23951625823975</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25609707832336</t>
+    <t xml:space="preserve">3.22151923179626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43800234794617</t>
+    <t xml:space="preserve">3.40149259567261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47438311576843</t>
+    <t xml:space="preserve">3.43748736381531</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69266939163208</t>
+    <t xml:space="preserve">3.65345525741577</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60171675682068</t>
+    <t xml:space="preserve">3.56346869468689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67447853088379</t>
+    <t xml:space="preserve">3.63545799255371</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91095495223999</t>
+    <t xml:space="preserve">3.86942291259766</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03828907012939</t>
+    <t xml:space="preserve">3.99540400505066</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05647897720337</t>
+    <t xml:space="preserve">4.01340055465698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98371696472168</t>
+    <t xml:space="preserve">3.94141221046448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80181217193604</t>
+    <t xml:space="preserve">3.76143884658813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96552681922913</t>
+    <t xml:space="preserve">3.92341494560242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0200982093811</t>
+    <t xml:space="preserve">3.9774067401886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92914533615112</t>
+    <t xml:space="preserve">3.88741970062256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89276504516602</t>
+    <t xml:space="preserve">3.85142540931702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94733643531799</t>
+    <t xml:space="preserve">3.90541791915894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22019338607788</t>
+    <t xml:space="preserve">4.175377368927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20200300216675</t>
+    <t xml:space="preserve">4.15737962722778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29295539855957</t>
+    <t xml:space="preserve">4.24736595153809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40209865570068</t>
+    <t xml:space="preserve">4.35535049438477</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43847990036011</t>
+    <t xml:space="preserve">4.39134502410889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36571741104126</t>
+    <t xml:space="preserve">4.31935596466064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34752702713013</t>
+    <t xml:space="preserve">4.30135917663574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37498474121094</t>
+    <t xml:space="preserve">4.32852554321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39329051971436</t>
+    <t xml:space="preserve">4.34663534164429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28345775604248</t>
+    <t xml:space="preserve">4.23796939849854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24684715270996</t>
+    <t xml:space="preserve">4.20174789428711</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26515245437622</t>
+    <t xml:space="preserve">4.21985912322998</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17362594604492</t>
+    <t xml:space="preserve">4.12930345535278</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10040378570557</t>
+    <t xml:space="preserve">4.05686044692993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21023607254028</t>
+    <t xml:space="preserve">4.16552591323853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13701486587524</t>
+    <t xml:space="preserve">4.09308195114136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48481702804565</t>
+    <t xml:space="preserve">4.43719148635864</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33837413787842</t>
+    <t xml:space="preserve">4.29230213165283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15532064437866</t>
+    <t xml:space="preserve">4.11119318008423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3017635345459</t>
+    <t xml:space="preserve">4.25608015060425</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46651220321655</t>
+    <t xml:space="preserve">4.41907978057861</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19193124771118</t>
+    <t xml:space="preserve">4.14741468429565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11870956420898</t>
+    <t xml:space="preserve">4.07497119903564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06379365921021</t>
+    <t xml:space="preserve">4.02063798904419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99057197570801</t>
+    <t xml:space="preserve">3.94819450378418</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97226667404175</t>
+    <t xml:space="preserve">3.93008351325989</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93565583229065</t>
+    <t xml:space="preserve">3.8938615322113</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02718257904053</t>
+    <t xml:space="preserve">3.98441624641418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08209848403931</t>
+    <t xml:space="preserve">4.03874826431274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95396089553833</t>
+    <t xml:space="preserve">3.91197204589844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91735053062439</t>
+    <t xml:space="preserve">3.87575006484985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78921270370483</t>
+    <t xml:space="preserve">3.74897336959839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86243438720703</t>
+    <t xml:space="preserve">3.82141733169556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88073921203613</t>
+    <t xml:space="preserve">3.83952832221985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66107535362244</t>
+    <t xml:space="preserve">3.62219667434692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77090740203857</t>
+    <t xml:space="preserve">3.73086285591125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69768571853638</t>
+    <t xml:space="preserve">3.65841841697693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82582354545593</t>
+    <t xml:space="preserve">3.78519511222839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04548835754395</t>
+    <t xml:space="preserve">4.00252723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2285418510437</t>
+    <t xml:space="preserve">4.1836371421814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35667943954468</t>
+    <t xml:space="preserve">4.31041479110718</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00887727737427</t>
+    <t xml:space="preserve">3.96630525588989</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84412860870361</t>
+    <t xml:space="preserve">3.80330610275269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75260186195374</t>
+    <t xml:space="preserve">3.71275115013123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47802138328552</t>
+    <t xml:space="preserve">3.44108653068542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56954836845398</t>
+    <t xml:space="preserve">3.53164172172546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5329372882843</t>
+    <t xml:space="preserve">3.4954195022583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42310523986816</t>
+    <t xml:space="preserve">3.38675379753113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18513536453247</t>
+    <t xml:space="preserve">3.15131115913391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76411175727844</t>
+    <t xml:space="preserve">2.73475861549377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83733296394348</t>
+    <t xml:space="preserve">2.80720210075378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72750115394592</t>
+    <t xml:space="preserve">2.69853615760803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61766862869263</t>
+    <t xml:space="preserve">2.58987045288086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80072259902954</t>
+    <t xml:space="preserve">2.77098035812378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9288604259491</t>
+    <t xml:space="preserve">2.89775776863098</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13021898269653</t>
+    <t xml:space="preserve">3.09697794914246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16682982444763</t>
+    <t xml:space="preserve">3.13320016860962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36818933486938</t>
+    <t xml:space="preserve">3.33242058753967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4047999382019</t>
+    <t xml:space="preserve">3.36864280700684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.441410779953</t>
+    <t xml:space="preserve">3.404865026474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34988379478455</t>
+    <t xml:space="preserve">3.31430959701538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22174620628357</t>
+    <t xml:space="preserve">3.18753290176392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25835680961609</t>
+    <t xml:space="preserve">3.2237548828125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6061589717865</t>
+    <t xml:space="preserve">3.56786346435547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58785390853882</t>
+    <t xml:space="preserve">3.54975247383118</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59700655937195</t>
+    <t xml:space="preserve">3.55880808830261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55124306678772</t>
+    <t xml:space="preserve">3.51353073120117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48717403411865</t>
+    <t xml:space="preserve">3.45014214515686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45971584320068</t>
+    <t xml:space="preserve">3.42297554016113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38649463653564</t>
+    <t xml:space="preserve">3.35053205490112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45056343078613</t>
+    <t xml:space="preserve">3.41392016410828</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37734174728394</t>
+    <t xml:space="preserve">3.34147620201111</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28581523895264</t>
+    <t xml:space="preserve">3.25092101097107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35903668403625</t>
+    <t xml:space="preserve">3.3233654499054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36844515800476</t>
+    <t xml:space="preserve">3.33267426490784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38726377487183</t>
+    <t xml:space="preserve">3.35129237174988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45312738418579</t>
+    <t xml:space="preserve">3.41645693778992</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52839994430542</t>
+    <t xml:space="preserve">3.49092984199524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40608167648315</t>
+    <t xml:space="preserve">3.36991095542908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57544493675232</t>
+    <t xml:space="preserve">3.5374755859375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66953563690186</t>
+    <t xml:space="preserve">3.63056755065918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63189911842346</t>
+    <t xml:space="preserve">3.59333038330078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78244423866272</t>
+    <t xml:space="preserve">3.74227690696716</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8859441280365</t>
+    <t xml:space="preserve">3.84467768669128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89535307884216</t>
+    <t xml:space="preserve">3.85398650169373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83889865875244</t>
+    <t xml:space="preserve">3.79813170433044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82008075714111</t>
+    <t xml:space="preserve">3.7795135974884</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79185342788696</t>
+    <t xml:space="preserve">3.75158619880676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71658086776733</t>
+    <t xml:space="preserve">3.67711281776428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70717191696167</t>
+    <t xml:space="preserve">3.66780376434326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69776296615601</t>
+    <t xml:space="preserve">3.65849447250366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41549110412598</t>
+    <t xml:space="preserve">3.37922048568726</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35903644561768</t>
+    <t xml:space="preserve">3.32336521148682</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48135423660278</t>
+    <t xml:space="preserve">3.44438433647156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24612760543823</t>
+    <t xml:space="preserve">3.21165561676025</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15203714370728</t>
+    <t xml:space="preserve">3.11856389045715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21790027618408</t>
+    <t xml:space="preserve">3.18372797966003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37785482406616</t>
+    <t xml:space="preserve">3.34198331832886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47194504737854</t>
+    <t xml:space="preserve">3.43507480621338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50017261505127</t>
+    <t xml:space="preserve">3.46300268173218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64130854606628</t>
+    <t xml:space="preserve">3.60263967514038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50958132743835</t>
+    <t xml:space="preserve">3.4723117351532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66012668609619</t>
+    <t xml:space="preserve">3.62125825881958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56603622436523</t>
+    <t xml:space="preserve">3.52816653251648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5189905166626</t>
+    <t xml:space="preserve">3.48162078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46253633499146</t>
+    <t xml:space="preserve">3.42576575279236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68835377693176</t>
+    <t xml:space="preserve">3.64918541908264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76362633705139</t>
+    <t xml:space="preserve">3.72365880012512</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55662679672241</t>
+    <t xml:space="preserve">3.51885747909546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81067180633545</t>
+    <t xml:space="preserve">3.77020454406738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6224901676178</t>
+    <t xml:space="preserve">3.58402132987976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74480819702148</t>
+    <t xml:space="preserve">3.70504021644592</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72599005699158</t>
+    <t xml:space="preserve">3.68642234802246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84830808639526</t>
+    <t xml:space="preserve">3.80744123458862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33080887794495</t>
+    <t xml:space="preserve">3.29543805122375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60367226600647</t>
+    <t xml:space="preserve">3.56540322303772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0458984375</t>
+    <t xml:space="preserve">4.00293302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97062587738037</t>
+    <t xml:space="preserve">3.92845988273621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82948994636536</t>
+    <t xml:space="preserve">3.78882265090942</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02708053588867</t>
+    <t xml:space="preserve">3.98431444168091</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90476250648499</t>
+    <t xml:space="preserve">3.8632960319519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85771703720093</t>
+    <t xml:space="preserve">3.81674981117249</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13057994842529</t>
+    <t xml:space="preserve">4.08671569824219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20585203170776</t>
+    <t xml:space="preserve">4.16118812561035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27171611785889</t>
+    <t xml:space="preserve">4.22635221481323</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43167018890381</t>
+    <t xml:space="preserve">4.38460779190063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53516960144043</t>
+    <t xml:space="preserve">4.48700904846191</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4034423828125</t>
+    <t xml:space="preserve">4.35668039321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55398797988892</t>
+    <t xml:space="preserve">4.50562715530396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68571424484253</t>
+    <t xml:space="preserve">4.6359543800354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54457950592041</t>
+    <t xml:space="preserve">4.49631786346436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5163516998291</t>
+    <t xml:space="preserve">4.46839046478271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32817029953003</t>
+    <t xml:space="preserve">4.28220748901367</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2528977394104</t>
+    <t xml:space="preserve">4.20773410797119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47871541976929</t>
+    <t xml:space="preserve">4.43115425109863</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6104416847229</t>
+    <t xml:space="preserve">4.56148242950439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61985158920288</t>
+    <t xml:space="preserve">4.57079076766968</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50694227218628</t>
+    <t xml:space="preserve">4.45908117294312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57280588150024</t>
+    <t xml:space="preserve">4.524245262146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63866949081421</t>
+    <t xml:space="preserve">4.58940887451172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64807844161987</t>
+    <t xml:space="preserve">4.59871864318848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48812437057495</t>
+    <t xml:space="preserve">4.44046306610107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42226076126099</t>
+    <t xml:space="preserve">4.37529850006104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4598970413208</t>
+    <t xml:space="preserve">4.41253471374512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33757972717285</t>
+    <t xml:space="preserve">4.29151678085327</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37521553039551</t>
+    <t xml:space="preserve">4.32875299453735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28112506866455</t>
+    <t xml:space="preserve">4.23566150665283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38462448120117</t>
+    <t xml:space="preserve">4.33806228637695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1964430809021</t>
+    <t xml:space="preserve">4.15187883377075</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17762517929077</t>
+    <t xml:space="preserve">4.13326120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23407983779907</t>
+    <t xml:space="preserve">4.18911600112915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39403390884399</t>
+    <t xml:space="preserve">4.34737110137939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24348926544189</t>
+    <t xml:space="preserve">4.19842576980591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36580657958984</t>
+    <t xml:space="preserve">4.31944370269775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31876134872437</t>
+    <t xml:space="preserve">4.27289819717407</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56339693069458</t>
+    <t xml:space="preserve">4.51493644714355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44107913970947</t>
+    <t xml:space="preserve">4.39391660690308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46930646896362</t>
+    <t xml:space="preserve">4.42184495925903</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93034982681274</t>
+    <t xml:space="preserve">4.87799263000488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76098728179932</t>
+    <t xml:space="preserve">4.71042823791504</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65748739242554</t>
+    <t xml:space="preserve">4.60802745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66689682006836</t>
+    <t xml:space="preserve">4.61733675003052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30935192108154</t>
+    <t xml:space="preserve">4.26358890533447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15880727767944</t>
+    <t xml:space="preserve">4.11464262008667</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14939785003662</t>
+    <t xml:space="preserve">4.10533380508423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22466993331909</t>
+    <t xml:space="preserve">4.17980623245239</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12117052078247</t>
+    <t xml:space="preserve">4.07740640640259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99885296821594</t>
+    <t xml:space="preserve">3.95638728141785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95180749893188</t>
+    <t xml:space="preserve">3.90984129905701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08353471755981</t>
+    <t xml:space="preserve">4.04017019271851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29994297027588</t>
+    <t xml:space="preserve">4.25428056716919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70453262329102</t>
+    <t xml:space="preserve">4.6545729637146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75157833099365</t>
+    <t xml:space="preserve">4.70111894607544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59162425994873</t>
+    <t xml:space="preserve">4.54286336898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34698867797852</t>
+    <t xml:space="preserve">4.30082559585571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49753332138062</t>
+    <t xml:space="preserve">4.44977283477783</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62926006317139</t>
+    <t xml:space="preserve">4.58010005950928</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84566974639893</t>
+    <t xml:space="preserve">4.79421043395996</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93975973129272</t>
+    <t xml:space="preserve">4.88730192184448</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66643905639648</t>
+    <t xml:space="preserve">4.61688470840454</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64739322662354</t>
+    <t xml:space="preserve">4.59804010391235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57120609283447</t>
+    <t xml:space="preserve">4.52266263961792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62834596633911</t>
+    <t xml:space="preserve">4.57919549942017</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60930013656616</t>
+    <t xml:space="preserve">4.56035137176514</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49501895904541</t>
+    <t xml:space="preserve">4.44728422164917</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72357988357544</t>
+    <t xml:space="preserve">4.67341804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74262571334839</t>
+    <t xml:space="preserve">4.69226217269897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85690689086914</t>
+    <t xml:space="preserve">4.80532836914062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95213937759399</t>
+    <t xml:space="preserve">4.89955043792725</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90452337265015</t>
+    <t xml:space="preserve">4.85244035720825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04737329483032</t>
+    <t xml:space="preserve">4.99377393722534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99975681304932</t>
+    <t xml:space="preserve">4.94666194915771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09499025344849</t>
+    <t xml:space="preserve">5.04088401794434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28545713424683</t>
+    <t xml:space="preserve">5.22932863235474</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66639041900635</t>
+    <t xml:space="preserve">5.60621690750122</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57115697860718</t>
+    <t xml:space="preserve">5.5119948387146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76162481307983</t>
+    <t xml:space="preserve">5.70043897628784</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71400785446167</t>
+    <t xml:space="preserve">5.65332794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">5.380690574646</t>
+    <t xml:space="preserve">5.32355117797852</t>
   </si>
   <si>
-    <t xml:space="preserve">5.428307056427</t>
+    <t xml:space="preserve">5.37066173553467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23784065246582</t>
+    <t xml:space="preserve">5.18221712112427</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1902232170105</t>
+    <t xml:space="preserve">5.1351056098938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14260721206665</t>
+    <t xml:space="preserve">5.08799505233765</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80928993225098</t>
+    <t xml:space="preserve">4.75821781158447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76167345046997</t>
+    <t xml:space="preserve">4.71110677719116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81835985183716</t>
+    <t xml:space="preserve">4.7671914100647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74126625061035</t>
+    <t xml:space="preserve">4.69091606140137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76053905487061</t>
+    <t xml:space="preserve">4.70998525619507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86654329299927</t>
+    <t xml:space="preserve">4.81486320495605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79908561706543</t>
+    <t xml:space="preserve">4.748122215271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72199201583862</t>
+    <t xml:space="preserve">4.67184782028198</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58707857131958</t>
+    <t xml:space="preserve">4.53836679458618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70271921157837</t>
+    <t xml:space="preserve">4.65277862548828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6256251335144</t>
+    <t xml:space="preserve">4.57650375366211</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77981281280518</t>
+    <t xml:space="preserve">4.72905397415161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91472721099854</t>
+    <t xml:space="preserve">4.86253452301025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96291065216064</t>
+    <t xml:space="preserve">4.91020727157593</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0110936164856</t>
+    <t xml:space="preserve">4.95787858963013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6834454536438</t>
+    <t xml:space="preserve">4.63370990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66417264938354</t>
+    <t xml:space="preserve">4.6146411895752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64489841461182</t>
+    <t xml:space="preserve">4.59557294845581</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60635185241699</t>
+    <t xml:space="preserve">4.55743551254272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79980039596558</t>
+    <t xml:space="preserve">4.74882841110229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76077699661255</t>
+    <t xml:space="preserve">4.71022081375122</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83882284164429</t>
+    <t xml:space="preserve">4.78743743896484</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07295894622803</t>
+    <t xml:space="preserve">5.01908683776855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21929454803467</t>
+    <t xml:space="preserve">5.16386842727661</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51196527481079</t>
+    <t xml:space="preserve">5.45343112945557</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41440868377686</t>
+    <t xml:space="preserve">5.35691070556641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36563014984131</t>
+    <t xml:space="preserve">5.30865001678467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46318674087524</t>
+    <t xml:space="preserve">5.40517044067383</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31685161590576</t>
+    <t xml:space="preserve">5.26038932800293</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56074333190918</t>
+    <t xml:space="preserve">5.5016918182373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80463600158691</t>
+    <t xml:space="preserve">5.74299383163452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65830087661743</t>
+    <t xml:space="preserve">5.59821271896362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70707941055298</t>
+    <t xml:space="preserve">5.64647340774536</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60952234268188</t>
+    <t xml:space="preserve">5.54995250701904</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26807355880737</t>
+    <t xml:space="preserve">5.21212911605835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12173795700073</t>
+    <t xml:space="preserve">5.06734752655029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97540235519409</t>
+    <t xml:space="preserve">4.92256593704224</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17051649093628</t>
+    <t xml:space="preserve">5.11560869216919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92662382125854</t>
+    <t xml:space="preserve">4.87430620193481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.877845287323</t>
+    <t xml:space="preserve">4.82604551315308</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02418088912964</t>
+    <t xml:space="preserve">4.97082710266113</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91560316085815</t>
+    <t xml:space="preserve">4.86340236663818</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98469829559326</t>
+    <t xml:space="preserve">4.93176364898682</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03405141830444</t>
+    <t xml:space="preserve">4.98059272766113</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93534469604492</t>
+    <t xml:space="preserve">4.88293409347534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8366379737854</t>
+    <t xml:space="preserve">4.78527545928955</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85637950897217</t>
+    <t xml:space="preserve">4.80480718612671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73793125152588</t>
+    <t xml:space="preserve">4.68761682510376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67870664596558</t>
+    <t xml:space="preserve">4.62902116775513</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6392240524292</t>
+    <t xml:space="preserve">4.58995771408081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65896511077881</t>
+    <t xml:space="preserve">4.60948991775513</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59974098205566</t>
+    <t xml:space="preserve">4.55089426040649</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56025838851929</t>
+    <t xml:space="preserve">4.51183128356934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57999992370605</t>
+    <t xml:space="preserve">4.53136253356934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54051685333252</t>
+    <t xml:space="preserve">4.49229907989502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.441810131073</t>
+    <t xml:space="preserve">4.39464044570923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40232753753662</t>
+    <t xml:space="preserve">4.35557699203491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75767230987549</t>
+    <t xml:space="preserve">4.70714855194092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34310340881348</t>
+    <t xml:space="preserve">4.29698181152344</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36284494400024</t>
+    <t xml:space="preserve">4.31651401519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32336235046387</t>
+    <t xml:space="preserve">4.27745056152344</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06672382354736</t>
+    <t xml:space="preserve">4.02353763580322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84956908226013</t>
+    <t xml:space="preserve">3.80868864059448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86931037902832</t>
+    <t xml:space="preserve">3.82822036743164</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92853450775146</t>
+    <t xml:space="preserve">3.88681554794312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1062068939209</t>
+    <t xml:space="preserve">4.06260108947754</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8100860118866</t>
+    <t xml:space="preserve">3.76962494850159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71137928962708</t>
+    <t xml:space="preserve">3.6719663143158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75086188316345</t>
+    <t xml:space="preserve">3.71102976799011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69163799285889</t>
+    <t xml:space="preserve">3.65243482589722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96801710128784</t>
+    <t xml:space="preserve">3.92587900161743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14568948745728</t>
+    <t xml:space="preserve">4.1016640663147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08646535873413</t>
+    <t xml:space="preserve">4.04306936264038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16543054580688</t>
+    <t xml:space="preserve">4.12119626998901</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22465515136719</t>
+    <t xml:space="preserve">4.17979192733765</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12594795227051</t>
+    <t xml:space="preserve">4.0821328163147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24439668655396</t>
+    <t xml:space="preserve">4.19932317733765</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20491409301758</t>
+    <t xml:space="preserve">4.16026020050049</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28387928009033</t>
+    <t xml:space="preserve">4.23838663101196</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26413822174072</t>
+    <t xml:space="preserve">4.21885538101196</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38258600234985</t>
+    <t xml:space="preserve">4.33604526519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3036208152771</t>
+    <t xml:space="preserve">4.25791835784912</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9087929725647</t>
+    <t xml:space="preserve">3.86728382110596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98775863647461</t>
+    <t xml:space="preserve">3.94541049003601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48129320144653</t>
+    <t xml:space="preserve">4.43370389938354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6399998664856</t>
+    <t xml:space="preserve">4.59072542190552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53999996185303</t>
+    <t xml:space="preserve">4.49178743362427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61999988555908</t>
+    <t xml:space="preserve">4.57093811035156</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59999990463257</t>
+    <t xml:space="preserve">4.55115032196045</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80000019073486</t>
+    <t xml:space="preserve">4.74902677536011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82000017166138</t>
+    <t xml:space="preserve">4.76881456375122</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84000015258789</t>
+    <t xml:space="preserve">4.78860187530518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8600001335144</t>
+    <t xml:space="preserve">4.80838966369629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88000011444092</t>
+    <t xml:space="preserve">4.82817697525024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96000003814697</t>
+    <t xml:space="preserve">4.90732765197754</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90000009536743</t>
+    <t xml:space="preserve">4.84796476364136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94000005722046</t>
+    <t xml:space="preserve">4.88753986358643</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15000009536743</t>
+    <t xml:space="preserve">5.09530973434448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34999990463257</t>
+    <t xml:space="preserve">5.29318571090698</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44999980926514</t>
+    <t xml:space="preserve">5.39212369918823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59999990463257</t>
+    <t xml:space="preserve">5.54053115844727</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75</t>
+    <t xml:space="preserve">5.68893814086914</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69999980926514</t>
+    <t xml:space="preserve">5.63946866989136</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55000019073486</t>
+    <t xml:space="preserve">5.49106216430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59000015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73840713500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78787612915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83734512329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34265518188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19424772262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14477872848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04584074020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24371719360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44159317016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93628311157227</t>
   </si>
   <si>
     <t xml:space="preserve">5.65000009536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80000019073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84999990463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90000009536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40000009536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19999980926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09999990463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30000019073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
   </si>
 </sst>
 </file>
@@ -45846,7 +45849,7 @@
     </row>
     <row r="1698">
       <c r="A1698" s="1" t="n">
-        <v>45947.6494444444</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B1698" t="n">
         <v>13800</v>
@@ -45867,6 +45870,32 @@
         <v>447</v>
       </c>
       <c r="H1698" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" s="1" t="n">
+        <v>45950.4329513889</v>
+      </c>
+      <c r="B1699" t="n">
+        <v>4200</v>
+      </c>
+      <c r="C1699" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="D1699" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="E1699" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="F1699" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="G1699" t="s">
+        <v>458</v>
+      </c>
+      <c r="H1699" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ILP.MI.xlsx
+++ b/data/ILP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="461">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,10 +44,10 @@
     <t xml:space="preserve">ILP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97638237476349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91543638706207</t>
+    <t xml:space="preserve">1.9763822555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91543662548065</t>
   </si>
   <si>
     <t xml:space="preserve">1.94112062454224</t>
@@ -56,67 +56,67 @@
     <t xml:space="preserve">2.00685524940491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97986459732056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93284952640533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95853364467621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92109608650208</t>
+    <t xml:space="preserve">1.97986495494843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93284976482391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9585337638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92109596729279</t>
   </si>
   <si>
     <t xml:space="preserve">1.94199156761169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95418083667755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93067288398743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88931703567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86798620223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8906227350235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91978991031647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94155621528625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93807339668274</t>
+    <t xml:space="preserve">1.95418047904968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93067264556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88931679725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86798572540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89062285423279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9197895526886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94155597686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93807315826416</t>
   </si>
   <si>
     <t xml:space="preserve">1.91717755794525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97551167011261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93459069728851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96767520904541</t>
+    <t xml:space="preserve">1.97551155090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93459093570709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96767580509186</t>
   </si>
   <si>
     <t xml:space="preserve">2.02775073051453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01556181907654</t>
+    <t xml:space="preserve">2.01556158065796</t>
   </si>
   <si>
     <t xml:space="preserve">2.00250148773193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0199146270752</t>
+    <t xml:space="preserve">2.01991438865662</t>
   </si>
   <si>
     <t xml:space="preserve">1.8980233669281</t>
@@ -125,19 +125,19 @@
     <t xml:space="preserve">1.98508858680725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88061046600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8457840681076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86319720745087</t>
+    <t xml:space="preserve">1.88061022758484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84578418731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86319744586945</t>
   </si>
   <si>
     <t xml:space="preserve">1.88994169235229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90777134895325</t>
+    <t xml:space="preserve">1.90777158737183</t>
   </si>
   <si>
     <t xml:space="preserve">1.87211203575134</t>
@@ -149,58 +149,61 @@
     <t xml:space="preserve">1.94343078136444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9612603187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97908985614777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83645308017731</t>
+    <t xml:space="preserve">1.96126043796539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97909021377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83645284175873</t>
   </si>
   <si>
     <t xml:space="preserve">1.81862306594849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76513433456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8542822599411</t>
+    <t xml:space="preserve">1.76513409614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85428237915039</t>
   </si>
   <si>
     <t xml:space="preserve">1.80079352855682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78296399116516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93451595306396</t>
+    <t xml:space="preserve">1.78296387195587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93451571464539</t>
   </si>
   <si>
     <t xml:space="preserve">1.95234537124634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88102698326111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89885652065277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82753789424896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8453676700592</t>
+    <t xml:space="preserve">1.88102686405182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89885687828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82753813266754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84536743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86319732666016</t>
   </si>
   <si>
     <t xml:space="preserve">1.72947514057159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7740490436554</t>
+    <t xml:space="preserve">1.77404916286469</t>
   </si>
   <si>
     <t xml:space="preserve">1.76959180831909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79187881946564</t>
+    <t xml:space="preserve">1.79187870025635</t>
   </si>
   <si>
     <t xml:space="preserve">1.80970859527588</t>
@@ -209,25 +212,25 @@
     <t xml:space="preserve">1.77850663661957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70718801021576</t>
+    <t xml:space="preserve">1.70718789100647</t>
   </si>
   <si>
     <t xml:space="preserve">1.72501742839813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74730467796326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73838996887207</t>
+    <t xml:space="preserve">1.74730479717255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73838984966278</t>
   </si>
   <si>
     <t xml:space="preserve">1.75621950626373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71164548397064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72055995464325</t>
+    <t xml:space="preserve">1.71164536476135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72056007385254</t>
   </si>
   <si>
     <t xml:space="preserve">1.69381558895111</t>
@@ -239,7 +242,7 @@
     <t xml:space="preserve">1.6492418050766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67598605155945</t>
+    <t xml:space="preserve">1.67598628997803</t>
   </si>
   <si>
     <t xml:space="preserve">1.56900823116302</t>
@@ -248,91 +251,91 @@
     <t xml:space="preserve">1.66707122325897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63141191005707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65815627574921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68490076065063</t>
+    <t xml:space="preserve">1.63141202926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6581563949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68490087985992</t>
   </si>
   <si>
     <t xml:space="preserve">1.70273053646088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61358225345612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03257870674133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19304537773132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13955640792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3891716003418</t>
+    <t xml:space="preserve">1.61358249187469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03257894515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1930456161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13955688476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38917207717896</t>
   </si>
   <si>
     <t xml:space="preserve">2.33568263053894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54963803291321</t>
+    <t xml:space="preserve">2.54963874816895</t>
   </si>
   <si>
     <t xml:space="preserve">2.58529758453369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03103852272034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42329096794128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22716450691223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19150519371033</t>
+    <t xml:space="preserve">3.03103876113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42329072952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22716498374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19150543212891</t>
   </si>
   <si>
     <t xml:space="preserve">3.13801646232605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01320934295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99537944793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97754979133606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08452773094177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88840198516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71010518074036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6922755241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67444610595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79925346374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8349130153656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90623140335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78142356872559</t>
+    <t xml:space="preserve">3.01320910453796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99537897109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9775493144989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08452796936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88840126991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7101047039032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69227528572083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67444586753845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7992537021637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83491253852844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90623092651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78142380714417</t>
   </si>
   <si>
     <t xml:space="preserve">2.87057185173035</t>
@@ -341,34 +344,34 @@
     <t xml:space="preserve">3.0055513381958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07754111289978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98755431175232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05954337120056</t>
+    <t xml:space="preserve">3.0775408744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9875545501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05954360961914</t>
   </si>
   <si>
     <t xml:space="preserve">3.14953017234802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2035219669342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32950377464294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38349556922913</t>
+    <t xml:space="preserve">3.20352220535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32950353622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38349580764771</t>
   </si>
   <si>
     <t xml:space="preserve">3.36549806594849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34750080108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27551174163818</t>
+    <t xml:space="preserve">3.34750056266785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2755115032196</t>
   </si>
   <si>
     <t xml:space="preserve">3.31150603294373</t>
@@ -380,13 +383,13 @@
     <t xml:space="preserve">3.41948986053467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25751399993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23951625823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22151923179626</t>
+    <t xml:space="preserve">3.25751423835754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23951697349548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22151970863342</t>
   </si>
   <si>
     <t xml:space="preserve">3.40149259567261</t>
@@ -395,25 +398,25 @@
     <t xml:space="preserve">3.43748736381531</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65345525741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56346869468689</t>
+    <t xml:space="preserve">3.65345549583435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56346797943115</t>
   </si>
   <si>
     <t xml:space="preserve">3.63545799255371</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86942291259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99540400505066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01340055465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94141221046448</t>
+    <t xml:space="preserve">3.86942362785339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9954047203064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0134015083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9414119720459</t>
   </si>
   <si>
     <t xml:space="preserve">3.76143884658813</t>
@@ -422,31 +425,31 @@
     <t xml:space="preserve">3.92341494560242</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9774067401886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88741970062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85142540931702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90541791915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.175377368927</t>
+    <t xml:space="preserve">3.97740697860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88742017745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8514256477356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9054172039032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17537641525269</t>
   </si>
   <si>
     <t xml:space="preserve">4.15737962722778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24736595153809</t>
+    <t xml:space="preserve">4.24736642837524</t>
   </si>
   <si>
     <t xml:space="preserve">4.35535049438477</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39134502410889</t>
+    <t xml:space="preserve">4.39134550094604</t>
   </si>
   <si>
     <t xml:space="preserve">4.31935596466064</t>
@@ -455,37 +458,37 @@
     <t xml:space="preserve">4.30135917663574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32852554321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34663534164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23796939849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20174789428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21985912322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12930345535278</t>
+    <t xml:space="preserve">4.32852506637573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34663581848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23796987533569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20174741744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21985864639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12930393218994</t>
   </si>
   <si>
     <t xml:space="preserve">4.05686044692993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16552591323853</t>
+    <t xml:space="preserve">4.16552495956421</t>
   </si>
   <si>
     <t xml:space="preserve">4.09308195114136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43719148635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29230213165283</t>
+    <t xml:space="preserve">4.43719100952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29230260848999</t>
   </si>
   <si>
     <t xml:space="preserve">4.11119318008423</t>
@@ -494,79 +497,79 @@
     <t xml:space="preserve">4.25608015060425</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41907978057861</t>
+    <t xml:space="preserve">4.41908025741577</t>
   </si>
   <si>
     <t xml:space="preserve">4.14741468429565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07497119903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02063798904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94819450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93008351325989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8938615322113</t>
+    <t xml:space="preserve">4.0749716758728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02063894271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9481942653656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93008279800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89386177062988</t>
   </si>
   <si>
     <t xml:space="preserve">3.98441624641418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03874826431274</t>
+    <t xml:space="preserve">4.03874921798706</t>
   </si>
   <si>
     <t xml:space="preserve">3.91197204589844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87575006484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74897336959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82141733169556</t>
+    <t xml:space="preserve">3.87575054168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74897313117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82141709327698</t>
   </si>
   <si>
     <t xml:space="preserve">3.83952832221985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62219667434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73086285591125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65841841697693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78519511222839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00252723693848</t>
+    <t xml:space="preserve">3.62219643592834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7308623790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65841865539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78519535064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00252771377563</t>
   </si>
   <si>
     <t xml:space="preserve">4.1836371421814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31041479110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96630525588989</t>
+    <t xml:space="preserve">4.31041383743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96630501747131</t>
   </si>
   <si>
     <t xml:space="preserve">3.80330610275269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71275115013123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44108653068542</t>
+    <t xml:space="preserve">3.7127513885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44108629226685</t>
   </si>
   <si>
     <t xml:space="preserve">3.53164172172546</t>
@@ -578,25 +581,25 @@
     <t xml:space="preserve">3.38675379753113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15131115913391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73475861549377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80720210075378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69853615760803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58987045288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77098035812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89775776863098</t>
+    <t xml:space="preserve">3.15131092071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73475813865662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80720233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69853639602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58987069129944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7709801197052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89775705337524</t>
   </si>
   <si>
     <t xml:space="preserve">3.09697794914246</t>
@@ -605,7 +608,7 @@
     <t xml:space="preserve">3.13320016860962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33242058753967</t>
+    <t xml:space="preserve">3.33242082595825</t>
   </si>
   <si>
     <t xml:space="preserve">3.36864280700684</t>
@@ -614,7 +617,7 @@
     <t xml:space="preserve">3.404865026474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31430959701538</t>
+    <t xml:space="preserve">3.31430983543396</t>
   </si>
   <si>
     <t xml:space="preserve">3.18753290176392</t>
@@ -623,16 +626,16 @@
     <t xml:space="preserve">3.2237548828125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56786346435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54975247383118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55880808830261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51353073120117</t>
+    <t xml:space="preserve">3.56786370277405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54975295066833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55880784988403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51353096961975</t>
   </si>
   <si>
     <t xml:space="preserve">3.45014214515686</t>
@@ -641,10 +644,10 @@
     <t xml:space="preserve">3.42297554016113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35053205490112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41392016410828</t>
+    <t xml:space="preserve">3.35053181648254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4139199256897</t>
   </si>
   <si>
     <t xml:space="preserve">3.34147620201111</t>
@@ -653,73 +656,70 @@
     <t xml:space="preserve">3.25092101097107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3233654499054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33267426490784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35129237174988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41645693778992</t>
+    <t xml:space="preserve">3.32336521148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33267450332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35129284858704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41645669937134</t>
   </si>
   <si>
     <t xml:space="preserve">3.49092984199524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36991095542908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5374755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63056755065918</t>
+    <t xml:space="preserve">3.36991119384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53747534751892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6305673122406</t>
   </si>
   <si>
     <t xml:space="preserve">3.59333038330078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74227690696716</t>
+    <t xml:space="preserve">3.74227666854858</t>
   </si>
   <si>
     <t xml:space="preserve">3.84467768669128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85398650169373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79813170433044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7795135974884</t>
+    <t xml:space="preserve">3.85398626327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79813146591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77951383590698</t>
   </si>
   <si>
     <t xml:space="preserve">3.75158619880676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67711281776428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66780376434326</t>
+    <t xml:space="preserve">3.67711305618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66780400276184</t>
   </si>
   <si>
     <t xml:space="preserve">3.65849447250366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37922048568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32336521148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44438433647156</t>
+    <t xml:space="preserve">3.37922024726868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44438457489014</t>
   </si>
   <si>
     <t xml:space="preserve">3.21165561676025</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11856389045715</t>
+    <t xml:space="preserve">3.11856412887573</t>
   </si>
   <si>
     <t xml:space="preserve">3.18372797966003</t>
@@ -728,37 +728,37 @@
     <t xml:space="preserve">3.34198331832886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43507480621338</t>
+    <t xml:space="preserve">3.43507528305054</t>
   </si>
   <si>
     <t xml:space="preserve">3.46300268173218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60263967514038</t>
+    <t xml:space="preserve">3.6026394367218</t>
   </si>
   <si>
     <t xml:space="preserve">3.4723117351532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62125825881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52816653251648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48162078857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42576575279236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64918541908264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72365880012512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51885747909546</t>
+    <t xml:space="preserve">3.62125778198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5281662940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4816210269928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42576599121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6491858959198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72365856170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51885724067688</t>
   </si>
   <si>
     <t xml:space="preserve">3.77020454406738</t>
@@ -767,61 +767,61 @@
     <t xml:space="preserve">3.58402132987976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70504021644592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68642234802246</t>
+    <t xml:space="preserve">3.7050404548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6864218711853</t>
   </si>
   <si>
     <t xml:space="preserve">3.80744123458862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29543805122375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56540322303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00293302536011</t>
+    <t xml:space="preserve">3.29543781280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56540274620056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00293350219727</t>
   </si>
   <si>
     <t xml:space="preserve">3.92845988273621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78882265090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98431444168091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8632960319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81674981117249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08671569824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16118812561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22635221481323</t>
+    <t xml:space="preserve">3.788822889328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98431491851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86329627037048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81675004959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08671522140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16118860244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22635316848755</t>
   </si>
   <si>
     <t xml:space="preserve">4.38460779190063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48700904846191</t>
+    <t xml:space="preserve">4.48700857162476</t>
   </si>
   <si>
     <t xml:space="preserve">4.35668039321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50562715530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6359543800354</t>
+    <t xml:space="preserve">4.5056266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63595485687256</t>
   </si>
   <si>
     <t xml:space="preserve">4.49631786346436</t>
@@ -830,16 +830,16 @@
     <t xml:space="preserve">4.46839046478271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28220748901367</t>
+    <t xml:space="preserve">4.28220653533936</t>
   </si>
   <si>
     <t xml:space="preserve">4.20773410797119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43115425109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56148242950439</t>
+    <t xml:space="preserve">4.43115377426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56148195266724</t>
   </si>
   <si>
     <t xml:space="preserve">4.57079076766968</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">4.45908117294312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.524245262146</t>
+    <t xml:space="preserve">4.52424573898315</t>
   </si>
   <si>
     <t xml:space="preserve">4.58940887451172</t>
@@ -860,31 +860,31 @@
     <t xml:space="preserve">4.44046306610107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37529850006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41253471374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29151678085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32875299453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23566150665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33806228637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15187883377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13326120376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18911600112915</t>
+    <t xml:space="preserve">4.37529802322388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41253519058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29151630401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32875347137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23566246032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33806180953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15187931060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13326168060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18911647796631</t>
   </si>
   <si>
     <t xml:space="preserve">4.34737110137939</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">4.19842576980591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31944370269775</t>
+    <t xml:space="preserve">4.3194432258606</t>
   </si>
   <si>
     <t xml:space="preserve">4.27289819717407</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">4.39391660690308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42184495925903</t>
+    <t xml:space="preserve">4.42184448242188</t>
   </si>
   <si>
     <t xml:space="preserve">4.87799263000488</t>
@@ -914,64 +914,64 @@
     <t xml:space="preserve">4.71042823791504</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60802745819092</t>
+    <t xml:space="preserve">4.60802698135376</t>
   </si>
   <si>
     <t xml:space="preserve">4.61733675003052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26358890533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11464262008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10533380508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17980623245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07740640640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95638728141785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90984129905701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04017019271851</t>
+    <t xml:space="preserve">4.26358938217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11464309692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10533332824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17980670928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07740592956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95638704299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90984153747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04016923904419</t>
   </si>
   <si>
     <t xml:space="preserve">4.25428056716919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6545729637146</t>
+    <t xml:space="preserve">4.65457391738892</t>
   </si>
   <si>
     <t xml:space="preserve">4.70111894607544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54286336898804</t>
+    <t xml:space="preserve">4.5428638458252</t>
   </si>
   <si>
     <t xml:space="preserve">4.30082559585571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44977283477783</t>
+    <t xml:space="preserve">4.44977235794067</t>
   </si>
   <si>
     <t xml:space="preserve">4.58010005950928</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79421043395996</t>
+    <t xml:space="preserve">4.79421091079712</t>
   </si>
   <si>
     <t xml:space="preserve">4.88730192184448</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61688470840454</t>
+    <t xml:space="preserve">4.61688423156738</t>
   </si>
   <si>
     <t xml:space="preserve">4.59804010391235</t>
@@ -986,7 +986,7 @@
     <t xml:space="preserve">4.56035137176514</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44728422164917</t>
+    <t xml:space="preserve">4.44728517532349</t>
   </si>
   <si>
     <t xml:space="preserve">4.67341804504395</t>
@@ -995,13 +995,13 @@
     <t xml:space="preserve">4.69226217269897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80532836914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89955043792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85244035720825</t>
+    <t xml:space="preserve">4.80532884597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8995509147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85243988037109</t>
   </si>
   <si>
     <t xml:space="preserve">4.99377393722534</t>
@@ -1013,13 +1013,13 @@
     <t xml:space="preserve">5.04088401794434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22932863235474</t>
+    <t xml:space="preserve">5.22932815551758</t>
   </si>
   <si>
     <t xml:space="preserve">5.60621690750122</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5119948387146</t>
+    <t xml:space="preserve">5.51199436187744</t>
   </si>
   <si>
     <t xml:space="preserve">5.70043897628784</t>
@@ -1028,19 +1028,19 @@
     <t xml:space="preserve">5.65332794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32355117797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37066173553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18221712112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1351056098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08799505233765</t>
+    <t xml:space="preserve">5.3235502243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37066125869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18221759796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13510608673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0879955291748</t>
   </si>
   <si>
     <t xml:space="preserve">4.75821781158447</t>
@@ -1052,64 +1052,67 @@
     <t xml:space="preserve">4.7671914100647</t>
   </si>
   <si>
+    <t xml:space="preserve">4.69091653823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70998525619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81486368179321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74812269210815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67184734344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53836584091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65277862548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57650375366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72905349731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86253499984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91020679473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95787906646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63370990753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61464166641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59557247161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55743503570557</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.69091606140137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70998525619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81486320495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.748122215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67184782028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53836679458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65277862548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57650375366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72905397415161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86253452301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91020727157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95787858963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63370990753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6146411895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59557294845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55743551254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74882841110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71022081375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78743743896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01908683776855</t>
+    <t xml:space="preserve">4.74882888793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71022033691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78743696212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01908731460571</t>
   </si>
   <si>
     <t xml:space="preserve">5.16386842727661</t>
@@ -1118,19 +1121,19 @@
     <t xml:space="preserve">5.45343112945557</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35691070556641</t>
+    <t xml:space="preserve">5.35691022872925</t>
   </si>
   <si>
     <t xml:space="preserve">5.30865001678467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40517044067383</t>
+    <t xml:space="preserve">5.40517091751099</t>
   </si>
   <si>
     <t xml:space="preserve">5.26038932800293</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5016918182373</t>
+    <t xml:space="preserve">5.50169134140015</t>
   </si>
   <si>
     <t xml:space="preserve">5.74299383163452</t>
@@ -1139,19 +1142,19 @@
     <t xml:space="preserve">5.59821271896362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64647340774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54995250701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21212911605835</t>
+    <t xml:space="preserve">5.6464729309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54995203018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21212959289551</t>
   </si>
   <si>
     <t xml:space="preserve">5.06734752655029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92256593704224</t>
+    <t xml:space="preserve">4.92256641387939</t>
   </si>
   <si>
     <t xml:space="preserve">5.11560869216919</t>
@@ -1163,7 +1166,7 @@
     <t xml:space="preserve">4.82604551315308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97082710266113</t>
+    <t xml:space="preserve">4.97082662582397</t>
   </si>
   <si>
     <t xml:space="preserve">4.86340236663818</t>
@@ -1389,6 +1392,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.65000009536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75</t>
   </si>
 </sst>
 </file>
@@ -8193,7 +8199,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G249" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -8219,7 +8225,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G250" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -8661,7 +8667,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G267" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -8687,7 +8693,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G268" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -8739,7 +8745,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G270" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -8765,7 +8771,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G271" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -8791,7 +8797,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G272" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -8817,7 +8823,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G273" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -8843,7 +8849,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G274" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -8973,7 +8979,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G279" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -8999,7 +9005,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G280" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -9025,7 +9031,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G281" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -9051,7 +9057,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G282" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -9077,7 +9083,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G283" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -9103,7 +9109,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G284" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -9181,7 +9187,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G287" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -9207,7 +9213,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G288" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -10429,7 +10435,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G335" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -10559,7 +10565,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G340" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -10585,7 +10591,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G341" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -10637,7 +10643,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G343" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -10689,7 +10695,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G345" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -10715,7 +10721,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G346" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -10741,7 +10747,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G347" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -10767,7 +10773,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G348" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -10793,7 +10799,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G349" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -10819,7 +10825,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G350" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -10845,7 +10851,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G351" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -10871,7 +10877,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G352" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -11079,7 +11085,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G360" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -11105,7 +11111,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G361" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -11131,7 +11137,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G362" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -11157,7 +11163,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G363" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -11183,7 +11189,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G364" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -11209,7 +11215,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G365" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -11235,7 +11241,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G366" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -11261,7 +11267,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G367" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -11287,7 +11293,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G368" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -11313,7 +11319,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G369" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -11339,7 +11345,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G370" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -11365,7 +11371,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G371" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -11391,7 +11397,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G372" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -11417,7 +11423,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G373" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -11443,7 +11449,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G374" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -11469,7 +11475,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G375" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -11495,7 +11501,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G376" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -11521,7 +11527,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G377" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -11547,7 +11553,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G378" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -11573,7 +11579,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G379" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -11599,7 +11605,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G380" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -11625,7 +11631,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G381" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -11651,7 +11657,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G382" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -11677,7 +11683,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G383" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -11703,7 +11709,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G384" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -11729,7 +11735,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G385" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -11755,7 +11761,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G386" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -11781,7 +11787,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G387" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -11807,7 +11813,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G388" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -11833,7 +11839,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G389" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -11859,7 +11865,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G390" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -11885,7 +11891,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G391" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -11911,7 +11917,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G392" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -11937,7 +11943,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G393" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -11963,7 +11969,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G394" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -11989,7 +11995,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G395" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -12015,7 +12021,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G396" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -12041,7 +12047,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G397" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -12067,7 +12073,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G398" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -12093,7 +12099,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G399" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -12119,7 +12125,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G400" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -12145,7 +12151,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G401" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -12171,7 +12177,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G402" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -12197,7 +12203,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G403" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -12223,7 +12229,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G404" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -12249,7 +12255,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G405" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -12275,7 +12281,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G406" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -12301,7 +12307,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G407" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -12327,7 +12333,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G408" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -12353,7 +12359,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G409" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -12379,7 +12385,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G410" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -12405,7 +12411,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G411" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -12431,7 +12437,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G412" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -12457,7 +12463,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G413" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -12483,7 +12489,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G414" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -12509,7 +12515,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G415" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -12535,7 +12541,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G416" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -12561,7 +12567,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G417" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -12587,7 +12593,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G418" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -12613,7 +12619,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G419" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -12639,7 +12645,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G420" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -12665,7 +12671,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G421" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -12691,7 +12697,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G422" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -12717,7 +12723,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G423" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -12743,7 +12749,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G424" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -12769,7 +12775,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G425" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -12795,7 +12801,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G426" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -12821,7 +12827,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G427" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -12847,7 +12853,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G428" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -12873,7 +12879,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G429" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -12899,7 +12905,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G430" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -12925,7 +12931,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G431" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -12951,7 +12957,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G432" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -12977,7 +12983,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G433" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -13003,7 +13009,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G434" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -13029,7 +13035,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G435" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -13055,7 +13061,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G436" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -13081,7 +13087,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G437" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -13107,7 +13113,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G438" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -13133,7 +13139,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G439" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -13159,7 +13165,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G440" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -13185,7 +13191,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G441" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -13211,7 +13217,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G442" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -13237,7 +13243,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G443" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -13263,7 +13269,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G444" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -13289,7 +13295,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G445" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -13315,7 +13321,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G446" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -13341,7 +13347,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G447" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -13367,7 +13373,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G448" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -13393,7 +13399,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G449" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -13419,7 +13425,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G450" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -13445,7 +13451,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G451" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -13471,7 +13477,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G452" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -13497,7 +13503,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G453" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -13523,7 +13529,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G454" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -13549,7 +13555,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G455" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -13575,7 +13581,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G456" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -13601,7 +13607,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G457" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -13627,7 +13633,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G458" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -13653,7 +13659,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G459" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -13679,7 +13685,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G460" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -13705,7 +13711,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G461" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -13731,7 +13737,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G462" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -13757,7 +13763,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G463" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -13783,7 +13789,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G464" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -13809,7 +13815,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G465" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -13835,7 +13841,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G466" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -13861,7 +13867,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G467" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -13887,7 +13893,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G468" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -13913,7 +13919,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G469" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -13939,7 +13945,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G470" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -13965,7 +13971,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G471" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -13991,7 +13997,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G472" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -14017,7 +14023,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G473" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -14485,7 +14491,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G491" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -14511,7 +14517,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G492" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -14589,7 +14595,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G495" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -14615,7 +14621,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G496" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -14719,7 +14725,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G500" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15655,7 +15661,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G536" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -15681,7 +15687,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G537" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -15707,7 +15713,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G538" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -15733,7 +15739,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G539" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -15759,7 +15765,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G540" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -15785,7 +15791,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G541" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -15811,7 +15817,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G542" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -15837,7 +15843,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G543" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -15863,7 +15869,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G544" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -15889,7 +15895,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G545" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -15915,7 +15921,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G546" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -15941,7 +15947,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G547" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -15967,7 +15973,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G548" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -15993,7 +15999,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G549" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -16019,7 +16025,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G550" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -16045,7 +16051,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G551" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -16071,7 +16077,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G552" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -16097,7 +16103,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G553" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -16123,7 +16129,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G554" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -16149,7 +16155,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G555" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -16175,7 +16181,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G556" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -16201,7 +16207,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G557" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -16227,7 +16233,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G558" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -16253,7 +16259,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G559" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -16279,7 +16285,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G560" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -16305,7 +16311,7 @@
         <v>3</v>
       </c>
       <c r="G561" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -16331,7 +16337,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G562" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -16357,7 +16363,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G563" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -16383,7 +16389,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G564" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -16409,7 +16415,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G565" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -16435,7 +16441,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G566" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -16461,7 +16467,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G567" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -16487,7 +16493,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G568" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -16513,7 +16519,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G569" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -16539,7 +16545,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G570" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -16565,7 +16571,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G571" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -16591,7 +16597,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G572" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -16617,7 +16623,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G573" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -16643,7 +16649,7 @@
         <v>3.5</v>
       </c>
       <c r="G574" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -16669,7 +16675,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G575" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -16695,7 +16701,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G576" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -16721,7 +16727,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G577" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -16747,7 +16753,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G578" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -16773,7 +16779,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G579" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -16799,7 +16805,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G580" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -16825,7 +16831,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G581" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -16851,7 +16857,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G582" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -16877,7 +16883,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G583" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -16903,7 +16909,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G584" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -16929,7 +16935,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G585" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -16955,7 +16961,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G586" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -16981,7 +16987,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G587" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -17007,7 +17013,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G588" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -17033,7 +17039,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G589" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -17059,7 +17065,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G590" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -17085,7 +17091,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G591" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -17111,7 +17117,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G592" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -17137,7 +17143,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G593" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -17163,7 +17169,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G594" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -17189,7 +17195,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G595" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -17215,7 +17221,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G596" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -17241,7 +17247,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G597" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -17267,7 +17273,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G598" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -17293,7 +17299,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G599" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -17319,7 +17325,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G600" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -17345,7 +17351,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G601" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -17371,7 +17377,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G602" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -17397,7 +17403,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G603" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -17423,7 +17429,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G604" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -17449,7 +17455,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G605" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -17475,7 +17481,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G606" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -17501,7 +17507,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G607" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -17527,7 +17533,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G608" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -17553,7 +17559,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G609" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -17579,7 +17585,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G610" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -17605,7 +17611,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G611" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -17631,7 +17637,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G612" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -17657,7 +17663,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G613" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -17683,7 +17689,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G614" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -17709,7 +17715,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G615" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -17735,7 +17741,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G616" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -17761,7 +17767,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G617" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -17787,7 +17793,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G618" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -17813,7 +17819,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G619" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -17839,7 +17845,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G620" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -17865,7 +17871,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G621" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -17891,7 +17897,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G622" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -17917,7 +17923,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G623" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -17943,7 +17949,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G624" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -17969,7 +17975,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G625" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -17995,7 +18001,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G626" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -18021,7 +18027,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G627" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -18047,7 +18053,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G628" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -18073,7 +18079,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G629" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -18099,7 +18105,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G630" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -18125,7 +18131,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G631" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -18151,7 +18157,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G632" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -18177,7 +18183,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G633" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -18203,7 +18209,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G634" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -18229,7 +18235,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G635" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -18255,7 +18261,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G636" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -18281,7 +18287,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G637" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -18307,7 +18313,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G638" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -18333,7 +18339,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G639" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -18359,7 +18365,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G640" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -18385,7 +18391,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G641" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -18411,7 +18417,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G642" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -18437,7 +18443,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G643" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -18463,7 +18469,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G644" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -18489,7 +18495,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G645" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -18515,7 +18521,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G646" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -18541,7 +18547,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G647" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -18567,7 +18573,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G648" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -18593,7 +18599,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G649" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -18619,7 +18625,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G650" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -18645,7 +18651,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G651" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -18671,7 +18677,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G652" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -18697,7 +18703,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G653" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -18723,7 +18729,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G654" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -18749,7 +18755,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G655" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -18775,7 +18781,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G656" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -18801,7 +18807,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G657" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -18827,7 +18833,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G658" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -18853,7 +18859,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G659" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -18879,7 +18885,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G660" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -18905,7 +18911,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G661" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -18931,7 +18937,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G662" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -18957,7 +18963,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G663" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -18983,7 +18989,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G664" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -19009,7 +19015,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G665" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -19035,7 +19041,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G666" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -19061,7 +19067,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G667" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -19087,7 +19093,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G668" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -19113,7 +19119,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G669" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -19139,7 +19145,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G670" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -19165,7 +19171,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G671" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -19191,7 +19197,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G672" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -19217,7 +19223,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G673" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -19243,7 +19249,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G674" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -19269,7 +19275,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G675" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -19295,7 +19301,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G676" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -19321,7 +19327,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G677" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -19347,7 +19353,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G678" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -19373,7 +19379,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G679" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -19399,7 +19405,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G680" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -19425,7 +19431,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G681" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -19451,7 +19457,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G682" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -19477,7 +19483,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G683" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -19503,7 +19509,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G684" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -19529,7 +19535,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G685" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -19555,7 +19561,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G686" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -19581,7 +19587,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G687" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -19607,7 +19613,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G688" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -19633,7 +19639,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G689" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -19659,7 +19665,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G690" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -19685,7 +19691,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G691" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -19711,7 +19717,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G692" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -19737,7 +19743,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G693" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -19763,7 +19769,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G694" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -19789,7 +19795,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G695" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -19815,7 +19821,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G696" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -19841,7 +19847,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G697" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -19867,7 +19873,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G698" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -19893,7 +19899,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G699" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -19919,7 +19925,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G700" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -19945,7 +19951,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G701" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -19971,7 +19977,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G702" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -19997,7 +20003,7 @@
         <v>4.5</v>
       </c>
       <c r="G703" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -20023,7 +20029,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G704" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -20049,7 +20055,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G705" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -20075,7 +20081,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G706" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -20101,7 +20107,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G707" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -20127,7 +20133,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G708" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -20153,7 +20159,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G709" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -20179,7 +20185,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G710" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -20205,7 +20211,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G711" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -20231,7 +20237,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G712" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -20257,7 +20263,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G713" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -20283,7 +20289,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G714" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -20309,7 +20315,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G715" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -20335,7 +20341,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G716" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -20361,7 +20367,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G717" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -20387,7 +20393,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G718" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -20413,7 +20419,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G719" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -20439,7 +20445,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G720" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -20465,7 +20471,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G721" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -20491,7 +20497,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G722" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -20517,7 +20523,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G723" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -20543,7 +20549,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G724" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -20569,7 +20575,7 @@
         <v>4</v>
       </c>
       <c r="G725" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -20595,7 +20601,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G726" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -20621,7 +20627,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G727" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -20647,7 +20653,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G728" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -20673,7 +20679,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G729" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -20699,7 +20705,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G730" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -20725,7 +20731,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G731" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -20751,7 +20757,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G732" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -20777,7 +20783,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G733" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -20803,7 +20809,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G734" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -20829,7 +20835,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G735" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -20855,7 +20861,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G736" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -20881,7 +20887,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G737" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -20907,7 +20913,7 @@
         <v>4.5</v>
       </c>
       <c r="G738" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -20933,7 +20939,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G739" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -20959,7 +20965,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G740" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -20985,7 +20991,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G741" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -21011,7 +21017,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G742" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -21037,7 +21043,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G743" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -21063,7 +21069,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G744" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -21089,7 +21095,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G745" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -21115,7 +21121,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G746" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -21141,7 +21147,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G747" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -21167,7 +21173,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G748" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -21193,7 +21199,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G749" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -21219,7 +21225,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G750" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -21245,7 +21251,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G751" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -21271,7 +21277,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G752" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -21297,7 +21303,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G753" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -21323,7 +21329,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G754" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -21349,7 +21355,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G755" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -21375,7 +21381,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G756" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -21401,7 +21407,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G757" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -21427,7 +21433,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G758" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -21453,7 +21459,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G759" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -21479,7 +21485,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G760" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -21505,7 +21511,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G761" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -21531,7 +21537,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G762" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -21557,7 +21563,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G763" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -21583,7 +21589,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G764" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -21609,7 +21615,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G765" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -21635,7 +21641,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G766" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -21661,7 +21667,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G767" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -21687,7 +21693,7 @@
         <v>4</v>
       </c>
       <c r="G768" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -21713,7 +21719,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G769" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -21739,7 +21745,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G770" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -21765,7 +21771,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G771" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -21791,7 +21797,7 @@
         <v>4</v>
       </c>
       <c r="G772" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -21817,7 +21823,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G773" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -21843,7 +21849,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G774" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -21869,7 +21875,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G775" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -21895,7 +21901,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G776" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -21921,7 +21927,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G777" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -21947,7 +21953,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G778" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -21973,7 +21979,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G779" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -21999,7 +22005,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G780" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -22025,7 +22031,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G781" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -22051,7 +22057,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G782" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -22077,7 +22083,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G783" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -22103,7 +22109,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G784" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -22129,7 +22135,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G785" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -22155,7 +22161,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G786" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -22181,7 +22187,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G787" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -22207,7 +22213,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G788" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -22233,7 +22239,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G789" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -22259,7 +22265,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G790" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -22285,7 +22291,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G791" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -22311,7 +22317,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G792" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -22337,7 +22343,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G793" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -22363,7 +22369,7 @@
         <v>4</v>
       </c>
       <c r="G794" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -22389,7 +22395,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G795" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -22415,7 +22421,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G796" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -22441,7 +22447,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G797" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -22467,7 +22473,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G798" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -22493,7 +22499,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G799" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -22519,7 +22525,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G800" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -22545,7 +22551,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G801" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -22571,7 +22577,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G802" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -22597,7 +22603,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G803" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -22623,7 +22629,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G804" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -22649,7 +22655,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G805" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -22675,7 +22681,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G806" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -22701,7 +22707,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G807" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -22727,7 +22733,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G808" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -22753,7 +22759,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G809" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -22779,7 +22785,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G810" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -22805,7 +22811,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G811" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -22831,7 +22837,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G812" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -22857,7 +22863,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G813" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -22883,7 +22889,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G814" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -22909,7 +22915,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G815" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -22935,7 +22941,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G816" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -22961,7 +22967,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G817" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -22987,7 +22993,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G818" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -23013,7 +23019,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G819" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -23039,7 +23045,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G820" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -23065,7 +23071,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G821" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -23091,7 +23097,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G822" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -23117,7 +23123,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G823" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -23143,7 +23149,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G824" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -23169,7 +23175,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G825" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -23195,7 +23201,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G826" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -23221,7 +23227,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G827" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -23247,7 +23253,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G828" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -23273,7 +23279,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G829" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -23299,7 +23305,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G830" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -23325,7 +23331,7 @@
         <v>3.75</v>
       </c>
       <c r="G831" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -23351,7 +23357,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G832" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -23377,7 +23383,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G833" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -23403,7 +23409,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G834" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -23429,7 +23435,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G835" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -23455,7 +23461,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G836" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -23481,7 +23487,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G837" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -23507,7 +23513,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G838" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -23533,7 +23539,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G839" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -23559,7 +23565,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G840" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -23585,7 +23591,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G841" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -23611,7 +23617,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G842" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -23637,7 +23643,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G843" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -23663,7 +23669,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G844" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -23689,7 +23695,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G845" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -23715,7 +23721,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G846" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -23741,7 +23747,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G847" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -23819,7 +23825,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G850" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24131,7 +24137,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G862" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -24183,7 +24189,7 @@
         <v>3.75</v>
       </c>
       <c r="G864" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -24261,7 +24267,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G867" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -24443,7 +24449,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G874" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -24495,7 +24501,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G876" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -24521,7 +24527,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G877" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -24547,7 +24553,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G878" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -24625,7 +24631,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G881" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -24651,7 +24657,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G882" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -24703,7 +24709,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G884" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -24729,7 +24735,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G885" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -24755,7 +24761,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G886" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -24833,7 +24839,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G889" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -24859,7 +24865,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G890" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -24885,7 +24891,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G891" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -24937,7 +24943,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G893" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -25067,7 +25073,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G898" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -25093,7 +25099,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G899" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -25197,7 +25203,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G903" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -25275,7 +25281,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G906" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -25431,7 +25437,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G912" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -25509,7 +25515,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G915" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -25535,7 +25541,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G916" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -25561,7 +25567,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G917" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -25587,7 +25593,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G918" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -25639,7 +25645,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G920" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -25665,7 +25671,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G921" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26107,7 +26113,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G938" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26367,7 +26373,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G948" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -26393,7 +26399,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G949" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26445,7 +26451,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G951" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -36533,7 +36539,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1339" t="s">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -36559,7 +36565,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1340" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -36585,7 +36591,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1341" t="s">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -36611,7 +36617,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1342" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -36637,7 +36643,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1343" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -36663,7 +36669,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1344" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -36689,7 +36695,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1345" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -36715,7 +36721,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1346" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -36741,7 +36747,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1347" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -36767,7 +36773,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1348" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -36793,7 +36799,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1349" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -36819,7 +36825,7 @@
         <v>5.5</v>
       </c>
       <c r="G1350" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -36845,7 +36851,7 @@
         <v>5.5</v>
       </c>
       <c r="G1351" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -36871,7 +36877,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1352" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -36897,7 +36903,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1353" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -36923,7 +36929,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1354" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -36949,7 +36955,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1355" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -36975,7 +36981,7 @@
         <v>5.5</v>
       </c>
       <c r="G1356" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37001,7 +37007,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1357" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37027,7 +37033,7 @@
         <v>5.5</v>
       </c>
       <c r="G1358" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -37053,7 +37059,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1359" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37079,7 +37085,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1360" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37105,7 +37111,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1361" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -37131,7 +37137,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1362" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37157,7 +37163,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1363" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -37183,7 +37189,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1364" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -37209,7 +37215,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1365" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -37235,7 +37241,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1366" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -37261,7 +37267,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1367" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -37287,7 +37293,7 @@
         <v>5.75</v>
       </c>
       <c r="G1368" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -37313,7 +37319,7 @@
         <v>5.75</v>
       </c>
       <c r="G1369" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -37339,7 +37345,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1370" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -37365,7 +37371,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1371" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -37391,7 +37397,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1372" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -37417,7 +37423,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1373" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -37443,7 +37449,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1374" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -37469,7 +37475,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1375" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -37495,7 +37501,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1376" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -37521,7 +37527,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1377" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -37547,7 +37553,7 @@
         <v>5.5</v>
       </c>
       <c r="G1378" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -37573,7 +37579,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1379" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -37599,7 +37605,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1380" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -37625,7 +37631,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1381" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -37651,7 +37657,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1382" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -37677,7 +37683,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1383" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -37703,7 +37709,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1384" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -37729,7 +37735,7 @@
         <v>5.5</v>
       </c>
       <c r="G1385" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -37755,7 +37761,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1386" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -37781,7 +37787,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1387" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -37807,7 +37813,7 @@
         <v>5.25</v>
       </c>
       <c r="G1388" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -37833,7 +37839,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1389" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -37859,7 +37865,7 @@
         <v>5.25</v>
       </c>
       <c r="G1390" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -37885,7 +37891,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1391" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -37911,7 +37917,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1392" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -37937,7 +37943,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1393" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -37963,7 +37969,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1394" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -37989,7 +37995,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1395" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38015,7 +38021,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1396" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38041,7 +38047,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1397" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38067,7 +38073,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1398" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -38093,7 +38099,7 @@
         <v>5</v>
       </c>
       <c r="G1399" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -38119,7 +38125,7 @@
         <v>5</v>
       </c>
       <c r="G1400" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -38145,7 +38151,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1401" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -38171,7 +38177,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1402" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -38197,7 +38203,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1403" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -38223,7 +38229,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1404" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -38249,7 +38255,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1405" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -38275,7 +38281,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1406" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -38301,7 +38307,7 @@
         <v>5.25</v>
       </c>
       <c r="G1407" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -38327,7 +38333,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1408" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -38353,7 +38359,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1409" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -38379,7 +38385,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1410" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -38405,7 +38411,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1411" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38431,7 +38437,7 @@
         <v>5.25</v>
       </c>
       <c r="G1412" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -38457,7 +38463,7 @@
         <v>5.25</v>
       </c>
       <c r="G1413" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -38483,7 +38489,7 @@
         <v>5.25</v>
       </c>
       <c r="G1414" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -38509,7 +38515,7 @@
         <v>5.25</v>
       </c>
       <c r="G1415" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -38535,7 +38541,7 @@
         <v>5.25</v>
       </c>
       <c r="G1416" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -38561,7 +38567,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1417" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -38587,7 +38593,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1418" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -38613,7 +38619,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1419" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -38639,7 +38645,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1420" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -38665,7 +38671,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1421" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -38691,7 +38697,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1422" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -38717,7 +38723,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1423" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -38743,7 +38749,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1424" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -38769,7 +38775,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1425" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -38795,7 +38801,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1426" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -38821,7 +38827,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1427" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -38847,7 +38853,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1428" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -38873,7 +38879,7 @@
         <v>5.25</v>
       </c>
       <c r="G1429" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -38899,7 +38905,7 @@
         <v>5.25</v>
       </c>
       <c r="G1430" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -38925,7 +38931,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1431" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -38951,7 +38957,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1432" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -38977,7 +38983,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1433" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39003,7 +39009,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1434" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39029,7 +39035,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1435" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -39055,7 +39061,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1436" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -39081,7 +39087,7 @@
         <v>5</v>
       </c>
       <c r="G1437" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39107,7 +39113,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1438" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39133,7 +39139,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1439" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39159,7 +39165,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1440" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -39185,7 +39191,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1441" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -39211,7 +39217,7 @@
         <v>5</v>
       </c>
       <c r="G1442" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39237,7 +39243,7 @@
         <v>5</v>
       </c>
       <c r="G1443" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -39263,7 +39269,7 @@
         <v>5</v>
       </c>
       <c r="G1444" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -39289,7 +39295,7 @@
         <v>5</v>
       </c>
       <c r="G1445" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -39315,7 +39321,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1446" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -39341,7 +39347,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1447" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -39367,7 +39373,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1448" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -39393,7 +39399,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1449" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39419,7 +39425,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1450" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39445,7 +39451,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1451" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39471,7 +39477,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1452" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39497,7 +39503,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1453" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39523,7 +39529,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1454" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39549,7 +39555,7 @@
         <v>5</v>
       </c>
       <c r="G1455" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39575,7 +39581,7 @@
         <v>5</v>
       </c>
       <c r="G1456" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39601,7 +39607,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1457" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39627,7 +39633,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1458" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39653,7 +39659,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1459" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39679,7 +39685,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1460" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -39705,7 +39711,7 @@
         <v>5</v>
       </c>
       <c r="G1461" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -39731,7 +39737,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1462" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -39757,7 +39763,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1463" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -39783,7 +39789,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1464" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -39809,7 +39815,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1465" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -39835,7 +39841,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1466" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -39861,7 +39867,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1467" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -39887,7 +39893,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1468" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -39913,7 +39919,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1469" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -39939,7 +39945,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1470" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -39965,7 +39971,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1471" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -39991,7 +39997,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1472" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40017,7 +40023,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1473" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40043,7 +40049,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1474" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40069,7 +40075,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1475" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -40095,7 +40101,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1476" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -40121,7 +40127,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1477" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -40147,7 +40153,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1478" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -40173,7 +40179,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1479" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -40199,7 +40205,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1480" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -40225,7 +40231,7 @@
         <v>4.5</v>
       </c>
       <c r="G1481" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -40251,7 +40257,7 @@
         <v>4.5</v>
       </c>
       <c r="G1482" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -40277,7 +40283,7 @@
         <v>4.5</v>
       </c>
       <c r="G1483" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -40303,7 +40309,7 @@
         <v>4.5</v>
       </c>
       <c r="G1484" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -40329,7 +40335,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1485" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -40355,7 +40361,7 @@
         <v>4.5</v>
       </c>
       <c r="G1486" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -40381,7 +40387,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1487" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -40407,7 +40413,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1488" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40433,7 +40439,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1489" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40459,7 +40465,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1490" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40485,7 +40491,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1491" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40511,7 +40517,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1492" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -40537,7 +40543,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1493" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40563,7 +40569,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1494" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -40589,7 +40595,7 @@
         <v>4.5</v>
       </c>
       <c r="G1495" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -40615,7 +40621,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1496" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -40641,7 +40647,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1497" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -40667,7 +40673,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1498" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -40693,7 +40699,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1499" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -40719,7 +40725,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1500" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -40745,7 +40751,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1501" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -40771,7 +40777,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1502" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -40797,7 +40803,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1503" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -40823,7 +40829,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1504" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -40849,7 +40855,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1505" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -40875,7 +40881,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1506" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -40901,7 +40907,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1507" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -40927,7 +40933,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1508" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -40953,7 +40959,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1509" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -40979,7 +40985,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1510" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41005,7 +41011,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1511" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41031,7 +41037,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1512" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41057,7 +41063,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1513" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41083,7 +41089,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1514" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41109,7 +41115,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1515" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41135,7 +41141,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1516" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41161,7 +41167,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1517" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -41187,7 +41193,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1518" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -41213,7 +41219,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1519" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41239,7 +41245,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1520" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -41265,7 +41271,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1521" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -41291,7 +41297,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1522" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -41317,7 +41323,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1523" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -41343,7 +41349,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1524" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -41369,7 +41375,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1525" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -41395,7 +41401,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1526" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41421,7 +41427,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1527" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41447,7 +41453,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1528" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41473,7 +41479,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1529" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41499,7 +41505,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1530" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41525,7 +41531,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1531" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41551,7 +41557,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1532" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41577,7 +41583,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1533" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41603,7 +41609,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1534" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41629,7 +41635,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1535" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41655,7 +41661,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1536" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41681,7 +41687,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1537" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -41707,7 +41713,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1538" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -41733,7 +41739,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1539" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -41759,7 +41765,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1540" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -41785,7 +41791,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1541" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -41811,7 +41817,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1542" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -41837,7 +41843,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1543" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -41863,7 +41869,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1544" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -41889,7 +41895,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1545" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -41915,7 +41921,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1546" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -41941,7 +41947,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1547" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -41967,7 +41973,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1548" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -41993,7 +41999,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1549" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42019,7 +42025,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1550" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42045,7 +42051,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1551" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42071,7 +42077,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1552" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42097,7 +42103,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1553" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42123,7 +42129,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1554" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42149,7 +42155,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1555" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42175,7 +42181,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1556" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42201,7 +42207,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1557" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -42227,7 +42233,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1558" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -42253,7 +42259,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1559" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -42279,7 +42285,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1560" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -42305,7 +42311,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1561" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -42331,7 +42337,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1562" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -42357,7 +42363,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1563" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -42383,7 +42389,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1564" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -42409,7 +42415,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1565" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42435,7 +42441,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1566" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42461,7 +42467,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1567" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42487,7 +42493,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1568" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42513,7 +42519,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1569" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42539,7 +42545,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1570" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42565,7 +42571,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1571" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42591,7 +42597,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1572" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42617,7 +42623,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1573" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42643,7 +42649,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1574" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42669,7 +42675,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1575" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -42695,7 +42701,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1576" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -42721,7 +42727,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1577" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -42747,7 +42753,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1578" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -42773,7 +42779,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1579" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -42799,7 +42805,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1580" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -42825,7 +42831,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1581" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -42851,7 +42857,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1582" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -42877,7 +42883,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1583" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -42903,7 +42909,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1584" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -42929,7 +42935,7 @@
         <v>4.5</v>
       </c>
       <c r="G1585" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -42955,7 +42961,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -42981,7 +42987,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1587" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43007,7 +43013,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1588" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43033,7 +43039,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1589" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43059,7 +43065,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1590" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43085,7 +43091,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1591" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43111,7 +43117,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1592" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43137,7 +43143,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1593" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43163,7 +43169,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1594" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43189,7 +43195,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1595" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -43215,7 +43221,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1596" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43241,7 +43247,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1597" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -43267,7 +43273,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1598" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -43293,7 +43299,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1599" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -43319,7 +43325,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1600" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -43345,7 +43351,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1601" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -43371,7 +43377,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1602" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -43397,7 +43403,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1603" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43423,7 +43429,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1604" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43449,7 +43455,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1605" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43475,7 +43481,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1606" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43501,7 +43507,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1607" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43527,7 +43533,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1608" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43553,7 +43559,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1609" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43579,7 +43585,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1610" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43605,7 +43611,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1611" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43631,7 +43637,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1612" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43657,7 +43663,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1613" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43683,7 +43689,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1614" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43709,7 +43715,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1615" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -43735,7 +43741,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1616" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43761,7 +43767,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1617" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43787,7 +43793,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1618" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43813,7 +43819,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1619" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43839,7 +43845,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1620" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -43865,7 +43871,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1621" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -43891,7 +43897,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1622" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -43917,7 +43923,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1623" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -43943,7 +43949,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1624" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -43969,7 +43975,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1625" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -43995,7 +44001,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1626" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44021,7 +44027,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1627" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44047,7 +44053,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1628" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44073,7 +44079,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1629" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44099,7 +44105,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1630" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44125,7 +44131,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1631" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44151,7 +44157,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1632" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44177,7 +44183,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1633" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44203,7 +44209,7 @@
         <v>5.75</v>
       </c>
       <c r="G1634" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44229,7 +44235,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1635" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44255,7 +44261,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1636" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44281,7 +44287,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1637" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44307,7 +44313,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1638" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44333,7 +44339,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1639" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44359,7 +44365,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1640" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44385,7 +44391,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1641" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44411,7 +44417,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1642" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44437,7 +44443,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1643" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44463,7 +44469,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1644" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44489,7 +44495,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1645" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44515,7 +44521,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1646" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44541,7 +44547,7 @@
         <v>5.75</v>
       </c>
       <c r="G1647" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44567,7 +44573,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1648" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44593,7 +44599,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1649" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44619,7 +44625,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1650" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44645,7 +44651,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1651" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44671,7 +44677,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1652" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44697,7 +44703,7 @@
         <v>5.25</v>
       </c>
       <c r="G1653" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44723,7 +44729,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1654" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44749,7 +44755,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1655" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44775,7 +44781,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1656" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44801,7 +44807,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1657" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44827,7 +44833,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1658" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44853,7 +44859,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1659" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -44879,7 +44885,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1660" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44905,7 +44911,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1661" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44931,7 +44937,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1662" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44957,7 +44963,7 @@
         <v>5.5</v>
       </c>
       <c r="G1663" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44983,7 +44989,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1664" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45009,7 +45015,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1665" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45035,7 +45041,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1666" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45061,7 +45067,7 @@
         <v>5.5</v>
       </c>
       <c r="G1667" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45087,7 +45093,7 @@
         <v>5.5</v>
       </c>
       <c r="G1668" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45113,7 +45119,7 @@
         <v>5.5</v>
       </c>
       <c r="G1669" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45139,7 +45145,7 @@
         <v>5.5</v>
       </c>
       <c r="G1670" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45165,7 +45171,7 @@
         <v>5.5</v>
       </c>
       <c r="G1671" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45191,7 +45197,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1672" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45217,7 +45223,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1673" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45243,7 +45249,7 @@
         <v>5.75</v>
       </c>
       <c r="G1674" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45269,7 +45275,7 @@
         <v>5.75</v>
       </c>
       <c r="G1675" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45295,7 +45301,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1676" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45321,7 +45327,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1677" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45347,7 +45353,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1678" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45373,7 +45379,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1679" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45399,7 +45405,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1680" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45425,7 +45431,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1681" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45451,7 +45457,7 @@
         <v>5.75</v>
       </c>
       <c r="G1682" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45477,7 +45483,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1683" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45503,7 +45509,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1684" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45529,7 +45535,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1685" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45555,7 +45561,7 @@
         <v>5.5</v>
       </c>
       <c r="G1686" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45581,7 +45587,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1687" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45607,7 +45613,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1688" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45633,7 +45639,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1689" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45659,7 +45665,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1690" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45685,7 +45691,7 @@
         <v>5.75</v>
       </c>
       <c r="G1691" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45711,7 +45717,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1692" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45737,7 +45743,7 @@
         <v>5.75</v>
       </c>
       <c r="G1693" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45763,7 +45769,7 @@
         <v>5.75</v>
       </c>
       <c r="G1694" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45789,7 +45795,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1695" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45815,7 +45821,7 @@
         <v>6</v>
       </c>
       <c r="G1696" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45841,7 +45847,7 @@
         <v>6</v>
       </c>
       <c r="G1697" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -45867,7 +45873,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1698" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -45875,7 +45881,7 @@
     </row>
     <row r="1699">
       <c r="A1699" s="1" t="n">
-        <v>45950.4329513889</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B1699" t="n">
         <v>4200</v>
@@ -45893,9 +45899,35 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1699" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1699" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" s="1" t="n">
+        <v>45951.3713194444</v>
+      </c>
+      <c r="B1700" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C1700" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D1700" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="E1700" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="F1700" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="G1700" t="s">
+        <v>460</v>
+      </c>
+      <c r="H1700" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ILP.MI.xlsx
+++ b/data/ILP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="464">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,10 +44,10 @@
     <t xml:space="preserve">ILP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97638249397278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91543662548065</t>
+    <t xml:space="preserve">1.9763822555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91543650627136</t>
   </si>
   <si>
     <t xml:space="preserve">1.94112062454224</t>
@@ -56,55 +56,55 @@
     <t xml:space="preserve">2.00685524940491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97986507415771</t>
+    <t xml:space="preserve">1.97986471652985</t>
   </si>
   <si>
     <t xml:space="preserve">1.93284976482391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95853388309479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92109560966492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94199168682098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95418071746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93067288398743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88931679725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86798572540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89062285423279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91978991031647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94155633449554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93807339668274</t>
+    <t xml:space="preserve">1.95853400230408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92109572887421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9419914484024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95418059825897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93067252635956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88931715488434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86798584461212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89062309265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91978943347931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94155609607697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93807351589203</t>
   </si>
   <si>
     <t xml:space="preserve">1.91717779636383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97551155090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93459069728851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96767544746399</t>
+    <t xml:space="preserve">1.97551143169403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93459057807922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96767556667328</t>
   </si>
   <si>
     <t xml:space="preserve">2.02775025367737</t>
@@ -119,97 +119,97 @@
     <t xml:space="preserve">2.01991486549377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8980233669281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98508846759796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88061022758484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84578394889832</t>
+    <t xml:space="preserve">1.89802372455597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98508882522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88061034679413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84578418731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86319756507874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88994169235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90777170658112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87211215496063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9256010055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94343090057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96126019954681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97908997535706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83645284175873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81862318515778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76513409614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85428214073181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80079340934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78296411037445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93451595306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95234537124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88102674484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89885652065277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82753801345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8453676700592</t>
   </si>
   <si>
     <t xml:space="preserve">1.86319744586945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88994133472443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90777158737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87211203575134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92560088634491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94343054294586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96126043796539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97909009456635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83645260334015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81862330436707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76513433456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85428249835968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80079352855682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78296387195587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93451583385468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95234537124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88102674484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89885663986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82753825187683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8453676700592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86319708824158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72947490215302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77404928207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76959156990051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79187881946564</t>
+    <t xml:space="preserve">1.7294750213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77404916286469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76959180831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79187870025635</t>
   </si>
   <si>
     <t xml:space="preserve">1.80970823764801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77850663661957</t>
+    <t xml:space="preserve">1.77850651741028</t>
   </si>
   <si>
     <t xml:space="preserve">1.70718789100647</t>
@@ -218,19 +218,19 @@
     <t xml:space="preserve">1.72501742839813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74730455875397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73838996887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75621950626373</t>
+    <t xml:space="preserve">1.74730467796326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73838984966278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75621962547302</t>
   </si>
   <si>
     <t xml:space="preserve">1.71164524555206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72056019306183</t>
+    <t xml:space="preserve">1.72056007385254</t>
   </si>
   <si>
     <t xml:space="preserve">1.69381558895111</t>
@@ -242,40 +242,40 @@
     <t xml:space="preserve">1.64924168586731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67598593235016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56900823116302</t>
+    <t xml:space="preserve">1.67598628997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56900811195374</t>
   </si>
   <si>
     <t xml:space="preserve">1.66707122325897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63141214847565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65815651416779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68490087985992</t>
+    <t xml:space="preserve">1.63141202926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6581563949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68490099906921</t>
   </si>
   <si>
     <t xml:space="preserve">1.70273041725159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61358237266541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03257870674133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19304585456848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1395571231842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38917183876038</t>
+    <t xml:space="preserve">1.61358225345612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03257894515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1930456161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13955688476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38917207717896</t>
   </si>
   <si>
     <t xml:space="preserve">2.33568263053894</t>
@@ -284,178 +284,178 @@
     <t xml:space="preserve">2.54963827133179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58529806137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03103876113892</t>
+    <t xml:space="preserve">2.58529758453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03103852272034</t>
   </si>
   <si>
     <t xml:space="preserve">3.42329049110413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22716474533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19150543212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13801646232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01320910453796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99537897109985</t>
+    <t xml:space="preserve">3.22716450691223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19150495529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13801622390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01320934295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99537944793701</t>
   </si>
   <si>
     <t xml:space="preserve">2.97754955291748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08452725410461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88840174674988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71010518074036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69227576255798</t>
+    <t xml:space="preserve">3.08452773094177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8884015083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71010494232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6922755241394</t>
   </si>
   <si>
     <t xml:space="preserve">2.67444586753845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79925298690796</t>
+    <t xml:space="preserve">2.79925346374512</t>
   </si>
   <si>
     <t xml:space="preserve">2.83491277694702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90623116493225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78142333030701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87057209014893</t>
+    <t xml:space="preserve">2.90623092651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78142356872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87057185173035</t>
   </si>
   <si>
     <t xml:space="preserve">3.00555181503296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07754111289978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98755407333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05954384803772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14952993392944</t>
+    <t xml:space="preserve">3.0775408744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98755431175232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05954313278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1495304107666</t>
   </si>
   <si>
     <t xml:space="preserve">3.20352220535278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32950329780579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38349509239197</t>
+    <t xml:space="preserve">3.32950305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38349556922913</t>
   </si>
   <si>
     <t xml:space="preserve">3.36549830436707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34750056266785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27551126480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31150603294373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29350876808167</t>
+    <t xml:space="preserve">3.34750080108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2755115032196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31150579452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29350852966309</t>
   </si>
   <si>
     <t xml:space="preserve">3.41948986053467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25751423835754</t>
+    <t xml:space="preserve">3.25751399993896</t>
   </si>
   <si>
     <t xml:space="preserve">3.2395167350769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22151947021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40149259567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43748712539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65345478057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56346845626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63545775413513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8694224357605</t>
+    <t xml:space="preserve">3.22151923179626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40149283409119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43748736381531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65345549583435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56346821784973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63545799255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86942338943481</t>
   </si>
   <si>
     <t xml:space="preserve">3.99540424346924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0134015083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94141221046448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76143860816956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.923415184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97740697860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88742065429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85142540931702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90541791915894</t>
+    <t xml:space="preserve">4.01340103149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9414119720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76143932342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92341494560242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97740650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88741970062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85142517089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90541768074036</t>
   </si>
   <si>
     <t xml:space="preserve">4.17537689208984</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15738010406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24736595153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35535097122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39134502410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31935548782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30135869979858</t>
+    <t xml:space="preserve">4.15737962722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24736642837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35535049438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39134550094604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31935596466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30135917663574</t>
   </si>
   <si>
     <t xml:space="preserve">4.32852458953857</t>
@@ -476,97 +476,97 @@
     <t xml:space="preserve">4.12930393218994</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05685997009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16552591323853</t>
+    <t xml:space="preserve">4.05686044692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16552543640137</t>
   </si>
   <si>
     <t xml:space="preserve">4.09308195114136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43719005584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29230308532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11119365692139</t>
+    <t xml:space="preserve">4.43719100952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29230260848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11119270324707</t>
   </si>
   <si>
     <t xml:space="preserve">4.25608062744141</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41907930374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14741516113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07497072219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02063751220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94819474220276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93008303642273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89386177062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98441553115845</t>
+    <t xml:space="preserve">4.41908073425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14741468429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07497119903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02063846588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9481942653656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93008351325989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89386200904846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98441624641418</t>
   </si>
   <si>
     <t xml:space="preserve">4.03874921798706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91197276115417</t>
+    <t xml:space="preserve">3.91197180747986</t>
   </si>
   <si>
     <t xml:space="preserve">3.87575006484985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74897336959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82141661643982</t>
+    <t xml:space="preserve">3.74897313117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82141733169556</t>
   </si>
   <si>
     <t xml:space="preserve">3.83952760696411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62219667434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73086190223694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65841865539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78519487380981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00252676010132</t>
+    <t xml:space="preserve">3.62219643592834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7308623790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65841841697693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78519535064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00252723693848</t>
   </si>
   <si>
     <t xml:space="preserve">4.1836371421814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31041431427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96630620956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80330610275269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71275162696838</t>
+    <t xml:space="preserve">4.31041383743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96630501747131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80330586433411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7127513885498</t>
   </si>
   <si>
     <t xml:space="preserve">3.44108653068542</t>
@@ -578,37 +578,37 @@
     <t xml:space="preserve">3.4954195022583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38675403594971</t>
+    <t xml:space="preserve">3.38675355911255</t>
   </si>
   <si>
     <t xml:space="preserve">3.15131092071533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73475861549377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80720233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69853663444519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58987069129944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77098035812378</t>
+    <t xml:space="preserve">2.73475790023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80720210075378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69853639602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58987045288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7709801197052</t>
   </si>
   <si>
     <t xml:space="preserve">2.89775729179382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09697794914246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13319993019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33242082595825</t>
+    <t xml:space="preserve">3.09697818756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13320016860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33242058753967</t>
   </si>
   <si>
     <t xml:space="preserve">3.36864280700684</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">3.31430983543396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18753266334534</t>
+    <t xml:space="preserve">3.18753290176392</t>
   </si>
   <si>
     <t xml:space="preserve">3.22375464439392</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">3.55880808830261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51353049278259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45014214515686</t>
+    <t xml:space="preserve">3.51353096961975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45014238357544</t>
   </si>
   <si>
     <t xml:space="preserve">3.42297554016113</t>
@@ -653,70 +653,73 @@
     <t xml:space="preserve">3.34147644042969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25092148780823</t>
+    <t xml:space="preserve">3.25092101097107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32336497306824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33267426490784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35129284858704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41645669937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49092984199524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36991095542908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5374755859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6305673122406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59333038330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74227690696716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84467792510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85398650169373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79813146591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7795135974884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75158619880676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67711329460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66780376434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65849447250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37922048568726</t>
   </si>
   <si>
     <t xml:space="preserve">3.32336521148682</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33267402648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35129261016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41645669937134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49092984199524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36991119384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5374755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6305673122406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59333062171936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74227690696716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84467768669128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85398650169373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79813194274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77951312065125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75158596038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67711305618286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66780376434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65849494934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37922048568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44438409805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21165537834167</t>
+    <t xml:space="preserve">3.44438433647156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21165561676025</t>
   </si>
   <si>
     <t xml:space="preserve">3.11856412887573</t>
@@ -725,49 +728,49 @@
     <t xml:space="preserve">3.18372821807861</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34198355674744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43507480621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4630024433136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60263991355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47231149673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.621258020401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52816653251648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4816210269928</t>
+    <t xml:space="preserve">3.34198331832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43507528305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46300268173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6026394367218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47231197357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62125778198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52816677093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48162055015564</t>
   </si>
   <si>
     <t xml:space="preserve">3.42576599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64918565750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72365832328796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51885747909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77020454406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58402132987976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7050404548645</t>
+    <t xml:space="preserve">3.64918541908264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72365856170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51885724067688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7702043056488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58402109146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70504069328308</t>
   </si>
   <si>
     <t xml:space="preserve">3.68642210960388</t>
@@ -776,22 +779,22 @@
     <t xml:space="preserve">3.80744123458862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29543781280518</t>
+    <t xml:space="preserve">3.29543805122375</t>
   </si>
   <si>
     <t xml:space="preserve">3.56540298461914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00293302536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92845940589905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.788822889328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98431515693665</t>
+    <t xml:space="preserve">4.00293350219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92845988273621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78882265090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98431444168091</t>
   </si>
   <si>
     <t xml:space="preserve">3.8632960319519</t>
@@ -800,7 +803,7 @@
     <t xml:space="preserve">3.81675004959106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671474456787</t>
+    <t xml:space="preserve">4.08671569824219</t>
   </si>
   <si>
     <t xml:space="preserve">4.16118860244751</t>
@@ -815,16 +818,16 @@
     <t xml:space="preserve">4.48700857162476</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35668087005615</t>
+    <t xml:space="preserve">4.35668039321899</t>
   </si>
   <si>
     <t xml:space="preserve">4.50562715530396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63595485687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4963173866272</t>
+    <t xml:space="preserve">4.63595533370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49631786346436</t>
   </si>
   <si>
     <t xml:space="preserve">4.46839094161987</t>
@@ -833,10 +836,10 @@
     <t xml:space="preserve">4.28220701217651</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20773410797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43115377426147</t>
+    <t xml:space="preserve">4.20773458480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43115425109863</t>
   </si>
   <si>
     <t xml:space="preserve">4.56148195266724</t>
@@ -848,43 +851,43 @@
     <t xml:space="preserve">4.45908164978027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52424621582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58940887451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59871816635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44046354293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37529850006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41253519058228</t>
+    <t xml:space="preserve">4.524245262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58940935134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59871864318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44046306610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37529802322388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41253566741943</t>
   </si>
   <si>
     <t xml:space="preserve">4.29151630401611</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32875394821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23566150665283</t>
+    <t xml:space="preserve">4.3287525177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23566198348999</t>
   </si>
   <si>
     <t xml:space="preserve">4.33806180953979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15187931060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13326072692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18911552429199</t>
+    <t xml:space="preserve">4.15187978744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13326168060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18911647796631</t>
   </si>
   <si>
     <t xml:space="preserve">4.34737110137939</t>
@@ -893,13 +896,13 @@
     <t xml:space="preserve">4.19842529296875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31944417953491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27289867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51493549346924</t>
+    <t xml:space="preserve">4.3194432258606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27289819717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51493644714355</t>
   </si>
   <si>
     <t xml:space="preserve">4.39391660690308</t>
@@ -911,13 +914,13 @@
     <t xml:space="preserve">4.87799263000488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71042776107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60802793502808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61733627319336</t>
+    <t xml:space="preserve">4.7104287147522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60802745819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61733675003052</t>
   </si>
   <si>
     <t xml:space="preserve">4.26358938217163</t>
@@ -926,25 +929,25 @@
     <t xml:space="preserve">4.11464309692383</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10533332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17980718612671</t>
+    <t xml:space="preserve">4.10533380508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17980670928955</t>
   </si>
   <si>
     <t xml:space="preserve">4.07740640640259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95638704299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90984177589417</t>
+    <t xml:space="preserve">3.95638751983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90984129905701</t>
   </si>
   <si>
     <t xml:space="preserve">4.04016971588135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25428009033203</t>
+    <t xml:space="preserve">4.25428056716919</t>
   </si>
   <si>
     <t xml:space="preserve">4.6545729637146</t>
@@ -953,49 +956,49 @@
     <t xml:space="preserve">4.70111894607544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5428638458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30082607269287</t>
+    <t xml:space="preserve">4.54286432266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30082511901855</t>
   </si>
   <si>
     <t xml:space="preserve">4.44977188110352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58010053634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7942099571228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88730239868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61688423156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59804058074951</t>
+    <t xml:space="preserve">4.58010005950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79421091079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88730144500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61688375473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59804010391235</t>
   </si>
   <si>
     <t xml:space="preserve">4.52266263961792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57919645309448</t>
+    <t xml:space="preserve">4.57919549942017</t>
   </si>
   <si>
     <t xml:space="preserve">4.56035137176514</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44728422164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67341756820679</t>
+    <t xml:space="preserve">4.44728469848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67341804504395</t>
   </si>
   <si>
     <t xml:space="preserve">4.69226217269897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80532884597778</t>
+    <t xml:space="preserve">4.80532789230347</t>
   </si>
   <si>
     <t xml:space="preserve">4.89955043792725</t>
@@ -1007,19 +1010,19 @@
     <t xml:space="preserve">4.99377346038818</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94666242599487</t>
+    <t xml:space="preserve">4.94666147232056</t>
   </si>
   <si>
     <t xml:space="preserve">5.04088401794434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22932910919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60621690750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51199531555176</t>
+    <t xml:space="preserve">5.22932863235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60621643066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51199436187744</t>
   </si>
   <si>
     <t xml:space="preserve">5.70043897628784</t>
@@ -1028,37 +1031,37 @@
     <t xml:space="preserve">5.65332794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32355070114136</t>
+    <t xml:space="preserve">5.3235502243042</t>
   </si>
   <si>
     <t xml:space="preserve">5.37066125869751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18221712112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1351056098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0879955291748</t>
+    <t xml:space="preserve">5.18221759796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13510608673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08799505233765</t>
   </si>
   <si>
     <t xml:space="preserve">4.75821781158447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71110677719116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76719093322754</t>
+    <t xml:space="preserve">4.711106300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7671914100647</t>
   </si>
   <si>
     <t xml:space="preserve">4.69091653823853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70998477935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81486320495605</t>
+    <t xml:space="preserve">4.70998525619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81486368179321</t>
   </si>
   <si>
     <t xml:space="preserve">4.748122215271</t>
@@ -1076,30 +1079,33 @@
     <t xml:space="preserve">4.57650375366211</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72905397415161</t>
+    <t xml:space="preserve">4.72905349731445</t>
   </si>
   <si>
     <t xml:space="preserve">4.86253499984741</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91020727157593</t>
+    <t xml:space="preserve">4.91020679473877</t>
   </si>
   <si>
     <t xml:space="preserve">4.95787858963013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6337103843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6146411895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59557199478149</t>
+    <t xml:space="preserve">4.63370990753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61464166641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59557247161865</t>
   </si>
   <si>
     <t xml:space="preserve">4.55743503570557</t>
   </si>
   <si>
+    <t xml:space="preserve">4.69091606140137</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.74882888793945</t>
   </si>
   <si>
@@ -1112,22 +1118,22 @@
     <t xml:space="preserve">5.01908683776855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16386842727661</t>
+    <t xml:space="preserve">5.16386890411377</t>
   </si>
   <si>
     <t xml:space="preserve">5.45343112945557</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35691070556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30865001678467</t>
+    <t xml:space="preserve">5.35691022872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30864953994751</t>
   </si>
   <si>
     <t xml:space="preserve">5.40517044067383</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26038932800293</t>
+    <t xml:space="preserve">5.26038980484009</t>
   </si>
   <si>
     <t xml:space="preserve">5.50169134140015</t>
@@ -1154,13 +1160,13 @@
     <t xml:space="preserve">4.92256641387939</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11560821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87430572509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82604503631592</t>
+    <t xml:space="preserve">5.11560869216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87430620193481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82604551315308</t>
   </si>
   <si>
     <t xml:space="preserve">4.97082662582397</t>
@@ -1395,6 +1401,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.59999990463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55000019073486</t>
   </si>
 </sst>
 </file>
@@ -23747,7 +23756,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G847" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -23773,7 +23782,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G848" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -23799,7 +23808,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G849" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -23851,7 +23860,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G851" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -23877,7 +23886,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G852" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -23903,7 +23912,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G853" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -23929,7 +23938,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G854" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -23955,7 +23964,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G855" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -23981,7 +23990,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G856" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24007,7 +24016,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G857" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -24033,7 +24042,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G858" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -24059,7 +24068,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G859" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -24085,7 +24094,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G860" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -24111,7 +24120,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G861" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -24163,7 +24172,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G863" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -24215,7 +24224,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G865" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -24241,7 +24250,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G866" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -24293,7 +24302,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G868" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -24319,7 +24328,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G869" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -24345,7 +24354,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G870" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -24371,7 +24380,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G871" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -24397,7 +24406,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G872" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -24423,7 +24432,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G873" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -24475,7 +24484,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G875" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -24579,7 +24588,7 @@
         <v>4</v>
       </c>
       <c r="G879" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -24605,7 +24614,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G880" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -24683,7 +24692,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G883" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -24787,7 +24796,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G887" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -24813,7 +24822,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G888" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -24917,7 +24926,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G892" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -24969,7 +24978,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G894" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -24995,7 +25004,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G895" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -25021,7 +25030,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G896" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -25047,7 +25056,7 @@
         <v>4</v>
       </c>
       <c r="G897" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -25125,7 +25134,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G900" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -25151,7 +25160,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G901" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -25177,7 +25186,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G902" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -25229,7 +25238,7 @@
         <v>4</v>
       </c>
       <c r="G904" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -25255,7 +25264,7 @@
         <v>4</v>
       </c>
       <c r="G905" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -25307,7 +25316,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G907" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -25333,7 +25342,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G908" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -25359,7 +25368,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G909" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -25385,7 +25394,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G910" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -25411,7 +25420,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G911" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -25463,7 +25472,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G913" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -25489,7 +25498,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G914" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -25619,7 +25628,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G919" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -25697,7 +25706,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G922" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -25723,7 +25732,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G923" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -25749,7 +25758,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G924" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -25775,7 +25784,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G925" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -25801,7 +25810,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G926" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -25827,7 +25836,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G927" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -25853,7 +25862,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G928" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -25879,7 +25888,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G929" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -25905,7 +25914,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G930" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -25931,7 +25940,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G931" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -25957,7 +25966,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G932" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -25983,7 +25992,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G933" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26009,7 +26018,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G934" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26035,7 +26044,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G935" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26061,7 +26070,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G936" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26087,7 +26096,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G937" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -26139,7 +26148,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G939" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26165,7 +26174,7 @@
         <v>4</v>
       </c>
       <c r="G940" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -26191,7 +26200,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G941" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -26217,7 +26226,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G942" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -26243,7 +26252,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G943" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -26269,7 +26278,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G944" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -26295,7 +26304,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G945" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -26321,7 +26330,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G946" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -26347,7 +26356,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G947" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -26425,7 +26434,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G950" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26477,7 +26486,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G952" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26503,7 +26512,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G953" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26529,7 +26538,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G954" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26555,7 +26564,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G955" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26581,7 +26590,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G956" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26607,7 +26616,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G957" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26633,7 +26642,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G958" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -26659,7 +26668,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G959" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -26685,7 +26694,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G960" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -26711,7 +26720,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G961" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -26737,7 +26746,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G962" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -26763,7 +26772,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G963" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -26789,7 +26798,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G964" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -26815,7 +26824,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G965" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -26841,7 +26850,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G966" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -26867,7 +26876,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G967" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -26893,7 +26902,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G968" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -26919,7 +26928,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G969" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -26945,7 +26954,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G970" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -26971,7 +26980,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G971" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -26997,7 +27006,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G972" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27023,7 +27032,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G973" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27049,7 +27058,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G974" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27075,7 +27084,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G975" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -27101,7 +27110,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G976" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27127,7 +27136,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G977" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27153,7 +27162,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G978" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -27179,7 +27188,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G979" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27205,7 +27214,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G980" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27231,7 +27240,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G981" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27257,7 +27266,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G982" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -27283,7 +27292,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G983" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -27309,7 +27318,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G984" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27335,7 +27344,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G985" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -27361,7 +27370,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G986" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -27387,7 +27396,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G987" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -27413,7 +27422,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G988" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -27439,7 +27448,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G989" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -27465,7 +27474,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G990" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -27491,7 +27500,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G991" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -27517,7 +27526,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G992" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -27543,7 +27552,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G993" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -27569,7 +27578,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G994" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -27595,7 +27604,7 @@
         <v>4.5</v>
       </c>
       <c r="G995" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -27621,7 +27630,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G996" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -27647,7 +27656,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G997" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -27673,7 +27682,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G998" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -27699,7 +27708,7 @@
         <v>4.5</v>
       </c>
       <c r="G999" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -27725,7 +27734,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1000" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -27751,7 +27760,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1001" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -27777,7 +27786,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1002" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -27803,7 +27812,7 @@
         <v>4.5</v>
       </c>
       <c r="G1003" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -27829,7 +27838,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1004" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -27855,7 +27864,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1005" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -27881,7 +27890,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1006" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -27907,7 +27916,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1007" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -27933,7 +27942,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1008" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -27959,7 +27968,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1009" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -27985,7 +27994,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1010" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -28011,7 +28020,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1011" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28037,7 +28046,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1012" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28063,7 +28072,7 @@
         <v>4.75</v>
       </c>
       <c r="G1013" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28089,7 +28098,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1014" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28115,7 +28124,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1015" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28141,7 +28150,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1016" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28167,7 +28176,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1017" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -28193,7 +28202,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1018" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -28219,7 +28228,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1019" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -28245,7 +28254,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1020" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28271,7 +28280,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1021" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28297,7 +28306,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1022" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -28323,7 +28332,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1023" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -28349,7 +28358,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1024" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28375,7 +28384,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1025" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28401,7 +28410,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1026" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28427,7 +28436,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1027" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28453,7 +28462,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1028" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28479,7 +28488,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1029" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28505,7 +28514,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1030" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28531,7 +28540,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1031" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28557,7 +28566,7 @@
         <v>4.5</v>
       </c>
       <c r="G1032" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28583,7 +28592,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1033" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28609,7 +28618,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1034" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28635,7 +28644,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1035" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -28661,7 +28670,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1036" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -28687,7 +28696,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1037" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -28713,7 +28722,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1038" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -28739,7 +28748,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1039" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -28765,7 +28774,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1040" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -28791,7 +28800,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1041" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -28817,7 +28826,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1042" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -28843,7 +28852,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1043" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -28869,7 +28878,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1044" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -28895,7 +28904,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1045" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -28921,7 +28930,7 @@
         <v>4.25</v>
       </c>
       <c r="G1046" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -28947,7 +28956,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1047" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -28973,7 +28982,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1048" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -28999,7 +29008,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1049" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29025,7 +29034,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1050" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29051,7 +29060,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1051" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29077,7 +29086,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1052" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -29103,7 +29112,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1053" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29129,7 +29138,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1054" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29155,7 +29164,7 @@
         <v>5</v>
       </c>
       <c r="G1055" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29181,7 +29190,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1056" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29207,7 +29216,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29233,7 +29242,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1058" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29259,7 +29268,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1059" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29285,7 +29294,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1060" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29311,7 +29320,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1061" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29337,7 +29346,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1062" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29363,7 +29372,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1063" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29389,7 +29398,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1064" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29415,7 +29424,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1065" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29441,7 +29450,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1066" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29467,7 +29476,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1067" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29493,7 +29502,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1068" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29519,7 +29528,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1069" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29545,7 +29554,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1070" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29571,7 +29580,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1071" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -29597,7 +29606,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1072" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -29623,7 +29632,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1073" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -29649,7 +29658,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1074" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -29675,7 +29684,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1075" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -29701,7 +29710,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1076" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -29727,7 +29736,7 @@
         <v>5.25</v>
       </c>
       <c r="G1077" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -29753,7 +29762,7 @@
         <v>5.25</v>
       </c>
       <c r="G1078" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -29779,7 +29788,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1079" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -29805,7 +29814,7 @@
         <v>5</v>
       </c>
       <c r="G1080" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -29831,7 +29840,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1081" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -29857,7 +29866,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1082" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -29883,7 +29892,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1083" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -29909,7 +29918,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1084" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -29935,7 +29944,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1085" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -29961,7 +29970,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1086" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -29987,7 +29996,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1087" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30013,7 +30022,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1088" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30039,7 +30048,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1089" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -30065,7 +30074,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1090" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30091,7 +30100,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1091" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30117,7 +30126,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1092" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30143,7 +30152,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1093" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30169,7 +30178,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1094" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -30195,7 +30204,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1095" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -30221,7 +30230,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1096" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -30247,7 +30256,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1097" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -30273,7 +30282,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1098" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -30299,7 +30308,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1099" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -30325,7 +30334,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1100" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -30351,7 +30360,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1101" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -30377,7 +30386,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1102" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -30403,7 +30412,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1103" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -30429,7 +30438,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1104" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -30455,7 +30464,7 @@
         <v>5.25</v>
       </c>
       <c r="G1105" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -30481,7 +30490,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1106" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30507,7 +30516,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1107" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30533,7 +30542,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1108" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -30559,7 +30568,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1109" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -30585,7 +30594,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1110" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -30611,7 +30620,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1111" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -30637,7 +30646,7 @@
         <v>6</v>
       </c>
       <c r="G1112" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -30663,7 +30672,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1113" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -30689,7 +30698,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1114" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -30715,7 +30724,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -30741,7 +30750,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1116" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -30767,7 +30776,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1117" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -30793,7 +30802,7 @@
         <v>5.5</v>
       </c>
       <c r="G1118" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -30819,7 +30828,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1119" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -30845,7 +30854,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1120" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -30871,7 +30880,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1121" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -30897,7 +30906,7 @@
         <v>5.5</v>
       </c>
       <c r="G1122" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -30923,7 +30932,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1123" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -30949,7 +30958,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1124" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -30975,7 +30984,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1125" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31001,7 +31010,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1126" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31027,7 +31036,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1127" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31053,7 +31062,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1128" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31079,7 +31088,7 @@
         <v>5.5</v>
       </c>
       <c r="G1129" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31105,7 +31114,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1130" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31131,7 +31140,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1131" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31157,7 +31166,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1132" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31183,7 +31192,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1133" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31209,7 +31218,7 @@
         <v>5.5</v>
       </c>
       <c r="G1134" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31235,7 +31244,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1135" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31261,7 +31270,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1136" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31287,7 +31296,7 @@
         <v>5.5</v>
       </c>
       <c r="G1137" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31313,7 +31322,7 @@
         <v>5.5</v>
       </c>
       <c r="G1138" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31339,7 +31348,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1139" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31365,7 +31374,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1140" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31391,7 +31400,7 @@
         <v>5.25</v>
       </c>
       <c r="G1141" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31417,7 +31426,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1142" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31443,7 +31452,7 @@
         <v>5.25</v>
       </c>
       <c r="G1143" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31469,7 +31478,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1144" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31495,7 +31504,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1145" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31521,7 +31530,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1146" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31547,7 +31556,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1147" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31573,7 +31582,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1148" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31599,7 +31608,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1149" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -31625,7 +31634,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1150" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -31651,7 +31660,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1151" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -31677,7 +31686,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1152" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -31703,7 +31712,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1153" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -31729,7 +31738,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1154" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -31755,7 +31764,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1155" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -31781,7 +31790,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1156" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -31807,7 +31816,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1157" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -31833,7 +31842,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1158" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -31859,7 +31868,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1159" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -31885,7 +31894,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1160" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -31911,7 +31920,7 @@
         <v>5.25</v>
       </c>
       <c r="G1161" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -31937,7 +31946,7 @@
         <v>5.25</v>
       </c>
       <c r="G1162" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -31963,7 +31972,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1163" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -31989,7 +31998,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1164" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32015,7 +32024,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1165" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32041,7 +32050,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1166" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -32067,7 +32076,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1167" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -32093,7 +32102,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1168" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -32119,7 +32128,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1169" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -32145,7 +32154,7 @@
         <v>5</v>
       </c>
       <c r="G1170" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -32171,7 +32180,7 @@
         <v>5</v>
       </c>
       <c r="G1171" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -32197,7 +32206,7 @@
         <v>5</v>
       </c>
       <c r="G1172" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -32223,7 +32232,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1173" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -32249,7 +32258,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1174" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -32275,7 +32284,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1175" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -32301,7 +32310,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1176" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -32327,7 +32336,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1177" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -32353,7 +32362,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1178" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -32379,7 +32388,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1179" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -32405,7 +32414,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1180" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -32431,7 +32440,7 @@
         <v>5.25</v>
       </c>
       <c r="G1181" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -32457,7 +32466,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1182" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -32483,7 +32492,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1183" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -32509,7 +32518,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1184" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -32535,7 +32544,7 @@
         <v>5.25</v>
       </c>
       <c r="G1185" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -32561,7 +32570,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1186" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -32587,7 +32596,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1187" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -32613,7 +32622,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1188" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -32639,7 +32648,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1189" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -32665,7 +32674,7 @@
         <v>5</v>
       </c>
       <c r="G1190" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -32691,7 +32700,7 @@
         <v>5</v>
       </c>
       <c r="G1191" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -32717,7 +32726,7 @@
         <v>5</v>
       </c>
       <c r="G1192" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -32743,7 +32752,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1193" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -32769,7 +32778,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1194" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -32795,7 +32804,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1195" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -32821,7 +32830,7 @@
         <v>5</v>
       </c>
       <c r="G1196" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -32847,7 +32856,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1197" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -32873,7 +32882,7 @@
         <v>5</v>
       </c>
       <c r="G1198" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -32899,7 +32908,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1199" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -32925,7 +32934,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1200" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -32951,7 +32960,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1201" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -32977,7 +32986,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1202" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33003,7 +33012,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1203" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33029,7 +33038,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1204" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -33055,7 +33064,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1205" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -33081,7 +33090,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1206" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -33107,7 +33116,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1207" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -33133,7 +33142,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1208" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -33159,7 +33168,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1209" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -33185,7 +33194,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1210" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -33211,7 +33220,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1211" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -33237,7 +33246,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1212" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -33263,7 +33272,7 @@
         <v>5</v>
       </c>
       <c r="G1213" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -33289,7 +33298,7 @@
         <v>5</v>
       </c>
       <c r="G1214" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -33315,7 +33324,7 @@
         <v>5</v>
       </c>
       <c r="G1215" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -33341,7 +33350,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1216" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -33367,7 +33376,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1217" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -33393,7 +33402,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1218" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -33419,7 +33428,7 @@
         <v>5</v>
       </c>
       <c r="G1219" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -33445,7 +33454,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1220" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -33471,7 +33480,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1221" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -33497,7 +33506,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1222" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -33523,7 +33532,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1223" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -33549,7 +33558,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1224" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -33575,7 +33584,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1225" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -33601,7 +33610,7 @@
         <v>5</v>
       </c>
       <c r="G1226" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -33627,7 +33636,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1227" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -33653,7 +33662,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1228" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -33679,7 +33688,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1229" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -33705,7 +33714,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1230" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -33731,7 +33740,7 @@
         <v>5</v>
       </c>
       <c r="G1231" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -33757,7 +33766,7 @@
         <v>5</v>
       </c>
       <c r="G1232" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -33783,7 +33792,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1233" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -33809,7 +33818,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1234" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -33835,7 +33844,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1235" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -33861,7 +33870,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1236" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -33887,7 +33896,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1237" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -33913,7 +33922,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1238" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -33939,7 +33948,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1239" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -33965,7 +33974,7 @@
         <v>5</v>
       </c>
       <c r="G1240" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -33991,7 +34000,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1241" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34017,7 +34026,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1242" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -34043,7 +34052,7 @@
         <v>5</v>
       </c>
       <c r="G1243" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -34069,7 +34078,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1244" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -34095,7 +34104,7 @@
         <v>5</v>
       </c>
       <c r="G1245" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34121,7 +34130,7 @@
         <v>5</v>
       </c>
       <c r="G1246" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34147,7 +34156,7 @@
         <v>5</v>
       </c>
       <c r="G1247" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -34173,7 +34182,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1248" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -34199,7 +34208,7 @@
         <v>5</v>
       </c>
       <c r="G1249" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -34225,7 +34234,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1250" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -34251,7 +34260,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1251" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -34277,7 +34286,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1252" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -34303,7 +34312,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1253" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -34329,7 +34338,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1254" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -34355,7 +34364,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1255" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -34381,7 +34390,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1256" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -34407,7 +34416,7 @@
         <v>5</v>
       </c>
       <c r="G1257" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -34433,7 +34442,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1258" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -34459,7 +34468,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1259" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -34485,7 +34494,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1260" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -34511,7 +34520,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1261" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -34537,7 +34546,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1262" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -34563,7 +34572,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1263" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -34589,7 +34598,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1264" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -34615,7 +34624,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1265" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -34641,7 +34650,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1266" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -34667,7 +34676,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1267" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -34693,7 +34702,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1268" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -34719,7 +34728,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1269" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -34745,7 +34754,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1270" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -34771,7 +34780,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1271" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -34797,7 +34806,7 @@
         <v>5</v>
       </c>
       <c r="G1272" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -34823,7 +34832,7 @@
         <v>5</v>
       </c>
       <c r="G1273" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -34849,7 +34858,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1274" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -34875,7 +34884,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1275" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -34901,7 +34910,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1276" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -34927,7 +34936,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1277" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -34953,7 +34962,7 @@
         <v>5</v>
       </c>
       <c r="G1278" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -34979,7 +34988,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1279" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35005,7 +35014,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1280" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -35031,7 +35040,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1281" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -35057,7 +35066,7 @@
         <v>5</v>
       </c>
       <c r="G1282" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -35083,7 +35092,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1283" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -35109,7 +35118,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1284" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -35135,7 +35144,7 @@
         <v>5</v>
       </c>
       <c r="G1285" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -35161,7 +35170,7 @@
         <v>5</v>
       </c>
       <c r="G1286" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -35187,7 +35196,7 @@
         <v>5</v>
       </c>
       <c r="G1287" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -35213,7 +35222,7 @@
         <v>5</v>
       </c>
       <c r="G1288" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -35239,7 +35248,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1289" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -35265,7 +35274,7 @@
         <v>5</v>
       </c>
       <c r="G1290" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35291,7 +35300,7 @@
         <v>5</v>
       </c>
       <c r="G1291" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35317,7 +35326,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1292" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35343,7 +35352,7 @@
         <v>5</v>
       </c>
       <c r="G1293" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35369,7 +35378,7 @@
         <v>5</v>
       </c>
       <c r="G1294" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35395,7 +35404,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1295" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35421,7 +35430,7 @@
         <v>5</v>
       </c>
       <c r="G1296" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35447,7 +35456,7 @@
         <v>5</v>
       </c>
       <c r="G1297" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -35473,7 +35482,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1298" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35499,7 +35508,7 @@
         <v>5</v>
       </c>
       <c r="G1299" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35525,7 +35534,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1300" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35551,7 +35560,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1301" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -35577,7 +35586,7 @@
         <v>5</v>
       </c>
       <c r="G1302" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35603,7 +35612,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1303" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35629,7 +35638,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1304" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -35655,7 +35664,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1305" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -35681,7 +35690,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1306" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -35707,7 +35716,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1307" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -35733,7 +35742,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1308" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -35759,7 +35768,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1309" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -35785,7 +35794,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1310" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -35811,7 +35820,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1311" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -35837,7 +35846,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1312" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -35863,7 +35872,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1313" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -35889,7 +35898,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1314" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -35915,7 +35924,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1315" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -35941,7 +35950,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1316" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -35967,7 +35976,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1317" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -35993,7 +36002,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1318" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36019,7 +36028,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1319" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -36045,7 +36054,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1320" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36071,7 +36080,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1321" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -36097,7 +36106,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1322" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -36123,7 +36132,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1323" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -36149,7 +36158,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1324" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -36175,7 +36184,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1325" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -36201,7 +36210,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1326" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -36227,7 +36236,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1327" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -36253,7 +36262,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1328" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -36279,7 +36288,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1329" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -36305,7 +36314,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1330" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -36331,7 +36340,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1331" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -36357,7 +36366,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1332" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -36383,7 +36392,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1333" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -36409,7 +36418,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1334" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -36435,7 +36444,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1335" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -36461,7 +36470,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1336" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -36487,7 +36496,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1337" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -36513,7 +36522,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1338" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -36539,7 +36548,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1339" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -36565,7 +36574,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1340" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -36591,7 +36600,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1341" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -36617,7 +36626,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1342" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -36643,7 +36652,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1343" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -36669,7 +36678,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1344" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -36695,7 +36704,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1345" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -36721,7 +36730,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1346" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -36747,7 +36756,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1347" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -36773,7 +36782,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1348" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -36799,7 +36808,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1349" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -36825,7 +36834,7 @@
         <v>5.5</v>
       </c>
       <c r="G1350" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -36851,7 +36860,7 @@
         <v>5.5</v>
       </c>
       <c r="G1351" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -36877,7 +36886,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1352" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -36903,7 +36912,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1353" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -36929,7 +36938,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1354" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -36955,7 +36964,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1355" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -36981,7 +36990,7 @@
         <v>5.5</v>
       </c>
       <c r="G1356" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37007,7 +37016,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1357" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37033,7 +37042,7 @@
         <v>5.5</v>
       </c>
       <c r="G1358" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -37059,7 +37068,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1359" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37085,7 +37094,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1360" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37111,7 +37120,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1361" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -37137,7 +37146,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1362" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37163,7 +37172,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1363" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -37189,7 +37198,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1364" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -37215,7 +37224,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1365" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -37241,7 +37250,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1366" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -37267,7 +37276,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1367" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -37293,7 +37302,7 @@
         <v>5.75</v>
       </c>
       <c r="G1368" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -37319,7 +37328,7 @@
         <v>5.75</v>
       </c>
       <c r="G1369" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -37345,7 +37354,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1370" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -37371,7 +37380,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1371" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -37397,7 +37406,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1372" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -37423,7 +37432,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1373" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -37449,7 +37458,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1374" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -37475,7 +37484,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1375" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -37501,7 +37510,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1376" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -37527,7 +37536,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1377" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -37553,7 +37562,7 @@
         <v>5.5</v>
       </c>
       <c r="G1378" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -37579,7 +37588,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1379" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -37605,7 +37614,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1380" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -37631,7 +37640,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1381" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -37657,7 +37666,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1382" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -37683,7 +37692,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1383" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -37709,7 +37718,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1384" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -37735,7 +37744,7 @@
         <v>5.5</v>
       </c>
       <c r="G1385" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -37761,7 +37770,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1386" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -37787,7 +37796,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1387" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -37813,7 +37822,7 @@
         <v>5.25</v>
       </c>
       <c r="G1388" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -37839,7 +37848,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1389" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -37865,7 +37874,7 @@
         <v>5.25</v>
       </c>
       <c r="G1390" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -37891,7 +37900,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1391" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -37917,7 +37926,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1392" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -37943,7 +37952,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1393" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -37969,7 +37978,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1394" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -37995,7 +38004,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1395" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38021,7 +38030,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1396" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38047,7 +38056,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1397" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38073,7 +38082,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1398" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -38099,7 +38108,7 @@
         <v>5</v>
       </c>
       <c r="G1399" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -38125,7 +38134,7 @@
         <v>5</v>
       </c>
       <c r="G1400" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -38151,7 +38160,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1401" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -38177,7 +38186,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1402" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -38203,7 +38212,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1403" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -38229,7 +38238,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1404" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -38255,7 +38264,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1405" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -38281,7 +38290,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1406" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -38307,7 +38316,7 @@
         <v>5.25</v>
       </c>
       <c r="G1407" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -38333,7 +38342,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1408" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -38359,7 +38368,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1409" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -38385,7 +38394,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1410" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -38411,7 +38420,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1411" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38437,7 +38446,7 @@
         <v>5.25</v>
       </c>
       <c r="G1412" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -38463,7 +38472,7 @@
         <v>5.25</v>
       </c>
       <c r="G1413" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -38489,7 +38498,7 @@
         <v>5.25</v>
       </c>
       <c r="G1414" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -38515,7 +38524,7 @@
         <v>5.25</v>
       </c>
       <c r="G1415" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -38541,7 +38550,7 @@
         <v>5.25</v>
       </c>
       <c r="G1416" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -38567,7 +38576,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1417" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -38593,7 +38602,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1418" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -38619,7 +38628,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1419" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -38645,7 +38654,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1420" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -38671,7 +38680,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1421" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -38697,7 +38706,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1422" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -38723,7 +38732,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1423" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -38749,7 +38758,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1424" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -38775,7 +38784,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1425" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -38801,7 +38810,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1426" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -38827,7 +38836,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1427" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -38853,7 +38862,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1428" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -38879,7 +38888,7 @@
         <v>5.25</v>
       </c>
       <c r="G1429" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -38905,7 +38914,7 @@
         <v>5.25</v>
       </c>
       <c r="G1430" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -38931,7 +38940,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1431" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -38957,7 +38966,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1432" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -38983,7 +38992,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1433" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39009,7 +39018,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1434" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39035,7 +39044,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1435" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -39061,7 +39070,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1436" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -39087,7 +39096,7 @@
         <v>5</v>
       </c>
       <c r="G1437" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39113,7 +39122,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1438" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39139,7 +39148,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1439" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39165,7 +39174,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1440" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -39191,7 +39200,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1441" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -39217,7 +39226,7 @@
         <v>5</v>
       </c>
       <c r="G1442" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39243,7 +39252,7 @@
         <v>5</v>
       </c>
       <c r="G1443" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -39269,7 +39278,7 @@
         <v>5</v>
       </c>
       <c r="G1444" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -39295,7 +39304,7 @@
         <v>5</v>
       </c>
       <c r="G1445" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -39321,7 +39330,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1446" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -39347,7 +39356,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1447" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -39373,7 +39382,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1448" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -39399,7 +39408,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1449" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39425,7 +39434,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1450" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39451,7 +39460,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1451" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39477,7 +39486,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1452" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39503,7 +39512,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1453" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39529,7 +39538,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1454" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39555,7 +39564,7 @@
         <v>5</v>
       </c>
       <c r="G1455" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39581,7 +39590,7 @@
         <v>5</v>
       </c>
       <c r="G1456" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39607,7 +39616,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1457" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39633,7 +39642,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1458" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39659,7 +39668,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1459" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39685,7 +39694,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1460" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -39711,7 +39720,7 @@
         <v>5</v>
       </c>
       <c r="G1461" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -39737,7 +39746,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1462" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -39763,7 +39772,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1463" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -39789,7 +39798,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1464" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -39815,7 +39824,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1465" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -39841,7 +39850,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1466" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -39867,7 +39876,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1467" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -39893,7 +39902,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1468" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -39919,7 +39928,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1469" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -39945,7 +39954,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1470" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -39971,7 +39980,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1471" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -39997,7 +40006,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1472" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40023,7 +40032,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1473" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40049,7 +40058,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1474" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40075,7 +40084,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1475" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -40101,7 +40110,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1476" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -40127,7 +40136,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1477" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -40153,7 +40162,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1478" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -40179,7 +40188,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1479" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -40205,7 +40214,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1480" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -40231,7 +40240,7 @@
         <v>4.5</v>
       </c>
       <c r="G1481" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -40257,7 +40266,7 @@
         <v>4.5</v>
       </c>
       <c r="G1482" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -40283,7 +40292,7 @@
         <v>4.5</v>
       </c>
       <c r="G1483" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -40309,7 +40318,7 @@
         <v>4.5</v>
       </c>
       <c r="G1484" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -40335,7 +40344,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1485" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -40361,7 +40370,7 @@
         <v>4.5</v>
       </c>
       <c r="G1486" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -40387,7 +40396,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1487" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -40413,7 +40422,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1488" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40439,7 +40448,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1489" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40465,7 +40474,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1490" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40491,7 +40500,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1491" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40517,7 +40526,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1492" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -40543,7 +40552,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1493" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40569,7 +40578,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1494" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -40595,7 +40604,7 @@
         <v>4.5</v>
       </c>
       <c r="G1495" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -40621,7 +40630,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1496" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -40647,7 +40656,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1497" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -40673,7 +40682,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1498" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -40699,7 +40708,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1499" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -40725,7 +40734,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1500" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -40751,7 +40760,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1501" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -40777,7 +40786,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1502" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -40803,7 +40812,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1503" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -40829,7 +40838,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1504" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -40855,7 +40864,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1505" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -40881,7 +40890,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1506" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -40907,7 +40916,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1507" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -40933,7 +40942,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1508" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -40959,7 +40968,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1509" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -40985,7 +40994,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1510" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41011,7 +41020,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1511" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41037,7 +41046,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1512" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41063,7 +41072,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1513" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41089,7 +41098,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1514" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41115,7 +41124,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1515" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41141,7 +41150,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1516" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41167,7 +41176,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1517" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -41193,7 +41202,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1518" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -41219,7 +41228,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1519" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41245,7 +41254,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1520" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -41271,7 +41280,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1521" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -41297,7 +41306,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1522" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -41323,7 +41332,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1523" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -41349,7 +41358,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1524" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -41375,7 +41384,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1525" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -41401,7 +41410,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1526" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41427,7 +41436,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1527" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41453,7 +41462,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1528" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41479,7 +41488,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1529" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41505,7 +41514,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1530" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41531,7 +41540,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1531" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41557,7 +41566,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1532" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41583,7 +41592,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1533" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41609,7 +41618,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1534" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41635,7 +41644,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1535" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41661,7 +41670,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1536" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41687,7 +41696,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1537" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -41713,7 +41722,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1538" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -41739,7 +41748,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1539" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -41765,7 +41774,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1540" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -41791,7 +41800,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1541" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -41817,7 +41826,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1542" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -41843,7 +41852,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1543" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -41869,7 +41878,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1544" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -41895,7 +41904,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1545" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -41921,7 +41930,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1546" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -41947,7 +41956,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1547" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -41973,7 +41982,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1548" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -41999,7 +42008,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1549" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42025,7 +42034,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1550" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42051,7 +42060,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1551" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42077,7 +42086,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1552" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42103,7 +42112,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1553" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42129,7 +42138,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1554" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42155,7 +42164,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1555" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42181,7 +42190,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1556" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42207,7 +42216,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1557" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -42233,7 +42242,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1558" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -42259,7 +42268,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1559" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -42285,7 +42294,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1560" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -42311,7 +42320,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1561" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -42337,7 +42346,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1562" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -42363,7 +42372,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1563" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -42389,7 +42398,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1564" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -42415,7 +42424,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1565" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42441,7 +42450,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1566" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42467,7 +42476,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1567" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42493,7 +42502,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1568" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42519,7 +42528,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1569" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42545,7 +42554,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1570" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42571,7 +42580,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1571" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42597,7 +42606,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1572" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42623,7 +42632,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1573" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42649,7 +42658,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1574" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42675,7 +42684,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1575" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -42701,7 +42710,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1576" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -42727,7 +42736,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1577" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -42753,7 +42762,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1578" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -42779,7 +42788,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1579" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -42805,7 +42814,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1580" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -42831,7 +42840,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1581" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -42857,7 +42866,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1582" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -42883,7 +42892,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1583" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -42909,7 +42918,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1584" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -42935,7 +42944,7 @@
         <v>4.5</v>
       </c>
       <c r="G1585" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -42961,7 +42970,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -42987,7 +42996,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1587" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43013,7 +43022,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1588" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43039,7 +43048,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1589" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43065,7 +43074,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1590" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43091,7 +43100,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1591" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43117,7 +43126,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1592" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43143,7 +43152,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1593" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43169,7 +43178,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1594" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43195,7 +43204,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1595" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -43221,7 +43230,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1596" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43247,7 +43256,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1597" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -43273,7 +43282,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1598" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -43299,7 +43308,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1599" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -43325,7 +43334,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1600" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -43351,7 +43360,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1601" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -43377,7 +43386,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1602" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -43403,7 +43412,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1603" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43429,7 +43438,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1604" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43455,7 +43464,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1605" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43481,7 +43490,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1606" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43507,7 +43516,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1607" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43533,7 +43542,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1608" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43559,7 +43568,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1609" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43585,7 +43594,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1610" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43611,7 +43620,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1611" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43637,7 +43646,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1612" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43663,7 +43672,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1613" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43689,7 +43698,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1614" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43715,7 +43724,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1615" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -43741,7 +43750,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1616" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43767,7 +43776,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1617" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43793,7 +43802,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1618" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43819,7 +43828,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1619" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43845,7 +43854,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1620" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -43871,7 +43880,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1621" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -43897,7 +43906,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1622" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -43923,7 +43932,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1623" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -43949,7 +43958,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1624" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -43975,7 +43984,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1625" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44001,7 +44010,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1626" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44027,7 +44036,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1627" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44053,7 +44062,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1628" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44079,7 +44088,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1629" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44105,7 +44114,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1630" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44131,7 +44140,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1631" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44157,7 +44166,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1632" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44183,7 +44192,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1633" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44209,7 +44218,7 @@
         <v>5.75</v>
       </c>
       <c r="G1634" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44235,7 +44244,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1635" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44261,7 +44270,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1636" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44287,7 +44296,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1637" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44313,7 +44322,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1638" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44339,7 +44348,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1639" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44365,7 +44374,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1640" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44391,7 +44400,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1641" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44417,7 +44426,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1642" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44443,7 +44452,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1643" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44469,7 +44478,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1644" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44495,7 +44504,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1645" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44521,7 +44530,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1646" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44547,7 +44556,7 @@
         <v>5.75</v>
       </c>
       <c r="G1647" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44573,7 +44582,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1648" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44599,7 +44608,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1649" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44625,7 +44634,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1650" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44651,7 +44660,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1651" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44677,7 +44686,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1652" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44703,7 +44712,7 @@
         <v>5.25</v>
       </c>
       <c r="G1653" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44729,7 +44738,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1654" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44755,7 +44764,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1655" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44781,7 +44790,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1656" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44807,7 +44816,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1657" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44833,7 +44842,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1658" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44859,7 +44868,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1659" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -44885,7 +44894,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1660" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44911,7 +44920,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1661" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44937,7 +44946,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1662" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44963,7 +44972,7 @@
         <v>5.5</v>
       </c>
       <c r="G1663" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44989,7 +44998,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1664" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45015,7 +45024,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1665" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45041,7 +45050,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1666" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45067,7 +45076,7 @@
         <v>5.5</v>
       </c>
       <c r="G1667" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45093,7 +45102,7 @@
         <v>5.5</v>
       </c>
       <c r="G1668" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45119,7 +45128,7 @@
         <v>5.5</v>
       </c>
       <c r="G1669" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45145,7 +45154,7 @@
         <v>5.5</v>
       </c>
       <c r="G1670" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45171,7 +45180,7 @@
         <v>5.5</v>
       </c>
       <c r="G1671" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45197,7 +45206,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1672" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45223,7 +45232,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1673" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45249,7 +45258,7 @@
         <v>5.75</v>
       </c>
       <c r="G1674" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45275,7 +45284,7 @@
         <v>5.75</v>
       </c>
       <c r="G1675" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45301,7 +45310,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1676" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45327,7 +45336,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1677" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45353,7 +45362,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1678" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45379,7 +45388,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1679" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45405,7 +45414,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1680" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45431,7 +45440,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1681" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45457,7 +45466,7 @@
         <v>5.75</v>
       </c>
       <c r="G1682" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45483,7 +45492,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1683" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45509,7 +45518,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1684" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45535,7 +45544,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1685" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45561,7 +45570,7 @@
         <v>5.5</v>
       </c>
       <c r="G1686" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45587,7 +45596,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1687" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45613,7 +45622,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1688" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45639,7 +45648,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1689" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45665,7 +45674,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1690" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45691,7 +45700,7 @@
         <v>5.75</v>
       </c>
       <c r="G1691" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45717,7 +45726,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1692" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45743,7 +45752,7 @@
         <v>5.75</v>
       </c>
       <c r="G1693" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45769,7 +45778,7 @@
         <v>5.75</v>
       </c>
       <c r="G1694" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45795,7 +45804,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1695" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45821,7 +45830,7 @@
         <v>6</v>
       </c>
       <c r="G1696" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45847,7 +45856,7 @@
         <v>6</v>
       </c>
       <c r="G1697" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -45873,7 +45882,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1698" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -45899,7 +45908,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1699" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -45925,7 +45934,7 @@
         <v>5.75</v>
       </c>
       <c r="G1700" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -45951,7 +45960,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1701" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -45959,7 +45968,7 @@
     </row>
     <row r="1702">
       <c r="A1702" s="1" t="n">
-        <v>45953.5640162037</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B1702" t="n">
         <v>2400</v>
@@ -45977,9 +45986,35 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1702" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="H1702" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" s="1" t="n">
+        <v>45954.6138425926</v>
+      </c>
+      <c r="B1703" t="n">
+        <v>10800</v>
+      </c>
+      <c r="C1703" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="D1703" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E1703" t="n">
+        <v>5.55000019073486</v>
+      </c>
+      <c r="F1703" t="n">
+        <v>5.55000019073486</v>
+      </c>
+      <c r="G1703" t="s">
+        <v>463</v>
+      </c>
+      <c r="H1703" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ILP.MI.xlsx
+++ b/data/ILP.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95026242733002</t>
+    <t xml:space="preserve">1.9502626657486</t>
   </si>
   <si>
     <t xml:space="preserve">ILP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97638213634491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91543686389923</t>
+    <t xml:space="preserve">1.97638201713562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91543638706207</t>
   </si>
   <si>
     <t xml:space="preserve">1.94112074375153</t>
@@ -56,16 +56,16 @@
     <t xml:space="preserve">2.00685501098633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97986435890198</t>
+    <t xml:space="preserve">1.97986495494843</t>
   </si>
   <si>
     <t xml:space="preserve">1.93284952640533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95853412151337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92109549045563</t>
+    <t xml:space="preserve">1.95853388309479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9210958480835</t>
   </si>
   <si>
     <t xml:space="preserve">1.94199132919312</t>
@@ -74,91 +74,91 @@
     <t xml:space="preserve">1.95418035984039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93067264556885</t>
+    <t xml:space="preserve">1.93067288398743</t>
   </si>
   <si>
     <t xml:space="preserve">1.88931667804718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8679860830307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89062285423279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91978967189789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94155597686768</t>
+    <t xml:space="preserve">1.86798596382141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89062309265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91978979110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94155621528625</t>
   </si>
   <si>
     <t xml:space="preserve">1.93807363510132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91717767715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9755117893219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93459057807922</t>
+    <t xml:space="preserve">1.91717779636383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97551155090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9345908164978</t>
   </si>
   <si>
     <t xml:space="preserve">1.96767544746399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02775049209595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01556181907654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00250196456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0199146270752</t>
+    <t xml:space="preserve">2.02775073051453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01556158065796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00250172615051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01991486549377</t>
   </si>
   <si>
     <t xml:space="preserve">1.89802360534668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98508834838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88061034679413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8457840681076</t>
+    <t xml:space="preserve">1.98508870601654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88061046600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84578430652618</t>
   </si>
   <si>
     <t xml:space="preserve">1.86319732666016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88994157314301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90777146816254</t>
+    <t xml:space="preserve">1.88994169235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90777182579041</t>
   </si>
   <si>
     <t xml:space="preserve">1.87211203575134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9256010055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94343090057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96126067638397</t>
+    <t xml:space="preserve">1.92560124397278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94343078136444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96126019954681</t>
   </si>
   <si>
     <t xml:space="preserve">1.97908997535706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83645308017731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81862318515778</t>
+    <t xml:space="preserve">1.83645284175873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81862330436707</t>
   </si>
   <si>
     <t xml:space="preserve">1.76513421535492</t>
@@ -167,238 +167,238 @@
     <t xml:space="preserve">1.85428237915039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80079340934753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78296375274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9345155954361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95234560966492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88102674484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89885675907135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82753777503967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84536743164062</t>
+    <t xml:space="preserve">1.80079352855682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78296387195587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93451595306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95234572887421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88102698326111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89885663986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82753789424896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84536778926849</t>
   </si>
   <si>
     <t xml:space="preserve">1.86319708824158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72947514057159</t>
+    <t xml:space="preserve">1.7294750213623</t>
   </si>
   <si>
     <t xml:space="preserve">1.7740490436554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7695916891098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79187870025635</t>
+    <t xml:space="preserve">1.76959156990051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79187858104706</t>
   </si>
   <si>
     <t xml:space="preserve">1.80970823764801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77850651741028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70718801021576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72501766681671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74730479717255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73838973045349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75621962547302</t>
+    <t xml:space="preserve">1.77850639820099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70718789100647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72501754760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74730467796326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73838996887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75621926784515</t>
   </si>
   <si>
     <t xml:space="preserve">1.71164536476135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72056019306183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69381558895111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64032673835754</t>
+    <t xml:space="preserve">1.72056031227112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6938157081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64032685756683</t>
   </si>
   <si>
     <t xml:space="preserve">1.64924156665802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67598617076874</t>
+    <t xml:space="preserve">1.67598605155945</t>
   </si>
   <si>
     <t xml:space="preserve">1.56900823116302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66707146167755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63141191005707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65815675258636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68490099906921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70273065567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61358237266541</t>
+    <t xml:space="preserve">1.66707122325897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63141202926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6581563949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68490087985992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70273041725159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61358213424683</t>
   </si>
   <si>
     <t xml:space="preserve">2.03257846832275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1930456161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13955688476562</t>
+    <t xml:space="preserve">2.19304537773132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13955664634705</t>
   </si>
   <si>
     <t xml:space="preserve">2.3891716003418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33568263053894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54963803291321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58529806137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03103876113892</t>
+    <t xml:space="preserve">2.3356831073761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54963850975037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58529734611511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0310389995575</t>
   </si>
   <si>
     <t xml:space="preserve">3.42329072952271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22716474533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19150543212891</t>
+    <t xml:space="preserve">3.22716426849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19150519371033</t>
   </si>
   <si>
     <t xml:space="preserve">3.13801646232605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01320910453796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99537944793701</t>
+    <t xml:space="preserve">3.01320934295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99537920951843</t>
   </si>
   <si>
     <t xml:space="preserve">2.97754955291748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08452725410461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88840174674988</t>
+    <t xml:space="preserve">3.08452796936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8884015083313</t>
   </si>
   <si>
     <t xml:space="preserve">2.71010518074036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6922755241394</t>
+    <t xml:space="preserve">2.69227528572083</t>
   </si>
   <si>
     <t xml:space="preserve">2.67444610595703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79925346374512</t>
+    <t xml:space="preserve">2.79925298690796</t>
   </si>
   <si>
     <t xml:space="preserve">2.83491277694702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90623140335083</t>
+    <t xml:space="preserve">2.90623116493225</t>
   </si>
   <si>
     <t xml:space="preserve">2.78142356872559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87057209014893</t>
+    <t xml:space="preserve">2.87057161331177</t>
   </si>
   <si>
     <t xml:space="preserve">3.00555157661438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0775408744812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98755431175232</t>
+    <t xml:space="preserve">3.07754135131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9875545501709</t>
   </si>
   <si>
     <t xml:space="preserve">3.05954384803772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14952993392944</t>
+    <t xml:space="preserve">3.1495304107666</t>
   </si>
   <si>
     <t xml:space="preserve">3.20352220535278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32950353622437</t>
+    <t xml:space="preserve">3.32950329780579</t>
   </si>
   <si>
     <t xml:space="preserve">3.38349533081055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36549806594849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34750080108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2755115032196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31150579452515</t>
+    <t xml:space="preserve">3.36549758911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34750056266785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27551174163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3115062713623</t>
   </si>
   <si>
     <t xml:space="preserve">3.29350876808167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41949009895325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25751423835754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23951649665833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22151923179626</t>
+    <t xml:space="preserve">3.41948986053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25751399993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2395167350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22151947021484</t>
   </si>
   <si>
     <t xml:space="preserve">3.40149259567261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43748736381531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65345478057861</t>
+    <t xml:space="preserve">3.43748712539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65345501899719</t>
   </si>
   <si>
     <t xml:space="preserve">3.56346845626831</t>
@@ -407,16 +407,16 @@
     <t xml:space="preserve">3.63545775413513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86942291259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99540400505066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01340103149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94141173362732</t>
+    <t xml:space="preserve">3.86942315101624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99540424346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0134015083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94141268730164</t>
   </si>
   <si>
     <t xml:space="preserve">3.76143860816956</t>
@@ -425,58 +425,58 @@
     <t xml:space="preserve">3.92341494560242</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97740626335144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88741993904114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85142588615417</t>
+    <t xml:space="preserve">3.97740721702576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8874204158783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85142660140991</t>
   </si>
   <si>
     <t xml:space="preserve">3.90541744232178</t>
   </si>
   <si>
-    <t xml:space="preserve">4.175377368927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15738010406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24736595153809</t>
+    <t xml:space="preserve">4.17537689208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15737962722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24736642837524</t>
   </si>
   <si>
     <t xml:space="preserve">4.35535049438477</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39134502410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3193564414978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30135917663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32852554321289</t>
+    <t xml:space="preserve">4.39134550094604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31935596466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30135869979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32852506637573</t>
   </si>
   <si>
     <t xml:space="preserve">4.3466362953186</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23796939849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20174789428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21985960006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1293044090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05686044692993</t>
+    <t xml:space="preserve">4.23796892166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20174741744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21985864639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12930345535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05685997009277</t>
   </si>
   <si>
     <t xml:space="preserve">4.16552591323853</t>
@@ -485,61 +485,61 @@
     <t xml:space="preserve">4.09308195114136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43719053268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29230213165283</t>
+    <t xml:space="preserve">4.43719005584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29230260848999</t>
   </si>
   <si>
     <t xml:space="preserve">4.11119270324707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25608110427856</t>
+    <t xml:space="preserve">4.25608015060425</t>
   </si>
   <si>
     <t xml:space="preserve">4.41907978057861</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14741563796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07497024536133</t>
+    <t xml:space="preserve">4.14741516113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07497119903564</t>
   </si>
   <si>
     <t xml:space="preserve">4.02063798904419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9481942653656</t>
+    <t xml:space="preserve">3.94819450378418</t>
   </si>
   <si>
     <t xml:space="preserve">3.93008327484131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89386129379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98441648483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0387487411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91197204589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87575054168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74897313117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82141709327698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83952808380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62219619750977</t>
+    <t xml:space="preserve">3.8938615322113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98441600799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03874921798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9119725227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87575101852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74897360801697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82141733169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83952832221985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62219643592834</t>
   </si>
   <si>
     <t xml:space="preserve">3.7308623790741</t>
@@ -548,43 +548,43 @@
     <t xml:space="preserve">3.65841841697693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78519487380981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00252676010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1836371421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31041383743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96630477905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80330657958984</t>
+    <t xml:space="preserve">3.78519511222839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00252723693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18363666534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31041431427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96630573272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80330610275269</t>
   </si>
   <si>
     <t xml:space="preserve">3.71275115013123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.441086769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53164148330688</t>
+    <t xml:space="preserve">3.44108653068542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53164172172546</t>
   </si>
   <si>
     <t xml:space="preserve">3.49541974067688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38675379753113</t>
+    <t xml:space="preserve">3.38675332069397</t>
   </si>
   <si>
     <t xml:space="preserve">3.15131092071533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7347583770752</t>
+    <t xml:space="preserve">2.73475813865662</t>
   </si>
   <si>
     <t xml:space="preserve">2.80720210075378</t>
@@ -596,22 +596,22 @@
     <t xml:space="preserve">2.58987045288086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7709801197052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8977575302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09697794914246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13319993019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33242058753967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36864280700684</t>
+    <t xml:space="preserve">2.77098059654236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89775729179382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09697818756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13320016860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33242082595825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36864256858826</t>
   </si>
   <si>
     <t xml:space="preserve">3.40486478805542</t>
@@ -620,25 +620,25 @@
     <t xml:space="preserve">3.31430983543396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18753266334534</t>
+    <t xml:space="preserve">3.18753290176392</t>
   </si>
   <si>
     <t xml:space="preserve">3.2237548828125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56786346435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54975295066833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55880784988403</t>
+    <t xml:space="preserve">3.56786322593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54975247383118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55880808830261</t>
   </si>
   <si>
     <t xml:space="preserve">3.51353073120117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45014238357544</t>
+    <t xml:space="preserve">3.45014190673828</t>
   </si>
   <si>
     <t xml:space="preserve">3.42297554016113</t>
@@ -650,22 +650,22 @@
     <t xml:space="preserve">3.4139199256897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34147620201111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25092124938965</t>
+    <t xml:space="preserve">3.34147644042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25092101097107</t>
   </si>
   <si>
     <t xml:space="preserve">3.32336568832397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33267426490784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35129261016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41645693778992</t>
+    <t xml:space="preserve">3.33267402648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35129284858704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4164571762085</t>
   </si>
   <si>
     <t xml:space="preserve">3.49092960357666</t>
@@ -674,22 +674,22 @@
     <t xml:space="preserve">3.36991095542908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53747582435608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63056707382202</t>
+    <t xml:space="preserve">3.5374755859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6305673122406</t>
   </si>
   <si>
     <t xml:space="preserve">3.59333062171936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74227714538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84467768669128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85398626327515</t>
+    <t xml:space="preserve">3.74227690696716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84467744827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8539867401123</t>
   </si>
   <si>
     <t xml:space="preserve">3.79813194274902</t>
@@ -698,19 +698,19 @@
     <t xml:space="preserve">3.77951335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75158667564392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67711281776428</t>
+    <t xml:space="preserve">3.75158643722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67711305618286</t>
   </si>
   <si>
     <t xml:space="preserve">3.66780376434326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65849447250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37922048568726</t>
+    <t xml:space="preserve">3.65849471092224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37922024726868</t>
   </si>
   <si>
     <t xml:space="preserve">3.3233654499054</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">3.44438433647156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21165561676025</t>
+    <t xml:space="preserve">3.21165537834167</t>
   </si>
   <si>
     <t xml:space="preserve">3.11856389045715</t>
@@ -728,46 +728,46 @@
     <t xml:space="preserve">3.18372821807861</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34198355674744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43507504463196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46300268173218</t>
+    <t xml:space="preserve">3.34198379516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43507552146912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4630024433136</t>
   </si>
   <si>
     <t xml:space="preserve">3.6026394367218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4723117351532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.621258020401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5281662940979</t>
+    <t xml:space="preserve">3.47231149673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62125825881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52816653251648</t>
   </si>
   <si>
     <t xml:space="preserve">3.4816210269928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42576575279236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64918565750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72365832328796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51885747909546</t>
+    <t xml:space="preserve">3.42576599121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64918541908264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72365856170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51885724067688</t>
   </si>
   <si>
     <t xml:space="preserve">3.77020454406738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58402132987976</t>
+    <t xml:space="preserve">3.58402109146118</t>
   </si>
   <si>
     <t xml:space="preserve">3.70504021644592</t>
@@ -779,43 +779,43 @@
     <t xml:space="preserve">3.80744099617004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2954375743866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56540298461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00293302536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92845964431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.788822889328</t>
+    <t xml:space="preserve">3.29543781280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56540274620056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00293254852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92845940589905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78882336616516</t>
   </si>
   <si>
     <t xml:space="preserve">3.98431515693665</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86329579353333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81674981117249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08671474456787</t>
+    <t xml:space="preserve">3.86329627037048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81674957275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08671522140503</t>
   </si>
   <si>
     <t xml:space="preserve">4.16118764877319</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22635173797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38460826873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48700857162476</t>
+    <t xml:space="preserve">4.22635221481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38460779190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48700904846191</t>
   </si>
   <si>
     <t xml:space="preserve">4.35668039321899</t>
@@ -827,28 +827,28 @@
     <t xml:space="preserve">4.63595485687256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4963173866272</t>
+    <t xml:space="preserve">4.49631786346436</t>
   </si>
   <si>
     <t xml:space="preserve">4.46839046478271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28220748901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20773410797119</t>
+    <t xml:space="preserve">4.28220701217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20773506164551</t>
   </si>
   <si>
     <t xml:space="preserve">4.43115377426147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56148147583008</t>
+    <t xml:space="preserve">4.56148242950439</t>
   </si>
   <si>
     <t xml:space="preserve">4.57079124450684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45908069610596</t>
+    <t xml:space="preserve">4.45908117294312</t>
   </si>
   <si>
     <t xml:space="preserve">4.52424573898315</t>
@@ -857,13 +857,13 @@
     <t xml:space="preserve">4.58940935134888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59871816635132</t>
+    <t xml:space="preserve">4.59871912002563</t>
   </si>
   <si>
     <t xml:space="preserve">4.44046306610107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37529897689819</t>
+    <t xml:space="preserve">4.37529850006104</t>
   </si>
   <si>
     <t xml:space="preserve">4.41253519058228</t>
@@ -872,13 +872,13 @@
     <t xml:space="preserve">4.29151630401611</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32875299453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23566246032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33806276321411</t>
+    <t xml:space="preserve">4.32875394821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23566198348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33806228637695</t>
   </si>
   <si>
     <t xml:space="preserve">4.15187883377075</t>
@@ -887,28 +887,28 @@
     <t xml:space="preserve">4.13326120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18911552429199</t>
+    <t xml:space="preserve">4.18911600112915</t>
   </si>
   <si>
     <t xml:space="preserve">4.34737157821655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19842576980591</t>
+    <t xml:space="preserve">4.19842529296875</t>
   </si>
   <si>
     <t xml:space="preserve">4.31944370269775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27289867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51493644714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39391660690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42184448242188</t>
+    <t xml:space="preserve">4.27289819717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5149359703064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39391708374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42184495925903</t>
   </si>
   <si>
     <t xml:space="preserve">4.87799263000488</t>
@@ -917,34 +917,34 @@
     <t xml:space="preserve">4.71042823791504</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60802698135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61733627319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26358985900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11464262008667</t>
+    <t xml:space="preserve">4.60802745819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61733675003052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26358938217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11464309692383</t>
   </si>
   <si>
     <t xml:space="preserve">4.10533380508423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17980623245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07740592956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95638704299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90984177589417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04016971588135</t>
+    <t xml:space="preserve">4.17980670928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07740640640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95638728141785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90984106063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04016923904419</t>
   </si>
   <si>
     <t xml:space="preserve">4.25428009033203</t>
@@ -959,22 +959,22 @@
     <t xml:space="preserve">4.54286336898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30082607269287</t>
+    <t xml:space="preserve">4.30082559585571</t>
   </si>
   <si>
     <t xml:space="preserve">4.44977235794067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58010005950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79421043395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88730192184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61688423156738</t>
+    <t xml:space="preserve">4.58010053634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7942099571228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88730144500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6168851852417</t>
   </si>
   <si>
     <t xml:space="preserve">4.59804010391235</t>
@@ -989,10 +989,10 @@
     <t xml:space="preserve">4.56035137176514</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44728422164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67341756820679</t>
+    <t xml:space="preserve">4.44728469848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67341804504395</t>
   </si>
   <si>
     <t xml:space="preserve">4.69226217269897</t>
@@ -1001,22 +1001,22 @@
     <t xml:space="preserve">4.80532884597778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89955139160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85243988037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99377298355103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94666194915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04088401794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22932863235474</t>
+    <t xml:space="preserve">4.8995509147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85243940353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99377346038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94666147232056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04088354110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22932815551758</t>
   </si>
   <si>
     <t xml:space="preserve">5.60621690750122</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">5.65332841873169</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32355070114136</t>
+    <t xml:space="preserve">5.3235502243042</t>
   </si>
   <si>
     <t xml:space="preserve">5.37066125869751</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">5.18221759796143</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13510656356812</t>
+    <t xml:space="preserve">5.13510608673096</t>
   </si>
   <si>
     <t xml:space="preserve">5.08799505233765</t>
@@ -1064,19 +1064,19 @@
     <t xml:space="preserve">4.81486320495605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74812269210815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67184734344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53836679458618</t>
+    <t xml:space="preserve">4.748122215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67184782028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53836631774902</t>
   </si>
   <si>
     <t xml:space="preserve">4.65277862548828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57650423049927</t>
+    <t xml:space="preserve">4.57650375366211</t>
   </si>
   <si>
     <t xml:space="preserve">4.72905397415161</t>
@@ -1085,16 +1085,16 @@
     <t xml:space="preserve">4.86253499984741</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91020727157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95787858963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63370990753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61464166641235</t>
+    <t xml:space="preserve">4.91020679473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95787906646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6337103843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6146411895752</t>
   </si>
   <si>
     <t xml:space="preserve">4.59557247161865</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">4.71022033691406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78743743896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01908683776855</t>
+    <t xml:space="preserve">4.78743696212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01908731460571</t>
   </si>
   <si>
     <t xml:space="preserve">5.16386842727661</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">5.45343112945557</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35691070556641</t>
+    <t xml:space="preserve">5.35691022872925</t>
   </si>
   <si>
     <t xml:space="preserve">5.30865001678467</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">5.26038932800293</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5016918182373</t>
+    <t xml:space="preserve">5.50169134140015</t>
   </si>
   <si>
     <t xml:space="preserve">5.74299383163452</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">5.59821271896362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64647340774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54995250701904</t>
+    <t xml:space="preserve">5.6464729309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54995203018188</t>
   </si>
   <si>
     <t xml:space="preserve">5.21212959289551</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06734800338745</t>
+    <t xml:space="preserve">5.06734752655029</t>
   </si>
   <si>
     <t xml:space="preserve">4.92256641387939</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">5.11560869216919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87430572509766</t>
+    <t xml:space="preserve">4.87430620193481</t>
   </si>
   <si>
     <t xml:space="preserve">4.82604551315308</t>
@@ -46046,7 +46046,7 @@
     </row>
     <row r="1705">
       <c r="A1705" s="1" t="n">
-        <v>45958.6207175926</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B1705" t="n">
         <v>600</v>
@@ -46067,6 +46067,32 @@
         <v>463</v>
       </c>
       <c r="H1705" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" s="1" t="n">
+        <v>45959.5916898148</v>
+      </c>
+      <c r="B1706" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C1706" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="D1706" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="E1706" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="F1706" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="G1706" t="s">
+        <v>463</v>
+      </c>
+      <c r="H1706" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ILP.MI.xlsx
+++ b/data/ILP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="463">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95026254653931</t>
+    <t xml:space="preserve">1.95026230812073</t>
   </si>
   <si>
     <t xml:space="preserve">ILP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97638249397278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91543638706207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94112074375153</t>
+    <t xml:space="preserve">1.97638201713562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91543614864349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94112062454224</t>
   </si>
   <si>
     <t xml:space="preserve">2.00685501098633</t>
@@ -59,178 +59,178 @@
     <t xml:space="preserve">1.97986471652985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93284964561462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95853400230408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92109572887421</t>
+    <t xml:space="preserve">1.93284976482391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95853364467621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92109620571136</t>
   </si>
   <si>
     <t xml:space="preserve">1.94199156761169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95418059825897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93067276477814</t>
+    <t xml:space="preserve">1.95418047904968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93067264556885</t>
   </si>
   <si>
     <t xml:space="preserve">1.88931715488434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86798596382141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89062261581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91978979110718</t>
+    <t xml:space="preserve">1.8679860830307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89062285423279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9197895526886</t>
   </si>
   <si>
     <t xml:space="preserve">1.94155621528625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93807315826416</t>
+    <t xml:space="preserve">1.93807339668274</t>
   </si>
   <si>
     <t xml:space="preserve">1.91717755794525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9755117893219</t>
+    <t xml:space="preserve">1.97551167011261</t>
   </si>
   <si>
     <t xml:space="preserve">1.93459069728851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96767568588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02775025367737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01556134223938</t>
+    <t xml:space="preserve">1.96767544746399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02775073051453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01556181907654</t>
   </si>
   <si>
     <t xml:space="preserve">2.00250172615051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01991438865662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89802360534668</t>
+    <t xml:space="preserve">2.0199146270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89802372455597</t>
   </si>
   <si>
     <t xml:space="preserve">1.98508870601654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.880610704422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8457840681076</t>
+    <t xml:space="preserve">1.88061046600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84578418731689</t>
   </si>
   <si>
     <t xml:space="preserve">1.86319732666016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88994181156158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90777158737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87211227416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92560124397278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94343042373657</t>
+    <t xml:space="preserve">1.88994145393372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90777170658112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87211215496063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9256010055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94343113899231</t>
   </si>
   <si>
     <t xml:space="preserve">1.9612603187561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97908997535706</t>
+    <t xml:space="preserve">1.97908985614777</t>
   </si>
   <si>
     <t xml:space="preserve">1.83645284175873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81862330436707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76513421535492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85428249835968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8007937669754</t>
+    <t xml:space="preserve">1.81862306594849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7651344537735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8542822599411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80079352855682</t>
   </si>
   <si>
     <t xml:space="preserve">1.78296399116516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93451571464539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95234525203705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88102674484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89885675907135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82753789424896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84536743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7294750213623</t>
+    <t xml:space="preserve">1.93451583385468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95234549045563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88102698326111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89885663986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82753813266754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84536778926849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72947525978088</t>
   </si>
   <si>
     <t xml:space="preserve">1.7740490436554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76959156990051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79187870025635</t>
+    <t xml:space="preserve">1.7695916891098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79187858104706</t>
   </si>
   <si>
     <t xml:space="preserve">1.80970847606659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77850639820099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70718789100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72501754760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74730479717255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73838996887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75621962547302</t>
+    <t xml:space="preserve">1.77850651741028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70718801021576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72501742839813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74730467796326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73838973045349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75621950626373</t>
   </si>
   <si>
     <t xml:space="preserve">1.71164536476135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72056019306183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6938157081604</t>
+    <t xml:space="preserve">1.72056007385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69381582736969</t>
   </si>
   <si>
     <t xml:space="preserve">1.64032685756683</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">1.64924156665802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67598617076874</t>
+    <t xml:space="preserve">1.67598593235016</t>
   </si>
   <si>
     <t xml:space="preserve">1.56900823116302</t>
@@ -248,40 +248,40 @@
     <t xml:space="preserve">1.66707122325897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63141191005707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65815663337708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68490099906921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70273053646088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61358213424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03257894515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1930456161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13955664634705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38917183876038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33568239212036</t>
+    <t xml:space="preserve">1.63141202926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65815651416779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68490087985992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70273041725159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61358225345612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03257870674133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19304537773132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1395571231842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3891716003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3356831073761</t>
   </si>
   <si>
     <t xml:space="preserve">2.54963850975037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58529782295227</t>
+    <t xml:space="preserve">2.58529806137085</t>
   </si>
   <si>
     <t xml:space="preserve">3.03103876113892</t>
@@ -290,16 +290,16 @@
     <t xml:space="preserve">3.42329072952271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22716426849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19150543212891</t>
+    <t xml:space="preserve">3.22716450691223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19150567054749</t>
   </si>
   <si>
     <t xml:space="preserve">3.13801646232605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01320862770081</t>
+    <t xml:space="preserve">3.01320910453796</t>
   </si>
   <si>
     <t xml:space="preserve">2.99537920951843</t>
@@ -308,34 +308,34 @@
     <t xml:space="preserve">2.97754955291748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08452773094177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88840174674988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71010565757751</t>
+    <t xml:space="preserve">3.08452749252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8884015083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71010494232178</t>
   </si>
   <si>
     <t xml:space="preserve">2.6922755241394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67444610595703</t>
+    <t xml:space="preserve">2.67444562911987</t>
   </si>
   <si>
     <t xml:space="preserve">2.79925346374512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8349130153656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90623140335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78142404556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87057185173035</t>
+    <t xml:space="preserve">2.83491277694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90623092651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78142356872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87057161331177</t>
   </si>
   <si>
     <t xml:space="preserve">3.00555157661438</t>
@@ -344,22 +344,22 @@
     <t xml:space="preserve">3.07754111289978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9875545501709</t>
+    <t xml:space="preserve">2.98755431175232</t>
   </si>
   <si>
     <t xml:space="preserve">3.05954384803772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14953017234802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20352220535278</t>
+    <t xml:space="preserve">3.14952993392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2035219669342</t>
   </si>
   <si>
     <t xml:space="preserve">3.32950329780579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38349580764771</t>
+    <t xml:space="preserve">3.38349509239197</t>
   </si>
   <si>
     <t xml:space="preserve">3.36549782752991</t>
@@ -377,121 +377,121 @@
     <t xml:space="preserve">3.29350876808167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41948986053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25751423835754</t>
+    <t xml:space="preserve">3.41949009895325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25751399993896</t>
   </si>
   <si>
     <t xml:space="preserve">3.2395167350769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22151947021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40149283409119</t>
+    <t xml:space="preserve">3.22151970863342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40149259567261</t>
   </si>
   <si>
     <t xml:space="preserve">3.43748712539673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65345501899719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56346845626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63545799255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86942362785339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99540424346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01340198516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9414119720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76143884658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9234139919281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9774067401886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8874204158783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85142588615417</t>
+    <t xml:space="preserve">3.65345525741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56346893310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63545775413513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86942219734192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99540376663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0134015083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94141221046448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76143908500671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92341566085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97740745544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88742017745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85142612457275</t>
   </si>
   <si>
     <t xml:space="preserve">3.90541744232178</t>
   </si>
   <si>
-    <t xml:space="preserve">4.175377368927</t>
+    <t xml:space="preserve">4.17537689208984</t>
   </si>
   <si>
     <t xml:space="preserve">4.15738010406494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24736595153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35535049438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3913459777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31935596466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30135917663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32852506637573</t>
+    <t xml:space="preserve">4.24736642837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35535097122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39134502410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3193564414978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30135822296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32852458953857</t>
   </si>
   <si>
     <t xml:space="preserve">4.34663581848145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23796939849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20174837112427</t>
+    <t xml:space="preserve">4.23797035217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20174741744995</t>
   </si>
   <si>
     <t xml:space="preserve">4.21985864639282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12930345535278</t>
+    <t xml:space="preserve">4.12930393218994</t>
   </si>
   <si>
     <t xml:space="preserve">4.05686044692993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16552639007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09308242797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43719100952148</t>
+    <t xml:space="preserve">4.16552591323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09308195114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43719053268433</t>
   </si>
   <si>
     <t xml:space="preserve">4.29230260848999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11119318008423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25608062744141</t>
+    <t xml:space="preserve">4.11119365692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25608110427856</t>
   </si>
   <si>
     <t xml:space="preserve">4.41907978057861</t>
@@ -500,34 +500,34 @@
     <t xml:space="preserve">4.14741468429565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07497024536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02063846588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9481942653656</t>
+    <t xml:space="preserve">4.07497072219849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02063798904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94819450378418</t>
   </si>
   <si>
     <t xml:space="preserve">3.93008327484131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89386177062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98441600799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03874969482422</t>
+    <t xml:space="preserve">3.89386081695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98441624641418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03874921798706</t>
   </si>
   <si>
     <t xml:space="preserve">3.9119725227356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87575030326843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74897313117981</t>
+    <t xml:space="preserve">3.87575101852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74897336959839</t>
   </si>
   <si>
     <t xml:space="preserve">3.82141733169556</t>
@@ -536,40 +536,40 @@
     <t xml:space="preserve">3.83952784538269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62219643592834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73086166381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65841865539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78519535064697</t>
+    <t xml:space="preserve">3.62219667434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7308623790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65841841697693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78519558906555</t>
   </si>
   <si>
     <t xml:space="preserve">4.00252723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18363666534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31041383743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96630525588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80330610275269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71275115013123</t>
+    <t xml:space="preserve">4.1836371421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31041431427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96630501747131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80330657958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71275162696838</t>
   </si>
   <si>
     <t xml:space="preserve">3.44108653068542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53164172172546</t>
+    <t xml:space="preserve">3.53164148330688</t>
   </si>
   <si>
     <t xml:space="preserve">3.4954195022583</t>
@@ -578,13 +578,13 @@
     <t xml:space="preserve">3.38675379753113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15131115913391</t>
+    <t xml:space="preserve">3.15131092071533</t>
   </si>
   <si>
     <t xml:space="preserve">2.7347583770752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80720233917236</t>
+    <t xml:space="preserve">2.80720210075378</t>
   </si>
   <si>
     <t xml:space="preserve">2.69853639602661</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">2.77098035812378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89775705337524</t>
+    <t xml:space="preserve">2.8977575302124</t>
   </si>
   <si>
     <t xml:space="preserve">3.09697818756104</t>
@@ -605,115 +605,118 @@
     <t xml:space="preserve">3.13319993019104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33242082595825</t>
+    <t xml:space="preserve">3.33242106437683</t>
   </si>
   <si>
     <t xml:space="preserve">3.36864280700684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40486478805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31430959701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18753266334534</t>
+    <t xml:space="preserve">3.40486454963684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31430983543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18753290176392</t>
   </si>
   <si>
     <t xml:space="preserve">3.22375464439392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56786370277405</t>
+    <t xml:space="preserve">3.56786346435547</t>
   </si>
   <si>
     <t xml:space="preserve">3.54975271224976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55880784988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51353049278259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45014190673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42297530174255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35053205490112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41392016410828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34147644042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25092148780823</t>
+    <t xml:space="preserve">3.55880808830261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51353096961975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45014238357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42297554016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35053181648254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41392040252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34147620201111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25092124938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32336521148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33267450332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35129261016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41645669937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49093008041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36991095542908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5374755859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63056707382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59333038330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74227666854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84467744827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8539867401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79813170433044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7795135974884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75158619880676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6771125793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66780376434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65849471092224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3792200088501</t>
   </si>
   <si>
     <t xml:space="preserve">3.3233654499054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33267426490784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35129284858704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41645693778992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49092984199524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3699107170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5374755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63056755065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59333062171936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74227690696716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84467744827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8539867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79813194274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77951335906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75158667564392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67711329460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66780400276184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65849494934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37922048568726</t>
-  </si>
-  <si>
     <t xml:space="preserve">3.44438433647156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21165537834167</t>
+    <t xml:space="preserve">3.21165561676025</t>
   </si>
   <si>
     <t xml:space="preserve">3.11856412887573</t>
@@ -725,7 +728,7 @@
     <t xml:space="preserve">3.34198355674744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43507528305054</t>
+    <t xml:space="preserve">3.43507504463196</t>
   </si>
   <si>
     <t xml:space="preserve">3.46300268173218</t>
@@ -734,40 +737,40 @@
     <t xml:space="preserve">3.6026394367218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47231197357178</t>
+    <t xml:space="preserve">3.47231149673462</t>
   </si>
   <si>
     <t xml:space="preserve">3.621258020401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52816653251648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4816210269928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42576599121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64918541908264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72365856170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51885747909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77020454406738</t>
+    <t xml:space="preserve">3.52816677093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48162078857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42576622962952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64918565750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72365880012512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51885724067688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7702043056488</t>
   </si>
   <si>
     <t xml:space="preserve">3.58402156829834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7050404548645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6864218711853</t>
+    <t xml:space="preserve">3.70504021644592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68642234802246</t>
   </si>
   <si>
     <t xml:space="preserve">3.80744099617004</t>
@@ -776,19 +779,19 @@
     <t xml:space="preserve">3.29543781280518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56540274620056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00293302536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92845940589905</t>
+    <t xml:space="preserve">3.56540298461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00293254852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92845988273621</t>
   </si>
   <si>
     <t xml:space="preserve">3.788822889328</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98431468009949</t>
+    <t xml:space="preserve">3.98431539535522</t>
   </si>
   <si>
     <t xml:space="preserve">3.8632960319519</t>
@@ -803,10 +806,10 @@
     <t xml:space="preserve">4.16118860244751</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22635221481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38460779190063</t>
+    <t xml:space="preserve">4.22635316848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38460826873779</t>
   </si>
   <si>
     <t xml:space="preserve">4.4870080947876</t>
@@ -815,10 +818,10 @@
     <t xml:space="preserve">4.35668087005615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50562715530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63595485687256</t>
+    <t xml:space="preserve">4.50562763214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6359543800354</t>
   </si>
   <si>
     <t xml:space="preserve">4.49631786346436</t>
@@ -839,55 +842,55 @@
     <t xml:space="preserve">4.56148147583008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57079124450684</t>
+    <t xml:space="preserve">4.57079076766968</t>
   </si>
   <si>
     <t xml:space="preserve">4.45908117294312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52424573898315</t>
+    <t xml:space="preserve">4.524245262146</t>
   </si>
   <si>
     <t xml:space="preserve">4.58940935134888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59871816635132</t>
+    <t xml:space="preserve">4.59871864318848</t>
   </si>
   <si>
     <t xml:space="preserve">4.44046306610107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37529850006104</t>
+    <t xml:space="preserve">4.37529897689819</t>
   </si>
   <si>
     <t xml:space="preserve">4.41253519058228</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29151630401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32875347137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23566198348999</t>
+    <t xml:space="preserve">4.29151678085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3287525177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23566246032715</t>
   </si>
   <si>
     <t xml:space="preserve">4.33806180953979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15187883377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13326120376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18911600112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34737157821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19842576980591</t>
+    <t xml:space="preserve">4.15187931060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13326072692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18911552429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34737205505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19842529296875</t>
   </si>
   <si>
     <t xml:space="preserve">4.31944370269775</t>
@@ -896,25 +899,25 @@
     <t xml:space="preserve">4.27289867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51493644714355</t>
+    <t xml:space="preserve">4.5149359703064</t>
   </si>
   <si>
     <t xml:space="preserve">4.39391660690308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42184543609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87799215316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71042776107788</t>
+    <t xml:space="preserve">4.42184448242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87799310684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71042823791504</t>
   </si>
   <si>
     <t xml:space="preserve">4.60802698135376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61733675003052</t>
+    <t xml:space="preserve">4.61733627319336</t>
   </si>
   <si>
     <t xml:space="preserve">4.26358890533447</t>
@@ -923,43 +926,43 @@
     <t xml:space="preserve">4.11464309692383</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10533332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17980718612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07740640640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95638728141785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90984129905701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04017019271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25428056716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6545729637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70111894607544</t>
+    <t xml:space="preserve">4.10533380508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17980623245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07740592956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95638680458069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90984177589417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04016971588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25427913665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65457344055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70111846923828</t>
   </si>
   <si>
     <t xml:space="preserve">4.54286336898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30082559585571</t>
+    <t xml:space="preserve">4.30082607269287</t>
   </si>
   <si>
     <t xml:space="preserve">4.44977188110352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58010053634644</t>
+    <t xml:space="preserve">4.58010005950928</t>
   </si>
   <si>
     <t xml:space="preserve">4.79421091079712</t>
@@ -968,7 +971,7 @@
     <t xml:space="preserve">4.88730239868164</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61688423156738</t>
+    <t xml:space="preserve">4.61688470840454</t>
   </si>
   <si>
     <t xml:space="preserve">4.59804010391235</t>
@@ -977,10 +980,10 @@
     <t xml:space="preserve">4.52266263961792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57919597625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56035137176514</t>
+    <t xml:space="preserve">4.57919549942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56035184860229</t>
   </si>
   <si>
     <t xml:space="preserve">4.44728422164917</t>
@@ -989,82 +992,82 @@
     <t xml:space="preserve">4.67341804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69226217269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80532884597778</t>
+    <t xml:space="preserve">4.69226169586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80532932281494</t>
   </si>
   <si>
     <t xml:space="preserve">4.89955043792725</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85244035720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99377346038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94666242599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04088449478149</t>
+    <t xml:space="preserve">4.85243988037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99377298355103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94666194915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04088401794434</t>
   </si>
   <si>
     <t xml:space="preserve">5.22932815551758</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60621690750122</t>
+    <t xml:space="preserve">5.60621643066406</t>
   </si>
   <si>
     <t xml:space="preserve">5.5119948387146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70043897628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65332794189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3235502243042</t>
+    <t xml:space="preserve">5.700439453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65332841873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32355070114136</t>
   </si>
   <si>
     <t xml:space="preserve">5.37066125869751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18221712112427</t>
+    <t xml:space="preserve">5.18221759796143</t>
   </si>
   <si>
     <t xml:space="preserve">5.13510608673096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0879955291748</t>
+    <t xml:space="preserve">5.08799505233765</t>
   </si>
   <si>
     <t xml:space="preserve">4.75821781158447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.711106300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76719093322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69091653823853</t>
+    <t xml:space="preserve">4.71110677719116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7671914100647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69091606140137</t>
   </si>
   <si>
     <t xml:space="preserve">4.70998477935791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81486320495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.748122215271</t>
+    <t xml:space="preserve">4.8148627281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74812173843384</t>
   </si>
   <si>
     <t xml:space="preserve">4.67184734344482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53836631774902</t>
+    <t xml:space="preserve">4.53836679458618</t>
   </si>
   <si>
     <t xml:space="preserve">4.65277862548828</t>
@@ -1076,7 +1079,7 @@
     <t xml:space="preserve">4.72905397415161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86253499984741</t>
+    <t xml:space="preserve">4.86253547668457</t>
   </si>
   <si>
     <t xml:space="preserve">4.91020727157593</t>
@@ -1085,16 +1088,16 @@
     <t xml:space="preserve">4.95787858963013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6337103843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6146411895752</t>
+    <t xml:space="preserve">4.63370990753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61464166641235</t>
   </si>
   <si>
     <t xml:space="preserve">4.59557199478149</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55743503570557</t>
+    <t xml:space="preserve">4.55743455886841</t>
   </si>
   <si>
     <t xml:space="preserve">4.74882888793945</t>
@@ -1109,22 +1112,22 @@
     <t xml:space="preserve">5.01908683776855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16386842727661</t>
+    <t xml:space="preserve">5.16386890411377</t>
   </si>
   <si>
     <t xml:space="preserve">5.45343112945557</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35691070556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30865001678467</t>
+    <t xml:space="preserve">5.35691022872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30864953994751</t>
   </si>
   <si>
     <t xml:space="preserve">5.40517044067383</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26038932800293</t>
+    <t xml:space="preserve">5.26038980484009</t>
   </si>
   <si>
     <t xml:space="preserve">5.50169134140015</t>
@@ -1151,13 +1154,13 @@
     <t xml:space="preserve">4.92256641387939</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11560821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87430572509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82604503631592</t>
+    <t xml:space="preserve">5.11560869216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87430620193481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82604551315308</t>
   </si>
   <si>
     <t xml:space="preserve">4.97082662582397</t>
@@ -23750,7 +23753,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G847" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -23776,7 +23779,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G848" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -23802,7 +23805,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G849" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -23854,7 +23857,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G851" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -23880,7 +23883,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G852" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -23906,7 +23909,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G853" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -23932,7 +23935,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G854" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -23958,7 +23961,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G855" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -23984,7 +23987,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G856" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24010,7 +24013,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G857" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -24036,7 +24039,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G858" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -24062,7 +24065,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G859" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -24088,7 +24091,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G860" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -24114,7 +24117,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G861" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -24166,7 +24169,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G863" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -24218,7 +24221,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G865" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -24244,7 +24247,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G866" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -24296,7 +24299,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G868" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -24322,7 +24325,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G869" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -24348,7 +24351,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G870" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -24374,7 +24377,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G871" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -24400,7 +24403,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G872" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -24426,7 +24429,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G873" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -24478,7 +24481,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G875" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -24582,7 +24585,7 @@
         <v>4</v>
       </c>
       <c r="G879" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -24608,7 +24611,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G880" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -24686,7 +24689,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G883" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -24790,7 +24793,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G887" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -24816,7 +24819,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G888" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -24920,7 +24923,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G892" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -24972,7 +24975,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G894" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -24998,7 +25001,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G895" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -25024,7 +25027,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G896" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -25050,7 +25053,7 @@
         <v>4</v>
       </c>
       <c r="G897" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -25128,7 +25131,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G900" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -25154,7 +25157,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G901" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -25180,7 +25183,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G902" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -25232,7 +25235,7 @@
         <v>4</v>
       </c>
       <c r="G904" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -25258,7 +25261,7 @@
         <v>4</v>
       </c>
       <c r="G905" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -25310,7 +25313,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G907" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -25336,7 +25339,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G908" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -25362,7 +25365,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G909" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -25388,7 +25391,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G910" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -25414,7 +25417,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G911" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -25466,7 +25469,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G913" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -25492,7 +25495,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G914" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -25622,7 +25625,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G919" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -25700,7 +25703,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G922" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -25726,7 +25729,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G923" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -25752,7 +25755,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G924" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -25778,7 +25781,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G925" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -25804,7 +25807,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G926" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -25830,7 +25833,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G927" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -25856,7 +25859,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G928" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -25882,7 +25885,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G929" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -25908,7 +25911,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G930" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -25934,7 +25937,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G931" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -25960,7 +25963,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G932" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -25986,7 +25989,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G933" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26012,7 +26015,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G934" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26038,7 +26041,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G935" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26064,7 +26067,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G936" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26090,7 +26093,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G937" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -26142,7 +26145,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G939" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26168,7 +26171,7 @@
         <v>4</v>
       </c>
       <c r="G940" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -26194,7 +26197,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G941" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -26220,7 +26223,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G942" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -26246,7 +26249,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G943" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -26272,7 +26275,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G944" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -26298,7 +26301,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G945" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -26324,7 +26327,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G946" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -26350,7 +26353,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G947" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -26428,7 +26431,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G950" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26480,7 +26483,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G952" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26506,7 +26509,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G953" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26532,7 +26535,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G954" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26558,7 +26561,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G955" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26584,7 +26587,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G956" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26610,7 +26613,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G957" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26636,7 +26639,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G958" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -26662,7 +26665,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G959" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -26688,7 +26691,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G960" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -26714,7 +26717,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G961" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -26740,7 +26743,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G962" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -26766,7 +26769,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G963" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -26792,7 +26795,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G964" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -26818,7 +26821,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G965" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -26844,7 +26847,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G966" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -26870,7 +26873,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G967" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -26896,7 +26899,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G968" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -26922,7 +26925,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G969" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -26948,7 +26951,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G970" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -26974,7 +26977,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G971" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27000,7 +27003,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G972" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27026,7 +27029,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G973" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27052,7 +27055,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G974" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27078,7 +27081,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G975" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -27104,7 +27107,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G976" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27130,7 +27133,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G977" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27156,7 +27159,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G978" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -27182,7 +27185,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G979" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27208,7 +27211,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G980" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27234,7 +27237,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G981" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27260,7 +27263,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G982" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -27286,7 +27289,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G983" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -27312,7 +27315,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G984" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27338,7 +27341,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G985" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -27364,7 +27367,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G986" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -27390,7 +27393,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G987" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -27416,7 +27419,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G988" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -27442,7 +27445,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G989" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -27468,7 +27471,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G990" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -27494,7 +27497,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G991" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -27520,7 +27523,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G992" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -27546,7 +27549,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G993" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -27572,7 +27575,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G994" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -27598,7 +27601,7 @@
         <v>4.5</v>
       </c>
       <c r="G995" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -27624,7 +27627,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G996" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -27650,7 +27653,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G997" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -27676,7 +27679,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G998" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -27702,7 +27705,7 @@
         <v>4.5</v>
       </c>
       <c r="G999" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -27728,7 +27731,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1000" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -27754,7 +27757,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1001" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -27780,7 +27783,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1002" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -27806,7 +27809,7 @@
         <v>4.5</v>
       </c>
       <c r="G1003" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -27832,7 +27835,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1004" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -27858,7 +27861,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1005" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -27884,7 +27887,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1006" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -27910,7 +27913,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1007" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -27936,7 +27939,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1008" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -27962,7 +27965,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1009" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -27988,7 +27991,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1010" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -28014,7 +28017,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1011" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28040,7 +28043,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1012" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28066,7 +28069,7 @@
         <v>4.75</v>
       </c>
       <c r="G1013" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28092,7 +28095,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1014" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28118,7 +28121,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1015" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28144,7 +28147,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1016" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28170,7 +28173,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1017" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -28196,7 +28199,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1018" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -28222,7 +28225,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1019" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -28248,7 +28251,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1020" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28274,7 +28277,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1021" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28300,7 +28303,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1022" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -28326,7 +28329,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1023" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -28352,7 +28355,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1024" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28378,7 +28381,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1025" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28404,7 +28407,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1026" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28430,7 +28433,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1027" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28456,7 +28459,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1028" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28482,7 +28485,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1029" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28508,7 +28511,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1030" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28534,7 +28537,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1031" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28560,7 +28563,7 @@
         <v>4.5</v>
       </c>
       <c r="G1032" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28586,7 +28589,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1033" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28612,7 +28615,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1034" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28638,7 +28641,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1035" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -28664,7 +28667,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1036" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -28690,7 +28693,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1037" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -28716,7 +28719,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1038" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -28742,7 +28745,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1039" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -28768,7 +28771,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1040" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -28794,7 +28797,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1041" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -28820,7 +28823,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1042" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -28846,7 +28849,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1043" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -28872,7 +28875,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1044" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -28898,7 +28901,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1045" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -28924,7 +28927,7 @@
         <v>4.25</v>
       </c>
       <c r="G1046" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -28950,7 +28953,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1047" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -28976,7 +28979,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1048" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29002,7 +29005,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1049" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29028,7 +29031,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1050" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29054,7 +29057,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1051" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29080,7 +29083,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1052" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -29106,7 +29109,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1053" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29132,7 +29135,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1054" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29158,7 +29161,7 @@
         <v>5</v>
       </c>
       <c r="G1055" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29184,7 +29187,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1056" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29210,7 +29213,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29236,7 +29239,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1058" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29262,7 +29265,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1059" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29288,7 +29291,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1060" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29314,7 +29317,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1061" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29340,7 +29343,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1062" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29366,7 +29369,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1063" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29392,7 +29395,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1064" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29418,7 +29421,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1065" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29444,7 +29447,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1066" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29470,7 +29473,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1067" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29496,7 +29499,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1068" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29522,7 +29525,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1069" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29548,7 +29551,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1070" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29574,7 +29577,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1071" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -29600,7 +29603,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1072" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -29626,7 +29629,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1073" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -29652,7 +29655,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1074" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -29678,7 +29681,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1075" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -29704,7 +29707,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1076" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -29730,7 +29733,7 @@
         <v>5.25</v>
       </c>
       <c r="G1077" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -29756,7 +29759,7 @@
         <v>5.25</v>
       </c>
       <c r="G1078" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -29782,7 +29785,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1079" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -29808,7 +29811,7 @@
         <v>5</v>
       </c>
       <c r="G1080" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -29834,7 +29837,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1081" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -29860,7 +29863,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1082" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -29886,7 +29889,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1083" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -29912,7 +29915,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1084" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -29938,7 +29941,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1085" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -29964,7 +29967,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1086" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -29990,7 +29993,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1087" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30016,7 +30019,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1088" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30042,7 +30045,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1089" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -30068,7 +30071,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1090" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30094,7 +30097,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1091" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30120,7 +30123,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1092" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30146,7 +30149,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1093" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30172,7 +30175,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1094" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -30198,7 +30201,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1095" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -30224,7 +30227,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1096" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -30250,7 +30253,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1097" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -30276,7 +30279,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1098" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -30302,7 +30305,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1099" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -30328,7 +30331,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1100" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -30354,7 +30357,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1101" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -30380,7 +30383,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1102" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -30406,7 +30409,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1103" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -30432,7 +30435,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1104" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -30458,7 +30461,7 @@
         <v>5.25</v>
       </c>
       <c r="G1105" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -30484,7 +30487,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1106" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30510,7 +30513,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1107" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30536,7 +30539,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1108" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -30562,7 +30565,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1109" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -30588,7 +30591,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1110" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -30614,7 +30617,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1111" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -30640,7 +30643,7 @@
         <v>6</v>
       </c>
       <c r="G1112" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -30666,7 +30669,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1113" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -30692,7 +30695,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1114" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -30718,7 +30721,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -30744,7 +30747,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1116" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -30770,7 +30773,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1117" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -30796,7 +30799,7 @@
         <v>5.5</v>
       </c>
       <c r="G1118" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -30822,7 +30825,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1119" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -30848,7 +30851,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1120" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -30874,7 +30877,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1121" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -30900,7 +30903,7 @@
         <v>5.5</v>
       </c>
       <c r="G1122" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -30926,7 +30929,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1123" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -30952,7 +30955,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1124" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -30978,7 +30981,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1125" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31004,7 +31007,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1126" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31030,7 +31033,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1127" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31056,7 +31059,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1128" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31082,7 +31085,7 @@
         <v>5.5</v>
       </c>
       <c r="G1129" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31108,7 +31111,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1130" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31134,7 +31137,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1131" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31160,7 +31163,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1132" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31186,7 +31189,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1133" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31212,7 +31215,7 @@
         <v>5.5</v>
       </c>
       <c r="G1134" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31238,7 +31241,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1135" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31264,7 +31267,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1136" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31290,7 +31293,7 @@
         <v>5.5</v>
       </c>
       <c r="G1137" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31316,7 +31319,7 @@
         <v>5.5</v>
       </c>
       <c r="G1138" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31342,7 +31345,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1139" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31368,7 +31371,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1140" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31394,7 +31397,7 @@
         <v>5.25</v>
       </c>
       <c r="G1141" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31420,7 +31423,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1142" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31446,7 +31449,7 @@
         <v>5.25</v>
       </c>
       <c r="G1143" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31472,7 +31475,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1144" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31498,7 +31501,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1145" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31524,7 +31527,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1146" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31550,7 +31553,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1147" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31576,7 +31579,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1148" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31602,7 +31605,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1149" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -31628,7 +31631,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1150" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -31654,7 +31657,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1151" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -31680,7 +31683,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1152" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -31706,7 +31709,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1153" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -31732,7 +31735,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1154" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -31758,7 +31761,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1155" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -31784,7 +31787,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1156" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -31810,7 +31813,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1157" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -31836,7 +31839,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1158" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -31862,7 +31865,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1159" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -31888,7 +31891,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1160" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -31914,7 +31917,7 @@
         <v>5.25</v>
       </c>
       <c r="G1161" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -31940,7 +31943,7 @@
         <v>5.25</v>
       </c>
       <c r="G1162" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -31966,7 +31969,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1163" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -31992,7 +31995,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1164" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32018,7 +32021,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1165" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32044,7 +32047,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1166" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -32070,7 +32073,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1167" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -32096,7 +32099,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1168" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -32122,7 +32125,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1169" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -32148,7 +32151,7 @@
         <v>5</v>
       </c>
       <c r="G1170" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -32174,7 +32177,7 @@
         <v>5</v>
       </c>
       <c r="G1171" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -32200,7 +32203,7 @@
         <v>5</v>
       </c>
       <c r="G1172" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -32226,7 +32229,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1173" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -32252,7 +32255,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1174" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -32278,7 +32281,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1175" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -32304,7 +32307,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1176" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -32330,7 +32333,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1177" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -32356,7 +32359,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1178" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -32382,7 +32385,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1179" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -32408,7 +32411,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1180" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -32434,7 +32437,7 @@
         <v>5.25</v>
       </c>
       <c r="G1181" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -32460,7 +32463,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1182" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -32486,7 +32489,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1183" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -32512,7 +32515,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1184" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -32538,7 +32541,7 @@
         <v>5.25</v>
       </c>
       <c r="G1185" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -32564,7 +32567,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1186" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -32590,7 +32593,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1187" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -32616,7 +32619,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1188" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -32642,7 +32645,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1189" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -32668,7 +32671,7 @@
         <v>5</v>
       </c>
       <c r="G1190" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -32694,7 +32697,7 @@
         <v>5</v>
       </c>
       <c r="G1191" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -32720,7 +32723,7 @@
         <v>5</v>
       </c>
       <c r="G1192" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -32746,7 +32749,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1193" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -32772,7 +32775,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1194" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -32798,7 +32801,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1195" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -32824,7 +32827,7 @@
         <v>5</v>
       </c>
       <c r="G1196" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -32850,7 +32853,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1197" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -32876,7 +32879,7 @@
         <v>5</v>
       </c>
       <c r="G1198" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -32902,7 +32905,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1199" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -32928,7 +32931,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1200" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -32954,7 +32957,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1201" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -32980,7 +32983,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1202" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33006,7 +33009,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1203" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33032,7 +33035,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1204" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -33058,7 +33061,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1205" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -33084,7 +33087,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1206" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -33110,7 +33113,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1207" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -33136,7 +33139,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1208" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -33162,7 +33165,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1209" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -33188,7 +33191,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1210" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -33214,7 +33217,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1211" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -33240,7 +33243,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1212" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -33266,7 +33269,7 @@
         <v>5</v>
       </c>
       <c r="G1213" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -33292,7 +33295,7 @@
         <v>5</v>
       </c>
       <c r="G1214" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -33318,7 +33321,7 @@
         <v>5</v>
       </c>
       <c r="G1215" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -33344,7 +33347,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1216" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -33370,7 +33373,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1217" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -33396,7 +33399,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1218" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -33422,7 +33425,7 @@
         <v>5</v>
       </c>
       <c r="G1219" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -33448,7 +33451,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1220" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -33474,7 +33477,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1221" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -33500,7 +33503,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1222" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -33526,7 +33529,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1223" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -33552,7 +33555,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1224" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -33578,7 +33581,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1225" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -33604,7 +33607,7 @@
         <v>5</v>
       </c>
       <c r="G1226" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -33630,7 +33633,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1227" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -33656,7 +33659,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1228" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -33682,7 +33685,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1229" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -33708,7 +33711,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1230" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -33734,7 +33737,7 @@
         <v>5</v>
       </c>
       <c r="G1231" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -33760,7 +33763,7 @@
         <v>5</v>
       </c>
       <c r="G1232" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -33786,7 +33789,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1233" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -33812,7 +33815,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1234" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -33838,7 +33841,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1235" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -33864,7 +33867,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1236" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -33890,7 +33893,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1237" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -33916,7 +33919,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1238" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -33942,7 +33945,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1239" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -33968,7 +33971,7 @@
         <v>5</v>
       </c>
       <c r="G1240" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -33994,7 +33997,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1241" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34020,7 +34023,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1242" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -34046,7 +34049,7 @@
         <v>5</v>
       </c>
       <c r="G1243" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -34072,7 +34075,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1244" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -34098,7 +34101,7 @@
         <v>5</v>
       </c>
       <c r="G1245" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34124,7 +34127,7 @@
         <v>5</v>
       </c>
       <c r="G1246" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34150,7 +34153,7 @@
         <v>5</v>
       </c>
       <c r="G1247" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -34176,7 +34179,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1248" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -34202,7 +34205,7 @@
         <v>5</v>
       </c>
       <c r="G1249" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -34228,7 +34231,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1250" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -34254,7 +34257,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1251" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -34280,7 +34283,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1252" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -34306,7 +34309,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1253" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -34332,7 +34335,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1254" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -34358,7 +34361,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1255" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -34384,7 +34387,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1256" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -34410,7 +34413,7 @@
         <v>5</v>
       </c>
       <c r="G1257" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -34436,7 +34439,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1258" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -34462,7 +34465,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1259" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -34488,7 +34491,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1260" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -34514,7 +34517,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1261" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -34540,7 +34543,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1262" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -34566,7 +34569,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1263" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -34592,7 +34595,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1264" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -34618,7 +34621,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1265" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -34644,7 +34647,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1266" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -34670,7 +34673,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1267" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -34696,7 +34699,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1268" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -34722,7 +34725,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1269" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -34748,7 +34751,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1270" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -34774,7 +34777,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1271" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -34800,7 +34803,7 @@
         <v>5</v>
       </c>
       <c r="G1272" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -34826,7 +34829,7 @@
         <v>5</v>
       </c>
       <c r="G1273" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -34852,7 +34855,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1274" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -34878,7 +34881,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1275" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -34904,7 +34907,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1276" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -34930,7 +34933,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1277" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -34956,7 +34959,7 @@
         <v>5</v>
       </c>
       <c r="G1278" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -34982,7 +34985,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1279" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35008,7 +35011,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1280" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -35034,7 +35037,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1281" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -35060,7 +35063,7 @@
         <v>5</v>
       </c>
       <c r="G1282" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -35086,7 +35089,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1283" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -35112,7 +35115,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1284" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -35138,7 +35141,7 @@
         <v>5</v>
       </c>
       <c r="G1285" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -35164,7 +35167,7 @@
         <v>5</v>
       </c>
       <c r="G1286" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -35190,7 +35193,7 @@
         <v>5</v>
       </c>
       <c r="G1287" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -35216,7 +35219,7 @@
         <v>5</v>
       </c>
       <c r="G1288" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -35242,7 +35245,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1289" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -35268,7 +35271,7 @@
         <v>5</v>
       </c>
       <c r="G1290" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35294,7 +35297,7 @@
         <v>5</v>
       </c>
       <c r="G1291" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35320,7 +35323,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1292" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35346,7 +35349,7 @@
         <v>5</v>
       </c>
       <c r="G1293" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35372,7 +35375,7 @@
         <v>5</v>
       </c>
       <c r="G1294" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35398,7 +35401,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1295" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35424,7 +35427,7 @@
         <v>5</v>
       </c>
       <c r="G1296" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35450,7 +35453,7 @@
         <v>5</v>
       </c>
       <c r="G1297" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -35476,7 +35479,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1298" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35502,7 +35505,7 @@
         <v>5</v>
       </c>
       <c r="G1299" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35528,7 +35531,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1300" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35554,7 +35557,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1301" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -35580,7 +35583,7 @@
         <v>5</v>
       </c>
       <c r="G1302" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35606,7 +35609,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1303" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35632,7 +35635,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1304" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -35658,7 +35661,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1305" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -35684,7 +35687,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1306" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -35710,7 +35713,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1307" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -35736,7 +35739,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1308" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -35762,7 +35765,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1309" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -35788,7 +35791,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1310" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -35814,7 +35817,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1311" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -35840,7 +35843,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1312" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -35866,7 +35869,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1313" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -35892,7 +35895,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1314" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -35918,7 +35921,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1315" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -35944,7 +35947,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1316" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -35970,7 +35973,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1317" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -35996,7 +35999,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1318" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36022,7 +36025,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1319" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -36048,7 +36051,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1320" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36074,7 +36077,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1321" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -36100,7 +36103,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1322" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -36126,7 +36129,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1323" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -36152,7 +36155,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1324" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -36178,7 +36181,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1325" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -36204,7 +36207,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1326" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -36230,7 +36233,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1327" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -36256,7 +36259,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1328" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -36282,7 +36285,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1329" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -36308,7 +36311,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1330" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -36334,7 +36337,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1331" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -36360,7 +36363,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1332" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -36386,7 +36389,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1333" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -36412,7 +36415,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1334" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -36438,7 +36441,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1335" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -36464,7 +36467,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1336" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -36490,7 +36493,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1337" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -36516,7 +36519,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1338" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -36542,7 +36545,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1339" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -36568,7 +36571,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1340" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -36594,7 +36597,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1341" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -36620,7 +36623,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1342" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -36646,7 +36649,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1343" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -36672,7 +36675,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1344" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -36698,7 +36701,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1345" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -36724,7 +36727,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1346" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -36750,7 +36753,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1347" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -36776,7 +36779,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1348" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -36802,7 +36805,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1349" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -36828,7 +36831,7 @@
         <v>5.5</v>
       </c>
       <c r="G1350" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -36854,7 +36857,7 @@
         <v>5.5</v>
       </c>
       <c r="G1351" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -36880,7 +36883,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1352" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -36906,7 +36909,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1353" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -36932,7 +36935,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1354" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -36958,7 +36961,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1355" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -36984,7 +36987,7 @@
         <v>5.5</v>
       </c>
       <c r="G1356" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37010,7 +37013,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1357" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37036,7 +37039,7 @@
         <v>5.5</v>
       </c>
       <c r="G1358" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -37062,7 +37065,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1359" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37088,7 +37091,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1360" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37114,7 +37117,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1361" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -37140,7 +37143,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1362" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37166,7 +37169,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1363" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -37192,7 +37195,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1364" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -37218,7 +37221,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1365" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -37244,7 +37247,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1366" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -37270,7 +37273,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1367" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -37296,7 +37299,7 @@
         <v>5.75</v>
       </c>
       <c r="G1368" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -37322,7 +37325,7 @@
         <v>5.75</v>
       </c>
       <c r="G1369" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -37348,7 +37351,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1370" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -37374,7 +37377,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1371" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -37400,7 +37403,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1372" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -37426,7 +37429,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1373" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -37452,7 +37455,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1374" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -37478,7 +37481,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1375" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -37504,7 +37507,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1376" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -37530,7 +37533,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1377" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -37556,7 +37559,7 @@
         <v>5.5</v>
       </c>
       <c r="G1378" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -37582,7 +37585,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1379" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -37608,7 +37611,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1380" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -37634,7 +37637,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1381" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -37660,7 +37663,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1382" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -37686,7 +37689,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1383" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -37712,7 +37715,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1384" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -37738,7 +37741,7 @@
         <v>5.5</v>
       </c>
       <c r="G1385" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -37764,7 +37767,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1386" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -37790,7 +37793,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1387" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -37816,7 +37819,7 @@
         <v>5.25</v>
       </c>
       <c r="G1388" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -37842,7 +37845,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1389" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -37868,7 +37871,7 @@
         <v>5.25</v>
       </c>
       <c r="G1390" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -37894,7 +37897,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1391" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -37920,7 +37923,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1392" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -37946,7 +37949,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1393" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -37972,7 +37975,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1394" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -37998,7 +38001,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1395" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38024,7 +38027,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1396" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38050,7 +38053,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1397" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38076,7 +38079,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1398" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -38102,7 +38105,7 @@
         <v>5</v>
       </c>
       <c r="G1399" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -38128,7 +38131,7 @@
         <v>5</v>
       </c>
       <c r="G1400" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -38154,7 +38157,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1401" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -38180,7 +38183,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1402" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -38206,7 +38209,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1403" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -38232,7 +38235,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1404" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -38258,7 +38261,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1405" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -38284,7 +38287,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1406" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -38310,7 +38313,7 @@
         <v>5.25</v>
       </c>
       <c r="G1407" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -38336,7 +38339,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1408" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -38362,7 +38365,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1409" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -38388,7 +38391,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1410" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -38414,7 +38417,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1411" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38440,7 +38443,7 @@
         <v>5.25</v>
       </c>
       <c r="G1412" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -38466,7 +38469,7 @@
         <v>5.25</v>
       </c>
       <c r="G1413" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -38492,7 +38495,7 @@
         <v>5.25</v>
       </c>
       <c r="G1414" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -38518,7 +38521,7 @@
         <v>5.25</v>
       </c>
       <c r="G1415" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -38544,7 +38547,7 @@
         <v>5.25</v>
       </c>
       <c r="G1416" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -38570,7 +38573,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1417" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -38596,7 +38599,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1418" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -38622,7 +38625,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1419" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -38648,7 +38651,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1420" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -38674,7 +38677,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1421" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -38700,7 +38703,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1422" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -38726,7 +38729,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1423" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -38752,7 +38755,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1424" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -38778,7 +38781,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1425" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -38804,7 +38807,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1426" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -38830,7 +38833,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1427" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -38856,7 +38859,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1428" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -38882,7 +38885,7 @@
         <v>5.25</v>
       </c>
       <c r="G1429" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -38908,7 +38911,7 @@
         <v>5.25</v>
       </c>
       <c r="G1430" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -38934,7 +38937,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1431" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -38960,7 +38963,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1432" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -38986,7 +38989,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1433" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39012,7 +39015,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1434" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39038,7 +39041,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1435" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -39064,7 +39067,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1436" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -39090,7 +39093,7 @@
         <v>5</v>
       </c>
       <c r="G1437" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39116,7 +39119,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1438" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39142,7 +39145,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1439" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39168,7 +39171,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1440" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -39194,7 +39197,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1441" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -39220,7 +39223,7 @@
         <v>5</v>
       </c>
       <c r="G1442" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39246,7 +39249,7 @@
         <v>5</v>
       </c>
       <c r="G1443" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -39272,7 +39275,7 @@
         <v>5</v>
       </c>
       <c r="G1444" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -39298,7 +39301,7 @@
         <v>5</v>
       </c>
       <c r="G1445" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -39324,7 +39327,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1446" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -39350,7 +39353,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1447" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -39376,7 +39379,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1448" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -39402,7 +39405,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1449" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39428,7 +39431,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1450" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39454,7 +39457,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1451" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39480,7 +39483,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1452" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39506,7 +39509,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1453" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39532,7 +39535,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1454" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39558,7 +39561,7 @@
         <v>5</v>
       </c>
       <c r="G1455" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39584,7 +39587,7 @@
         <v>5</v>
       </c>
       <c r="G1456" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39610,7 +39613,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1457" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39636,7 +39639,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1458" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39662,7 +39665,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1459" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39688,7 +39691,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1460" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -39714,7 +39717,7 @@
         <v>5</v>
       </c>
       <c r="G1461" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -39740,7 +39743,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1462" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -39766,7 +39769,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1463" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -39792,7 +39795,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1464" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -39818,7 +39821,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1465" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -39844,7 +39847,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1466" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -39870,7 +39873,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1467" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -39896,7 +39899,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1468" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -39922,7 +39925,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1469" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -39948,7 +39951,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1470" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -39974,7 +39977,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1471" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40000,7 +40003,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1472" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40026,7 +40029,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1473" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40052,7 +40055,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1474" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40078,7 +40081,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1475" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -40104,7 +40107,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1476" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -40130,7 +40133,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1477" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -40156,7 +40159,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1478" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -40182,7 +40185,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1479" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -40208,7 +40211,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1480" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -40234,7 +40237,7 @@
         <v>4.5</v>
       </c>
       <c r="G1481" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -40260,7 +40263,7 @@
         <v>4.5</v>
       </c>
       <c r="G1482" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -40286,7 +40289,7 @@
         <v>4.5</v>
       </c>
       <c r="G1483" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -40312,7 +40315,7 @@
         <v>4.5</v>
       </c>
       <c r="G1484" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -40338,7 +40341,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1485" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -40364,7 +40367,7 @@
         <v>4.5</v>
       </c>
       <c r="G1486" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -40390,7 +40393,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1487" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -40416,7 +40419,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1488" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40442,7 +40445,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1489" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40468,7 +40471,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1490" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40494,7 +40497,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1491" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40520,7 +40523,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1492" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -40546,7 +40549,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1493" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40572,7 +40575,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1494" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -40598,7 +40601,7 @@
         <v>4.5</v>
       </c>
       <c r="G1495" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -40624,7 +40627,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1496" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -40650,7 +40653,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1497" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -40676,7 +40679,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1498" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -40702,7 +40705,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1499" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -40728,7 +40731,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1500" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -40754,7 +40757,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1501" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -40780,7 +40783,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1502" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -40806,7 +40809,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1503" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -40832,7 +40835,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1504" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -40858,7 +40861,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1505" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -40884,7 +40887,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1506" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -40910,7 +40913,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1507" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -40936,7 +40939,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1508" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -40962,7 +40965,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1509" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -40988,7 +40991,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1510" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41014,7 +41017,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1511" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41040,7 +41043,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1512" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41066,7 +41069,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1513" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41092,7 +41095,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1514" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41118,7 +41121,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1515" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41144,7 +41147,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1516" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41170,7 +41173,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1517" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -41196,7 +41199,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1518" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -41222,7 +41225,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1519" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41248,7 +41251,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1520" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -41274,7 +41277,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1521" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -41300,7 +41303,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1522" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -41326,7 +41329,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1523" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -41352,7 +41355,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1524" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -41378,7 +41381,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1525" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -41404,7 +41407,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1526" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41430,7 +41433,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1527" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41456,7 +41459,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1528" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41482,7 +41485,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1529" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41508,7 +41511,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1530" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41534,7 +41537,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1531" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41560,7 +41563,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1532" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41586,7 +41589,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1533" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41612,7 +41615,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1534" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41638,7 +41641,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1535" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41664,7 +41667,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1536" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41690,7 +41693,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1537" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -41716,7 +41719,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1538" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -41742,7 +41745,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1539" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -41768,7 +41771,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1540" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -41794,7 +41797,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1541" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -41820,7 +41823,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1542" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -41846,7 +41849,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1543" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -41872,7 +41875,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1544" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -41898,7 +41901,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1545" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -41924,7 +41927,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1546" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -41950,7 +41953,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1547" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -41976,7 +41979,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1548" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42002,7 +42005,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1549" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42028,7 +42031,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1550" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42054,7 +42057,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1551" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42080,7 +42083,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1552" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42106,7 +42109,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1553" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42132,7 +42135,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1554" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42158,7 +42161,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1555" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42184,7 +42187,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1556" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42210,7 +42213,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1557" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -42236,7 +42239,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1558" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -42262,7 +42265,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1559" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -42288,7 +42291,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1560" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -42314,7 +42317,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1561" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -42340,7 +42343,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1562" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -42366,7 +42369,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1563" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -42392,7 +42395,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1564" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -42418,7 +42421,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1565" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42444,7 +42447,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1566" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42470,7 +42473,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1567" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42496,7 +42499,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1568" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42522,7 +42525,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1569" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42548,7 +42551,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1570" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42574,7 +42577,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1571" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42600,7 +42603,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1572" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42626,7 +42629,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1573" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42652,7 +42655,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1574" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42678,7 +42681,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1575" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -42704,7 +42707,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1576" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -42730,7 +42733,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1577" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -42756,7 +42759,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1578" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -42782,7 +42785,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1579" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -42808,7 +42811,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1580" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -42834,7 +42837,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1581" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -42860,7 +42863,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1582" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -42886,7 +42889,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1583" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -42912,7 +42915,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1584" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -42938,7 +42941,7 @@
         <v>4.5</v>
       </c>
       <c r="G1585" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -42964,7 +42967,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -42990,7 +42993,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1587" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43016,7 +43019,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1588" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43042,7 +43045,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1589" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43068,7 +43071,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1590" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43094,7 +43097,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1591" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43120,7 +43123,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1592" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43146,7 +43149,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1593" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43172,7 +43175,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1594" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43198,7 +43201,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1595" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -43224,7 +43227,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1596" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43250,7 +43253,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1597" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -43276,7 +43279,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1598" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -43302,7 +43305,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1599" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -43328,7 +43331,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1600" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -43354,7 +43357,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1601" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -43380,7 +43383,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1602" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -43406,7 +43409,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1603" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43432,7 +43435,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1604" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43458,7 +43461,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1605" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43484,7 +43487,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1606" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43510,7 +43513,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1607" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43536,7 +43539,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1608" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43562,7 +43565,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1609" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43588,7 +43591,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1610" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43614,7 +43617,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1611" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43640,7 +43643,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1612" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43666,7 +43669,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1613" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43692,7 +43695,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1614" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43718,7 +43721,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1615" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -43744,7 +43747,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1616" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43770,7 +43773,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1617" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43796,7 +43799,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1618" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43822,7 +43825,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1619" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43848,7 +43851,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1620" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -43874,7 +43877,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1621" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -43900,7 +43903,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1622" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -43926,7 +43929,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1623" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -43952,7 +43955,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1624" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -43978,7 +43981,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1625" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44004,7 +44007,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1626" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44030,7 +44033,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1627" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44056,7 +44059,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1628" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44082,7 +44085,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1629" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44108,7 +44111,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1630" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44134,7 +44137,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1631" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44160,7 +44163,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1632" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44186,7 +44189,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1633" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44212,7 +44215,7 @@
         <v>5.75</v>
       </c>
       <c r="G1634" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44238,7 +44241,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1635" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44264,7 +44267,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1636" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44290,7 +44293,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1637" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44316,7 +44319,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1638" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44342,7 +44345,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1639" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44368,7 +44371,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1640" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44394,7 +44397,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1641" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44420,7 +44423,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1642" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44446,7 +44449,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1643" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44472,7 +44475,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1644" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44498,7 +44501,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1645" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44524,7 +44527,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1646" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44550,7 +44553,7 @@
         <v>5.75</v>
       </c>
       <c r="G1647" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44576,7 +44579,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1648" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44602,7 +44605,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1649" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44628,7 +44631,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1650" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44654,7 +44657,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1651" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44680,7 +44683,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1652" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44706,7 +44709,7 @@
         <v>5.25</v>
       </c>
       <c r="G1653" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44732,7 +44735,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1654" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44758,7 +44761,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1655" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44784,7 +44787,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1656" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44810,7 +44813,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1657" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44836,7 +44839,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1658" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44862,7 +44865,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1659" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -44888,7 +44891,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1660" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44914,7 +44917,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1661" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44940,7 +44943,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1662" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44966,7 +44969,7 @@
         <v>5.5</v>
       </c>
       <c r="G1663" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44992,7 +44995,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1664" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45018,7 +45021,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1665" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45044,7 +45047,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1666" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45070,7 +45073,7 @@
         <v>5.5</v>
       </c>
       <c r="G1667" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45096,7 +45099,7 @@
         <v>5.5</v>
       </c>
       <c r="G1668" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45122,7 +45125,7 @@
         <v>5.5</v>
       </c>
       <c r="G1669" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45148,7 +45151,7 @@
         <v>5.5</v>
       </c>
       <c r="G1670" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45174,7 +45177,7 @@
         <v>5.5</v>
       </c>
       <c r="G1671" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45200,7 +45203,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1672" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45226,7 +45229,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1673" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45252,7 +45255,7 @@
         <v>5.75</v>
       </c>
       <c r="G1674" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45278,7 +45281,7 @@
         <v>5.75</v>
       </c>
       <c r="G1675" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45304,7 +45307,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1676" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45330,7 +45333,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1677" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45356,7 +45359,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1678" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45382,7 +45385,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1679" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45408,7 +45411,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1680" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45434,7 +45437,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1681" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45460,7 +45463,7 @@
         <v>5.75</v>
       </c>
       <c r="G1682" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45486,7 +45489,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1683" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45512,7 +45515,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1684" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45538,7 +45541,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1685" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45564,7 +45567,7 @@
         <v>5.5</v>
       </c>
       <c r="G1686" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45590,7 +45593,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1687" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45616,7 +45619,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1688" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45642,7 +45645,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1689" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45668,7 +45671,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1690" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45694,7 +45697,7 @@
         <v>5.75</v>
       </c>
       <c r="G1691" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45720,7 +45723,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1692" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45746,7 +45749,7 @@
         <v>5.75</v>
       </c>
       <c r="G1693" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45772,7 +45775,7 @@
         <v>5.75</v>
       </c>
       <c r="G1694" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45798,7 +45801,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1695" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45824,7 +45827,7 @@
         <v>6</v>
       </c>
       <c r="G1696" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45850,7 +45853,7 @@
         <v>6</v>
       </c>
       <c r="G1697" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -45876,7 +45879,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1698" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -45902,7 +45905,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1699" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -45928,7 +45931,7 @@
         <v>5.75</v>
       </c>
       <c r="G1700" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -45954,7 +45957,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1701" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -45980,7 +45983,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1702" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46006,7 +46009,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1703" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46032,7 +46035,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1704" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46058,7 +46061,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1705" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46084,9 +46087,61 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1706" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1706" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" s="1" t="n">
+        <v>45960.3333333333</v>
+      </c>
+      <c r="B1707" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1707" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="D1707" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="E1707" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="F1707" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="G1707" t="s">
+        <v>462</v>
+      </c>
+      <c r="H1707" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" s="1" t="n">
+        <v>45961.5530439815</v>
+      </c>
+      <c r="B1708" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C1708" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="D1708" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="E1708" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="F1708" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="G1708" t="s">
+        <v>462</v>
+      </c>
+      <c r="H1708" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ILP.MI.xlsx
+++ b/data/ILP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="462">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,190 +38,190 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95026230812073</t>
+    <t xml:space="preserve">1.95026290416718</t>
   </si>
   <si>
     <t xml:space="preserve">ILP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97638201713562</t>
+    <t xml:space="preserve">1.97638237476349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91543614864349</t>
+    <t xml:space="preserve">1.91543686389923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94112062454224</t>
+    <t xml:space="preserve">1.94112086296082</t>
   </si>
   <si>
     <t xml:space="preserve">2.00685501098633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97986471652985</t>
+    <t xml:space="preserve">1.97986483573914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93284976482391</t>
+    <t xml:space="preserve">1.93284952640533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95853364467621</t>
+    <t xml:space="preserve">1.9585337638855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92109620571136</t>
+    <t xml:space="preserve">1.9210958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94199156761169</t>
+    <t xml:space="preserve">1.94199132919312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95418047904968</t>
+    <t xml:space="preserve">1.95418035984039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93067264556885</t>
+    <t xml:space="preserve">1.93067276477814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88931715488434</t>
+    <t xml:space="preserve">1.88931691646576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8679860830307</t>
+    <t xml:space="preserve">1.86798584461212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89062285423279</t>
+    <t xml:space="preserve">1.8906227350235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9197895526886</t>
+    <t xml:space="preserve">1.91978967189789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94155621528625</t>
+    <t xml:space="preserve">1.94155609607697</t>
   </si>
   <si>
     <t xml:space="preserve">1.93807339668274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91717755794525</t>
+    <t xml:space="preserve">1.91717779636383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97551167011261</t>
+    <t xml:space="preserve">1.97551155090332</t>
   </si>
   <si>
     <t xml:space="preserve">1.93459069728851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96767544746399</t>
+    <t xml:space="preserve">1.9676753282547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02775073051453</t>
+    <t xml:space="preserve">2.02775096893311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01556181907654</t>
+    <t xml:space="preserve">2.01556134223938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00250172615051</t>
+    <t xml:space="preserve">2.00250196456909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0199146270752</t>
+    <t xml:space="preserve">2.01991510391235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89802372455597</t>
+    <t xml:space="preserve">1.8980233669281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98508870601654</t>
+    <t xml:space="preserve">1.98508846759796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88061046600342</t>
+    <t xml:space="preserve">1.88061034679413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84578418731689</t>
+    <t xml:space="preserve">1.84578382968903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86319732666016</t>
+    <t xml:space="preserve">1.86319708824158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88994145393372</t>
+    <t xml:space="preserve">1.88994133472443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90777170658112</t>
+    <t xml:space="preserve">1.90777122974396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87211215496063</t>
+    <t xml:space="preserve">1.87211203575134</t>
   </si>
   <si>
     <t xml:space="preserve">1.9256010055542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94343113899231</t>
+    <t xml:space="preserve">1.94343054294586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9612603187561</t>
+    <t xml:space="preserve">1.96126067638397</t>
   </si>
   <si>
     <t xml:space="preserve">1.97908985614777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83645284175873</t>
+    <t xml:space="preserve">1.83645260334015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81862306594849</t>
+    <t xml:space="preserve">1.81862318515778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7651344537735</t>
+    <t xml:space="preserve">1.76513421535492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8542822599411</t>
+    <t xml:space="preserve">1.85428249835968</t>
   </si>
   <si>
     <t xml:space="preserve">1.80079352855682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78296399116516</t>
+    <t xml:space="preserve">1.78296375274658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93451583385468</t>
+    <t xml:space="preserve">1.93451595306396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95234549045563</t>
+    <t xml:space="preserve">1.95234537124634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88102698326111</t>
+    <t xml:space="preserve">1.88102662563324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89885663986206</t>
+    <t xml:space="preserve">1.89885687828064</t>
   </si>
   <si>
     <t xml:space="preserve">1.82753813266754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84536778926849</t>
+    <t xml:space="preserve">1.8453676700592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72947525978088</t>
+    <t xml:space="preserve">1.72947490215302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7740490436554</t>
+    <t xml:space="preserve">1.77404916286469</t>
   </si>
   <si>
     <t xml:space="preserve">1.7695916891098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79187858104706</t>
+    <t xml:space="preserve">1.79187881946564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80970847606659</t>
+    <t xml:space="preserve">1.80970823764801</t>
   </si>
   <si>
     <t xml:space="preserve">1.77850651741028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70718801021576</t>
+    <t xml:space="preserve">1.70718789100647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72501742839813</t>
+    <t xml:space="preserve">1.72501754760742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74730467796326</t>
+    <t xml:space="preserve">1.74730455875397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73838973045349</t>
+    <t xml:space="preserve">1.73838996887207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75621950626373</t>
+    <t xml:space="preserve">1.75621938705444</t>
   </si>
   <si>
     <t xml:space="preserve">1.71164536476135</t>
@@ -230,22 +230,22 @@
     <t xml:space="preserve">1.72056007385254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69381582736969</t>
+    <t xml:space="preserve">1.69381558895111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64032685756683</t>
+    <t xml:space="preserve">1.64032673835754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64924156665802</t>
+    <t xml:space="preserve">1.64924168586731</t>
   </si>
   <si>
     <t xml:space="preserve">1.67598593235016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56900823116302</t>
+    <t xml:space="preserve">1.56900835037231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66707122325897</t>
+    <t xml:space="preserve">1.66707134246826</t>
   </si>
   <si>
     <t xml:space="preserve">1.63141202926636</t>
@@ -254,34 +254,34 @@
     <t xml:space="preserve">1.65815651416779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68490087985992</t>
+    <t xml:space="preserve">1.68490076065063</t>
   </si>
   <si>
     <t xml:space="preserve">1.70273041725159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61358225345612</t>
+    <t xml:space="preserve">1.61358237266541</t>
   </si>
   <si>
     <t xml:space="preserve">2.03257870674133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19304537773132</t>
+    <t xml:space="preserve">2.1930456161499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1395571231842</t>
+    <t xml:space="preserve">2.13955688476562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3891716003418</t>
+    <t xml:space="preserve">2.38917183876038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3356831073761</t>
+    <t xml:space="preserve">2.33568263053894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54963850975037</t>
+    <t xml:space="preserve">2.54963803291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58529806137085</t>
+    <t xml:space="preserve">2.58529758453369</t>
   </si>
   <si>
     <t xml:space="preserve">3.03103876113892</t>
@@ -290,16 +290,16 @@
     <t xml:space="preserve">3.42329072952271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22716450691223</t>
+    <t xml:space="preserve">3.22716474533081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19150567054749</t>
+    <t xml:space="preserve">3.19150543212891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13801646232605</t>
+    <t xml:space="preserve">3.13801670074463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01320910453796</t>
+    <t xml:space="preserve">3.01320934295654</t>
   </si>
   <si>
     <t xml:space="preserve">2.99537920951843</t>
@@ -329,16 +329,16 @@
     <t xml:space="preserve">2.83491277694702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90623092651367</t>
+    <t xml:space="preserve">2.90623116493225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78142356872559</t>
+    <t xml:space="preserve">2.78142333030701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87057161331177</t>
+    <t xml:space="preserve">2.87057209014893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00555157661438</t>
+    <t xml:space="preserve">3.00555181503296</t>
   </si>
   <si>
     <t xml:space="preserve">3.07754111289978</t>
@@ -350,34 +350,34 @@
     <t xml:space="preserve">3.05954384803772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14952993392944</t>
+    <t xml:space="preserve">3.14953017234802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2035219669342</t>
+    <t xml:space="preserve">3.20352244377136</t>
   </si>
   <si>
     <t xml:space="preserve">3.32950329780579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38349509239197</t>
+    <t xml:space="preserve">3.38349533081055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36549782752991</t>
+    <t xml:space="preserve">3.36549806594849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34750080108643</t>
+    <t xml:space="preserve">3.34750056266785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27551174163818</t>
+    <t xml:space="preserve">3.2755115032196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3115062713623</t>
+    <t xml:space="preserve">3.31150603294373</t>
   </si>
   <si>
     <t xml:space="preserve">3.29350876808167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41949009895325</t>
+    <t xml:space="preserve">3.41948962211609</t>
   </si>
   <si>
     <t xml:space="preserve">3.25751399993896</t>
@@ -386,25 +386,25 @@
     <t xml:space="preserve">3.2395167350769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22151970863342</t>
+    <t xml:space="preserve">3.22151899337769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40149259567261</t>
+    <t xml:space="preserve">3.40149283409119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43748712539673</t>
+    <t xml:space="preserve">3.43748736381531</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65345525741577</t>
+    <t xml:space="preserve">3.65345478057861</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56346893310547</t>
+    <t xml:space="preserve">3.56346845626831</t>
   </si>
   <si>
     <t xml:space="preserve">3.63545775413513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86942219734192</t>
+    <t xml:space="preserve">3.86942291259766</t>
   </si>
   <si>
     <t xml:space="preserve">3.99540376663208</t>
@@ -413,25 +413,25 @@
     <t xml:space="preserve">4.0134015083313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94141221046448</t>
+    <t xml:space="preserve">3.94141268730164</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76143908500671</t>
+    <t xml:space="preserve">3.76143884658813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92341566085815</t>
+    <t xml:space="preserve">3.923415184021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97740745544434</t>
+    <t xml:space="preserve">3.97740697860718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88742017745972</t>
+    <t xml:space="preserve">3.8874204158783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85142612457275</t>
+    <t xml:space="preserve">3.85142540931702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90541744232178</t>
+    <t xml:space="preserve">3.90541791915894</t>
   </si>
   <si>
     <t xml:space="preserve">4.17537689208984</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">4.15738010406494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24736642837524</t>
+    <t xml:space="preserve">4.24736595153809</t>
   </si>
   <si>
     <t xml:space="preserve">4.35535097122192</t>
@@ -449,34 +449,34 @@
     <t xml:space="preserve">4.39134502410889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3193564414978</t>
+    <t xml:space="preserve">4.31935596466064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30135822296143</t>
+    <t xml:space="preserve">4.30135869979858</t>
   </si>
   <si>
     <t xml:space="preserve">4.32852458953857</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34663581848145</t>
+    <t xml:space="preserve">4.3466362953186</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797035217285</t>
+    <t xml:space="preserve">4.23796987533569</t>
   </si>
   <si>
     <t xml:space="preserve">4.20174741744995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21985864639282</t>
+    <t xml:space="preserve">4.21985816955566</t>
   </si>
   <si>
     <t xml:space="preserve">4.12930393218994</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05686044692993</t>
+    <t xml:space="preserve">4.05685949325562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16552591323853</t>
+    <t xml:space="preserve">4.16552543640137</t>
   </si>
   <si>
     <t xml:space="preserve">4.09308195114136</t>
@@ -485,70 +485,70 @@
     <t xml:space="preserve">4.43719053268433</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29230260848999</t>
+    <t xml:space="preserve">4.29230308532715</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11119365692139</t>
+    <t xml:space="preserve">4.11119318008423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25608110427856</t>
+    <t xml:space="preserve">4.25608062744141</t>
   </si>
   <si>
     <t xml:space="preserve">4.41907978057861</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14741468429565</t>
+    <t xml:space="preserve">4.14741516113281</t>
   </si>
   <si>
     <t xml:space="preserve">4.07497072219849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02063798904419</t>
+    <t xml:space="preserve">4.02063751220703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94819450378418</t>
+    <t xml:space="preserve">3.9481942653656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93008327484131</t>
+    <t xml:space="preserve">3.93008303642273</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89386081695557</t>
+    <t xml:space="preserve">3.89386129379272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98441624641418</t>
+    <t xml:space="preserve">3.98441553115845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03874921798706</t>
+    <t xml:space="preserve">4.0387487411499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9119725227356</t>
+    <t xml:space="preserve">3.91197228431702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87575101852417</t>
+    <t xml:space="preserve">3.87574982643127</t>
   </si>
   <si>
     <t xml:space="preserve">3.74897336959839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82141733169556</t>
+    <t xml:space="preserve">3.8214168548584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83952784538269</t>
+    <t xml:space="preserve">3.83952808380127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62219667434692</t>
+    <t xml:space="preserve">3.62219643592834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7308623790741</t>
+    <t xml:space="preserve">3.73086190223694</t>
   </si>
   <si>
     <t xml:space="preserve">3.65841841697693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78519558906555</t>
+    <t xml:space="preserve">3.78519487380981</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00252723693848</t>
+    <t xml:space="preserve">4.00252676010132</t>
   </si>
   <si>
     <t xml:space="preserve">4.1836371421814</t>
@@ -557,37 +557,37 @@
     <t xml:space="preserve">4.31041431427002</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96630501747131</t>
+    <t xml:space="preserve">3.96630573272705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80330657958984</t>
+    <t xml:space="preserve">3.80330610275269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71275162696838</t>
+    <t xml:space="preserve">3.7127513885498</t>
   </si>
   <si>
     <t xml:space="preserve">3.44108653068542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53164148330688</t>
+    <t xml:space="preserve">3.53164172172546</t>
   </si>
   <si>
     <t xml:space="preserve">3.4954195022583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38675379753113</t>
+    <t xml:space="preserve">3.38675403594971</t>
   </si>
   <si>
     <t xml:space="preserve">3.15131092071533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7347583770752</t>
+    <t xml:space="preserve">2.73475861549377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80720210075378</t>
+    <t xml:space="preserve">2.80720233917236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69853639602661</t>
+    <t xml:space="preserve">2.69853663444519</t>
   </si>
   <si>
     <t xml:space="preserve">2.58987045288086</t>
@@ -596,10 +596,10 @@
     <t xml:space="preserve">2.77098035812378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8977575302124</t>
+    <t xml:space="preserve">2.89775729179382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09697818756104</t>
+    <t xml:space="preserve">3.09697794914246</t>
   </si>
   <si>
     <t xml:space="preserve">3.13319993019104</t>
@@ -611,13 +611,13 @@
     <t xml:space="preserve">3.36864280700684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40486454963684</t>
+    <t xml:space="preserve">3.40486478805542</t>
   </si>
   <si>
     <t xml:space="preserve">3.31430983543396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18753290176392</t>
+    <t xml:space="preserve">3.18753266334534</t>
   </si>
   <si>
     <t xml:space="preserve">3.22375464439392</t>
@@ -626,16 +626,16 @@
     <t xml:space="preserve">3.56786346435547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54975271224976</t>
+    <t xml:space="preserve">3.54975295066833</t>
   </si>
   <si>
     <t xml:space="preserve">3.55880808830261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51353096961975</t>
+    <t xml:space="preserve">3.51353049278259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45014238357544</t>
+    <t xml:space="preserve">3.45014214515686</t>
   </si>
   <si>
     <t xml:space="preserve">3.42297554016113</t>
@@ -647,16 +647,16 @@
     <t xml:space="preserve">3.41392040252686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34147620201111</t>
+    <t xml:space="preserve">3.34147644042969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25092124938965</t>
+    <t xml:space="preserve">3.25092148780823</t>
   </si>
   <si>
     <t xml:space="preserve">3.32336521148682</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33267450332642</t>
+    <t xml:space="preserve">3.33267426490784</t>
   </si>
   <si>
     <t xml:space="preserve">3.35129261016846</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">3.41645669937134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49093008041382</t>
+    <t xml:space="preserve">3.49092984199524</t>
   </si>
   <si>
     <t xml:space="preserve">3.36991095542908</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">3.5374755859375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63056707382202</t>
+    <t xml:space="preserve">3.63056755065918</t>
   </si>
   <si>
     <t xml:space="preserve">3.59333038330078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74227666854858</t>
+    <t xml:space="preserve">3.74227690696716</t>
   </si>
   <si>
     <t xml:space="preserve">3.84467744827271</t>
@@ -689,34 +689,31 @@
     <t xml:space="preserve">3.8539867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79813170433044</t>
+    <t xml:space="preserve">3.79813194274902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7795135974884</t>
+    <t xml:space="preserve">3.77951312065125</t>
   </si>
   <si>
     <t xml:space="preserve">3.75158619880676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6771125793457</t>
+    <t xml:space="preserve">3.67711305618286</t>
   </si>
   <si>
     <t xml:space="preserve">3.66780376434326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65849471092224</t>
+    <t xml:space="preserve">3.65849494934082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3792200088501</t>
+    <t xml:space="preserve">3.37922024726868</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3233654499054</t>
+    <t xml:space="preserve">3.44438409805298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44438433647156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21165561676025</t>
+    <t xml:space="preserve">3.2116551399231</t>
   </si>
   <si>
     <t xml:space="preserve">3.11856412887573</t>
@@ -725,55 +722,55 @@
     <t xml:space="preserve">3.18372821807861</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34198355674744</t>
+    <t xml:space="preserve">3.34198331832886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43507504463196</t>
+    <t xml:space="preserve">3.43507480621338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46300268173218</t>
+    <t xml:space="preserve">3.46300220489502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6026394367218</t>
+    <t xml:space="preserve">3.60263991355896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47231149673462</t>
+    <t xml:space="preserve">3.47231197357178</t>
   </si>
   <si>
     <t xml:space="preserve">3.621258020401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52816677093506</t>
+    <t xml:space="preserve">3.5281662940979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48162078857422</t>
+    <t xml:space="preserve">3.48162126541138</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42576622962952</t>
+    <t xml:space="preserve">3.42576599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64918565750122</t>
+    <t xml:space="preserve">3.64918541908264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72365880012512</t>
+    <t xml:space="preserve">3.72365856170654</t>
   </si>
   <si>
     <t xml:space="preserve">3.51885724067688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7702043056488</t>
+    <t xml:space="preserve">3.77020454406738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58402156829834</t>
+    <t xml:space="preserve">3.58402132987976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70504021644592</t>
+    <t xml:space="preserve">3.7050404548645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68642234802246</t>
+    <t xml:space="preserve">3.68642210960388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80744099617004</t>
+    <t xml:space="preserve">3.80744123458862</t>
   </si>
   <si>
     <t xml:space="preserve">3.29543781280518</t>
@@ -782,64 +779,64 @@
     <t xml:space="preserve">3.56540298461914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00293254852295</t>
+    <t xml:space="preserve">4.00293350219727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92845988273621</t>
+    <t xml:space="preserve">3.92845892906189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.788822889328</t>
+    <t xml:space="preserve">3.78882265090942</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98431539535522</t>
+    <t xml:space="preserve">3.98431468009949</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8632960319519</t>
+    <t xml:space="preserve">3.86329579353333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81675028800964</t>
+    <t xml:space="preserve">3.81675004959106</t>
   </si>
   <si>
     <t xml:space="preserve">4.08671522140503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16118860244751</t>
+    <t xml:space="preserve">4.16118812561035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22635316848755</t>
+    <t xml:space="preserve">4.22635269165039</t>
   </si>
   <si>
     <t xml:space="preserve">4.38460826873779</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4870080947876</t>
+    <t xml:space="preserve">4.48700857162476</t>
   </si>
   <si>
     <t xml:space="preserve">4.35668087005615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50562763214111</t>
+    <t xml:space="preserve">4.50562715530396</t>
   </si>
   <si>
     <t xml:space="preserve">4.6359543800354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49631786346436</t>
+    <t xml:space="preserve">4.4963173866272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46839046478271</t>
+    <t xml:space="preserve">4.46839094161987</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28220748901367</t>
+    <t xml:space="preserve">4.28220701217651</t>
   </si>
   <si>
     <t xml:space="preserve">4.20773410797119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43115425109863</t>
+    <t xml:space="preserve">4.43115377426147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56148147583008</t>
+    <t xml:space="preserve">4.56148195266724</t>
   </si>
   <si>
     <t xml:space="preserve">4.57079076766968</t>
@@ -848,34 +845,34 @@
     <t xml:space="preserve">4.45908117294312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.524245262146</t>
+    <t xml:space="preserve">4.52424573898315</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58940935134888</t>
+    <t xml:space="preserve">4.58940887451172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59871864318848</t>
+    <t xml:space="preserve">4.59871816635132</t>
   </si>
   <si>
     <t xml:space="preserve">4.44046306610107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37529897689819</t>
+    <t xml:space="preserve">4.37529850006104</t>
   </si>
   <si>
     <t xml:space="preserve">4.41253519058228</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29151678085327</t>
+    <t xml:space="preserve">4.29151630401611</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3287525177002</t>
+    <t xml:space="preserve">4.32875347137451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23566246032715</t>
+    <t xml:space="preserve">4.23566150665283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33806180953979</t>
+    <t xml:space="preserve">4.33806228637695</t>
   </si>
   <si>
     <t xml:space="preserve">4.15187931060791</t>
@@ -887,13 +884,13 @@
     <t xml:space="preserve">4.18911552429199</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34737205505371</t>
+    <t xml:space="preserve">4.34737110137939</t>
   </si>
   <si>
     <t xml:space="preserve">4.19842529296875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31944370269775</t>
+    <t xml:space="preserve">4.31944465637207</t>
   </si>
   <si>
     <t xml:space="preserve">4.27289867401123</t>
@@ -905,19 +902,19 @@
     <t xml:space="preserve">4.39391660690308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42184448242188</t>
+    <t xml:space="preserve">4.42184495925903</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87799310684204</t>
+    <t xml:space="preserve">4.87799263000488</t>
   </si>
   <si>
     <t xml:space="preserve">4.71042823791504</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60802698135376</t>
+    <t xml:space="preserve">4.60802745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61733627319336</t>
+    <t xml:space="preserve">4.61733675003052</t>
   </si>
   <si>
     <t xml:space="preserve">4.26358890533447</t>
@@ -926,28 +923,28 @@
     <t xml:space="preserve">4.11464309692383</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10533380508423</t>
+    <t xml:space="preserve">4.10533332824707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17980623245239</t>
+    <t xml:space="preserve">4.17980670928955</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07740592956543</t>
+    <t xml:space="preserve">4.07740640640259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95638680458069</t>
+    <t xml:space="preserve">3.95638751983643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90984177589417</t>
+    <t xml:space="preserve">3.90984153747559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04016971588135</t>
+    <t xml:space="preserve">4.04016923904419</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25427913665771</t>
+    <t xml:space="preserve">4.25428104400635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65457344055176</t>
+    <t xml:space="preserve">4.6545729637146</t>
   </si>
   <si>
     <t xml:space="preserve">4.70111846923828</t>
@@ -956,22 +953,22 @@
     <t xml:space="preserve">4.54286336898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30082607269287</t>
+    <t xml:space="preserve">4.30082559585571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44977188110352</t>
+    <t xml:space="preserve">4.44977235794067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58010005950928</t>
+    <t xml:space="preserve">4.58010053634644</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79421091079712</t>
+    <t xml:space="preserve">4.79421043395996</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88730239868164</t>
+    <t xml:space="preserve">4.88730192184448</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61688470840454</t>
+    <t xml:space="preserve">4.61688423156738</t>
   </si>
   <si>
     <t xml:space="preserve">4.59804010391235</t>
@@ -980,10 +977,10 @@
     <t xml:space="preserve">4.52266263961792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57919549942017</t>
+    <t xml:space="preserve">4.57919597625732</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56035184860229</t>
+    <t xml:space="preserve">4.56035137176514</t>
   </si>
   <si>
     <t xml:space="preserve">4.44728422164917</t>
@@ -995,10 +992,10 @@
     <t xml:space="preserve">4.69226169586182</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80532932281494</t>
+    <t xml:space="preserve">4.80532884597778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89955043792725</t>
+    <t xml:space="preserve">4.8995509147644</t>
   </si>
   <si>
     <t xml:space="preserve">4.85243988037109</t>
@@ -1013,10 +1010,10 @@
     <t xml:space="preserve">5.04088401794434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22932815551758</t>
+    <t xml:space="preserve">5.22932863235474</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60621643066406</t>
+    <t xml:space="preserve">5.60621690750122</t>
   </si>
   <si>
     <t xml:space="preserve">5.5119948387146</t>
@@ -1025,25 +1022,25 @@
     <t xml:space="preserve">5.700439453125</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65332841873169</t>
+    <t xml:space="preserve">5.65332794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32355070114136</t>
+    <t xml:space="preserve">5.32355117797852</t>
   </si>
   <si>
     <t xml:space="preserve">5.37066125869751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18221759796143</t>
+    <t xml:space="preserve">5.18221712112427</t>
   </si>
   <si>
     <t xml:space="preserve">5.13510608673096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08799505233765</t>
+    <t xml:space="preserve">5.0879955291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75821781158447</t>
+    <t xml:space="preserve">4.75821733474731</t>
   </si>
   <si>
     <t xml:space="preserve">4.71110677719116</t>
@@ -1052,13 +1049,13 @@
     <t xml:space="preserve">4.7671914100647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69091606140137</t>
+    <t xml:space="preserve">4.69091653823853</t>
   </si>
   <si>
     <t xml:space="preserve">4.70998477935791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8148627281189</t>
+    <t xml:space="preserve">4.81486320495605</t>
   </si>
   <si>
     <t xml:space="preserve">4.74812173843384</t>
@@ -1067,37 +1064,37 @@
     <t xml:space="preserve">4.67184734344482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53836679458618</t>
+    <t xml:space="preserve">4.53836631774902</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65277862548828</t>
+    <t xml:space="preserve">4.65277910232544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57650375366211</t>
+    <t xml:space="preserve">4.57650327682495</t>
   </si>
   <si>
     <t xml:space="preserve">4.72905397415161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86253547668457</t>
+    <t xml:space="preserve">4.86253499984741</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91020727157593</t>
+    <t xml:space="preserve">4.91020679473877</t>
   </si>
   <si>
     <t xml:space="preserve">4.95787858963013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63370990753174</t>
+    <t xml:space="preserve">4.6337103843689</t>
   </si>
   <si>
     <t xml:space="preserve">4.61464166641235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59557199478149</t>
+    <t xml:space="preserve">4.59557247161865</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55743455886841</t>
+    <t xml:space="preserve">4.55743503570557</t>
   </si>
   <si>
     <t xml:space="preserve">4.74882888793945</t>
@@ -1112,22 +1109,22 @@
     <t xml:space="preserve">5.01908683776855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16386890411377</t>
+    <t xml:space="preserve">5.16386842727661</t>
   </si>
   <si>
     <t xml:space="preserve">5.45343112945557</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35691022872925</t>
+    <t xml:space="preserve">5.35691070556641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30864953994751</t>
+    <t xml:space="preserve">5.30865001678467</t>
   </si>
   <si>
     <t xml:space="preserve">5.40517044067383</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26038980484009</t>
+    <t xml:space="preserve">5.26038932800293</t>
   </si>
   <si>
     <t xml:space="preserve">5.50169134140015</t>
@@ -1154,13 +1151,13 @@
     <t xml:space="preserve">4.92256641387939</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11560869216919</t>
+    <t xml:space="preserve">5.11560821533203</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87430620193481</t>
+    <t xml:space="preserve">4.87430572509766</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82604551315308</t>
+    <t xml:space="preserve">4.82604503631592</t>
   </si>
   <si>
     <t xml:space="preserve">4.97082662582397</t>
@@ -23753,7 +23750,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G847" t="s">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -23779,7 +23776,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G848" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -23805,7 +23802,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G849" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -23857,7 +23854,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G851" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -23883,7 +23880,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G852" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -23909,7 +23906,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G853" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -23935,7 +23932,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G854" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -23961,7 +23958,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G855" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -23987,7 +23984,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G856" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24013,7 +24010,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G857" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -24039,7 +24036,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G858" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -24065,7 +24062,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G859" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -24091,7 +24088,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G860" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -24117,7 +24114,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G861" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -24169,7 +24166,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G863" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -24221,7 +24218,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G865" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -24247,7 +24244,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G866" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -24299,7 +24296,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G868" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -24325,7 +24322,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G869" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -24351,7 +24348,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G870" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -24377,7 +24374,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G871" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -24403,7 +24400,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G872" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -24429,7 +24426,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G873" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -24481,7 +24478,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G875" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -24585,7 +24582,7 @@
         <v>4</v>
       </c>
       <c r="G879" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -24611,7 +24608,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G880" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -24689,7 +24686,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G883" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -24793,7 +24790,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G887" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -24819,7 +24816,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G888" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -24923,7 +24920,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G892" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -24975,7 +24972,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G894" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -25001,7 +24998,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G895" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -25027,7 +25024,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G896" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -25053,7 +25050,7 @@
         <v>4</v>
       </c>
       <c r="G897" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -25131,7 +25128,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G900" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -25157,7 +25154,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G901" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -25183,7 +25180,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G902" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -25235,7 +25232,7 @@
         <v>4</v>
       </c>
       <c r="G904" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -25261,7 +25258,7 @@
         <v>4</v>
       </c>
       <c r="G905" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -25313,7 +25310,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G907" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -25339,7 +25336,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G908" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -25365,7 +25362,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G909" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -25391,7 +25388,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G910" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -25417,7 +25414,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G911" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -25469,7 +25466,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G913" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -25495,7 +25492,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G914" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -25625,7 +25622,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G919" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -25703,7 +25700,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G922" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -25729,7 +25726,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G923" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -25755,7 +25752,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G924" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -25781,7 +25778,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G925" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -25807,7 +25804,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G926" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -25833,7 +25830,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G927" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -25859,7 +25856,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G928" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -25885,7 +25882,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G929" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -25911,7 +25908,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G930" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -25937,7 +25934,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G931" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -25963,7 +25960,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G932" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -25989,7 +25986,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G933" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26015,7 +26012,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G934" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26041,7 +26038,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G935" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26067,7 +26064,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G936" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26093,7 +26090,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G937" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -26145,7 +26142,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G939" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26171,7 +26168,7 @@
         <v>4</v>
       </c>
       <c r="G940" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -26197,7 +26194,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G941" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -26223,7 +26220,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G942" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -26249,7 +26246,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G943" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -26275,7 +26272,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G944" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -26301,7 +26298,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G945" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -26327,7 +26324,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G946" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -26353,7 +26350,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G947" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -26431,7 +26428,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G950" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26483,7 +26480,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G952" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26509,7 +26506,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G953" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26535,7 +26532,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G954" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26561,7 +26558,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G955" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26587,7 +26584,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G956" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26613,7 +26610,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G957" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26639,7 +26636,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G958" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -26665,7 +26662,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G959" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -26691,7 +26688,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G960" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -26717,7 +26714,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G961" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -26743,7 +26740,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G962" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -26769,7 +26766,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G963" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -26795,7 +26792,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G964" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -26821,7 +26818,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G965" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -26847,7 +26844,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G966" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -26873,7 +26870,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G967" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -26899,7 +26896,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G968" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -26925,7 +26922,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G969" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -26951,7 +26948,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G970" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -26977,7 +26974,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G971" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27003,7 +27000,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G972" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27029,7 +27026,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G973" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27055,7 +27052,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G974" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27081,7 +27078,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G975" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -27107,7 +27104,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G976" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27133,7 +27130,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G977" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27159,7 +27156,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G978" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -27185,7 +27182,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G979" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27211,7 +27208,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G980" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27237,7 +27234,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G981" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27263,7 +27260,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G982" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -27289,7 +27286,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G983" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -27315,7 +27312,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G984" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27341,7 +27338,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G985" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -27367,7 +27364,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G986" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -27393,7 +27390,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G987" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -27419,7 +27416,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G988" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -27445,7 +27442,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G989" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -27471,7 +27468,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G990" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -27497,7 +27494,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G991" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -27523,7 +27520,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G992" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -27549,7 +27546,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G993" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -27575,7 +27572,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G994" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -27601,7 +27598,7 @@
         <v>4.5</v>
       </c>
       <c r="G995" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -27627,7 +27624,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G996" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -27653,7 +27650,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G997" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -27679,7 +27676,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G998" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -27705,7 +27702,7 @@
         <v>4.5</v>
       </c>
       <c r="G999" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -27731,7 +27728,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1000" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -27757,7 +27754,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1001" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -27783,7 +27780,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1002" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -27809,7 +27806,7 @@
         <v>4.5</v>
       </c>
       <c r="G1003" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -27835,7 +27832,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1004" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -27861,7 +27858,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1005" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -27887,7 +27884,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1006" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -27913,7 +27910,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1007" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -27939,7 +27936,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1008" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -27965,7 +27962,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1009" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -27991,7 +27988,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1010" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -28017,7 +28014,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1011" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28043,7 +28040,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1012" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28069,7 +28066,7 @@
         <v>4.75</v>
       </c>
       <c r="G1013" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28095,7 +28092,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1014" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28121,7 +28118,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1015" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28147,7 +28144,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1016" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28173,7 +28170,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1017" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -28199,7 +28196,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1018" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -28225,7 +28222,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1019" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -28251,7 +28248,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1020" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28277,7 +28274,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1021" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28303,7 +28300,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1022" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -28329,7 +28326,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1023" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -28355,7 +28352,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1024" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28381,7 +28378,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1025" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28407,7 +28404,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1026" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28433,7 +28430,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1027" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28459,7 +28456,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1028" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28485,7 +28482,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1029" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28511,7 +28508,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1030" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28537,7 +28534,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1031" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28563,7 +28560,7 @@
         <v>4.5</v>
       </c>
       <c r="G1032" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28589,7 +28586,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1033" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28615,7 +28612,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1034" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28641,7 +28638,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1035" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -28667,7 +28664,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1036" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -28693,7 +28690,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1037" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -28719,7 +28716,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1038" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -28745,7 +28742,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1039" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -28771,7 +28768,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1040" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -28797,7 +28794,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1041" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -28823,7 +28820,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1042" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -28849,7 +28846,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1043" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -28875,7 +28872,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1044" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -28901,7 +28898,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1045" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -28927,7 +28924,7 @@
         <v>4.25</v>
       </c>
       <c r="G1046" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -28953,7 +28950,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1047" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -28979,7 +28976,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1048" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29005,7 +29002,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1049" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29031,7 +29028,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1050" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29057,7 +29054,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1051" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29083,7 +29080,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1052" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -29109,7 +29106,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1053" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29135,7 +29132,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1054" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29161,7 +29158,7 @@
         <v>5</v>
       </c>
       <c r="G1055" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29187,7 +29184,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1056" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29213,7 +29210,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29239,7 +29236,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1058" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29265,7 +29262,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1059" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29291,7 +29288,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1060" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29317,7 +29314,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1061" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29343,7 +29340,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1062" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29369,7 +29366,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1063" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29395,7 +29392,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1064" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29421,7 +29418,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1065" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29447,7 +29444,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1066" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29473,7 +29470,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1067" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29499,7 +29496,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1068" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29525,7 +29522,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1069" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29551,7 +29548,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1070" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29577,7 +29574,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1071" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -29603,7 +29600,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1072" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -29629,7 +29626,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1073" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -29655,7 +29652,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1074" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -29681,7 +29678,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1075" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -29707,7 +29704,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1076" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -29733,7 +29730,7 @@
         <v>5.25</v>
       </c>
       <c r="G1077" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -29759,7 +29756,7 @@
         <v>5.25</v>
       </c>
       <c r="G1078" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -29785,7 +29782,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1079" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -29811,7 +29808,7 @@
         <v>5</v>
       </c>
       <c r="G1080" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -29837,7 +29834,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1081" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -29863,7 +29860,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1082" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -29889,7 +29886,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1083" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -29915,7 +29912,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1084" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -29941,7 +29938,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1085" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -29967,7 +29964,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1086" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -29993,7 +29990,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1087" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30019,7 +30016,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1088" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30045,7 +30042,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1089" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -30071,7 +30068,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1090" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30097,7 +30094,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1091" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30123,7 +30120,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1092" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30149,7 +30146,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1093" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30175,7 +30172,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1094" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -30201,7 +30198,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1095" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -30227,7 +30224,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1096" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -30253,7 +30250,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1097" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -30279,7 +30276,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1098" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -30305,7 +30302,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1099" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -30331,7 +30328,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1100" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -30357,7 +30354,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1101" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -30383,7 +30380,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1102" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -30409,7 +30406,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1103" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -30435,7 +30432,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1104" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -30461,7 +30458,7 @@
         <v>5.25</v>
       </c>
       <c r="G1105" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -30487,7 +30484,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1106" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30513,7 +30510,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1107" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30539,7 +30536,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1108" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -30565,7 +30562,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1109" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -30591,7 +30588,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1110" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -30617,7 +30614,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1111" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -30643,7 +30640,7 @@
         <v>6</v>
       </c>
       <c r="G1112" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -30669,7 +30666,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1113" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -30695,7 +30692,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1114" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -30721,7 +30718,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -30747,7 +30744,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1116" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -30773,7 +30770,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1117" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -30799,7 +30796,7 @@
         <v>5.5</v>
       </c>
       <c r="G1118" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -30825,7 +30822,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1119" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -30851,7 +30848,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1120" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -30877,7 +30874,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1121" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -30903,7 +30900,7 @@
         <v>5.5</v>
       </c>
       <c r="G1122" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -30929,7 +30926,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1123" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -30955,7 +30952,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1124" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -30981,7 +30978,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1125" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31007,7 +31004,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1126" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31033,7 +31030,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1127" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31059,7 +31056,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1128" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31085,7 +31082,7 @@
         <v>5.5</v>
       </c>
       <c r="G1129" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31111,7 +31108,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1130" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31137,7 +31134,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1131" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31163,7 +31160,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1132" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31189,7 +31186,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1133" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31215,7 +31212,7 @@
         <v>5.5</v>
       </c>
       <c r="G1134" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31241,7 +31238,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1135" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31267,7 +31264,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1136" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31293,7 +31290,7 @@
         <v>5.5</v>
       </c>
       <c r="G1137" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31319,7 +31316,7 @@
         <v>5.5</v>
       </c>
       <c r="G1138" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31345,7 +31342,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1139" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31371,7 +31368,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1140" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31397,7 +31394,7 @@
         <v>5.25</v>
       </c>
       <c r="G1141" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31423,7 +31420,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1142" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31449,7 +31446,7 @@
         <v>5.25</v>
       </c>
       <c r="G1143" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31475,7 +31472,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1144" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31501,7 +31498,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1145" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31527,7 +31524,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1146" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31553,7 +31550,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1147" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31579,7 +31576,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1148" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31605,7 +31602,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1149" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -31631,7 +31628,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1150" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -31657,7 +31654,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1151" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -31683,7 +31680,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1152" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -31709,7 +31706,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1153" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -31735,7 +31732,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1154" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -31761,7 +31758,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1155" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -31787,7 +31784,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1156" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -31813,7 +31810,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1157" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -31839,7 +31836,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1158" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -31865,7 +31862,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1159" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -31891,7 +31888,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1160" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -31917,7 +31914,7 @@
         <v>5.25</v>
       </c>
       <c r="G1161" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -31943,7 +31940,7 @@
         <v>5.25</v>
       </c>
       <c r="G1162" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -31969,7 +31966,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1163" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -31995,7 +31992,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1164" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32021,7 +32018,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1165" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32047,7 +32044,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1166" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -32073,7 +32070,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1167" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -32099,7 +32096,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1168" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -32125,7 +32122,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1169" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -32151,7 +32148,7 @@
         <v>5</v>
       </c>
       <c r="G1170" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -32177,7 +32174,7 @@
         <v>5</v>
       </c>
       <c r="G1171" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -32203,7 +32200,7 @@
         <v>5</v>
       </c>
       <c r="G1172" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -32229,7 +32226,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1173" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -32255,7 +32252,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1174" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -32281,7 +32278,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1175" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -32307,7 +32304,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1176" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -32333,7 +32330,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1177" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -32359,7 +32356,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1178" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -32385,7 +32382,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1179" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -32411,7 +32408,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1180" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -32437,7 +32434,7 @@
         <v>5.25</v>
       </c>
       <c r="G1181" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -32463,7 +32460,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1182" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -32489,7 +32486,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1183" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -32515,7 +32512,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1184" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -32541,7 +32538,7 @@
         <v>5.25</v>
       </c>
       <c r="G1185" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -32567,7 +32564,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1186" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -32593,7 +32590,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1187" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -32619,7 +32616,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1188" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -32645,7 +32642,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1189" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -32671,7 +32668,7 @@
         <v>5</v>
       </c>
       <c r="G1190" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -32697,7 +32694,7 @@
         <v>5</v>
       </c>
       <c r="G1191" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -32723,7 +32720,7 @@
         <v>5</v>
       </c>
       <c r="G1192" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -32749,7 +32746,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1193" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -32775,7 +32772,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1194" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -32801,7 +32798,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1195" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -32827,7 +32824,7 @@
         <v>5</v>
       </c>
       <c r="G1196" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -32853,7 +32850,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1197" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -32879,7 +32876,7 @@
         <v>5</v>
       </c>
       <c r="G1198" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -32905,7 +32902,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1199" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -32931,7 +32928,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1200" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -32957,7 +32954,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1201" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -32983,7 +32980,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1202" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33009,7 +33006,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1203" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33035,7 +33032,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1204" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -33061,7 +33058,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1205" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -33087,7 +33084,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1206" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -33113,7 +33110,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1207" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -33139,7 +33136,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1208" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -33165,7 +33162,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1209" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -33191,7 +33188,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1210" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -33217,7 +33214,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1211" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -33243,7 +33240,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1212" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -33269,7 +33266,7 @@
         <v>5</v>
       </c>
       <c r="G1213" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -33295,7 +33292,7 @@
         <v>5</v>
       </c>
       <c r="G1214" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -33321,7 +33318,7 @@
         <v>5</v>
       </c>
       <c r="G1215" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -33347,7 +33344,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1216" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -33373,7 +33370,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1217" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -33399,7 +33396,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1218" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -33425,7 +33422,7 @@
         <v>5</v>
       </c>
       <c r="G1219" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -33451,7 +33448,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1220" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -33477,7 +33474,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1221" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -33503,7 +33500,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1222" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -33529,7 +33526,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1223" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -33555,7 +33552,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1224" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -33581,7 +33578,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1225" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -33607,7 +33604,7 @@
         <v>5</v>
       </c>
       <c r="G1226" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -33633,7 +33630,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1227" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -33659,7 +33656,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1228" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -33685,7 +33682,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1229" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -33711,7 +33708,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1230" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -33737,7 +33734,7 @@
         <v>5</v>
       </c>
       <c r="G1231" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -33763,7 +33760,7 @@
         <v>5</v>
       </c>
       <c r="G1232" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -33789,7 +33786,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1233" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -33815,7 +33812,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1234" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -33841,7 +33838,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1235" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -33867,7 +33864,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1236" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -33893,7 +33890,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1237" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -33919,7 +33916,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1238" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -33945,7 +33942,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1239" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -33971,7 +33968,7 @@
         <v>5</v>
       </c>
       <c r="G1240" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -33997,7 +33994,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1241" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34023,7 +34020,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1242" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -34049,7 +34046,7 @@
         <v>5</v>
       </c>
       <c r="G1243" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -34075,7 +34072,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1244" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -34101,7 +34098,7 @@
         <v>5</v>
       </c>
       <c r="G1245" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34127,7 +34124,7 @@
         <v>5</v>
       </c>
       <c r="G1246" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34153,7 +34150,7 @@
         <v>5</v>
       </c>
       <c r="G1247" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -34179,7 +34176,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1248" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -34205,7 +34202,7 @@
         <v>5</v>
       </c>
       <c r="G1249" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -34231,7 +34228,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1250" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -34257,7 +34254,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1251" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -34283,7 +34280,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1252" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -34309,7 +34306,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1253" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -34335,7 +34332,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1254" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -34361,7 +34358,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1255" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -34387,7 +34384,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1256" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -34413,7 +34410,7 @@
         <v>5</v>
       </c>
       <c r="G1257" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -34439,7 +34436,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1258" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -34465,7 +34462,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1259" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -34491,7 +34488,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1260" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -34517,7 +34514,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1261" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -34543,7 +34540,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1262" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -34569,7 +34566,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1263" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -34595,7 +34592,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1264" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -34621,7 +34618,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1265" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -34647,7 +34644,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1266" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -34673,7 +34670,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1267" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -34699,7 +34696,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1268" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -34725,7 +34722,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1269" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -34751,7 +34748,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1270" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -34777,7 +34774,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1271" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -34803,7 +34800,7 @@
         <v>5</v>
       </c>
       <c r="G1272" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -34829,7 +34826,7 @@
         <v>5</v>
       </c>
       <c r="G1273" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -34855,7 +34852,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1274" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -34881,7 +34878,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1275" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -34907,7 +34904,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1276" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -34933,7 +34930,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1277" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -34959,7 +34956,7 @@
         <v>5</v>
       </c>
       <c r="G1278" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -34985,7 +34982,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1279" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35011,7 +35008,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1280" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -35037,7 +35034,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1281" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -35063,7 +35060,7 @@
         <v>5</v>
       </c>
       <c r="G1282" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -35089,7 +35086,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1283" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -35115,7 +35112,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1284" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -35141,7 +35138,7 @@
         <v>5</v>
       </c>
       <c r="G1285" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -35167,7 +35164,7 @@
         <v>5</v>
       </c>
       <c r="G1286" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -35193,7 +35190,7 @@
         <v>5</v>
       </c>
       <c r="G1287" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -35219,7 +35216,7 @@
         <v>5</v>
       </c>
       <c r="G1288" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -35245,7 +35242,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1289" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -35271,7 +35268,7 @@
         <v>5</v>
       </c>
       <c r="G1290" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35297,7 +35294,7 @@
         <v>5</v>
       </c>
       <c r="G1291" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35323,7 +35320,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1292" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35349,7 +35346,7 @@
         <v>5</v>
       </c>
       <c r="G1293" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35375,7 +35372,7 @@
         <v>5</v>
       </c>
       <c r="G1294" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35401,7 +35398,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1295" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35427,7 +35424,7 @@
         <v>5</v>
       </c>
       <c r="G1296" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35453,7 +35450,7 @@
         <v>5</v>
       </c>
       <c r="G1297" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -35479,7 +35476,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1298" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35505,7 +35502,7 @@
         <v>5</v>
       </c>
       <c r="G1299" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35531,7 +35528,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1300" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35557,7 +35554,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1301" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -35583,7 +35580,7 @@
         <v>5</v>
       </c>
       <c r="G1302" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35609,7 +35606,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1303" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35635,7 +35632,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1304" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -35661,7 +35658,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1305" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -35687,7 +35684,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1306" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -35713,7 +35710,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1307" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -35739,7 +35736,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1308" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -35765,7 +35762,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1309" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -35791,7 +35788,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1310" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -35817,7 +35814,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1311" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -35843,7 +35840,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1312" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -35869,7 +35866,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1313" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -35895,7 +35892,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1314" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -35921,7 +35918,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1315" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -35947,7 +35944,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1316" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -35973,7 +35970,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1317" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -35999,7 +35996,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1318" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36025,7 +36022,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1319" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -36051,7 +36048,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1320" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36077,7 +36074,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1321" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -36103,7 +36100,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1322" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -36129,7 +36126,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1323" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -36155,7 +36152,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1324" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -36181,7 +36178,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1325" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -36207,7 +36204,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1326" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -36233,7 +36230,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1327" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -36259,7 +36256,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1328" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -36285,7 +36282,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1329" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -36311,7 +36308,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1330" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -36337,7 +36334,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1331" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -36363,7 +36360,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1332" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -36389,7 +36386,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1333" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -36415,7 +36412,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1334" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -36441,7 +36438,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1335" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -36467,7 +36464,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1336" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -36493,7 +36490,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1337" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -36519,7 +36516,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1338" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -36545,7 +36542,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1339" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -36571,7 +36568,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1340" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -36597,7 +36594,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1341" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -36623,7 +36620,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1342" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -36649,7 +36646,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1343" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -36675,7 +36672,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1344" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -36701,7 +36698,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1345" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -36727,7 +36724,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1346" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -36753,7 +36750,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1347" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -36779,7 +36776,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1348" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -36805,7 +36802,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1349" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -36831,7 +36828,7 @@
         <v>5.5</v>
       </c>
       <c r="G1350" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -36857,7 +36854,7 @@
         <v>5.5</v>
       </c>
       <c r="G1351" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -36883,7 +36880,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1352" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -36909,7 +36906,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1353" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -36935,7 +36932,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1354" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -36961,7 +36958,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1355" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -36987,7 +36984,7 @@
         <v>5.5</v>
       </c>
       <c r="G1356" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37013,7 +37010,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1357" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37039,7 +37036,7 @@
         <v>5.5</v>
       </c>
       <c r="G1358" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -37065,7 +37062,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1359" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37091,7 +37088,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1360" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37117,7 +37114,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1361" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -37143,7 +37140,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1362" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37169,7 +37166,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1363" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -37195,7 +37192,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1364" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -37221,7 +37218,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1365" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -37247,7 +37244,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1366" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -37273,7 +37270,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1367" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -37299,7 +37296,7 @@
         <v>5.75</v>
       </c>
       <c r="G1368" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -37325,7 +37322,7 @@
         <v>5.75</v>
       </c>
       <c r="G1369" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -37351,7 +37348,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1370" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -37377,7 +37374,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1371" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -37403,7 +37400,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1372" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -37429,7 +37426,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1373" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -37455,7 +37452,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1374" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -37481,7 +37478,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1375" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -37507,7 +37504,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1376" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -37533,7 +37530,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1377" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -37559,7 +37556,7 @@
         <v>5.5</v>
       </c>
       <c r="G1378" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -37585,7 +37582,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1379" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -37611,7 +37608,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1380" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -37637,7 +37634,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1381" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -37663,7 +37660,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1382" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -37689,7 +37686,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1383" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -37715,7 +37712,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1384" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -37741,7 +37738,7 @@
         <v>5.5</v>
       </c>
       <c r="G1385" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -37767,7 +37764,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1386" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -37793,7 +37790,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1387" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -37819,7 +37816,7 @@
         <v>5.25</v>
       </c>
       <c r="G1388" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -37845,7 +37842,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1389" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -37871,7 +37868,7 @@
         <v>5.25</v>
       </c>
       <c r="G1390" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -37897,7 +37894,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1391" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -37923,7 +37920,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1392" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -37949,7 +37946,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1393" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -37975,7 +37972,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1394" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38001,7 +37998,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1395" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38027,7 +38024,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1396" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38053,7 +38050,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1397" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38079,7 +38076,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1398" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -38105,7 +38102,7 @@
         <v>5</v>
       </c>
       <c r="G1399" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -38131,7 +38128,7 @@
         <v>5</v>
       </c>
       <c r="G1400" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -38157,7 +38154,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1401" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -38183,7 +38180,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1402" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -38209,7 +38206,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1403" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -38235,7 +38232,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1404" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -38261,7 +38258,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1405" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -38287,7 +38284,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1406" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -38313,7 +38310,7 @@
         <v>5.25</v>
       </c>
       <c r="G1407" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -38339,7 +38336,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1408" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -38365,7 +38362,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1409" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -38391,7 +38388,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1410" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -38417,7 +38414,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1411" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38443,7 +38440,7 @@
         <v>5.25</v>
       </c>
       <c r="G1412" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -38469,7 +38466,7 @@
         <v>5.25</v>
       </c>
       <c r="G1413" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -38495,7 +38492,7 @@
         <v>5.25</v>
       </c>
       <c r="G1414" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -38521,7 +38518,7 @@
         <v>5.25</v>
       </c>
       <c r="G1415" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -38547,7 +38544,7 @@
         <v>5.25</v>
       </c>
       <c r="G1416" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -38573,7 +38570,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1417" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -38599,7 +38596,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1418" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -38625,7 +38622,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1419" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -38651,7 +38648,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1420" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -38677,7 +38674,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1421" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -38703,7 +38700,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1422" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -38729,7 +38726,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1423" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -38755,7 +38752,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1424" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -38781,7 +38778,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1425" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -38807,7 +38804,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1426" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -38833,7 +38830,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1427" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -38859,7 +38856,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1428" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -38885,7 +38882,7 @@
         <v>5.25</v>
       </c>
       <c r="G1429" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -38911,7 +38908,7 @@
         <v>5.25</v>
       </c>
       <c r="G1430" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -38937,7 +38934,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1431" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -38963,7 +38960,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1432" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -38989,7 +38986,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1433" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39015,7 +39012,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1434" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39041,7 +39038,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1435" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -39067,7 +39064,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1436" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -39093,7 +39090,7 @@
         <v>5</v>
       </c>
       <c r="G1437" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39119,7 +39116,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1438" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39145,7 +39142,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1439" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39171,7 +39168,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1440" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -39197,7 +39194,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1441" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -39223,7 +39220,7 @@
         <v>5</v>
       </c>
       <c r="G1442" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39249,7 +39246,7 @@
         <v>5</v>
       </c>
       <c r="G1443" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -39275,7 +39272,7 @@
         <v>5</v>
       </c>
       <c r="G1444" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -39301,7 +39298,7 @@
         <v>5</v>
       </c>
       <c r="G1445" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -39327,7 +39324,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1446" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -39353,7 +39350,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1447" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -39379,7 +39376,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1448" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -39405,7 +39402,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1449" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39431,7 +39428,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1450" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39457,7 +39454,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1451" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39483,7 +39480,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1452" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39509,7 +39506,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1453" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39535,7 +39532,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1454" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39561,7 +39558,7 @@
         <v>5</v>
       </c>
       <c r="G1455" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39587,7 +39584,7 @@
         <v>5</v>
       </c>
       <c r="G1456" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39613,7 +39610,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1457" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39639,7 +39636,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1458" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39665,7 +39662,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1459" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39691,7 +39688,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1460" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -39717,7 +39714,7 @@
         <v>5</v>
       </c>
       <c r="G1461" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -39743,7 +39740,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1462" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -39769,7 +39766,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1463" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -39795,7 +39792,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1464" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -39821,7 +39818,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1465" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -39847,7 +39844,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1466" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -39873,7 +39870,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1467" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -39899,7 +39896,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1468" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -39925,7 +39922,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1469" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -39951,7 +39948,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1470" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -39977,7 +39974,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1471" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40003,7 +40000,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1472" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40029,7 +40026,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1473" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40055,7 +40052,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1474" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40081,7 +40078,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1475" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -40107,7 +40104,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1476" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -40133,7 +40130,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1477" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -40159,7 +40156,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1478" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -40185,7 +40182,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1479" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -40211,7 +40208,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1480" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -40237,7 +40234,7 @@
         <v>4.5</v>
       </c>
       <c r="G1481" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -40263,7 +40260,7 @@
         <v>4.5</v>
       </c>
       <c r="G1482" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -40289,7 +40286,7 @@
         <v>4.5</v>
       </c>
       <c r="G1483" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -40315,7 +40312,7 @@
         <v>4.5</v>
       </c>
       <c r="G1484" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -40341,7 +40338,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1485" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -40367,7 +40364,7 @@
         <v>4.5</v>
       </c>
       <c r="G1486" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -40393,7 +40390,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1487" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -40419,7 +40416,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1488" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40445,7 +40442,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1489" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40471,7 +40468,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1490" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40497,7 +40494,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1491" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40523,7 +40520,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1492" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -40549,7 +40546,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1493" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40575,7 +40572,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1494" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -40601,7 +40598,7 @@
         <v>4.5</v>
       </c>
       <c r="G1495" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -40627,7 +40624,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1496" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -40653,7 +40650,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1497" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -40679,7 +40676,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1498" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -40705,7 +40702,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1499" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -40731,7 +40728,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1500" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -40757,7 +40754,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1501" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -40783,7 +40780,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1502" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -40809,7 +40806,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1503" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -40835,7 +40832,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1504" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -40861,7 +40858,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1505" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -40887,7 +40884,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1506" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -40913,7 +40910,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1507" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -40939,7 +40936,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1508" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -40965,7 +40962,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1509" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -40991,7 +40988,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1510" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41017,7 +41014,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1511" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41043,7 +41040,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1512" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41069,7 +41066,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1513" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41095,7 +41092,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1514" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41121,7 +41118,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1515" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41147,7 +41144,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1516" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41173,7 +41170,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1517" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -41199,7 +41196,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1518" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -41225,7 +41222,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1519" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41251,7 +41248,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1520" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -41277,7 +41274,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1521" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -41303,7 +41300,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1522" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -41329,7 +41326,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1523" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -41355,7 +41352,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1524" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -41381,7 +41378,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1525" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -41407,7 +41404,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1526" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41433,7 +41430,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1527" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41459,7 +41456,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1528" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41485,7 +41482,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1529" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41511,7 +41508,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1530" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41537,7 +41534,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1531" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41563,7 +41560,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1532" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41589,7 +41586,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1533" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41615,7 +41612,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1534" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41641,7 +41638,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1535" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41667,7 +41664,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1536" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41693,7 +41690,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1537" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -41719,7 +41716,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1538" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -41745,7 +41742,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1539" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -41771,7 +41768,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1540" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -41797,7 +41794,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1541" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -41823,7 +41820,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1542" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -41849,7 +41846,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1543" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -41875,7 +41872,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1544" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -41901,7 +41898,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1545" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -41927,7 +41924,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1546" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -41953,7 +41950,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1547" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -41979,7 +41976,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1548" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42005,7 +42002,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1549" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42031,7 +42028,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1550" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42057,7 +42054,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1551" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42083,7 +42080,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1552" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42109,7 +42106,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1553" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42135,7 +42132,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1554" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42161,7 +42158,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1555" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42187,7 +42184,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1556" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42213,7 +42210,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1557" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -42239,7 +42236,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1558" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -42265,7 +42262,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1559" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -42291,7 +42288,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1560" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -42317,7 +42314,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1561" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -42343,7 +42340,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1562" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -42369,7 +42366,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1563" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -42395,7 +42392,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1564" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -42421,7 +42418,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1565" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42447,7 +42444,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1566" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42473,7 +42470,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1567" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42499,7 +42496,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1568" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42525,7 +42522,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1569" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42551,7 +42548,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1570" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42577,7 +42574,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1571" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42603,7 +42600,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1572" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42629,7 +42626,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1573" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42655,7 +42652,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1574" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42681,7 +42678,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1575" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -42707,7 +42704,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1576" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -42733,7 +42730,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1577" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -42759,7 +42756,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1578" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -42785,7 +42782,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1579" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -42811,7 +42808,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1580" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -42837,7 +42834,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1581" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -42863,7 +42860,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1582" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -42889,7 +42886,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1583" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -42915,7 +42912,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1584" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -42941,7 +42938,7 @@
         <v>4.5</v>
       </c>
       <c r="G1585" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -42967,7 +42964,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -42993,7 +42990,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1587" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43019,7 +43016,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1588" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43045,7 +43042,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1589" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43071,7 +43068,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1590" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43097,7 +43094,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1591" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43123,7 +43120,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1592" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43149,7 +43146,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1593" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43175,7 +43172,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1594" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43201,7 +43198,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1595" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -43227,7 +43224,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1596" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43253,7 +43250,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1597" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -43279,7 +43276,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1598" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -43305,7 +43302,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1599" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -43331,7 +43328,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1600" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -43357,7 +43354,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1601" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -43383,7 +43380,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1602" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -43409,7 +43406,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1603" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43435,7 +43432,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1604" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43461,7 +43458,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1605" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43487,7 +43484,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1606" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43513,7 +43510,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1607" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43539,7 +43536,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1608" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43565,7 +43562,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1609" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43591,7 +43588,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1610" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43617,7 +43614,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1611" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43643,7 +43640,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1612" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43669,7 +43666,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1613" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43695,7 +43692,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1614" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43721,7 +43718,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1615" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -43747,7 +43744,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1616" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43773,7 +43770,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1617" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43799,7 +43796,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1618" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43825,7 +43822,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1619" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43851,7 +43848,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1620" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -43877,7 +43874,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1621" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -43903,7 +43900,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1622" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -43929,7 +43926,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1623" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -43955,7 +43952,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1624" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -43981,7 +43978,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1625" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44007,7 +44004,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1626" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44033,7 +44030,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1627" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44059,7 +44056,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1628" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44085,7 +44082,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1629" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44111,7 +44108,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1630" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44137,7 +44134,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1631" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44163,7 +44160,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1632" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44189,7 +44186,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1633" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44215,7 +44212,7 @@
         <v>5.75</v>
       </c>
       <c r="G1634" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44241,7 +44238,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1635" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44267,7 +44264,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1636" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44293,7 +44290,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1637" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44319,7 +44316,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1638" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44345,7 +44342,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1639" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44371,7 +44368,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1640" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44397,7 +44394,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1641" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44423,7 +44420,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1642" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44449,7 +44446,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1643" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44475,7 +44472,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1644" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44501,7 +44498,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1645" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44527,7 +44524,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1646" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44553,7 +44550,7 @@
         <v>5.75</v>
       </c>
       <c r="G1647" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44579,7 +44576,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1648" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44605,7 +44602,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1649" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44631,7 +44628,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1650" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44657,7 +44654,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1651" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44683,7 +44680,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1652" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44709,7 +44706,7 @@
         <v>5.25</v>
       </c>
       <c r="G1653" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44735,7 +44732,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1654" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44761,7 +44758,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1655" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44787,7 +44784,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1656" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44813,7 +44810,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1657" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44839,7 +44836,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1658" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44865,7 +44862,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1659" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -44891,7 +44888,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1660" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44917,7 +44914,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1661" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44943,7 +44940,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1662" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44969,7 +44966,7 @@
         <v>5.5</v>
       </c>
       <c r="G1663" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44995,7 +44992,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1664" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45021,7 +45018,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1665" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45047,7 +45044,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1666" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45073,7 +45070,7 @@
         <v>5.5</v>
       </c>
       <c r="G1667" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45099,7 +45096,7 @@
         <v>5.5</v>
       </c>
       <c r="G1668" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45125,7 +45122,7 @@
         <v>5.5</v>
       </c>
       <c r="G1669" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45151,7 +45148,7 @@
         <v>5.5</v>
       </c>
       <c r="G1670" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45177,7 +45174,7 @@
         <v>5.5</v>
       </c>
       <c r="G1671" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45203,7 +45200,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1672" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45229,7 +45226,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1673" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45255,7 +45252,7 @@
         <v>5.75</v>
       </c>
       <c r="G1674" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45281,7 +45278,7 @@
         <v>5.75</v>
       </c>
       <c r="G1675" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45307,7 +45304,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1676" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45333,7 +45330,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1677" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45359,7 +45356,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1678" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45385,7 +45382,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1679" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45411,7 +45408,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1680" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45437,7 +45434,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1681" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45463,7 +45460,7 @@
         <v>5.75</v>
       </c>
       <c r="G1682" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45489,7 +45486,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1683" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45515,7 +45512,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1684" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45541,7 +45538,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1685" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45567,7 +45564,7 @@
         <v>5.5</v>
       </c>
       <c r="G1686" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45593,7 +45590,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1687" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45619,7 +45616,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1688" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45645,7 +45642,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1689" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45671,7 +45668,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1690" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45697,7 +45694,7 @@
         <v>5.75</v>
       </c>
       <c r="G1691" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45723,7 +45720,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1692" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45749,7 +45746,7 @@
         <v>5.75</v>
       </c>
       <c r="G1693" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45775,7 +45772,7 @@
         <v>5.75</v>
       </c>
       <c r="G1694" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45801,7 +45798,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1695" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45827,7 +45824,7 @@
         <v>6</v>
       </c>
       <c r="G1696" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45853,7 +45850,7 @@
         <v>6</v>
       </c>
       <c r="G1697" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -45879,7 +45876,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1698" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -45905,7 +45902,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1699" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -45931,7 +45928,7 @@
         <v>5.75</v>
       </c>
       <c r="G1700" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -45957,7 +45954,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1701" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -45983,7 +45980,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1702" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46009,7 +46006,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1703" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46035,7 +46032,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1704" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46061,7 +46058,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1705" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46087,7 +46084,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1706" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46113,7 +46110,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1707" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46121,7 +46118,7 @@
     </row>
     <row r="1708">
       <c r="A1708" s="1" t="n">
-        <v>45961.5530439815</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B1708" t="n">
         <v>2400</v>
@@ -46139,7 +46136,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1708" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>

--- a/data/ILP.MI.xlsx
+++ b/data/ILP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="465">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,193 +38,193 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95026230812073</t>
+    <t xml:space="preserve">1.9502626657486</t>
   </si>
   <si>
     <t xml:space="preserve">ILP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97638201713562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91543638706207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9411209821701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00685477256775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97986495494843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93284976482391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95853388309479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92109572887421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94199168682098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9541802406311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93067288398743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88931691646576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86798584461212</t>
+    <t xml:space="preserve">1.97638213634491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91543650627136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94112086296082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00685501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.979865193367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9328498840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95853412151337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92109596729279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94199132919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95418047904968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93067300319672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88931679725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86798596382141</t>
   </si>
   <si>
     <t xml:space="preserve">1.89062285423279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9197895526886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94155597686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9380738735199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91717791557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97551155090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93459093570709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96767592430115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02775049209595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01556158065796</t>
+    <t xml:space="preserve">1.91978943347931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94155609607697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93807351589203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91717767715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97551131248474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93459057807922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96767580509186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02775096893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01556181907654</t>
   </si>
   <si>
     <t xml:space="preserve">2.00250172615051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01991438865662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89802360534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98508846759796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88061034679413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84578430652618</t>
+    <t xml:space="preserve">2.0199146270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89802372455597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98508882522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88061046600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8457840681076</t>
   </si>
   <si>
     <t xml:space="preserve">1.86319744586945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88994169235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90777158737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87211203575134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92560112476349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94343078136444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96125996112823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97909021377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83645296096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81862330436707</t>
+    <t xml:space="preserve">1.88994157314301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90777146816254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87211155891418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92560124397278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94343090057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96126043796539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97909033298492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83645284175873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81862306594849</t>
   </si>
   <si>
     <t xml:space="preserve">1.76513421535492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85428237915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80079364776611</t>
+    <t xml:space="preserve">1.8542822599411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80079352855682</t>
   </si>
   <si>
     <t xml:space="preserve">1.78296387195587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93451607227325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95234537124634</t>
+    <t xml:space="preserve">1.93451571464539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95234525203705</t>
   </si>
   <si>
     <t xml:space="preserve">1.88102698326111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89885663986206</t>
+    <t xml:space="preserve">1.89885652065277</t>
   </si>
   <si>
     <t xml:space="preserve">1.82753789424896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84536755084991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86319708824158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72947490215302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7740490436554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76959180831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79187881946564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80970823764801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77850651741028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70718789100647</t>
+    <t xml:space="preserve">1.8453676700592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86319732666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7294750213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77404916286469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7695916891098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79187870025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80970859527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7785062789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70718777179718</t>
   </si>
   <si>
     <t xml:space="preserve">1.72501766681671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74730455875397</t>
+    <t xml:space="preserve">1.74730479717255</t>
   </si>
   <si>
     <t xml:space="preserve">1.73838984966278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75621950626373</t>
+    <t xml:space="preserve">1.75621938705444</t>
   </si>
   <si>
     <t xml:space="preserve">1.71164524555206</t>
@@ -233,73 +233,73 @@
     <t xml:space="preserve">1.72055995464325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69381582736969</t>
+    <t xml:space="preserve">1.69381558895111</t>
   </si>
   <si>
     <t xml:space="preserve">1.64032673835754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64924168586731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67598605155945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56900835037231</t>
+    <t xml:space="preserve">1.6492418050766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67598617076874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56900823116302</t>
   </si>
   <si>
     <t xml:space="preserve">1.66707134246826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63141202926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65815663337708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68490076065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70273053646088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61358225345612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03257870674133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1930456161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13955664634705</t>
+    <t xml:space="preserve">1.63141214847565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65815651416779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68490087985992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70273065567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61358237266541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03257894515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19304537773132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13955688476562</t>
   </si>
   <si>
     <t xml:space="preserve">2.38917136192322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33568286895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54963850975037</t>
+    <t xml:space="preserve">2.33568263053894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54963803291321</t>
   </si>
   <si>
     <t xml:space="preserve">2.58529758453369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03103852272034</t>
+    <t xml:space="preserve">3.03103876113892</t>
   </si>
   <si>
     <t xml:space="preserve">3.42329049110413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22716450691223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19150495529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13801670074463</t>
+    <t xml:space="preserve">3.22716474533081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19150519371033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13801646232605</t>
   </si>
   <si>
     <t xml:space="preserve">3.01320910453796</t>
@@ -308,10 +308,10 @@
     <t xml:space="preserve">2.99537920951843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97754955291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08452773094177</t>
+    <t xml:space="preserve">2.97755002975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08452749252319</t>
   </si>
   <si>
     <t xml:space="preserve">2.8884015083313</t>
@@ -326,43 +326,43 @@
     <t xml:space="preserve">2.67444610595703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7992537021637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83491277694702</t>
+    <t xml:space="preserve">2.79925346374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8349130153656</t>
   </si>
   <si>
     <t xml:space="preserve">2.90623116493225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78142404556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8705723285675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00555181503296</t>
+    <t xml:space="preserve">2.78142333030701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87057209014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00555157661438</t>
   </si>
   <si>
     <t xml:space="preserve">3.07754111289978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98755431175232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05954337120056</t>
+    <t xml:space="preserve">2.98755478858948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0595440864563</t>
   </si>
   <si>
     <t xml:space="preserve">3.14953017234802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20352244377136</t>
+    <t xml:space="preserve">3.2035219669342</t>
   </si>
   <si>
     <t xml:space="preserve">3.32950353622437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38349509239197</t>
+    <t xml:space="preserve">3.38349556922913</t>
   </si>
   <si>
     <t xml:space="preserve">3.36549806594849</t>
@@ -371,22 +371,22 @@
     <t xml:space="preserve">3.34750056266785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27551174163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31150603294373</t>
+    <t xml:space="preserve">3.27551126480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31150579452515</t>
   </si>
   <si>
     <t xml:space="preserve">3.29350900650024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41949009895325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25751399993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23951697349548</t>
+    <t xml:space="preserve">3.41948962211609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25751423835754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2395167350769</t>
   </si>
   <si>
     <t xml:space="preserve">3.22151947021484</t>
@@ -398,22 +398,22 @@
     <t xml:space="preserve">3.43748712539673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65345478057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56346869468689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63545799255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86942315101624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99540424346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01340103149414</t>
+    <t xml:space="preserve">3.65345525741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56346845626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63545751571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86942291259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9954047203064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0134015083313</t>
   </si>
   <si>
     <t xml:space="preserve">3.94141221046448</t>
@@ -425,37 +425,37 @@
     <t xml:space="preserve">3.92341470718384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9774067401886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88742017745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8514256477356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90541768074036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.175377368927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15738010406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24736595153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35535049438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39134502410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31935501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30135917663574</t>
+    <t xml:space="preserve">3.97740697860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8874204158783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85142588615417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90541744232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17537689208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1573805809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24736642837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35535001754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39134550094604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31935596466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30135869979858</t>
   </si>
   <si>
     <t xml:space="preserve">4.32852506637573</t>
@@ -464,70 +464,70 @@
     <t xml:space="preserve">4.34663581848145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23796939849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20174789428711</t>
+    <t xml:space="preserve">4.23796987533569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20174741744995</t>
   </si>
   <si>
     <t xml:space="preserve">4.21985960006714</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1293044090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05686044692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16552591323853</t>
+    <t xml:space="preserve">4.12930393218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05685997009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16552543640137</t>
   </si>
   <si>
     <t xml:space="preserve">4.09308195114136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43719053268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29230260848999</t>
+    <t xml:space="preserve">4.43719100952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29230308532715</t>
   </si>
   <si>
     <t xml:space="preserve">4.11119318008423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25608062744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41907978057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14741516113281</t>
+    <t xml:space="preserve">4.25608110427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41908025741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1474142074585</t>
   </si>
   <si>
     <t xml:space="preserve">4.07497119903564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02063846588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9481942653656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93008303642273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8938615322113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98441648483276</t>
+    <t xml:space="preserve">4.02063894271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94819402694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93008327484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89386129379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98441624641418</t>
   </si>
   <si>
     <t xml:space="preserve">4.03874921798706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91197228431702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87575054168701</t>
+    <t xml:space="preserve">3.9119725227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87575078010559</t>
   </si>
   <si>
     <t xml:space="preserve">3.74897336959839</t>
@@ -536,49 +536,49 @@
     <t xml:space="preserve">3.82141757011414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83952832221985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6221969127655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73086214065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65841841697693</t>
+    <t xml:space="preserve">3.83952808380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62219643592834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73086285591125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65841817855835</t>
   </si>
   <si>
     <t xml:space="preserve">3.78519535064697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00252676010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18363761901855</t>
+    <t xml:space="preserve">4.00252723693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1836371421814</t>
   </si>
   <si>
     <t xml:space="preserve">4.31041383743286</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96630525588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80330586433411</t>
+    <t xml:space="preserve">3.96630549430847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80330562591553</t>
   </si>
   <si>
     <t xml:space="preserve">3.7127513885498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.441086769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53164172172546</t>
+    <t xml:space="preserve">3.44108629226685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53164148330688</t>
   </si>
   <si>
     <t xml:space="preserve">3.4954195022583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38675355911255</t>
+    <t xml:space="preserve">3.38675379753113</t>
   </si>
   <si>
     <t xml:space="preserve">3.15131115913391</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">2.89775705337524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09697794914246</t>
+    <t xml:space="preserve">3.09697818756104</t>
   </si>
   <si>
     <t xml:space="preserve">3.13319993019104</t>
@@ -611,25 +611,25 @@
     <t xml:space="preserve">3.33242058753967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36864280700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40486478805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31430983543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18753290176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2237548828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56786370277405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54975295066833</t>
+    <t xml:space="preserve">3.36864256858826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.404865026474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31431007385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1875331401825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22375464439392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56786322593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54975271224976</t>
   </si>
   <si>
     <t xml:space="preserve">3.55880808830261</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">3.33267426490784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35129308700562</t>
+    <t xml:space="preserve">3.35129261016846</t>
   </si>
   <si>
     <t xml:space="preserve">3.41645669937134</t>
@@ -671,46 +671,46 @@
     <t xml:space="preserve">3.49092984199524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3699107170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53747582435608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6305673122406</t>
+    <t xml:space="preserve">3.36991119384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53747534751892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63056707382202</t>
   </si>
   <si>
     <t xml:space="preserve">3.59333038330078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74227690696716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84467768669128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85398650169373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79813194274902</t>
+    <t xml:space="preserve">3.74227666854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84467744827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8539867401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79813146591187</t>
   </si>
   <si>
     <t xml:space="preserve">3.7795135974884</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75158619880676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67711281776428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66780376434326</t>
+    <t xml:space="preserve">3.75158643722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67711329460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66780352592468</t>
   </si>
   <si>
     <t xml:space="preserve">3.65849471092224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37922024726868</t>
+    <t xml:space="preserve">3.37922048568726</t>
   </si>
   <si>
     <t xml:space="preserve">3.3233654499054</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">3.44438433647156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21165537834167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11856412887573</t>
+    <t xml:space="preserve">3.2116551399231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11856389045715</t>
   </si>
   <si>
     <t xml:space="preserve">3.18372821807861</t>
@@ -740,22 +740,22 @@
     <t xml:space="preserve">3.60263967514038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4723117351532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62125778198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5281662940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4816210269928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42576599121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64918541908264</t>
+    <t xml:space="preserve">3.47231197357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.621258020401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52816653251648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48162078857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42576575279236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64918565750122</t>
   </si>
   <si>
     <t xml:space="preserve">3.72365856170654</t>
@@ -764,7 +764,7 @@
     <t xml:space="preserve">3.51885724067688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7702043056488</t>
+    <t xml:space="preserve">3.77020454406738</t>
   </si>
   <si>
     <t xml:space="preserve">3.58402132987976</t>
@@ -776,19 +776,19 @@
     <t xml:space="preserve">3.6864218711853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80744099617004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29543781280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56540298461914</t>
+    <t xml:space="preserve">3.80744123458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29543805122375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56540274620056</t>
   </si>
   <si>
     <t xml:space="preserve">4.00293302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92846035957336</t>
+    <t xml:space="preserve">3.92846012115479</t>
   </si>
   <si>
     <t xml:space="preserve">3.788822889328</t>
@@ -797,13 +797,13 @@
     <t xml:space="preserve">3.98431515693665</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86329627037048</t>
+    <t xml:space="preserve">3.86329579353333</t>
   </si>
   <si>
     <t xml:space="preserve">3.81675004959106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671569824219</t>
+    <t xml:space="preserve">4.08671522140503</t>
   </si>
   <si>
     <t xml:space="preserve">4.16118812561035</t>
@@ -815,22 +815,22 @@
     <t xml:space="preserve">4.38460826873779</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48700857162476</t>
+    <t xml:space="preserve">4.48700904846191</t>
   </si>
   <si>
     <t xml:space="preserve">4.35668039321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50562715530396</t>
+    <t xml:space="preserve">4.5056266784668</t>
   </si>
   <si>
     <t xml:space="preserve">4.63595485687256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4963173866272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46838998794556</t>
+    <t xml:space="preserve">4.49631786346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46839046478271</t>
   </si>
   <si>
     <t xml:space="preserve">4.28220701217651</t>
@@ -839,10 +839,10 @@
     <t xml:space="preserve">4.20773410797119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43115425109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56148147583008</t>
+    <t xml:space="preserve">4.43115377426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56148195266724</t>
   </si>
   <si>
     <t xml:space="preserve">4.57079076766968</t>
@@ -851,16 +851,16 @@
     <t xml:space="preserve">4.45908117294312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.524245262146</t>
+    <t xml:space="preserve">4.52424573898315</t>
   </si>
   <si>
     <t xml:space="preserve">4.58940887451172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59871816635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44046258926392</t>
+    <t xml:space="preserve">4.59871864318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44046306610107</t>
   </si>
   <si>
     <t xml:space="preserve">4.37529897689819</t>
@@ -872,31 +872,31 @@
     <t xml:space="preserve">4.29151630401611</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32875347137451</t>
+    <t xml:space="preserve">4.32875299453735</t>
   </si>
   <si>
     <t xml:space="preserve">4.23566198348999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33806228637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15187883377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13326120376587</t>
+    <t xml:space="preserve">4.33806276321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15187931060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13326168060303</t>
   </si>
   <si>
     <t xml:space="preserve">4.18911600112915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34737205505371</t>
+    <t xml:space="preserve">4.34737157821655</t>
   </si>
   <si>
     <t xml:space="preserve">4.19842576980591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31944417953491</t>
+    <t xml:space="preserve">4.31944370269775</t>
   </si>
   <si>
     <t xml:space="preserve">4.27289867401123</t>
@@ -905,25 +905,25 @@
     <t xml:space="preserve">4.5149359703064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39391660690308</t>
+    <t xml:space="preserve">4.39391708374023</t>
   </si>
   <si>
     <t xml:space="preserve">4.42184495925903</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87799215316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71042823791504</t>
+    <t xml:space="preserve">4.87799263000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71042776107788</t>
   </si>
   <si>
     <t xml:space="preserve">4.60802745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61733675003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26358890533447</t>
+    <t xml:space="preserve">4.61733627319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26358842849731</t>
   </si>
   <si>
     <t xml:space="preserve">4.11464309692383</t>
@@ -932,28 +932,28 @@
     <t xml:space="preserve">4.10533332824707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17980623245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07740592956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95638728141785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90984129905701</t>
+    <t xml:space="preserve">4.17980670928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07740640640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95638680458069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90984082221985</t>
   </si>
   <si>
     <t xml:space="preserve">4.04016971588135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25427961349487</t>
+    <t xml:space="preserve">4.25428009033203</t>
   </si>
   <si>
     <t xml:space="preserve">4.65457344055176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70111894607544</t>
+    <t xml:space="preserve">4.7011194229126</t>
   </si>
   <si>
     <t xml:space="preserve">4.5428638458252</t>
@@ -968,22 +968,22 @@
     <t xml:space="preserve">4.58010005950928</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79421043395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88730144500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61688423156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59804058074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52266216278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57919549942017</t>
+    <t xml:space="preserve">4.79421091079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88730192184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61688470840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59804010391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52266263961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57919597625732</t>
   </si>
   <si>
     <t xml:space="preserve">4.56035137176514</t>
@@ -992,13 +992,13 @@
     <t xml:space="preserve">4.44728422164917</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67341804504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69226217269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80532884597778</t>
+    <t xml:space="preserve">4.67341756820679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69226169586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80532836914062</t>
   </si>
   <si>
     <t xml:space="preserve">4.8995509147644</t>
@@ -1007,10 +1007,10 @@
     <t xml:space="preserve">4.85243988037109</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99377298355103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94666147232056</t>
+    <t xml:space="preserve">4.99377393722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94666194915771</t>
   </si>
   <si>
     <t xml:space="preserve">5.04088401794434</t>
@@ -1022,19 +1022,19 @@
     <t xml:space="preserve">5.60621690750122</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5119948387146</t>
+    <t xml:space="preserve">5.51199436187744</t>
   </si>
   <si>
     <t xml:space="preserve">5.70043897628784</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65332794189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32355070114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37066173553467</t>
+    <t xml:space="preserve">5.65332841873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32355117797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37066125869751</t>
   </si>
   <si>
     <t xml:space="preserve">5.18221712112427</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">4.71110677719116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76719093322754</t>
+    <t xml:space="preserve">4.7671914100647</t>
   </si>
   <si>
     <t xml:space="preserve">4.69091606140137</t>
@@ -1067,22 +1067,22 @@
     <t xml:space="preserve">4.748122215271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67184734344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53836631774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65277910232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57650327682495</t>
+    <t xml:space="preserve">4.67184782028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53836679458618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65277862548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57650375366211</t>
   </si>
   <si>
     <t xml:space="preserve">4.72905397415161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86253547668457</t>
+    <t xml:space="preserve">4.86253452301025</t>
   </si>
   <si>
     <t xml:space="preserve">4.91020727157593</t>
@@ -1097,10 +1097,10 @@
     <t xml:space="preserve">4.6146411895752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59557247161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55743503570557</t>
+    <t xml:space="preserve">4.59557294845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55743551254272</t>
   </si>
   <si>
     <t xml:space="preserve">4.74882841110229</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">4.71022081375122</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78743696212769</t>
+    <t xml:space="preserve">4.78743743896484</t>
   </si>
   <si>
     <t xml:space="preserve">5.01908683776855</t>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">5.64647340774536</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54995203018188</t>
+    <t xml:space="preserve">5.54995250701904</t>
   </si>
   <si>
     <t xml:space="preserve">5.21212911605835</t>
@@ -1154,10 +1154,10 @@
     <t xml:space="preserve">5.06734752655029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92256641387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11560821533203</t>
+    <t xml:space="preserve">4.92256593704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11560869216919</t>
   </si>
   <si>
     <t xml:space="preserve">4.87430620193481</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">4.82604551315308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97082662582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86340188980103</t>
+    <t xml:space="preserve">4.97082710266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86340236663818</t>
   </si>
   <si>
     <t xml:space="preserve">4.93176364898682</t>
@@ -1193,19 +1193,19 @@
     <t xml:space="preserve">4.62902116775513</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58995819091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60948944091797</t>
+    <t xml:space="preserve">4.58995771408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60948991775513</t>
   </si>
   <si>
     <t xml:space="preserve">4.55089426040649</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51183080673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53136301040649</t>
+    <t xml:space="preserve">4.51183128356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53136253356934</t>
   </si>
   <si>
     <t xml:space="preserve">4.49229907989502</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">3.76962494850159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67196655273438</t>
+    <t xml:space="preserve">3.6719663143158</t>
   </si>
   <si>
     <t xml:space="preserve">3.71102976799011</t>
@@ -1259,22 +1259,22 @@
     <t xml:space="preserve">3.92587900161743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10166454315186</t>
+    <t xml:space="preserve">4.1016640663147</t>
   </si>
   <si>
     <t xml:space="preserve">4.04306936264038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12119579315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17979145050049</t>
+    <t xml:space="preserve">4.12119626998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17979192733765</t>
   </si>
   <si>
     <t xml:space="preserve">4.0821328163147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1993236541748</t>
+    <t xml:space="preserve">4.19932317733765</t>
   </si>
   <si>
     <t xml:space="preserve">4.16026020050049</t>
@@ -1289,16 +1289,16 @@
     <t xml:space="preserve">4.33604526519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25791883468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86728358268738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94541072845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4337043762207</t>
+    <t xml:space="preserve">4.25791835784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86728382110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94541049003601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43370389938354</t>
   </si>
   <si>
     <t xml:space="preserve">4.59072542190552</t>
@@ -1404,6 +1404,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.69999980926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80000019073486</t>
   </si>
 </sst>
 </file>
@@ -46176,7 +46179,7 @@
     </row>
     <row r="1710">
       <c r="A1710" s="1" t="n">
-        <v>45965.3515509259</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B1710" t="n">
         <v>1200</v>
@@ -46197,6 +46200,32 @@
         <v>463</v>
       </c>
       <c r="H1710" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" s="1" t="n">
+        <v>45966.6072569444</v>
+      </c>
+      <c r="B1711" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C1711" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="D1711" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="E1711" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="F1711" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="G1711" t="s">
+        <v>464</v>
+      </c>
+      <c r="H1711" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ILP.MI.xlsx
+++ b/data/ILP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="464">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9502626657486</t>
+    <t xml:space="preserve">1.95026290416718</t>
   </si>
   <si>
     <t xml:space="preserve">ILP.MI</t>
@@ -50,10 +50,10 @@
     <t xml:space="preserve">1.91543650627136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94112086296082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00685501098633</t>
+    <t xml:space="preserve">1.94112074375153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00685524940491</t>
   </si>
   <si>
     <t xml:space="preserve">1.979865193367</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">1.9328498840332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95853412151337</t>
+    <t xml:space="preserve">1.95853388309479</t>
   </si>
   <si>
     <t xml:space="preserve">1.92109596729279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94199132919312</t>
+    <t xml:space="preserve">1.94199109077454</t>
   </si>
   <si>
     <t xml:space="preserve">1.95418047904968</t>
@@ -77,16 +77,16 @@
     <t xml:space="preserve">1.93067300319672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88931679725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86798596382141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89062285423279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91978943347931</t>
+    <t xml:space="preserve">1.88931715488434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86798584461212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89062297344208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91978967189789</t>
   </si>
   <si>
     <t xml:space="preserve">1.94155609607697</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">1.91717767715454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97551131248474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93459057807922</t>
+    <t xml:space="preserve">1.9755117893219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9345908164978</t>
   </si>
   <si>
     <t xml:space="preserve">1.96767580509186</t>
@@ -110,43 +110,43 @@
     <t xml:space="preserve">2.02775096893311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01556181907654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00250172615051</t>
+    <t xml:space="preserve">2.01556158065796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00250220298767</t>
   </si>
   <si>
     <t xml:space="preserve">2.0199146270752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89802372455597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98508882522583</t>
+    <t xml:space="preserve">1.89802360534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98508858680725</t>
   </si>
   <si>
     <t xml:space="preserve">1.88061046600342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8457840681076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86319744586945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88994157314301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90777146816254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87211155891418</t>
+    <t xml:space="preserve">1.84578430652618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86319768428802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88994181156158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90777170658112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87211191654205</t>
   </si>
   <si>
     <t xml:space="preserve">1.92560124397278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94343090057373</t>
+    <t xml:space="preserve">1.94343078136444</t>
   </si>
   <si>
     <t xml:space="preserve">1.96126043796539</t>
@@ -158,13 +158,13 @@
     <t xml:space="preserve">1.83645284175873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81862306594849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76513421535492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8542822599411</t>
+    <t xml:space="preserve">1.81862318515778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76513433456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85428237915039</t>
   </si>
   <si>
     <t xml:space="preserve">1.80079352855682</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">1.78296387195587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93451571464539</t>
+    <t xml:space="preserve">1.93451607227325</t>
   </si>
   <si>
     <t xml:space="preserve">1.95234525203705</t>
@@ -182,142 +182,142 @@
     <t xml:space="preserve">1.88102698326111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89885652065277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82753789424896</t>
+    <t xml:space="preserve">1.89885663986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82753801345825</t>
   </si>
   <si>
     <t xml:space="preserve">1.8453676700592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86319732666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7294750213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77404916286469</t>
+    <t xml:space="preserve">1.86319756507874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72947514057159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7740490436554</t>
   </si>
   <si>
     <t xml:space="preserve">1.7695916891098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79187870025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80970859527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7785062789917</t>
+    <t xml:space="preserve">1.79187881946564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80970847606659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77850639820099</t>
   </si>
   <si>
     <t xml:space="preserve">1.70718777179718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72501766681671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74730479717255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73838984966278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75621938705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71164524555206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72055995464325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69381558895111</t>
+    <t xml:space="preserve">1.72501754760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74730455875397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73838996887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75621950626373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71164548397064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72056007385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6938157081604</t>
   </si>
   <si>
     <t xml:space="preserve">1.64032673835754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6492418050766</t>
+    <t xml:space="preserve">1.64924156665802</t>
   </si>
   <si>
     <t xml:space="preserve">1.67598617076874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56900823116302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66707134246826</t>
+    <t xml:space="preserve">1.56900835037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66707122325897</t>
   </si>
   <si>
     <t xml:space="preserve">1.63141214847565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65815651416779</t>
+    <t xml:space="preserve">1.65815663337708</t>
   </si>
   <si>
     <t xml:space="preserve">1.68490087985992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70273065567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61358237266541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03257894515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19304537773132</t>
+    <t xml:space="preserve">1.70273053646088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61358213424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03257870674133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19304585456848</t>
   </si>
   <si>
     <t xml:space="preserve">2.13955688476562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38917136192322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33568263053894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54963803291321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58529758453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03103876113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42329049110413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22716474533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19150519371033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13801646232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01320910453796</t>
+    <t xml:space="preserve">2.3891716003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33568239212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54963827133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58529782295227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03103852272034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42329096794128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22716426849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19150543212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13801670074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01320862770081</t>
   </si>
   <si>
     <t xml:space="preserve">2.99537920951843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97755002975464</t>
+    <t xml:space="preserve">2.97754955291748</t>
   </si>
   <si>
     <t xml:space="preserve">3.08452749252319</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8884015083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71010518074036</t>
+    <t xml:space="preserve">2.88840174674988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71010494232178</t>
   </si>
   <si>
     <t xml:space="preserve">2.6922755241394</t>
@@ -326,19 +326,19 @@
     <t xml:space="preserve">2.67444610595703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79925346374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8349130153656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90623116493225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78142333030701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87057209014893</t>
+    <t xml:space="preserve">2.79925322532654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83491253852844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90623092651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78142356872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87057161331177</t>
   </si>
   <si>
     <t xml:space="preserve">3.00555157661438</t>
@@ -347,31 +347,31 @@
     <t xml:space="preserve">3.07754111289978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98755478858948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0595440864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14953017234802</t>
+    <t xml:space="preserve">2.98755431175232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05954360961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14952993392944</t>
   </si>
   <si>
     <t xml:space="preserve">3.2035219669342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32950353622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38349556922913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36549806594849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34750056266785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27551126480103</t>
+    <t xml:space="preserve">3.32950329780579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38349533081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36549782752991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34750080108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2755115032196</t>
   </si>
   <si>
     <t xml:space="preserve">3.31150579452515</t>
@@ -380,13 +380,13 @@
     <t xml:space="preserve">3.29350900650024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41948962211609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25751423835754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2395167350769</t>
+    <t xml:space="preserve">3.41949009895325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25751376152039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23951697349548</t>
   </si>
   <si>
     <t xml:space="preserve">3.22151947021484</t>
@@ -401,13 +401,13 @@
     <t xml:space="preserve">3.65345525741577</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56346845626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63545751571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86942291259766</t>
+    <t xml:space="preserve">3.56346869468689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63545775413513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86942315101624</t>
   </si>
   <si>
     <t xml:space="preserve">3.9954047203064</t>
@@ -416,13 +416,13 @@
     <t xml:space="preserve">4.0134015083313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94141221046448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76143884658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92341470718384</t>
+    <t xml:space="preserve">3.94141173362732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76143956184387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.923415184021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97740697860718</t>
@@ -431,25 +431,25 @@
     <t xml:space="preserve">3.8874204158783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85142588615417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90541744232178</t>
+    <t xml:space="preserve">3.85142612457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90541791915894</t>
   </si>
   <si>
     <t xml:space="preserve">4.17537689208984</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1573805809021</t>
+    <t xml:space="preserve">4.15738010406494</t>
   </si>
   <si>
     <t xml:space="preserve">4.24736642837524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35535001754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39134550094604</t>
+    <t xml:space="preserve">4.35535049438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39134502410889</t>
   </si>
   <si>
     <t xml:space="preserve">4.31935596466064</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">4.30135869979858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32852506637573</t>
+    <t xml:space="preserve">4.32852458953857</t>
   </si>
   <si>
     <t xml:space="preserve">4.34663581848145</t>
@@ -467,10 +467,10 @@
     <t xml:space="preserve">4.23796987533569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20174741744995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21985960006714</t>
+    <t xml:space="preserve">4.20174789428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21985912322998</t>
   </si>
   <si>
     <t xml:space="preserve">4.12930393218994</t>
@@ -479,34 +479,34 @@
     <t xml:space="preserve">4.05685997009277</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16552543640137</t>
+    <t xml:space="preserve">4.16552591323853</t>
   </si>
   <si>
     <t xml:space="preserve">4.09308195114136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43719100952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29230308532715</t>
+    <t xml:space="preserve">4.43719053268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29230260848999</t>
   </si>
   <si>
     <t xml:space="preserve">4.11119318008423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25608110427856</t>
+    <t xml:space="preserve">4.25608062744141</t>
   </si>
   <si>
     <t xml:space="preserve">4.41908025741577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1474142074585</t>
+    <t xml:space="preserve">4.14741468429565</t>
   </si>
   <si>
     <t xml:space="preserve">4.07497119903564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02063894271851</t>
+    <t xml:space="preserve">4.02063846588135</t>
   </si>
   <si>
     <t xml:space="preserve">3.94819402694702</t>
@@ -524,31 +524,31 @@
     <t xml:space="preserve">4.03874921798706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9119725227356</t>
+    <t xml:space="preserve">3.91197204589844</t>
   </si>
   <si>
     <t xml:space="preserve">3.87575078010559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74897336959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82141757011414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83952808380127</t>
+    <t xml:space="preserve">3.74897313117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82141733169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83952760696411</t>
   </si>
   <si>
     <t xml:space="preserve">3.62219643592834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73086285591125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65841817855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78519535064697</t>
+    <t xml:space="preserve">3.7308623790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65841841697693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78519558906555</t>
   </si>
   <si>
     <t xml:space="preserve">4.00252723693848</t>
@@ -560,16 +560,16 @@
     <t xml:space="preserve">4.31041383743286</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96630549430847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80330562591553</t>
+    <t xml:space="preserve">3.96630501747131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80330634117126</t>
   </si>
   <si>
     <t xml:space="preserve">3.7127513885498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44108629226685</t>
+    <t xml:space="preserve">3.44108653068542</t>
   </si>
   <si>
     <t xml:space="preserve">3.53164148330688</t>
@@ -581,55 +581,55 @@
     <t xml:space="preserve">3.38675379753113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15131115913391</t>
+    <t xml:space="preserve">3.15131092071533</t>
   </si>
   <si>
     <t xml:space="preserve">2.7347583770752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80720233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69853639602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58987021446228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7709801197052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89775705337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09697818756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13319993019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33242058753967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36864256858826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.404865026474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31431007385254</t>
+    <t xml:space="preserve">2.80720210075378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69853663444519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58987045288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77098035812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8977575302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09697794914246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13319969177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33242082595825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36864280700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40486478805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31430983543396</t>
   </si>
   <si>
     <t xml:space="preserve">3.1875331401825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22375464439392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56786322593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54975271224976</t>
+    <t xml:space="preserve">3.2237548828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56786346435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54975247383118</t>
   </si>
   <si>
     <t xml:space="preserve">3.55880808830261</t>
@@ -638,124 +638,124 @@
     <t xml:space="preserve">3.51353073120117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45014214515686</t>
+    <t xml:space="preserve">3.45014190673828</t>
   </si>
   <si>
     <t xml:space="preserve">3.42297554016113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35053181648254</t>
+    <t xml:space="preserve">3.35053157806396</t>
   </si>
   <si>
     <t xml:space="preserve">3.41392016410828</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34147620201111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25092124938965</t>
+    <t xml:space="preserve">3.34147596359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25092148780823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3233654499054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33267402648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35129284858704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41645693778992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4909303188324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36991095542908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5374755859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63056707382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59333038330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74227666854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84467744827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85398650169373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79813170433044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7795135974884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75158596038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67711281776428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66780376434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65849471092224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37922048568726</t>
   </si>
   <si>
     <t xml:space="preserve">3.32336521148682</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33267426490784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35129261016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41645669937134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49092984199524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36991119384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53747534751892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63056707382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59333038330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74227666854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84467744827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8539867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79813146591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7795135974884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75158643722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67711329460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66780352592468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65849471092224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37922048568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3233654499054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44438433647156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2116551399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11856389045715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18372821807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34198355674744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43507504463196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4630024433136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60263967514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47231197357178</t>
+    <t xml:space="preserve">3.44438409805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21165537834167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11856412887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18372797966003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34198379516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43507480621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46300268173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60263991355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47231149673462</t>
   </si>
   <si>
     <t xml:space="preserve">3.621258020401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52816653251648</t>
+    <t xml:space="preserve">3.52816677093506</t>
   </si>
   <si>
     <t xml:space="preserve">3.48162078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42576575279236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64918565750122</t>
+    <t xml:space="preserve">3.42576599121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64918541908264</t>
   </si>
   <si>
     <t xml:space="preserve">3.72365856170654</t>
@@ -773,22 +773,22 @@
     <t xml:space="preserve">3.7050404548645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6864218711853</t>
+    <t xml:space="preserve">3.68642210960388</t>
   </si>
   <si>
     <t xml:space="preserve">3.80744123458862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29543805122375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56540274620056</t>
+    <t xml:space="preserve">3.2954375743866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56540322303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.00293302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92846012115479</t>
+    <t xml:space="preserve">3.92845988273621</t>
   </si>
   <si>
     <t xml:space="preserve">3.788822889328</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">3.98431515693665</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86329579353333</t>
+    <t xml:space="preserve">3.8632960319519</t>
   </si>
   <si>
     <t xml:space="preserve">3.81675004959106</t>
@@ -815,25 +815,25 @@
     <t xml:space="preserve">4.38460826873779</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48700904846191</t>
+    <t xml:space="preserve">4.48700857162476</t>
   </si>
   <si>
     <t xml:space="preserve">4.35668039321899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5056266784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63595485687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49631786346436</t>
+    <t xml:space="preserve">4.50562715530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6359543800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49631834030151</t>
   </si>
   <si>
     <t xml:space="preserve">4.46839046478271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28220701217651</t>
+    <t xml:space="preserve">4.28220748901367</t>
   </si>
   <si>
     <t xml:space="preserve">4.20773410797119</t>
@@ -842,34 +842,34 @@
     <t xml:space="preserve">4.43115377426147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56148195266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57079076766968</t>
+    <t xml:space="preserve">4.56148147583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57079124450684</t>
   </si>
   <si>
     <t xml:space="preserve">4.45908117294312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52424573898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58940887451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59871864318848</t>
+    <t xml:space="preserve">4.524245262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58940935134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59871816635132</t>
   </si>
   <si>
     <t xml:space="preserve">4.44046306610107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37529897689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41253566741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29151630401611</t>
+    <t xml:space="preserve">4.37529850006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41253519058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29151678085327</t>
   </si>
   <si>
     <t xml:space="preserve">4.32875299453735</t>
@@ -878,13 +878,13 @@
     <t xml:space="preserve">4.23566198348999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33806276321411</t>
+    <t xml:space="preserve">4.33806228637695</t>
   </si>
   <si>
     <t xml:space="preserve">4.15187931060791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13326168060303</t>
+    <t xml:space="preserve">4.13326120376587</t>
   </si>
   <si>
     <t xml:space="preserve">4.18911600112915</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">4.19842576980591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31944370269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27289867401123</t>
+    <t xml:space="preserve">4.31944417953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27289819717407</t>
   </si>
   <si>
     <t xml:space="preserve">4.5149359703064</t>
@@ -911,19 +911,19 @@
     <t xml:space="preserve">4.42184495925903</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87799263000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71042776107788</t>
+    <t xml:space="preserve">4.87799215316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71042823791504</t>
   </si>
   <si>
     <t xml:space="preserve">4.60802745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61733627319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26358842849731</t>
+    <t xml:space="preserve">4.61733675003052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26358890533447</t>
   </si>
   <si>
     <t xml:space="preserve">4.11464309692383</t>
@@ -932,16 +932,16 @@
     <t xml:space="preserve">4.10533332824707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17980670928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07740640640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95638680458069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90984082221985</t>
+    <t xml:space="preserve">4.17980623245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07740592956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95638728141785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90984153747559</t>
   </si>
   <si>
     <t xml:space="preserve">4.04016971588135</t>
@@ -950,10 +950,10 @@
     <t xml:space="preserve">4.25428009033203</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65457344055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7011194229126</t>
+    <t xml:space="preserve">4.6545729637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70111894607544</t>
   </si>
   <si>
     <t xml:space="preserve">4.5428638458252</t>
@@ -962,52 +962,52 @@
     <t xml:space="preserve">4.30082607269287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44977235794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58010005950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79421091079712</t>
+    <t xml:space="preserve">4.44977188110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58009958267212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79421138763428</t>
   </si>
   <si>
     <t xml:space="preserve">4.88730192184448</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61688470840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59804010391235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52266263961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57919597625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56035137176514</t>
+    <t xml:space="preserve">4.61688375473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59804058074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52266216278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57919549942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56035184860229</t>
   </si>
   <si>
     <t xml:space="preserve">4.44728422164917</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67341756820679</t>
+    <t xml:space="preserve">4.67341804504395</t>
   </si>
   <si>
     <t xml:space="preserve">4.69226169586182</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80532836914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8995509147644</t>
+    <t xml:space="preserve">4.80532932281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89955043792725</t>
   </si>
   <si>
     <t xml:space="preserve">4.85243988037109</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99377393722534</t>
+    <t xml:space="preserve">4.99377298355103</t>
   </si>
   <si>
     <t xml:space="preserve">4.94666194915771</t>
@@ -1019,70 +1019,70 @@
     <t xml:space="preserve">5.22932863235474</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60621690750122</t>
+    <t xml:space="preserve">5.60621643066406</t>
   </si>
   <si>
     <t xml:space="preserve">5.51199436187744</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70043897628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65332841873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32355117797852</t>
+    <t xml:space="preserve">5.700439453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65332794189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32355070114136</t>
   </si>
   <si>
     <t xml:space="preserve">5.37066125869751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18221712112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13510608673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08799505233765</t>
+    <t xml:space="preserve">5.18221759796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1351056098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0879955291748</t>
   </si>
   <si>
     <t xml:space="preserve">4.75821781158447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71110677719116</t>
+    <t xml:space="preserve">4.71110725402832</t>
   </si>
   <si>
     <t xml:space="preserve">4.7671914100647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69091606140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70998525619507</t>
+    <t xml:space="preserve">4.69091653823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70998477935791</t>
   </si>
   <si>
     <t xml:space="preserve">4.81486320495605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.748122215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67184782028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53836679458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65277862548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57650375366211</t>
+    <t xml:space="preserve">4.74812173843384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67184686660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53836631774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65277910232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57650327682495</t>
   </si>
   <si>
     <t xml:space="preserve">4.72905397415161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86253452301025</t>
+    <t xml:space="preserve">4.86253547668457</t>
   </si>
   <si>
     <t xml:space="preserve">4.91020727157593</t>
@@ -1094,22 +1094,22 @@
     <t xml:space="preserve">4.63370990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6146411895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59557294845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55743551254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74882841110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71022081375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78743743896484</t>
+    <t xml:space="preserve">4.61464166641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59557199478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55743503570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74882888793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71022033691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78743696212769</t>
   </si>
   <si>
     <t xml:space="preserve">5.01908683776855</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">5.26038932800293</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5016918182373</t>
+    <t xml:space="preserve">5.50169134140015</t>
   </si>
   <si>
     <t xml:space="preserve">5.74299383163452</t>
@@ -1145,31 +1145,31 @@
     <t xml:space="preserve">5.64647340774536</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54995250701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21212911605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06734752655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92256593704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11560869216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87430620193481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82604551315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97082710266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86340236663818</t>
+    <t xml:space="preserve">5.54995203018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21212959289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06734800338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92256641387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11560821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87430572509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82604503631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97082662582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86340188980103</t>
   </si>
   <si>
     <t xml:space="preserve">4.93176364898682</t>
@@ -1193,19 +1193,19 @@
     <t xml:space="preserve">4.62902116775513</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58995771408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60948991775513</t>
+    <t xml:space="preserve">4.58995819091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60948944091797</t>
   </si>
   <si>
     <t xml:space="preserve">4.55089426040649</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51183128356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53136253356934</t>
+    <t xml:space="preserve">4.51183080673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53136301040649</t>
   </si>
   <si>
     <t xml:space="preserve">4.49229907989502</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">3.76962494850159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6719663143158</t>
+    <t xml:space="preserve">3.67196655273438</t>
   </si>
   <si>
     <t xml:space="preserve">3.71102976799011</t>
@@ -1259,22 +1259,22 @@
     <t xml:space="preserve">3.92587900161743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1016640663147</t>
+    <t xml:space="preserve">4.10166454315186</t>
   </si>
   <si>
     <t xml:space="preserve">4.04306936264038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12119626998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17979192733765</t>
+    <t xml:space="preserve">4.12119579315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17979145050049</t>
   </si>
   <si>
     <t xml:space="preserve">4.0821328163147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19932317733765</t>
+    <t xml:space="preserve">4.1993236541748</t>
   </si>
   <si>
     <t xml:space="preserve">4.16026020050049</t>
@@ -1289,16 +1289,16 @@
     <t xml:space="preserve">4.33604526519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25791835784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86728382110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94541049003601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43370389938354</t>
+    <t xml:space="preserve">4.25791883468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86728358268738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94541072845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4337043762207</t>
   </si>
   <si>
     <t xml:space="preserve">4.59072542190552</t>
@@ -1404,9 +1404,6 @@
   </si>
   <si>
     <t xml:space="preserve">5.69999980926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80000019073486</t>
   </si>
 </sst>
 </file>
@@ -46205,25 +46202,25 @@
     </row>
     <row r="1711">
       <c r="A1711" s="1" t="n">
-        <v>45966.6072569444</v>
+        <v>45967.6651736111</v>
       </c>
       <c r="B1711" t="n">
-        <v>2400</v>
+        <v>1800</v>
       </c>
       <c r="C1711" t="n">
-        <v>5.80000019073486</v>
+        <v>5.69999980926514</v>
       </c>
       <c r="D1711" t="n">
-        <v>5.69999980926514</v>
+        <v>5.59999990463257</v>
       </c>
       <c r="E1711" t="n">
         <v>5.69999980926514</v>
       </c>
       <c r="F1711" t="n">
-        <v>5.80000019073486</v>
+        <v>5.59999990463257</v>
       </c>
       <c r="G1711" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>

--- a/data/ILP.MI.xlsx
+++ b/data/ILP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="464">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95026254653931</t>
+    <t xml:space="preserve">1.95026230812073</t>
   </si>
   <si>
     <t xml:space="preserve">ILP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9763822555542</t>
+    <t xml:space="preserve">1.97638201713562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91543626785278</t>
+    <t xml:space="preserve">1.91543650627136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94112074375153</t>
+    <t xml:space="preserve">1.9411209821701</t>
   </si>
   <si>
     <t xml:space="preserve">2.00685524940491</t>
@@ -59,58 +59,58 @@
     <t xml:space="preserve">1.97986471652985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93284928798676</t>
+    <t xml:space="preserve">1.93284964561462</t>
   </si>
   <si>
     <t xml:space="preserve">1.95853388309479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92109608650208</t>
+    <t xml:space="preserve">1.9210958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94199156761169</t>
+    <t xml:space="preserve">1.9419914484024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95418059825897</t>
+    <t xml:space="preserve">1.95418083667755</t>
   </si>
   <si>
     <t xml:space="preserve">1.93067300319672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88931679725647</t>
+    <t xml:space="preserve">1.88931703567505</t>
   </si>
   <si>
     <t xml:space="preserve">1.86798584461212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89062297344208</t>
+    <t xml:space="preserve">1.89062285423279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9197895526886</t>
+    <t xml:space="preserve">1.91979002952576</t>
   </si>
   <si>
     <t xml:space="preserve">1.94155609607697</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93807315826416</t>
+    <t xml:space="preserve">1.93807363510132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91717779636383</t>
+    <t xml:space="preserve">1.91717791557312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97551143169403</t>
+    <t xml:space="preserve">1.97551167011261</t>
   </si>
   <si>
     <t xml:space="preserve">1.93459057807922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9676753282547</t>
+    <t xml:space="preserve">1.96767556667328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02775049209595</t>
+    <t xml:space="preserve">2.02775025367737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01556205749512</t>
+    <t xml:space="preserve">2.01556158065796</t>
   </si>
   <si>
     <t xml:space="preserve">2.00250148773193</t>
@@ -122,40 +122,40 @@
     <t xml:space="preserve">1.89802360534668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98508894443512</t>
+    <t xml:space="preserve">1.98508846759796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88061046600342</t>
+    <t xml:space="preserve">1.88061058521271</t>
   </si>
   <si>
     <t xml:space="preserve">1.8457840681076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86319720745087</t>
+    <t xml:space="preserve">1.86319756507874</t>
   </si>
   <si>
     <t xml:space="preserve">1.88994169235229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90777158737183</t>
+    <t xml:space="preserve">1.90777170658112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87211215496063</t>
+    <t xml:space="preserve">1.87211227416992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9256010055542</t>
+    <t xml:space="preserve">1.92560112476349</t>
   </si>
   <si>
     <t xml:space="preserve">1.94343090057373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96126019954681</t>
+    <t xml:space="preserve">1.96126043796539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9790894985199</t>
+    <t xml:space="preserve">1.97908997535706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83645272254944</t>
+    <t xml:space="preserve">1.83645308017731</t>
   </si>
   <si>
     <t xml:space="preserve">1.81862318515778</t>
@@ -164,16 +164,16 @@
     <t xml:space="preserve">1.76513433456421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85428261756897</t>
+    <t xml:space="preserve">1.85428237915039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80079352855682</t>
+    <t xml:space="preserve">1.80079364776611</t>
   </si>
   <si>
     <t xml:space="preserve">1.78296387195587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93451583385468</t>
+    <t xml:space="preserve">1.93451595306396</t>
   </si>
   <si>
     <t xml:space="preserve">1.95234560966492</t>
@@ -185,88 +185,88 @@
     <t xml:space="preserve">1.89885699748993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82753789424896</t>
+    <t xml:space="preserve">1.82753777503967</t>
   </si>
   <si>
     <t xml:space="preserve">1.84536778926849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86319708824158</t>
+    <t xml:space="preserve">1.86319720745087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7294750213623</t>
+    <t xml:space="preserve">1.72947490215302</t>
   </si>
   <si>
     <t xml:space="preserve">1.77404892444611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76959180831909</t>
+    <t xml:space="preserve">1.7695916891098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79187870025635</t>
+    <t xml:space="preserve">1.79187881946564</t>
   </si>
   <si>
     <t xml:space="preserve">1.8097083568573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77850639820099</t>
+    <t xml:space="preserve">1.77850651741028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70718777179718</t>
+    <t xml:space="preserve">1.70718789100647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72501766681671</t>
+    <t xml:space="preserve">1.72501742839813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74730467796326</t>
+    <t xml:space="preserve">1.74730479717255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73839008808136</t>
+    <t xml:space="preserve">1.73838984966278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75621962547302</t>
+    <t xml:space="preserve">1.75621950626373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71164536476135</t>
+    <t xml:space="preserve">1.71164524555206</t>
   </si>
   <si>
     <t xml:space="preserve">1.72056007385254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6938157081604</t>
+    <t xml:space="preserve">1.69381582736969</t>
   </si>
   <si>
     <t xml:space="preserve">1.64032673835754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64924168586731</t>
+    <t xml:space="preserve">1.64924156665802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67598605155945</t>
+    <t xml:space="preserve">1.67598617076874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56900835037231</t>
+    <t xml:space="preserve">1.56900823116302</t>
   </si>
   <si>
     <t xml:space="preserve">1.66707134246826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63141214847565</t>
+    <t xml:space="preserve">1.63141202926636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6581563949585</t>
+    <t xml:space="preserve">1.65815651416779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68490087985992</t>
+    <t xml:space="preserve">1.68490099906921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70273053646088</t>
+    <t xml:space="preserve">1.7027302980423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61358213424683</t>
+    <t xml:space="preserve">1.61358225345612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03257894515991</t>
+    <t xml:space="preserve">2.03257846832275</t>
   </si>
   <si>
     <t xml:space="preserve">2.19304585456848</t>
@@ -275,73 +275,73 @@
     <t xml:space="preserve">2.13955664634705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3891716003418</t>
+    <t xml:space="preserve">2.38917207717896</t>
   </si>
   <si>
     <t xml:space="preserve">2.33568263053894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54963850975037</t>
+    <t xml:space="preserve">2.54963827133179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58529758453369</t>
+    <t xml:space="preserve">2.58529782295227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03103876113892</t>
+    <t xml:space="preserve">3.03103852272034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42329072952271</t>
+    <t xml:space="preserve">3.42329049110413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22716426849365</t>
+    <t xml:space="preserve">3.22716450691223</t>
   </si>
   <si>
     <t xml:space="preserve">3.19150543212891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13801670074463</t>
+    <t xml:space="preserve">3.13801646232605</t>
   </si>
   <si>
     <t xml:space="preserve">3.01320934295654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99537944793701</t>
+    <t xml:space="preserve">2.99537897109985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97754979133606</t>
+    <t xml:space="preserve">2.97754955291748</t>
   </si>
   <si>
     <t xml:space="preserve">3.08452773094177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8884015083313</t>
+    <t xml:space="preserve">2.88840174674988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71010518074036</t>
+    <t xml:space="preserve">2.71010494232178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6922755241394</t>
+    <t xml:space="preserve">2.69227576255798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67444586753845</t>
+    <t xml:space="preserve">2.67444634437561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79925346374512</t>
+    <t xml:space="preserve">2.79925322532654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83491253852844</t>
+    <t xml:space="preserve">2.83491277694702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90623116493225</t>
+    <t xml:space="preserve">2.90623140335083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78142356872559</t>
+    <t xml:space="preserve">2.78142333030701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87057209014893</t>
+    <t xml:space="preserve">2.8705723285675</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00555181503296</t>
+    <t xml:space="preserve">3.00555157661438</t>
   </si>
   <si>
     <t xml:space="preserve">3.0775408744812</t>
@@ -350,25 +350,25 @@
     <t xml:space="preserve">2.98755431175232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05954360961914</t>
+    <t xml:space="preserve">3.05954337120056</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14952993392944</t>
+    <t xml:space="preserve">3.14953017234802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2035219669342</t>
+    <t xml:space="preserve">3.20352220535278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32950353622437</t>
+    <t xml:space="preserve">3.32950329780579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38349533081055</t>
+    <t xml:space="preserve">3.38349556922913</t>
   </si>
   <si>
     <t xml:space="preserve">3.36549806594849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34750056266785</t>
+    <t xml:space="preserve">3.34750080108643</t>
   </si>
   <si>
     <t xml:space="preserve">3.2755115032196</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">3.31150603294373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29350900650024</t>
+    <t xml:space="preserve">3.29350876808167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41948986053467</t>
+    <t xml:space="preserve">3.41949009895325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25751376152039</t>
+    <t xml:space="preserve">3.25751399993896</t>
   </si>
   <si>
     <t xml:space="preserve">3.2395167350769</t>
@@ -392,10 +392,10 @@
     <t xml:space="preserve">3.22151947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40149259567261</t>
+    <t xml:space="preserve">3.40149283409119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43748736381531</t>
+    <t xml:space="preserve">3.43748688697815</t>
   </si>
   <si>
     <t xml:space="preserve">3.65345501899719</t>
@@ -404,13 +404,13 @@
     <t xml:space="preserve">3.56346869468689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63545775413513</t>
+    <t xml:space="preserve">3.63545799255371</t>
   </si>
   <si>
     <t xml:space="preserve">3.86942291259766</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99540328979492</t>
+    <t xml:space="preserve">3.99540424346924</t>
   </si>
   <si>
     <t xml:space="preserve">4.0134015083313</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">3.94141221046448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76143860816956</t>
+    <t xml:space="preserve">3.76143884658813</t>
   </si>
   <si>
     <t xml:space="preserve">3.923415184021</t>
@@ -428,22 +428,22 @@
     <t xml:space="preserve">3.9774067401886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88742017745972</t>
+    <t xml:space="preserve">3.8874204158783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85142588615417</t>
+    <t xml:space="preserve">3.85142612457275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90541744232178</t>
+    <t xml:space="preserve">3.90541768074036</t>
   </si>
   <si>
     <t xml:space="preserve">4.17537689208984</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15737962722778</t>
+    <t xml:space="preserve">4.15737915039062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24736595153809</t>
+    <t xml:space="preserve">4.24736642837524</t>
   </si>
   <si>
     <t xml:space="preserve">4.35535097122192</t>
@@ -455,46 +455,46 @@
     <t xml:space="preserve">4.31935548782349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30135869979858</t>
+    <t xml:space="preserve">4.30135917663574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32852506637573</t>
+    <t xml:space="preserve">4.32852458953857</t>
   </si>
   <si>
     <t xml:space="preserve">4.3466362953186</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23796987533569</t>
+    <t xml:space="preserve">4.23796939849854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20174789428711</t>
+    <t xml:space="preserve">4.20174741744995</t>
   </si>
   <si>
     <t xml:space="preserve">4.21985912322998</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12930345535278</t>
+    <t xml:space="preserve">4.1293044090271</t>
   </si>
   <si>
     <t xml:space="preserve">4.05685997009277</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16552639007568</t>
+    <t xml:space="preserve">4.16552591323853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09308195114136</t>
+    <t xml:space="preserve">4.0930814743042</t>
   </si>
   <si>
     <t xml:space="preserve">4.43719053268433</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29230260848999</t>
+    <t xml:space="preserve">4.29230213165283</t>
   </si>
   <si>
     <t xml:space="preserve">4.11119318008423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25608015060425</t>
+    <t xml:space="preserve">4.25608062744141</t>
   </si>
   <si>
     <t xml:space="preserve">4.41907930374146</t>
@@ -503,52 +503,52 @@
     <t xml:space="preserve">4.14741468429565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07497072219849</t>
+    <t xml:space="preserve">4.07497119903564</t>
   </si>
   <si>
     <t xml:space="preserve">4.02063798904419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9481942653656</t>
+    <t xml:space="preserve">3.94819474220276</t>
   </si>
   <si>
     <t xml:space="preserve">3.93008327484131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89386177062988</t>
+    <t xml:space="preserve">3.89386129379272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98441600799561</t>
+    <t xml:space="preserve">3.98441648483276</t>
   </si>
   <si>
     <t xml:space="preserve">4.03874921798706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91197323799133</t>
+    <t xml:space="preserve">3.91197228431702</t>
   </si>
   <si>
     <t xml:space="preserve">3.87575054168701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74897336959839</t>
+    <t xml:space="preserve">3.74897360801697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8214168548584</t>
+    <t xml:space="preserve">3.82141709327698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83952784538269</t>
+    <t xml:space="preserve">3.83952832221985</t>
   </si>
   <si>
     <t xml:space="preserve">3.62219667434692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73086190223694</t>
+    <t xml:space="preserve">3.73086166381836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65841865539551</t>
+    <t xml:space="preserve">3.65841841697693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78519511222839</t>
+    <t xml:space="preserve">3.78519487380981</t>
   </si>
   <si>
     <t xml:space="preserve">4.00252676010132</t>
@@ -560,28 +560,28 @@
     <t xml:space="preserve">4.31041431427002</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96630573272705</t>
+    <t xml:space="preserve">3.96630525588989</t>
   </si>
   <si>
     <t xml:space="preserve">3.80330634117126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7127513885498</t>
+    <t xml:space="preserve">3.71275115013123</t>
   </si>
   <si>
     <t xml:space="preserve">3.44108653068542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53164196014404</t>
+    <t xml:space="preserve">3.53164172172546</t>
   </si>
   <si>
     <t xml:space="preserve">3.4954195022583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38675379753113</t>
+    <t xml:space="preserve">3.38675355911255</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15131092071533</t>
+    <t xml:space="preserve">3.15131115913391</t>
   </si>
   <si>
     <t xml:space="preserve">2.73475861549377</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">2.58987045288086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77098035812378</t>
+    <t xml:space="preserve">2.7709801197052</t>
   </si>
   <si>
     <t xml:space="preserve">2.89775705337524</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">3.13319993019104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33242082595825</t>
+    <t xml:space="preserve">3.33242058753967</t>
   </si>
   <si>
     <t xml:space="preserve">3.36864280700684</t>
@@ -626,13 +626,13 @@
     <t xml:space="preserve">3.22375464439392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56786370277405</t>
+    <t xml:space="preserve">3.56786346435547</t>
   </si>
   <si>
     <t xml:space="preserve">3.54975271224976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55880808830261</t>
+    <t xml:space="preserve">3.55880832672119</t>
   </si>
   <si>
     <t xml:space="preserve">3.51353073120117</t>
@@ -641,10 +641,10 @@
     <t xml:space="preserve">3.45014190673828</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42297554016113</t>
+    <t xml:space="preserve">3.42297577857971</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35053181648254</t>
+    <t xml:space="preserve">3.35053205490112</t>
   </si>
   <si>
     <t xml:space="preserve">3.4139199256897</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">3.25092101097107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32336568832397</t>
+    <t xml:space="preserve">3.3233654499054</t>
   </si>
   <si>
     <t xml:space="preserve">3.33267426490784</t>
@@ -711,9 +711,6 @@
   </si>
   <si>
     <t xml:space="preserve">3.37922048568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3233654499054</t>
   </si>
   <si>
     <t xml:space="preserve">3.44438433647156</t>
@@ -23759,7 +23756,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G847" t="s">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -23785,7 +23782,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G848" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -23811,7 +23808,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G849" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -23863,7 +23860,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G851" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -23889,7 +23886,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G852" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -23915,7 +23912,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G853" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -23941,7 +23938,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G854" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -23967,7 +23964,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G855" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -23993,7 +23990,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G856" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24019,7 +24016,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G857" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -24045,7 +24042,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G858" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -24071,7 +24068,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G859" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -24097,7 +24094,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G860" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -24123,7 +24120,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G861" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -24175,7 +24172,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G863" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -24227,7 +24224,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G865" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -24253,7 +24250,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G866" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -24305,7 +24302,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G868" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -24331,7 +24328,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G869" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -24357,7 +24354,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G870" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -24383,7 +24380,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G871" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -24409,7 +24406,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G872" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -24435,7 +24432,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G873" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -24487,7 +24484,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G875" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -24591,7 +24588,7 @@
         <v>4</v>
       </c>
       <c r="G879" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -24617,7 +24614,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G880" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -24695,7 +24692,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G883" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -24799,7 +24796,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G887" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -24825,7 +24822,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G888" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -24929,7 +24926,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G892" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -24981,7 +24978,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G894" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -25007,7 +25004,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G895" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -25033,7 +25030,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G896" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -25059,7 +25056,7 @@
         <v>4</v>
       </c>
       <c r="G897" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -25137,7 +25134,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G900" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -25163,7 +25160,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G901" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -25189,7 +25186,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G902" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -25241,7 +25238,7 @@
         <v>4</v>
       </c>
       <c r="G904" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -25267,7 +25264,7 @@
         <v>4</v>
       </c>
       <c r="G905" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -25319,7 +25316,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G907" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -25345,7 +25342,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G908" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -25371,7 +25368,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G909" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -25397,7 +25394,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G910" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -25423,7 +25420,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G911" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -25475,7 +25472,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G913" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -25501,7 +25498,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G914" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -25631,7 +25628,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G919" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -25709,7 +25706,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G922" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -25735,7 +25732,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G923" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -25761,7 +25758,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G924" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -25787,7 +25784,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G925" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -25813,7 +25810,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G926" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -25839,7 +25836,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G927" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -25865,7 +25862,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G928" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -25891,7 +25888,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G929" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -25917,7 +25914,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G930" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -25943,7 +25940,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G931" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -25969,7 +25966,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G932" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -25995,7 +25992,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G933" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26021,7 +26018,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G934" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26047,7 +26044,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G935" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26073,7 +26070,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G936" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26099,7 +26096,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G937" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -26151,7 +26148,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G939" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26177,7 +26174,7 @@
         <v>4</v>
       </c>
       <c r="G940" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -26203,7 +26200,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G941" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -26229,7 +26226,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G942" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -26255,7 +26252,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G943" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -26281,7 +26278,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G944" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -26307,7 +26304,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G945" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -26333,7 +26330,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G946" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -26359,7 +26356,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G947" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -26437,7 +26434,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G950" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26489,7 +26486,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G952" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26515,7 +26512,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G953" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26541,7 +26538,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G954" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26567,7 +26564,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G955" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26593,7 +26590,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G956" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26619,7 +26616,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G957" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26645,7 +26642,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G958" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -26671,7 +26668,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G959" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -26697,7 +26694,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G960" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -26723,7 +26720,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G961" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -26749,7 +26746,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G962" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -26775,7 +26772,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G963" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -26801,7 +26798,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G964" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -26827,7 +26824,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G965" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -26853,7 +26850,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G966" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -26879,7 +26876,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G967" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -26905,7 +26902,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G968" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -26931,7 +26928,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G969" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -26957,7 +26954,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G970" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -26983,7 +26980,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G971" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27009,7 +27006,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G972" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27035,7 +27032,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G973" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27061,7 +27058,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G974" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27087,7 +27084,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G975" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -27113,7 +27110,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G976" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27139,7 +27136,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G977" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27165,7 +27162,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G978" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -27191,7 +27188,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G979" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27217,7 +27214,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G980" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27243,7 +27240,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G981" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27269,7 +27266,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G982" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -27295,7 +27292,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G983" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -27321,7 +27318,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G984" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27347,7 +27344,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G985" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -27373,7 +27370,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G986" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -27399,7 +27396,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G987" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -27425,7 +27422,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G988" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -27451,7 +27448,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G989" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -27477,7 +27474,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G990" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -27503,7 +27500,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G991" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -27529,7 +27526,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G992" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -27555,7 +27552,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G993" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -27581,7 +27578,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G994" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -27607,7 +27604,7 @@
         <v>4.5</v>
       </c>
       <c r="G995" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -27633,7 +27630,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G996" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -27659,7 +27656,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G997" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -27685,7 +27682,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G998" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -27711,7 +27708,7 @@
         <v>4.5</v>
       </c>
       <c r="G999" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -27737,7 +27734,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1000" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -27763,7 +27760,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1001" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -27789,7 +27786,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1002" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -27815,7 +27812,7 @@
         <v>4.5</v>
       </c>
       <c r="G1003" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -27841,7 +27838,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1004" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -27867,7 +27864,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1005" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -27893,7 +27890,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1006" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -27919,7 +27916,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1007" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -27945,7 +27942,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1008" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -27971,7 +27968,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1009" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -27997,7 +27994,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1010" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -28023,7 +28020,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1011" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28049,7 +28046,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1012" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28075,7 +28072,7 @@
         <v>4.75</v>
       </c>
       <c r="G1013" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28101,7 +28098,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1014" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28127,7 +28124,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1015" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28153,7 +28150,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1016" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28179,7 +28176,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1017" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -28205,7 +28202,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1018" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -28231,7 +28228,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1019" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -28257,7 +28254,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1020" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28283,7 +28280,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1021" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28309,7 +28306,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1022" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -28335,7 +28332,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1023" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -28361,7 +28358,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1024" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28387,7 +28384,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1025" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28413,7 +28410,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1026" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28439,7 +28436,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1027" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28465,7 +28462,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1028" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28491,7 +28488,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1029" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28517,7 +28514,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1030" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28543,7 +28540,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1031" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28569,7 +28566,7 @@
         <v>4.5</v>
       </c>
       <c r="G1032" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28595,7 +28592,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1033" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28621,7 +28618,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1034" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28647,7 +28644,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1035" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -28673,7 +28670,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1036" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -28699,7 +28696,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1037" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -28725,7 +28722,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1038" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -28751,7 +28748,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1039" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -28777,7 +28774,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1040" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -28803,7 +28800,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1041" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -28829,7 +28826,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1042" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -28855,7 +28852,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1043" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -28881,7 +28878,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1044" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -28907,7 +28904,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1045" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -28933,7 +28930,7 @@
         <v>4.25</v>
       </c>
       <c r="G1046" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -28959,7 +28956,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1047" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -28985,7 +28982,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1048" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29011,7 +29008,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1049" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29037,7 +29034,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1050" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29063,7 +29060,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1051" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29089,7 +29086,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1052" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -29115,7 +29112,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1053" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29141,7 +29138,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1054" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29167,7 +29164,7 @@
         <v>5</v>
       </c>
       <c r="G1055" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29193,7 +29190,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1056" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29219,7 +29216,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29245,7 +29242,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1058" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29271,7 +29268,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1059" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29297,7 +29294,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1060" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29323,7 +29320,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1061" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29349,7 +29346,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1062" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29375,7 +29372,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1063" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29401,7 +29398,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1064" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29427,7 +29424,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1065" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29453,7 +29450,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1066" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29479,7 +29476,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1067" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29505,7 +29502,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1068" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29531,7 +29528,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1069" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29557,7 +29554,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1070" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29583,7 +29580,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1071" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -29609,7 +29606,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1072" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -29635,7 +29632,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1073" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -29661,7 +29658,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1074" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -29687,7 +29684,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1075" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -29713,7 +29710,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1076" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -29739,7 +29736,7 @@
         <v>5.25</v>
       </c>
       <c r="G1077" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -29765,7 +29762,7 @@
         <v>5.25</v>
       </c>
       <c r="G1078" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -29791,7 +29788,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1079" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -29817,7 +29814,7 @@
         <v>5</v>
       </c>
       <c r="G1080" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -29843,7 +29840,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1081" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -29869,7 +29866,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1082" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -29895,7 +29892,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1083" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -29921,7 +29918,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1084" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -29947,7 +29944,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1085" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -29973,7 +29970,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1086" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -29999,7 +29996,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1087" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30025,7 +30022,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1088" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30051,7 +30048,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1089" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -30077,7 +30074,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1090" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30103,7 +30100,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1091" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30129,7 +30126,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1092" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30155,7 +30152,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1093" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30181,7 +30178,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1094" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -30207,7 +30204,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1095" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -30233,7 +30230,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1096" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -30259,7 +30256,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1097" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -30285,7 +30282,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1098" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -30311,7 +30308,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1099" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -30337,7 +30334,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1100" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -30363,7 +30360,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1101" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -30389,7 +30386,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1102" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -30415,7 +30412,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1103" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -30441,7 +30438,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1104" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -30467,7 +30464,7 @@
         <v>5.25</v>
       </c>
       <c r="G1105" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -30493,7 +30490,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1106" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30519,7 +30516,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1107" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30545,7 +30542,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1108" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -30571,7 +30568,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1109" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -30597,7 +30594,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1110" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -30623,7 +30620,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1111" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -30649,7 +30646,7 @@
         <v>6</v>
       </c>
       <c r="G1112" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -30675,7 +30672,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1113" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -30701,7 +30698,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1114" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -30727,7 +30724,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -30753,7 +30750,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1116" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -30779,7 +30776,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1117" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -30805,7 +30802,7 @@
         <v>5.5</v>
       </c>
       <c r="G1118" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -30831,7 +30828,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1119" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -30857,7 +30854,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1120" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -30883,7 +30880,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1121" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -30909,7 +30906,7 @@
         <v>5.5</v>
       </c>
       <c r="G1122" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -30935,7 +30932,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1123" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -30961,7 +30958,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1124" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -30987,7 +30984,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1125" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31013,7 +31010,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1126" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31039,7 +31036,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1127" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31065,7 +31062,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1128" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31091,7 +31088,7 @@
         <v>5.5</v>
       </c>
       <c r="G1129" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31117,7 +31114,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1130" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31143,7 +31140,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1131" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31169,7 +31166,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1132" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31195,7 +31192,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1133" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31221,7 +31218,7 @@
         <v>5.5</v>
       </c>
       <c r="G1134" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31247,7 +31244,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1135" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31273,7 +31270,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1136" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31299,7 +31296,7 @@
         <v>5.5</v>
       </c>
       <c r="G1137" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31325,7 +31322,7 @@
         <v>5.5</v>
       </c>
       <c r="G1138" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31351,7 +31348,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1139" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31377,7 +31374,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1140" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31403,7 +31400,7 @@
         <v>5.25</v>
       </c>
       <c r="G1141" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31429,7 +31426,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1142" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31455,7 +31452,7 @@
         <v>5.25</v>
       </c>
       <c r="G1143" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31481,7 +31478,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1144" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31507,7 +31504,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1145" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31533,7 +31530,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1146" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31559,7 +31556,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1147" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31585,7 +31582,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1148" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31611,7 +31608,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1149" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -31637,7 +31634,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1150" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -31663,7 +31660,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1151" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -31689,7 +31686,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1152" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -31715,7 +31712,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1153" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -31741,7 +31738,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1154" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -31767,7 +31764,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1155" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -31793,7 +31790,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1156" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -31819,7 +31816,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1157" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -31845,7 +31842,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1158" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -31871,7 +31868,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1159" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -31897,7 +31894,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1160" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -31923,7 +31920,7 @@
         <v>5.25</v>
       </c>
       <c r="G1161" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -31949,7 +31946,7 @@
         <v>5.25</v>
       </c>
       <c r="G1162" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -31975,7 +31972,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1163" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32001,7 +31998,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1164" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32027,7 +32024,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1165" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32053,7 +32050,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1166" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -32079,7 +32076,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1167" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -32105,7 +32102,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1168" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -32131,7 +32128,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1169" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -32157,7 +32154,7 @@
         <v>5</v>
       </c>
       <c r="G1170" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -32183,7 +32180,7 @@
         <v>5</v>
       </c>
       <c r="G1171" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -32209,7 +32206,7 @@
         <v>5</v>
       </c>
       <c r="G1172" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -32235,7 +32232,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1173" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -32261,7 +32258,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1174" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -32287,7 +32284,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1175" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -32313,7 +32310,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1176" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -32339,7 +32336,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1177" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -32365,7 +32362,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1178" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -32391,7 +32388,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1179" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -32417,7 +32414,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1180" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -32443,7 +32440,7 @@
         <v>5.25</v>
       </c>
       <c r="G1181" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -32469,7 +32466,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1182" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -32495,7 +32492,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1183" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -32521,7 +32518,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1184" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -32547,7 +32544,7 @@
         <v>5.25</v>
       </c>
       <c r="G1185" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -32573,7 +32570,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1186" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -32599,7 +32596,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1187" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -32625,7 +32622,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1188" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -32651,7 +32648,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1189" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -32677,7 +32674,7 @@
         <v>5</v>
       </c>
       <c r="G1190" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -32703,7 +32700,7 @@
         <v>5</v>
       </c>
       <c r="G1191" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -32729,7 +32726,7 @@
         <v>5</v>
       </c>
       <c r="G1192" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -32755,7 +32752,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1193" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -32781,7 +32778,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1194" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -32807,7 +32804,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1195" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -32833,7 +32830,7 @@
         <v>5</v>
       </c>
       <c r="G1196" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -32859,7 +32856,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1197" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -32885,7 +32882,7 @@
         <v>5</v>
       </c>
       <c r="G1198" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -32911,7 +32908,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1199" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -32937,7 +32934,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1200" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -32963,7 +32960,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1201" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -32989,7 +32986,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1202" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33015,7 +33012,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1203" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33041,7 +33038,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1204" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -33067,7 +33064,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1205" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -33093,7 +33090,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1206" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -33119,7 +33116,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1207" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -33145,7 +33142,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1208" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -33171,7 +33168,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1209" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -33197,7 +33194,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1210" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -33223,7 +33220,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1211" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -33249,7 +33246,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1212" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -33275,7 +33272,7 @@
         <v>5</v>
       </c>
       <c r="G1213" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -33301,7 +33298,7 @@
         <v>5</v>
       </c>
       <c r="G1214" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -33327,7 +33324,7 @@
         <v>5</v>
       </c>
       <c r="G1215" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -33353,7 +33350,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1216" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -33379,7 +33376,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1217" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -33405,7 +33402,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1218" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -33431,7 +33428,7 @@
         <v>5</v>
       </c>
       <c r="G1219" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -33457,7 +33454,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1220" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -33483,7 +33480,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1221" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -33509,7 +33506,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1222" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -33535,7 +33532,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1223" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -33561,7 +33558,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1224" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -33587,7 +33584,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1225" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -33613,7 +33610,7 @@
         <v>5</v>
       </c>
       <c r="G1226" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -33639,7 +33636,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1227" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -33665,7 +33662,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1228" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -33691,7 +33688,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1229" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -33717,7 +33714,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1230" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -33743,7 +33740,7 @@
         <v>5</v>
       </c>
       <c r="G1231" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -33769,7 +33766,7 @@
         <v>5</v>
       </c>
       <c r="G1232" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -33795,7 +33792,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1233" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -33821,7 +33818,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1234" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -33847,7 +33844,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1235" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -33873,7 +33870,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1236" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -33899,7 +33896,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1237" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -33925,7 +33922,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1238" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -33951,7 +33948,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1239" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -33977,7 +33974,7 @@
         <v>5</v>
       </c>
       <c r="G1240" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -34003,7 +34000,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1241" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34029,7 +34026,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1242" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -34055,7 +34052,7 @@
         <v>5</v>
       </c>
       <c r="G1243" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -34081,7 +34078,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1244" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -34107,7 +34104,7 @@
         <v>5</v>
       </c>
       <c r="G1245" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34133,7 +34130,7 @@
         <v>5</v>
       </c>
       <c r="G1246" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34159,7 +34156,7 @@
         <v>5</v>
       </c>
       <c r="G1247" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -34185,7 +34182,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1248" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -34211,7 +34208,7 @@
         <v>5</v>
       </c>
       <c r="G1249" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -34237,7 +34234,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1250" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -34263,7 +34260,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1251" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -34289,7 +34286,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1252" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -34315,7 +34312,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1253" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -34341,7 +34338,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1254" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -34367,7 +34364,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1255" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -34393,7 +34390,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1256" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -34419,7 +34416,7 @@
         <v>5</v>
       </c>
       <c r="G1257" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -34445,7 +34442,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1258" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -34471,7 +34468,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1259" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -34497,7 +34494,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1260" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -34523,7 +34520,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1261" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -34549,7 +34546,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1262" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -34575,7 +34572,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1263" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -34601,7 +34598,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1264" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -34627,7 +34624,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1265" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -34653,7 +34650,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1266" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -34679,7 +34676,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1267" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -34705,7 +34702,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1268" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -34731,7 +34728,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1269" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -34757,7 +34754,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1270" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -34783,7 +34780,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1271" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -34809,7 +34806,7 @@
         <v>5</v>
       </c>
       <c r="G1272" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -34835,7 +34832,7 @@
         <v>5</v>
       </c>
       <c r="G1273" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -34861,7 +34858,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1274" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -34887,7 +34884,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1275" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -34913,7 +34910,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1276" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -34939,7 +34936,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1277" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -34965,7 +34962,7 @@
         <v>5</v>
       </c>
       <c r="G1278" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -34991,7 +34988,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1279" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35017,7 +35014,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1280" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -35043,7 +35040,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1281" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -35069,7 +35066,7 @@
         <v>5</v>
       </c>
       <c r="G1282" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -35095,7 +35092,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1283" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -35121,7 +35118,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1284" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -35147,7 +35144,7 @@
         <v>5</v>
       </c>
       <c r="G1285" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -35173,7 +35170,7 @@
         <v>5</v>
       </c>
       <c r="G1286" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -35199,7 +35196,7 @@
         <v>5</v>
       </c>
       <c r="G1287" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -35225,7 +35222,7 @@
         <v>5</v>
       </c>
       <c r="G1288" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -35251,7 +35248,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1289" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -35277,7 +35274,7 @@
         <v>5</v>
       </c>
       <c r="G1290" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35303,7 +35300,7 @@
         <v>5</v>
       </c>
       <c r="G1291" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35329,7 +35326,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1292" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35355,7 +35352,7 @@
         <v>5</v>
       </c>
       <c r="G1293" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35381,7 +35378,7 @@
         <v>5</v>
       </c>
       <c r="G1294" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35407,7 +35404,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1295" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35433,7 +35430,7 @@
         <v>5</v>
       </c>
       <c r="G1296" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35459,7 +35456,7 @@
         <v>5</v>
       </c>
       <c r="G1297" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -35485,7 +35482,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1298" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35511,7 +35508,7 @@
         <v>5</v>
       </c>
       <c r="G1299" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35537,7 +35534,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1300" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35563,7 +35560,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1301" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -35589,7 +35586,7 @@
         <v>5</v>
       </c>
       <c r="G1302" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35615,7 +35612,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1303" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35641,7 +35638,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1304" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -35667,7 +35664,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1305" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -35693,7 +35690,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1306" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -35719,7 +35716,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1307" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -35745,7 +35742,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1308" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -35771,7 +35768,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1309" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -35797,7 +35794,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1310" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -35823,7 +35820,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1311" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -35849,7 +35846,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1312" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -35875,7 +35872,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1313" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -35901,7 +35898,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1314" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -35927,7 +35924,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1315" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -35953,7 +35950,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1316" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -35979,7 +35976,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1317" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -36005,7 +36002,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1318" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36031,7 +36028,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1319" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -36057,7 +36054,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1320" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36083,7 +36080,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1321" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -36109,7 +36106,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1322" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -36135,7 +36132,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1323" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -36161,7 +36158,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1324" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -36187,7 +36184,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1325" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -36213,7 +36210,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1326" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -36239,7 +36236,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1327" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -36265,7 +36262,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1328" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -36291,7 +36288,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1329" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -36317,7 +36314,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1330" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -36343,7 +36340,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1331" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -36369,7 +36366,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1332" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -36395,7 +36392,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1333" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -36421,7 +36418,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1334" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -36447,7 +36444,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1335" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -36473,7 +36470,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1336" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -36499,7 +36496,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1337" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -36525,7 +36522,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1338" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -36551,7 +36548,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1339" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -36577,7 +36574,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1340" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -36603,7 +36600,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1341" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -36629,7 +36626,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1342" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -36655,7 +36652,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1343" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -36681,7 +36678,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1344" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -36707,7 +36704,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1345" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -36733,7 +36730,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1346" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -36759,7 +36756,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1347" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -36785,7 +36782,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1348" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -36811,7 +36808,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1349" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -36837,7 +36834,7 @@
         <v>5.5</v>
       </c>
       <c r="G1350" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -36863,7 +36860,7 @@
         <v>5.5</v>
       </c>
       <c r="G1351" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -36889,7 +36886,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1352" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -36915,7 +36912,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1353" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -36941,7 +36938,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1354" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -36967,7 +36964,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1355" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -36993,7 +36990,7 @@
         <v>5.5</v>
       </c>
       <c r="G1356" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37019,7 +37016,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1357" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37045,7 +37042,7 @@
         <v>5.5</v>
       </c>
       <c r="G1358" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -37071,7 +37068,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1359" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37097,7 +37094,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1360" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37123,7 +37120,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1361" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -37149,7 +37146,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1362" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37175,7 +37172,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1363" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -37201,7 +37198,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1364" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -37227,7 +37224,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1365" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -37253,7 +37250,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1366" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -37279,7 +37276,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1367" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -37305,7 +37302,7 @@
         <v>5.75</v>
       </c>
       <c r="G1368" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -37331,7 +37328,7 @@
         <v>5.75</v>
       </c>
       <c r="G1369" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -37357,7 +37354,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1370" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -37383,7 +37380,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1371" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -37409,7 +37406,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1372" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -37435,7 +37432,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1373" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -37461,7 +37458,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1374" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -37487,7 +37484,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1375" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -37513,7 +37510,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1376" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -37539,7 +37536,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1377" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -37565,7 +37562,7 @@
         <v>5.5</v>
       </c>
       <c r="G1378" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -37591,7 +37588,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1379" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -37617,7 +37614,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1380" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -37643,7 +37640,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1381" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -37669,7 +37666,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1382" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -37695,7 +37692,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1383" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -37721,7 +37718,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1384" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -37747,7 +37744,7 @@
         <v>5.5</v>
       </c>
       <c r="G1385" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -37773,7 +37770,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1386" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -37799,7 +37796,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1387" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -37825,7 +37822,7 @@
         <v>5.25</v>
       </c>
       <c r="G1388" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -37851,7 +37848,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1389" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -37877,7 +37874,7 @@
         <v>5.25</v>
       </c>
       <c r="G1390" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -37903,7 +37900,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1391" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -37929,7 +37926,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1392" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -37955,7 +37952,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1393" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -37981,7 +37978,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1394" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38007,7 +38004,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1395" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38033,7 +38030,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1396" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38059,7 +38056,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1397" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38085,7 +38082,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1398" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -38111,7 +38108,7 @@
         <v>5</v>
       </c>
       <c r="G1399" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -38137,7 +38134,7 @@
         <v>5</v>
       </c>
       <c r="G1400" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -38163,7 +38160,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1401" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -38189,7 +38186,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1402" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -38215,7 +38212,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1403" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -38241,7 +38238,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1404" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -38267,7 +38264,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1405" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -38293,7 +38290,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1406" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -38319,7 +38316,7 @@
         <v>5.25</v>
       </c>
       <c r="G1407" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -38345,7 +38342,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1408" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -38371,7 +38368,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1409" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -38397,7 +38394,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1410" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -38423,7 +38420,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1411" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38449,7 +38446,7 @@
         <v>5.25</v>
       </c>
       <c r="G1412" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -38475,7 +38472,7 @@
         <v>5.25</v>
       </c>
       <c r="G1413" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -38501,7 +38498,7 @@
         <v>5.25</v>
       </c>
       <c r="G1414" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -38527,7 +38524,7 @@
         <v>5.25</v>
       </c>
       <c r="G1415" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -38553,7 +38550,7 @@
         <v>5.25</v>
       </c>
       <c r="G1416" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -38579,7 +38576,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1417" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -38605,7 +38602,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1418" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -38631,7 +38628,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1419" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -38657,7 +38654,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1420" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -38683,7 +38680,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1421" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -38709,7 +38706,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1422" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -38735,7 +38732,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1423" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -38761,7 +38758,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1424" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -38787,7 +38784,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1425" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -38813,7 +38810,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1426" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -38839,7 +38836,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1427" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -38865,7 +38862,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1428" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -38891,7 +38888,7 @@
         <v>5.25</v>
       </c>
       <c r="G1429" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -38917,7 +38914,7 @@
         <v>5.25</v>
       </c>
       <c r="G1430" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -38943,7 +38940,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1431" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -38969,7 +38966,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1432" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -38995,7 +38992,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1433" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39021,7 +39018,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1434" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39047,7 +39044,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1435" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -39073,7 +39070,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1436" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -39099,7 +39096,7 @@
         <v>5</v>
       </c>
       <c r="G1437" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39125,7 +39122,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1438" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39151,7 +39148,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1439" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39177,7 +39174,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1440" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -39203,7 +39200,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1441" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -39229,7 +39226,7 @@
         <v>5</v>
       </c>
       <c r="G1442" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39255,7 +39252,7 @@
         <v>5</v>
       </c>
       <c r="G1443" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -39281,7 +39278,7 @@
         <v>5</v>
       </c>
       <c r="G1444" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -39307,7 +39304,7 @@
         <v>5</v>
       </c>
       <c r="G1445" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -39333,7 +39330,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1446" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -39359,7 +39356,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1447" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -39385,7 +39382,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1448" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -39411,7 +39408,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1449" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39437,7 +39434,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1450" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39463,7 +39460,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1451" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39489,7 +39486,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1452" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39515,7 +39512,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1453" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39541,7 +39538,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1454" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39567,7 +39564,7 @@
         <v>5</v>
       </c>
       <c r="G1455" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39593,7 +39590,7 @@
         <v>5</v>
       </c>
       <c r="G1456" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39619,7 +39616,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1457" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39645,7 +39642,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1458" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39671,7 +39668,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1459" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39697,7 +39694,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1460" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -39723,7 +39720,7 @@
         <v>5</v>
       </c>
       <c r="G1461" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -39749,7 +39746,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1462" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -39775,7 +39772,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1463" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -39801,7 +39798,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1464" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -39827,7 +39824,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1465" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -39853,7 +39850,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1466" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -39879,7 +39876,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1467" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -39905,7 +39902,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1468" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -39931,7 +39928,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1469" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -39957,7 +39954,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1470" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -39983,7 +39980,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1471" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40009,7 +40006,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1472" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40035,7 +40032,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1473" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40061,7 +40058,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1474" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40087,7 +40084,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1475" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -40113,7 +40110,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1476" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -40139,7 +40136,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1477" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -40165,7 +40162,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1478" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -40191,7 +40188,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1479" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -40217,7 +40214,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1480" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -40243,7 +40240,7 @@
         <v>4.5</v>
       </c>
       <c r="G1481" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -40269,7 +40266,7 @@
         <v>4.5</v>
       </c>
       <c r="G1482" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -40295,7 +40292,7 @@
         <v>4.5</v>
       </c>
       <c r="G1483" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -40321,7 +40318,7 @@
         <v>4.5</v>
       </c>
       <c r="G1484" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -40347,7 +40344,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1485" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -40373,7 +40370,7 @@
         <v>4.5</v>
       </c>
       <c r="G1486" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -40399,7 +40396,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1487" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -40425,7 +40422,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1488" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40451,7 +40448,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1489" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40477,7 +40474,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1490" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40503,7 +40500,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1491" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40529,7 +40526,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1492" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -40555,7 +40552,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1493" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40581,7 +40578,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1494" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -40607,7 +40604,7 @@
         <v>4.5</v>
       </c>
       <c r="G1495" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -40633,7 +40630,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1496" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -40659,7 +40656,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1497" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -40685,7 +40682,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1498" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -40711,7 +40708,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1499" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -40737,7 +40734,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1500" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -40763,7 +40760,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1501" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -40789,7 +40786,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1502" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -40815,7 +40812,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1503" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -40841,7 +40838,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1504" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -40867,7 +40864,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1505" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -40893,7 +40890,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1506" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -40919,7 +40916,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1507" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -40945,7 +40942,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1508" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -40971,7 +40968,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1509" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -40997,7 +40994,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1510" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41023,7 +41020,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1511" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41049,7 +41046,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1512" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41075,7 +41072,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1513" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41101,7 +41098,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1514" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41127,7 +41124,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1515" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41153,7 +41150,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1516" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41179,7 +41176,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1517" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -41205,7 +41202,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1518" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -41231,7 +41228,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1519" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41257,7 +41254,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1520" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -41283,7 +41280,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1521" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -41309,7 +41306,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1522" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -41335,7 +41332,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1523" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -41361,7 +41358,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1524" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -41387,7 +41384,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1525" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -41413,7 +41410,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1526" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41439,7 +41436,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1527" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41465,7 +41462,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1528" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41491,7 +41488,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1529" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41517,7 +41514,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1530" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41543,7 +41540,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1531" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41569,7 +41566,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1532" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41595,7 +41592,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1533" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41621,7 +41618,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1534" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41647,7 +41644,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1535" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41673,7 +41670,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1536" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41699,7 +41696,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1537" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -41725,7 +41722,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1538" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -41751,7 +41748,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1539" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -41777,7 +41774,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1540" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -41803,7 +41800,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1541" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -41829,7 +41826,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1542" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -41855,7 +41852,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1543" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -41881,7 +41878,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1544" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -41907,7 +41904,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1545" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -41933,7 +41930,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1546" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -41959,7 +41956,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1547" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -41985,7 +41982,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1548" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42011,7 +42008,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1549" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42037,7 +42034,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1550" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42063,7 +42060,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1551" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42089,7 +42086,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1552" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42115,7 +42112,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1553" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42141,7 +42138,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1554" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42167,7 +42164,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1555" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42193,7 +42190,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1556" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42219,7 +42216,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1557" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -42245,7 +42242,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1558" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -42271,7 +42268,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1559" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -42297,7 +42294,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1560" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -42323,7 +42320,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1561" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -42349,7 +42346,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1562" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -42375,7 +42372,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1563" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -42401,7 +42398,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1564" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -42427,7 +42424,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1565" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42453,7 +42450,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1566" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42479,7 +42476,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1567" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42505,7 +42502,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1568" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42531,7 +42528,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1569" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42557,7 +42554,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1570" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42583,7 +42580,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1571" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42609,7 +42606,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1572" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42635,7 +42632,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1573" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42661,7 +42658,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1574" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42687,7 +42684,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1575" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -42713,7 +42710,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1576" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -42739,7 +42736,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1577" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -42765,7 +42762,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1578" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -42791,7 +42788,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1579" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -42817,7 +42814,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1580" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -42843,7 +42840,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1581" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -42869,7 +42866,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1582" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -42895,7 +42892,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1583" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -42921,7 +42918,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1584" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -42947,7 +42944,7 @@
         <v>4.5</v>
       </c>
       <c r="G1585" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -42973,7 +42970,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -42999,7 +42996,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1587" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43025,7 +43022,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1588" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43051,7 +43048,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1589" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43077,7 +43074,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1590" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43103,7 +43100,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1591" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43129,7 +43126,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1592" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43155,7 +43152,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1593" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43181,7 +43178,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1594" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43207,7 +43204,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1595" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -43233,7 +43230,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1596" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43259,7 +43256,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1597" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -43285,7 +43282,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1598" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -43311,7 +43308,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1599" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -43337,7 +43334,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1600" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -43363,7 +43360,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1601" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -43389,7 +43386,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1602" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -43415,7 +43412,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1603" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43441,7 +43438,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1604" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43467,7 +43464,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1605" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43493,7 +43490,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1606" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43519,7 +43516,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1607" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43545,7 +43542,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1608" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43571,7 +43568,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1609" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43597,7 +43594,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1610" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43623,7 +43620,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1611" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43649,7 +43646,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1612" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43675,7 +43672,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1613" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43701,7 +43698,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1614" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43727,7 +43724,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1615" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -43753,7 +43750,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1616" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43779,7 +43776,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1617" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43805,7 +43802,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1618" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43831,7 +43828,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1619" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43857,7 +43854,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1620" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -43883,7 +43880,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1621" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -43909,7 +43906,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1622" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -43935,7 +43932,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1623" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -43961,7 +43958,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1624" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -43987,7 +43984,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1625" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44013,7 +44010,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1626" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44039,7 +44036,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1627" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44065,7 +44062,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1628" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44091,7 +44088,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1629" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44117,7 +44114,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1630" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44143,7 +44140,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1631" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44169,7 +44166,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1632" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44195,7 +44192,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1633" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44221,7 +44218,7 @@
         <v>5.75</v>
       </c>
       <c r="G1634" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44247,7 +44244,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1635" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44273,7 +44270,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1636" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44299,7 +44296,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1637" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44325,7 +44322,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1638" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44351,7 +44348,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1639" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44377,7 +44374,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1640" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44403,7 +44400,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1641" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44429,7 +44426,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1642" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44455,7 +44452,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1643" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44481,7 +44478,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1644" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44507,7 +44504,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1645" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44533,7 +44530,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1646" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44559,7 +44556,7 @@
         <v>5.75</v>
       </c>
       <c r="G1647" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44585,7 +44582,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1648" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44611,7 +44608,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1649" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44637,7 +44634,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1650" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44663,7 +44660,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1651" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44689,7 +44686,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1652" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44715,7 +44712,7 @@
         <v>5.25</v>
       </c>
       <c r="G1653" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44741,7 +44738,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1654" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44767,7 +44764,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1655" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44793,7 +44790,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1656" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44819,7 +44816,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1657" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44845,7 +44842,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1658" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44871,7 +44868,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1659" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -44897,7 +44894,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1660" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44923,7 +44920,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1661" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44949,7 +44946,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1662" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44975,7 +44972,7 @@
         <v>5.5</v>
       </c>
       <c r="G1663" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45001,7 +44998,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1664" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45027,7 +45024,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1665" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45053,7 +45050,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1666" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45079,7 +45076,7 @@
         <v>5.5</v>
       </c>
       <c r="G1667" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45105,7 +45102,7 @@
         <v>5.5</v>
       </c>
       <c r="G1668" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45131,7 +45128,7 @@
         <v>5.5</v>
       </c>
       <c r="G1669" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45157,7 +45154,7 @@
         <v>5.5</v>
       </c>
       <c r="G1670" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45183,7 +45180,7 @@
         <v>5.5</v>
       </c>
       <c r="G1671" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45209,7 +45206,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1672" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45235,7 +45232,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1673" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45261,7 +45258,7 @@
         <v>5.75</v>
       </c>
       <c r="G1674" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45287,7 +45284,7 @@
         <v>5.75</v>
       </c>
       <c r="G1675" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45313,7 +45310,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1676" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45339,7 +45336,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1677" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45365,7 +45362,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1678" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45391,7 +45388,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1679" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45417,7 +45414,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1680" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45443,7 +45440,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1681" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45469,7 +45466,7 @@
         <v>5.75</v>
       </c>
       <c r="G1682" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45495,7 +45492,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1683" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45521,7 +45518,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1684" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45547,7 +45544,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1685" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45573,7 +45570,7 @@
         <v>5.5</v>
       </c>
       <c r="G1686" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45599,7 +45596,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1687" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45625,7 +45622,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1688" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45651,7 +45648,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1689" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45677,7 +45674,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1690" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45703,7 +45700,7 @@
         <v>5.75</v>
       </c>
       <c r="G1691" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45729,7 +45726,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1692" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45755,7 +45752,7 @@
         <v>5.75</v>
       </c>
       <c r="G1693" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45781,7 +45778,7 @@
         <v>5.75</v>
       </c>
       <c r="G1694" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45807,7 +45804,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1695" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45833,7 +45830,7 @@
         <v>6</v>
       </c>
       <c r="G1696" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45859,7 +45856,7 @@
         <v>6</v>
       </c>
       <c r="G1697" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -45885,7 +45882,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1698" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -45911,7 +45908,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1699" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -45937,7 +45934,7 @@
         <v>5.75</v>
       </c>
       <c r="G1700" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -45963,7 +45960,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1701" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -45989,7 +45986,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1702" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46015,7 +46012,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1703" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46041,7 +46038,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1704" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46067,7 +46064,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1705" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46093,7 +46090,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1706" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46119,7 +46116,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1707" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46145,7 +46142,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1708" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46171,7 +46168,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1709" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46197,7 +46194,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1710" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46223,7 +46220,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1711" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46249,7 +46246,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1712" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46275,9 +46272,61 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1713" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1713" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" s="1" t="n">
+        <v>45971.3333333333</v>
+      </c>
+      <c r="B1714" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1714" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="D1714" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="E1714" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="F1714" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="G1714" t="s">
+        <v>458</v>
+      </c>
+      <c r="H1714" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" s="1" t="n">
+        <v>45972.4699884259</v>
+      </c>
+      <c r="B1715" t="n">
+        <v>39600</v>
+      </c>
+      <c r="C1715" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="D1715" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="E1715" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="F1715" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="G1715" t="s">
+        <v>462</v>
+      </c>
+      <c r="H1715" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ILP.MI.xlsx
+++ b/data/ILP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="466">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95026230812073</t>
+    <t xml:space="preserve">1.95026278495789</t>
   </si>
   <si>
     <t xml:space="preserve">ILP.MI</t>
@@ -50,214 +50,214 @@
     <t xml:space="preserve">1.91543650627136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9411209821701</t>
+    <t xml:space="preserve">1.94112062454224</t>
   </si>
   <si>
     <t xml:space="preserve">2.00685524940491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97986471652985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93284964561462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95853388309479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9210958480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9419914484024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95418083667755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93067300319672</t>
+    <t xml:space="preserve">1.97986459732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93284940719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9585337638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92109572887421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94199132919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95418035984039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93067276477814</t>
   </si>
   <si>
     <t xml:space="preserve">1.88931703567505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86798584461212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89062285423279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91979002952576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94155609607697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93807363510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91717791557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97551167011261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93459057807922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96767556667328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02775025367737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01556158065796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00250148773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0199146270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89802360534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98508846759796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88061058521271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8457840681076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86319756507874</t>
+    <t xml:space="preserve">1.8679860830307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8906227350235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9197895526886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94155621528625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93807339668274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91717755794525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97551143169403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93459069728851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9676753282547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02775073051453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01556181907654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00250172615051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01991438865662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89802348613739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98508870601654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88061046600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84578430652618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86319744586945</t>
   </si>
   <si>
     <t xml:space="preserve">1.88994169235229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90777170658112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87211227416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92560112476349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94343090057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96126043796539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97908997535706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83645308017731</t>
+    <t xml:space="preserve">1.90777158737183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87211191654205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9256010055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94343078136444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9612603187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97908973693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83645296096802</t>
   </si>
   <si>
     <t xml:space="preserve">1.81862318515778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76513433456421</t>
+    <t xml:space="preserve">1.76513421535492</t>
   </si>
   <si>
     <t xml:space="preserve">1.85428237915039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80079364776611</t>
+    <t xml:space="preserve">1.80079352855682</t>
   </si>
   <si>
     <t xml:space="preserve">1.78296387195587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93451595306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95234560966492</t>
+    <t xml:space="preserve">1.93451583385468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95234549045563</t>
   </si>
   <si>
     <t xml:space="preserve">1.88102674484253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89885699748993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82753777503967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84536778926849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86319720745087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72947490215302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77404892444611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7695916891098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79187881946564</t>
+    <t xml:space="preserve">1.89885675907135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82753789424896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84536755084991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86319708824158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72947514057159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77404916286469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76959180831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79187870025635</t>
   </si>
   <si>
     <t xml:space="preserve">1.8097083568573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77850651741028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70718789100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72501742839813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74730479717255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73838984966278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75621950626373</t>
+    <t xml:space="preserve">1.77850663661957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70718812942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72501754760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74730455875397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73838973045349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75621962547302</t>
   </si>
   <si>
     <t xml:space="preserve">1.71164524555206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72056007385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69381582736969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64032673835754</t>
+    <t xml:space="preserve">1.72056019306183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6938157081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64032685756683</t>
   </si>
   <si>
     <t xml:space="preserve">1.64924156665802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67598617076874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56900823116302</t>
+    <t xml:space="preserve">1.67598605155945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56900835037231</t>
   </si>
   <si>
     <t xml:space="preserve">1.66707134246826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63141202926636</t>
+    <t xml:space="preserve">1.63141214847565</t>
   </si>
   <si>
     <t xml:space="preserve">1.65815651416779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68490099906921</t>
+    <t xml:space="preserve">1.68490076065063</t>
   </si>
   <si>
     <t xml:space="preserve">1.7027302980423</t>
@@ -266,28 +266,28 @@
     <t xml:space="preserve">1.61358225345612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03257846832275</t>
+    <t xml:space="preserve">2.03257870674133</t>
   </si>
   <si>
     <t xml:space="preserve">2.19304585456848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13955664634705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38917207717896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33568263053894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54963827133179</t>
+    <t xml:space="preserve">2.13955688476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38917183876038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33568286895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54963803291321</t>
   </si>
   <si>
     <t xml:space="preserve">2.58529782295227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03103852272034</t>
+    <t xml:space="preserve">3.03103876113892</t>
   </si>
   <si>
     <t xml:space="preserve">3.42329049110413</t>
@@ -296,34 +296,34 @@
     <t xml:space="preserve">3.22716450691223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19150543212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13801646232605</t>
+    <t xml:space="preserve">3.19150495529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13801670074463</t>
   </si>
   <si>
     <t xml:space="preserve">3.01320934295654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99537897109985</t>
+    <t xml:space="preserve">2.99537920951843</t>
   </si>
   <si>
     <t xml:space="preserve">2.97754955291748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08452773094177</t>
+    <t xml:space="preserve">3.08452796936035</t>
   </si>
   <si>
     <t xml:space="preserve">2.88840174674988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71010494232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69227576255798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67444634437561</t>
+    <t xml:space="preserve">2.71010541915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6922755241394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67444562911987</t>
   </si>
   <si>
     <t xml:space="preserve">2.79925322532654</t>
@@ -332,37 +332,37 @@
     <t xml:space="preserve">2.83491277694702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90623140335083</t>
+    <t xml:space="preserve">2.90623116493225</t>
   </si>
   <si>
     <t xml:space="preserve">2.78142333030701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8705723285675</t>
+    <t xml:space="preserve">2.87057185173035</t>
   </si>
   <si>
     <t xml:space="preserve">3.00555157661438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0775408744812</t>
+    <t xml:space="preserve">3.07754111289978</t>
   </si>
   <si>
     <t xml:space="preserve">2.98755431175232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05954337120056</t>
+    <t xml:space="preserve">3.05954384803772</t>
   </si>
   <si>
     <t xml:space="preserve">3.14953017234802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20352220535278</t>
+    <t xml:space="preserve">3.20352172851562</t>
   </si>
   <si>
     <t xml:space="preserve">3.32950329780579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38349556922913</t>
+    <t xml:space="preserve">3.38349533081055</t>
   </si>
   <si>
     <t xml:space="preserve">3.36549806594849</t>
@@ -371,28 +371,28 @@
     <t xml:space="preserve">3.34750080108643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2755115032196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31150603294373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29350876808167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41949009895325</t>
+    <t xml:space="preserve">3.27551174163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3115062713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29350900650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41948986053467</t>
   </si>
   <si>
     <t xml:space="preserve">3.25751399993896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2395167350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22151947021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40149283409119</t>
+    <t xml:space="preserve">3.23951649665833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22151899337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40149235725403</t>
   </si>
   <si>
     <t xml:space="preserve">3.43748688697815</t>
@@ -401,67 +401,67 @@
     <t xml:space="preserve">3.65345501899719</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56346869468689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63545799255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86942291259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99540424346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0134015083313</t>
+    <t xml:space="preserve">3.56346845626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63545775413513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8694224357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9954035282135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01340198516846</t>
   </si>
   <si>
     <t xml:space="preserve">3.94141221046448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76143884658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.923415184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9774067401886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8874204158783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85142612457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90541768074036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17537689208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15737915039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24736642837524</t>
+    <t xml:space="preserve">3.76143860816956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92341494560242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97740697860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88742017745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85142588615417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90541744232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17537641525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15738105773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2473669052124</t>
   </si>
   <si>
     <t xml:space="preserve">4.35535097122192</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39134550094604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31935548782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30135917663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32852458953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3466362953186</t>
+    <t xml:space="preserve">4.39134502410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31935596466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30135869979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32852506637573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34663581848145</t>
   </si>
   <si>
     <t xml:space="preserve">4.23796939849854</t>
@@ -470,13 +470,13 @@
     <t xml:space="preserve">4.20174741744995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21985912322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1293044090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05685997009277</t>
+    <t xml:space="preserve">4.21985864639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12930393218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05686044692993</t>
   </si>
   <si>
     <t xml:space="preserve">4.16552591323853</t>
@@ -488,40 +488,40 @@
     <t xml:space="preserve">4.43719053268433</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29230213165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11119318008423</t>
+    <t xml:space="preserve">4.29230308532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11119270324707</t>
   </si>
   <si>
     <t xml:space="preserve">4.25608062744141</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41907930374146</t>
+    <t xml:space="preserve">4.41907978057861</t>
   </si>
   <si>
     <t xml:space="preserve">4.14741468429565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07497119903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02063798904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94819474220276</t>
+    <t xml:space="preserve">4.0749716758728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02063751220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9481942653656</t>
   </si>
   <si>
     <t xml:space="preserve">3.93008327484131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89386129379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98441648483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03874921798706</t>
+    <t xml:space="preserve">3.89386081695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98441624641418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03874969482422</t>
   </si>
   <si>
     <t xml:space="preserve">3.91197228431702</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">3.87575054168701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74897360801697</t>
+    <t xml:space="preserve">3.74897313117981</t>
   </si>
   <si>
     <t xml:space="preserve">3.82141709327698</t>
@@ -539,181 +539,184 @@
     <t xml:space="preserve">3.83952832221985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62219667434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73086166381836</t>
+    <t xml:space="preserve">3.62219643592834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73086261749268</t>
   </si>
   <si>
     <t xml:space="preserve">3.65841841697693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78519487380981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00252676010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18363666534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31041431427002</t>
+    <t xml:space="preserve">3.78519511222839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00252723693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18363761901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31041383743286</t>
   </si>
   <si>
     <t xml:space="preserve">3.96630525588989</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80330634117126</t>
+    <t xml:space="preserve">3.80330610275269</t>
   </si>
   <si>
     <t xml:space="preserve">3.71275115013123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44108653068542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53164172172546</t>
+    <t xml:space="preserve">3.441086769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53164148330688</t>
   </si>
   <si>
     <t xml:space="preserve">3.4954195022583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38675355911255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15131115913391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73475861549377</t>
+    <t xml:space="preserve">3.38675379753113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15131092071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73475813865662</t>
   </si>
   <si>
     <t xml:space="preserve">2.80720233917236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69853615760803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58987045288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7709801197052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89775705337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09697794914246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13319993019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33242058753967</t>
+    <t xml:space="preserve">2.69853639602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58987021446228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77098035812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89775729179382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09697818756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13320016860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33242106437683</t>
   </si>
   <si>
     <t xml:space="preserve">3.36864280700684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.404865026474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31430959701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18753290176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22375464439392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56786346435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54975271224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55880832672119</t>
+    <t xml:space="preserve">3.40486478805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31431007385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1875331401825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22375440597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56786394119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54975247383118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55880808830261</t>
   </si>
   <si>
     <t xml:space="preserve">3.51353073120117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45014190673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42297577857971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35053205490112</t>
+    <t xml:space="preserve">3.45014214515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42297554016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35053157806396</t>
   </si>
   <si>
     <t xml:space="preserve">3.4139199256897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34147620201111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25092101097107</t>
+    <t xml:space="preserve">3.34147644042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25092148780823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32336521148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33267426490784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35129261016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41645669937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49092984199524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36991119384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5374755859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63056707382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59333038330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74227690696716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84467744827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85398650169373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79813170433044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77951335906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75158619880676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67711281776428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66780400276184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65849471092224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37922024726868</t>
   </si>
   <si>
     <t xml:space="preserve">3.3233654499054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33267426490784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35129284858704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41645669937134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49092984199524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3699107170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53747534751892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6305673122406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59333062171936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74227690696716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84467744827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8539867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79813194274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77951335906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75158643722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67711281776428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66780376434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65849494934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37922048568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44438433647156</t>
+    <t xml:space="preserve">3.44438409805298</t>
   </si>
   <si>
     <t xml:space="preserve">3.21165537834167</t>
@@ -722,13 +725,13 @@
     <t xml:space="preserve">3.11856412887573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18372821807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34198331832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43507504463196</t>
+    <t xml:space="preserve">3.18372845649719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34198355674744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43507528305054</t>
   </si>
   <si>
     <t xml:space="preserve">3.4630024433136</t>
@@ -737,13 +740,13 @@
     <t xml:space="preserve">3.60263967514038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4723117351532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62125778198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52816653251648</t>
+    <t xml:space="preserve">3.47231149673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62125825881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52816677093506</t>
   </si>
   <si>
     <t xml:space="preserve">3.48162078857422</t>
@@ -752,79 +755,79 @@
     <t xml:space="preserve">3.42576599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64918541908264</t>
+    <t xml:space="preserve">3.64918518066406</t>
   </si>
   <si>
     <t xml:space="preserve">3.72365856170654</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51885747909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7702043056488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58402156829834</t>
+    <t xml:space="preserve">3.5188570022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77020478248596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58402132987976</t>
   </si>
   <si>
     <t xml:space="preserve">3.7050404548645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6864218711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80744123458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29543781280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56540274620056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00293302536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92845940589905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78882265090942</t>
+    <t xml:space="preserve">3.68642210960388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80744075775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29543805122375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5654034614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00293254852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92845964431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.788822889328</t>
   </si>
   <si>
     <t xml:space="preserve">3.98431515693665</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86329627037048</t>
+    <t xml:space="preserve">3.86329579353333</t>
   </si>
   <si>
     <t xml:space="preserve">3.81674981117249</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671474456787</t>
+    <t xml:space="preserve">4.08671522140503</t>
   </si>
   <si>
     <t xml:space="preserve">4.16118812561035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22635269165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38460731506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48700857162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35668039321899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50562715530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63595485687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4963173866272</t>
+    <t xml:space="preserve">4.22635221481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38460779190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48700904846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35667991638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50562763214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63595390319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49631786346436</t>
   </si>
   <si>
     <t xml:space="preserve">4.46839046478271</t>
@@ -833,67 +836,67 @@
     <t xml:space="preserve">4.28220701217651</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20773410797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43115425109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56148147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57079076766968</t>
+    <t xml:space="preserve">4.20773363113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43115377426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56148195266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57079124450684</t>
   </si>
   <si>
     <t xml:space="preserve">4.45908117294312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52424621582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58940935134888</t>
+    <t xml:space="preserve">4.524245262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58940887451172</t>
   </si>
   <si>
     <t xml:space="preserve">4.59871816635132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44046306610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37529850006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41253519058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29151630401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32875347137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23566150665283</t>
+    <t xml:space="preserve">4.44046258926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37529897689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41253566741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29151678085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32875299453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23566198348999</t>
   </si>
   <si>
     <t xml:space="preserve">4.33806228637695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15187883377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13326120376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18911600112915</t>
+    <t xml:space="preserve">4.15187978744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13326072692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18911647796631</t>
   </si>
   <si>
     <t xml:space="preserve">4.34737157821655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19842576980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31944370269775</t>
+    <t xml:space="preserve">4.19842529296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3194432258606</t>
   </si>
   <si>
     <t xml:space="preserve">4.27289867401123</t>
@@ -902,25 +905,25 @@
     <t xml:space="preserve">4.5149359703064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39391660690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42184495925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87799215316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71042776107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60802698135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61733675003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26358890533447</t>
+    <t xml:space="preserve">4.39391756057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42184448242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87799263000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71042823791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60802793502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61733722686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26358938217163</t>
   </si>
   <si>
     <t xml:space="preserve">4.11464309692383</t>
@@ -935,13 +938,13 @@
     <t xml:space="preserve">4.07740640640259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95638704299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90984177589417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04017019271851</t>
+    <t xml:space="preserve">3.95638728141785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90984129905701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04016971588135</t>
   </si>
   <si>
     <t xml:space="preserve">4.25428009033203</t>
@@ -950,16 +953,16 @@
     <t xml:space="preserve">4.65457344055176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70111846923828</t>
+    <t xml:space="preserve">4.70111894607544</t>
   </si>
   <si>
     <t xml:space="preserve">4.54286336898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30082511901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44977188110352</t>
+    <t xml:space="preserve">4.30082654953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44977235794067</t>
   </si>
   <si>
     <t xml:space="preserve">4.58010053634644</t>
@@ -968,7 +971,7 @@
     <t xml:space="preserve">4.79421043395996</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88730239868164</t>
+    <t xml:space="preserve">4.88730192184448</t>
   </si>
   <si>
     <t xml:space="preserve">4.61688423156738</t>
@@ -980,25 +983,25 @@
     <t xml:space="preserve">4.52266263961792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57919645309448</t>
+    <t xml:space="preserve">4.57919597625732</t>
   </si>
   <si>
     <t xml:space="preserve">4.56035137176514</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44728422164917</t>
+    <t xml:space="preserve">4.44728469848633</t>
   </si>
   <si>
     <t xml:space="preserve">4.67341804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69226217269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80532884597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89955043792725</t>
+    <t xml:space="preserve">4.69226169586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80532932281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8995509147644</t>
   </si>
   <si>
     <t xml:space="preserve">4.85243988037109</t>
@@ -1007,34 +1010,34 @@
     <t xml:space="preserve">4.99377346038818</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94666242599487</t>
+    <t xml:space="preserve">4.94666194915771</t>
   </si>
   <si>
     <t xml:space="preserve">5.04088401794434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22932910919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60621690750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51199531555176</t>
+    <t xml:space="preserve">5.22932863235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60621643066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5119948387146</t>
   </si>
   <si>
     <t xml:space="preserve">5.700439453125</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65332746505737</t>
+    <t xml:space="preserve">5.65332841873169</t>
   </si>
   <si>
     <t xml:space="preserve">5.32355070114136</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37066078186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18221712112427</t>
+    <t xml:space="preserve">5.37066125869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18221759796143</t>
   </si>
   <si>
     <t xml:space="preserve">5.13510608673096</t>
@@ -1049,7 +1052,7 @@
     <t xml:space="preserve">4.71110677719116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76719093322754</t>
+    <t xml:space="preserve">4.7671914100647</t>
   </si>
   <si>
     <t xml:space="preserve">4.69091653823853</t>
@@ -1067,13 +1070,13 @@
     <t xml:space="preserve">4.67184734344482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53836631774902</t>
+    <t xml:space="preserve">4.53836679458618</t>
   </si>
   <si>
     <t xml:space="preserve">4.65277862548828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57650375366211</t>
+    <t xml:space="preserve">4.57650423049927</t>
   </si>
   <si>
     <t xml:space="preserve">4.72905397415161</t>
@@ -1088,25 +1091,28 @@
     <t xml:space="preserve">4.95787858963013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6337103843689</t>
+    <t xml:space="preserve">4.63370990753174</t>
   </si>
   <si>
     <t xml:space="preserve">4.6146411895752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59557199478149</t>
+    <t xml:space="preserve">4.59557247161865</t>
   </si>
   <si>
     <t xml:space="preserve">4.55743503570557</t>
   </si>
   <si>
+    <t xml:space="preserve">4.69091606140137</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.74882888793945</t>
   </si>
   <si>
     <t xml:space="preserve">4.71022033691406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78743696212769</t>
+    <t xml:space="preserve">4.78743743896484</t>
   </si>
   <si>
     <t xml:space="preserve">5.01908683776855</t>
@@ -1124,13 +1130,13 @@
     <t xml:space="preserve">5.30865001678467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40517044067383</t>
+    <t xml:space="preserve">5.40517091751099</t>
   </si>
   <si>
     <t xml:space="preserve">5.26038932800293</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50169134140015</t>
+    <t xml:space="preserve">5.5016918182373</t>
   </si>
   <si>
     <t xml:space="preserve">5.74299383163452</t>
@@ -1142,7 +1148,7 @@
     <t xml:space="preserve">5.64647340774536</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54995203018188</t>
+    <t xml:space="preserve">5.54995250701904</t>
   </si>
   <si>
     <t xml:space="preserve">5.21212959289551</t>
@@ -1154,19 +1160,19 @@
     <t xml:space="preserve">4.92256641387939</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11560821533203</t>
+    <t xml:space="preserve">5.11560869216919</t>
   </si>
   <si>
     <t xml:space="preserve">4.87430572509766</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82604503631592</t>
+    <t xml:space="preserve">4.82604551315308</t>
   </si>
   <si>
     <t xml:space="preserve">4.97082662582397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86340188980103</t>
+    <t xml:space="preserve">4.86340236663818</t>
   </si>
   <si>
     <t xml:space="preserve">4.93176364898682</t>
@@ -1190,19 +1196,19 @@
     <t xml:space="preserve">4.62902116775513</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58995819091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60948944091797</t>
+    <t xml:space="preserve">4.58995771408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60948991775513</t>
   </si>
   <si>
     <t xml:space="preserve">4.55089426040649</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51183080673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53136301040649</t>
+    <t xml:space="preserve">4.51183128356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53136253356934</t>
   </si>
   <si>
     <t xml:space="preserve">4.49229907989502</t>
@@ -1244,7 +1250,7 @@
     <t xml:space="preserve">3.76962494850159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67196655273438</t>
+    <t xml:space="preserve">3.6719663143158</t>
   </si>
   <si>
     <t xml:space="preserve">3.71102976799011</t>
@@ -1256,22 +1262,22 @@
     <t xml:space="preserve">3.92587900161743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10166454315186</t>
+    <t xml:space="preserve">4.1016640663147</t>
   </si>
   <si>
     <t xml:space="preserve">4.04306936264038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12119579315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17979145050049</t>
+    <t xml:space="preserve">4.12119626998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17979192733765</t>
   </si>
   <si>
     <t xml:space="preserve">4.0821328163147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1993236541748</t>
+    <t xml:space="preserve">4.19932317733765</t>
   </si>
   <si>
     <t xml:space="preserve">4.16026020050049</t>
@@ -1286,16 +1292,16 @@
     <t xml:space="preserve">4.33604526519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25791883468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86728358268738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94541072845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4337043762207</t>
+    <t xml:space="preserve">4.25791835784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86728382110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94541049003601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43370389938354</t>
   </si>
   <si>
     <t xml:space="preserve">4.59072542190552</t>
@@ -23756,7 +23762,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G847" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -23782,7 +23788,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G848" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -23808,7 +23814,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G849" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -23860,7 +23866,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G851" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -23886,7 +23892,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G852" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -23912,7 +23918,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G853" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -23938,7 +23944,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G854" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -23964,7 +23970,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G855" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -23990,7 +23996,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G856" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24016,7 +24022,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G857" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -24042,7 +24048,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G858" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -24068,7 +24074,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G859" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -24094,7 +24100,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G860" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -24120,7 +24126,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G861" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -24172,7 +24178,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G863" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -24224,7 +24230,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G865" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -24250,7 +24256,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G866" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -24302,7 +24308,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G868" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -24328,7 +24334,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G869" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -24354,7 +24360,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G870" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -24380,7 +24386,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G871" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -24406,7 +24412,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G872" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -24432,7 +24438,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G873" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -24484,7 +24490,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G875" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -24588,7 +24594,7 @@
         <v>4</v>
       </c>
       <c r="G879" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -24614,7 +24620,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G880" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -24692,7 +24698,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G883" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -24796,7 +24802,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G887" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -24822,7 +24828,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G888" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -24926,7 +24932,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G892" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -24978,7 +24984,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G894" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -25004,7 +25010,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G895" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -25030,7 +25036,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G896" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -25056,7 +25062,7 @@
         <v>4</v>
       </c>
       <c r="G897" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -25134,7 +25140,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G900" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -25160,7 +25166,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G901" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -25186,7 +25192,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G902" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -25238,7 +25244,7 @@
         <v>4</v>
       </c>
       <c r="G904" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -25264,7 +25270,7 @@
         <v>4</v>
       </c>
       <c r="G905" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -25316,7 +25322,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G907" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -25342,7 +25348,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G908" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -25368,7 +25374,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G909" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -25394,7 +25400,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G910" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -25420,7 +25426,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G911" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -25472,7 +25478,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G913" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -25498,7 +25504,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G914" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -25628,7 +25634,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G919" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -25706,7 +25712,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G922" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -25732,7 +25738,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G923" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -25758,7 +25764,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G924" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -25784,7 +25790,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G925" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -25810,7 +25816,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G926" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -25836,7 +25842,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G927" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -25862,7 +25868,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G928" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -25888,7 +25894,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G929" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -25914,7 +25920,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G930" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -25940,7 +25946,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G931" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -25966,7 +25972,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G932" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -25992,7 +25998,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G933" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26018,7 +26024,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G934" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26044,7 +26050,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G935" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26070,7 +26076,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G936" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26096,7 +26102,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G937" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -26148,7 +26154,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G939" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26174,7 +26180,7 @@
         <v>4</v>
       </c>
       <c r="G940" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -26200,7 +26206,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G941" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -26226,7 +26232,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G942" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -26252,7 +26258,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G943" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -26278,7 +26284,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G944" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -26304,7 +26310,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G945" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -26330,7 +26336,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G946" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -26356,7 +26362,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G947" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -26434,7 +26440,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G950" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26486,7 +26492,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G952" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26512,7 +26518,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G953" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26538,7 +26544,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G954" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26564,7 +26570,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G955" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26590,7 +26596,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G956" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26616,7 +26622,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G957" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26642,7 +26648,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G958" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -26668,7 +26674,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G959" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -26694,7 +26700,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G960" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -26720,7 +26726,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G961" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -26746,7 +26752,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G962" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -26772,7 +26778,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G963" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -26798,7 +26804,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G964" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -26824,7 +26830,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G965" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -26850,7 +26856,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G966" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -26876,7 +26882,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G967" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -26902,7 +26908,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G968" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -26928,7 +26934,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G969" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -26954,7 +26960,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G970" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -26980,7 +26986,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G971" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27006,7 +27012,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G972" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27032,7 +27038,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G973" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27058,7 +27064,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G974" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27084,7 +27090,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G975" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -27110,7 +27116,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G976" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27136,7 +27142,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G977" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27162,7 +27168,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G978" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -27188,7 +27194,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G979" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27214,7 +27220,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G980" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27240,7 +27246,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G981" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27266,7 +27272,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G982" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -27292,7 +27298,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G983" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -27318,7 +27324,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G984" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27344,7 +27350,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G985" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -27370,7 +27376,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G986" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -27396,7 +27402,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G987" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -27422,7 +27428,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G988" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -27448,7 +27454,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G989" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -27474,7 +27480,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G990" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -27500,7 +27506,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G991" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -27526,7 +27532,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G992" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -27552,7 +27558,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G993" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -27578,7 +27584,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G994" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -27604,7 +27610,7 @@
         <v>4.5</v>
       </c>
       <c r="G995" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -27630,7 +27636,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G996" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -27656,7 +27662,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G997" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -27682,7 +27688,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G998" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -27708,7 +27714,7 @@
         <v>4.5</v>
       </c>
       <c r="G999" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -27734,7 +27740,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1000" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -27760,7 +27766,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1001" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -27786,7 +27792,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1002" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -27812,7 +27818,7 @@
         <v>4.5</v>
       </c>
       <c r="G1003" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -27838,7 +27844,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1004" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -27864,7 +27870,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1005" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -27890,7 +27896,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1006" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -27916,7 +27922,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1007" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -27942,7 +27948,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1008" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -27968,7 +27974,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1009" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -27994,7 +28000,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1010" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -28020,7 +28026,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1011" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28046,7 +28052,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1012" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28072,7 +28078,7 @@
         <v>4.75</v>
       </c>
       <c r="G1013" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28098,7 +28104,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1014" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28124,7 +28130,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1015" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28150,7 +28156,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1016" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28176,7 +28182,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1017" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -28202,7 +28208,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1018" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -28228,7 +28234,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1019" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -28254,7 +28260,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1020" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28280,7 +28286,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1021" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28306,7 +28312,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1022" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -28332,7 +28338,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1023" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -28358,7 +28364,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1024" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28384,7 +28390,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1025" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28410,7 +28416,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1026" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28436,7 +28442,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1027" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28462,7 +28468,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1028" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28488,7 +28494,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1029" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28514,7 +28520,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1030" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28540,7 +28546,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1031" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28566,7 +28572,7 @@
         <v>4.5</v>
       </c>
       <c r="G1032" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28592,7 +28598,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1033" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28618,7 +28624,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1034" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28644,7 +28650,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1035" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -28670,7 +28676,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1036" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -28696,7 +28702,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1037" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -28722,7 +28728,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1038" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -28748,7 +28754,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1039" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -28774,7 +28780,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1040" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -28800,7 +28806,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1041" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -28826,7 +28832,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1042" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -28852,7 +28858,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1043" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -28878,7 +28884,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1044" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -28904,7 +28910,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1045" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -28930,7 +28936,7 @@
         <v>4.25</v>
       </c>
       <c r="G1046" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -28956,7 +28962,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1047" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -28982,7 +28988,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1048" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29008,7 +29014,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1049" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29034,7 +29040,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1050" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29060,7 +29066,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1051" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29086,7 +29092,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1052" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -29112,7 +29118,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1053" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29138,7 +29144,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1054" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29164,7 +29170,7 @@
         <v>5</v>
       </c>
       <c r="G1055" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29190,7 +29196,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1056" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29216,7 +29222,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29242,7 +29248,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1058" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29268,7 +29274,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1059" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29294,7 +29300,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1060" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29320,7 +29326,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1061" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29346,7 +29352,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1062" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29372,7 +29378,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1063" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29398,7 +29404,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1064" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29424,7 +29430,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1065" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29450,7 +29456,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1066" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29476,7 +29482,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1067" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29502,7 +29508,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1068" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29528,7 +29534,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1069" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29554,7 +29560,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1070" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29580,7 +29586,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1071" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -29606,7 +29612,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1072" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -29632,7 +29638,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1073" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -29658,7 +29664,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1074" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -29684,7 +29690,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1075" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -29710,7 +29716,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1076" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -29736,7 +29742,7 @@
         <v>5.25</v>
       </c>
       <c r="G1077" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -29762,7 +29768,7 @@
         <v>5.25</v>
       </c>
       <c r="G1078" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -29788,7 +29794,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1079" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -29814,7 +29820,7 @@
         <v>5</v>
       </c>
       <c r="G1080" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -29840,7 +29846,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1081" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -29866,7 +29872,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1082" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -29892,7 +29898,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1083" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -29918,7 +29924,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1084" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -29944,7 +29950,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1085" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -29970,7 +29976,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1086" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -29996,7 +30002,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1087" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30022,7 +30028,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1088" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30048,7 +30054,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1089" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -30074,7 +30080,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1090" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30100,7 +30106,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1091" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30126,7 +30132,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1092" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30152,7 +30158,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1093" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30178,7 +30184,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1094" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -30204,7 +30210,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1095" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -30230,7 +30236,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1096" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -30256,7 +30262,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1097" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -30282,7 +30288,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1098" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -30308,7 +30314,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1099" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -30334,7 +30340,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1100" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -30360,7 +30366,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1101" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -30386,7 +30392,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1102" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -30412,7 +30418,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1103" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -30438,7 +30444,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1104" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -30464,7 +30470,7 @@
         <v>5.25</v>
       </c>
       <c r="G1105" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -30490,7 +30496,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1106" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30516,7 +30522,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1107" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30542,7 +30548,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1108" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -30568,7 +30574,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1109" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -30594,7 +30600,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1110" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -30620,7 +30626,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1111" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -30646,7 +30652,7 @@
         <v>6</v>
       </c>
       <c r="G1112" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -30672,7 +30678,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1113" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -30698,7 +30704,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1114" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -30724,7 +30730,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -30750,7 +30756,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1116" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -30776,7 +30782,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1117" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -30802,7 +30808,7 @@
         <v>5.5</v>
       </c>
       <c r="G1118" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -30828,7 +30834,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1119" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -30854,7 +30860,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1120" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -30880,7 +30886,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1121" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -30906,7 +30912,7 @@
         <v>5.5</v>
       </c>
       <c r="G1122" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -30932,7 +30938,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1123" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -30958,7 +30964,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1124" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -30984,7 +30990,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1125" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31010,7 +31016,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1126" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31036,7 +31042,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1127" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31062,7 +31068,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1128" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31088,7 +31094,7 @@
         <v>5.5</v>
       </c>
       <c r="G1129" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31114,7 +31120,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1130" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31140,7 +31146,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1131" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31166,7 +31172,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1132" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31192,7 +31198,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1133" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31218,7 +31224,7 @@
         <v>5.5</v>
       </c>
       <c r="G1134" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31244,7 +31250,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1135" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31270,7 +31276,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1136" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31296,7 +31302,7 @@
         <v>5.5</v>
       </c>
       <c r="G1137" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31322,7 +31328,7 @@
         <v>5.5</v>
       </c>
       <c r="G1138" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31348,7 +31354,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1139" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31374,7 +31380,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1140" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31400,7 +31406,7 @@
         <v>5.25</v>
       </c>
       <c r="G1141" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31426,7 +31432,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1142" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31452,7 +31458,7 @@
         <v>5.25</v>
       </c>
       <c r="G1143" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31478,7 +31484,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1144" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31504,7 +31510,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1145" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31530,7 +31536,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1146" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31556,7 +31562,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1147" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31582,7 +31588,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1148" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31608,7 +31614,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1149" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -31634,7 +31640,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1150" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -31660,7 +31666,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1151" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -31686,7 +31692,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1152" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -31712,7 +31718,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1153" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -31738,7 +31744,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1154" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -31764,7 +31770,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1155" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -31790,7 +31796,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1156" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -31816,7 +31822,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1157" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -31842,7 +31848,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1158" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -31868,7 +31874,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1159" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -31894,7 +31900,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1160" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -31920,7 +31926,7 @@
         <v>5.25</v>
       </c>
       <c r="G1161" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -31946,7 +31952,7 @@
         <v>5.25</v>
       </c>
       <c r="G1162" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -31972,7 +31978,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1163" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -31998,7 +32004,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1164" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32024,7 +32030,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1165" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32050,7 +32056,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1166" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -32076,7 +32082,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1167" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -32102,7 +32108,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1168" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -32128,7 +32134,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1169" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -32154,7 +32160,7 @@
         <v>5</v>
       </c>
       <c r="G1170" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -32180,7 +32186,7 @@
         <v>5</v>
       </c>
       <c r="G1171" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -32206,7 +32212,7 @@
         <v>5</v>
       </c>
       <c r="G1172" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -32232,7 +32238,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1173" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -32258,7 +32264,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1174" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -32284,7 +32290,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1175" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -32310,7 +32316,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1176" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -32336,7 +32342,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1177" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -32362,7 +32368,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1178" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -32388,7 +32394,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1179" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -32414,7 +32420,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1180" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -32440,7 +32446,7 @@
         <v>5.25</v>
       </c>
       <c r="G1181" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -32466,7 +32472,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1182" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -32492,7 +32498,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1183" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -32518,7 +32524,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1184" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -32544,7 +32550,7 @@
         <v>5.25</v>
       </c>
       <c r="G1185" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -32570,7 +32576,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1186" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -32596,7 +32602,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1187" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -32622,7 +32628,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1188" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -32648,7 +32654,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1189" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -32674,7 +32680,7 @@
         <v>5</v>
       </c>
       <c r="G1190" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -32700,7 +32706,7 @@
         <v>5</v>
       </c>
       <c r="G1191" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -32726,7 +32732,7 @@
         <v>5</v>
       </c>
       <c r="G1192" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -32752,7 +32758,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1193" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -32778,7 +32784,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1194" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -32804,7 +32810,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1195" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -32830,7 +32836,7 @@
         <v>5</v>
       </c>
       <c r="G1196" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -32856,7 +32862,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1197" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -32882,7 +32888,7 @@
         <v>5</v>
       </c>
       <c r="G1198" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -32908,7 +32914,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1199" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -32934,7 +32940,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1200" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -32960,7 +32966,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1201" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -32986,7 +32992,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1202" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33012,7 +33018,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1203" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33038,7 +33044,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1204" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -33064,7 +33070,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1205" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -33090,7 +33096,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1206" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -33116,7 +33122,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1207" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -33142,7 +33148,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1208" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -33168,7 +33174,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1209" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -33194,7 +33200,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1210" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -33220,7 +33226,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1211" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -33246,7 +33252,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1212" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -33272,7 +33278,7 @@
         <v>5</v>
       </c>
       <c r="G1213" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -33298,7 +33304,7 @@
         <v>5</v>
       </c>
       <c r="G1214" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -33324,7 +33330,7 @@
         <v>5</v>
       </c>
       <c r="G1215" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -33350,7 +33356,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1216" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -33376,7 +33382,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1217" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -33402,7 +33408,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1218" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -33428,7 +33434,7 @@
         <v>5</v>
       </c>
       <c r="G1219" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -33454,7 +33460,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1220" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -33480,7 +33486,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1221" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -33506,7 +33512,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1222" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -33532,7 +33538,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1223" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -33558,7 +33564,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1224" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -33584,7 +33590,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1225" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -33610,7 +33616,7 @@
         <v>5</v>
       </c>
       <c r="G1226" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -33636,7 +33642,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1227" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -33662,7 +33668,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1228" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -33688,7 +33694,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1229" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -33714,7 +33720,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1230" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -33740,7 +33746,7 @@
         <v>5</v>
       </c>
       <c r="G1231" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -33766,7 +33772,7 @@
         <v>5</v>
       </c>
       <c r="G1232" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -33792,7 +33798,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1233" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -33818,7 +33824,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1234" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -33844,7 +33850,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1235" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -33870,7 +33876,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1236" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -33896,7 +33902,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1237" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -33922,7 +33928,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1238" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -33948,7 +33954,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1239" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -33974,7 +33980,7 @@
         <v>5</v>
       </c>
       <c r="G1240" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -34000,7 +34006,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1241" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34026,7 +34032,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1242" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -34052,7 +34058,7 @@
         <v>5</v>
       </c>
       <c r="G1243" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -34078,7 +34084,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1244" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -34104,7 +34110,7 @@
         <v>5</v>
       </c>
       <c r="G1245" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34130,7 +34136,7 @@
         <v>5</v>
       </c>
       <c r="G1246" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34156,7 +34162,7 @@
         <v>5</v>
       </c>
       <c r="G1247" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -34182,7 +34188,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1248" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -34208,7 +34214,7 @@
         <v>5</v>
       </c>
       <c r="G1249" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -34234,7 +34240,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1250" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -34260,7 +34266,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1251" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -34286,7 +34292,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1252" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -34312,7 +34318,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1253" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -34338,7 +34344,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1254" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -34364,7 +34370,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1255" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -34390,7 +34396,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1256" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -34416,7 +34422,7 @@
         <v>5</v>
       </c>
       <c r="G1257" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -34442,7 +34448,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1258" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -34468,7 +34474,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1259" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -34494,7 +34500,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1260" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -34520,7 +34526,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1261" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -34546,7 +34552,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1262" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -34572,7 +34578,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1263" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -34598,7 +34604,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1264" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -34624,7 +34630,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1265" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -34650,7 +34656,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1266" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -34676,7 +34682,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1267" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -34702,7 +34708,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1268" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -34728,7 +34734,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1269" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -34754,7 +34760,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1270" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -34780,7 +34786,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1271" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -34806,7 +34812,7 @@
         <v>5</v>
       </c>
       <c r="G1272" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -34832,7 +34838,7 @@
         <v>5</v>
       </c>
       <c r="G1273" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -34858,7 +34864,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1274" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -34884,7 +34890,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1275" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -34910,7 +34916,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1276" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -34936,7 +34942,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1277" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -34962,7 +34968,7 @@
         <v>5</v>
       </c>
       <c r="G1278" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -34988,7 +34994,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1279" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35014,7 +35020,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1280" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -35040,7 +35046,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1281" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -35066,7 +35072,7 @@
         <v>5</v>
       </c>
       <c r="G1282" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -35092,7 +35098,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1283" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -35118,7 +35124,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1284" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -35144,7 +35150,7 @@
         <v>5</v>
       </c>
       <c r="G1285" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -35170,7 +35176,7 @@
         <v>5</v>
       </c>
       <c r="G1286" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -35196,7 +35202,7 @@
         <v>5</v>
       </c>
       <c r="G1287" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -35222,7 +35228,7 @@
         <v>5</v>
       </c>
       <c r="G1288" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -35248,7 +35254,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1289" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -35274,7 +35280,7 @@
         <v>5</v>
       </c>
       <c r="G1290" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35300,7 +35306,7 @@
         <v>5</v>
       </c>
       <c r="G1291" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35326,7 +35332,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1292" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35352,7 +35358,7 @@
         <v>5</v>
       </c>
       <c r="G1293" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35378,7 +35384,7 @@
         <v>5</v>
       </c>
       <c r="G1294" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35404,7 +35410,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1295" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35430,7 +35436,7 @@
         <v>5</v>
       </c>
       <c r="G1296" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35456,7 +35462,7 @@
         <v>5</v>
       </c>
       <c r="G1297" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -35482,7 +35488,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1298" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35508,7 +35514,7 @@
         <v>5</v>
       </c>
       <c r="G1299" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35534,7 +35540,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1300" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35560,7 +35566,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1301" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -35586,7 +35592,7 @@
         <v>5</v>
       </c>
       <c r="G1302" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35612,7 +35618,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1303" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35638,7 +35644,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1304" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -35664,7 +35670,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1305" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -35690,7 +35696,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1306" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -35716,7 +35722,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1307" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -35742,7 +35748,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1308" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -35768,7 +35774,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1309" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -35794,7 +35800,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1310" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -35820,7 +35826,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1311" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -35846,7 +35852,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1312" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -35872,7 +35878,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1313" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -35898,7 +35904,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1314" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -35924,7 +35930,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1315" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -35950,7 +35956,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1316" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -35976,7 +35982,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1317" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -36002,7 +36008,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1318" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36028,7 +36034,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1319" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -36054,7 +36060,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1320" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36080,7 +36086,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1321" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -36106,7 +36112,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1322" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -36132,7 +36138,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1323" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -36158,7 +36164,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1324" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -36184,7 +36190,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1325" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -36210,7 +36216,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1326" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -36236,7 +36242,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1327" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -36262,7 +36268,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1328" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -36288,7 +36294,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1329" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -36314,7 +36320,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1330" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -36340,7 +36346,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1331" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -36366,7 +36372,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1332" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -36392,7 +36398,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1333" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -36418,7 +36424,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1334" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -36444,7 +36450,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1335" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -36470,7 +36476,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1336" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -36496,7 +36502,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1337" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -36522,7 +36528,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1338" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -36548,7 +36554,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1339" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -36574,7 +36580,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1340" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -36600,7 +36606,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1341" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -36626,7 +36632,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1342" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -36652,7 +36658,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1343" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -36678,7 +36684,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1344" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -36704,7 +36710,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1345" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -36730,7 +36736,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1346" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -36756,7 +36762,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1347" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -36782,7 +36788,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1348" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -36808,7 +36814,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1349" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -36834,7 +36840,7 @@
         <v>5.5</v>
       </c>
       <c r="G1350" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -36860,7 +36866,7 @@
         <v>5.5</v>
       </c>
       <c r="G1351" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -36886,7 +36892,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1352" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -36912,7 +36918,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1353" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -36938,7 +36944,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1354" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -36964,7 +36970,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1355" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -36990,7 +36996,7 @@
         <v>5.5</v>
       </c>
       <c r="G1356" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37016,7 +37022,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1357" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37042,7 +37048,7 @@
         <v>5.5</v>
       </c>
       <c r="G1358" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -37068,7 +37074,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1359" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37094,7 +37100,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1360" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37120,7 +37126,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1361" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -37146,7 +37152,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1362" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37172,7 +37178,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1363" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -37198,7 +37204,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1364" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -37224,7 +37230,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1365" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -37250,7 +37256,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1366" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -37276,7 +37282,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1367" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -37302,7 +37308,7 @@
         <v>5.75</v>
       </c>
       <c r="G1368" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -37328,7 +37334,7 @@
         <v>5.75</v>
       </c>
       <c r="G1369" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -37354,7 +37360,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1370" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -37380,7 +37386,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1371" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -37406,7 +37412,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1372" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -37432,7 +37438,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1373" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -37458,7 +37464,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1374" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -37484,7 +37490,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1375" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -37510,7 +37516,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1376" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -37536,7 +37542,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1377" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -37562,7 +37568,7 @@
         <v>5.5</v>
       </c>
       <c r="G1378" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -37588,7 +37594,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1379" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -37614,7 +37620,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1380" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -37640,7 +37646,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1381" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -37666,7 +37672,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1382" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -37692,7 +37698,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1383" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -37718,7 +37724,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1384" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -37744,7 +37750,7 @@
         <v>5.5</v>
       </c>
       <c r="G1385" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -37770,7 +37776,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1386" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -37796,7 +37802,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1387" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -37822,7 +37828,7 @@
         <v>5.25</v>
       </c>
       <c r="G1388" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -37848,7 +37854,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1389" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -37874,7 +37880,7 @@
         <v>5.25</v>
       </c>
       <c r="G1390" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -37900,7 +37906,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1391" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -37926,7 +37932,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1392" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -37952,7 +37958,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1393" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -37978,7 +37984,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1394" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38004,7 +38010,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1395" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38030,7 +38036,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1396" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38056,7 +38062,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1397" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38082,7 +38088,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1398" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -38108,7 +38114,7 @@
         <v>5</v>
       </c>
       <c r="G1399" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -38134,7 +38140,7 @@
         <v>5</v>
       </c>
       <c r="G1400" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -38160,7 +38166,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1401" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -38186,7 +38192,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1402" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -38212,7 +38218,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1403" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -38238,7 +38244,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1404" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -38264,7 +38270,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1405" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -38290,7 +38296,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1406" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -38316,7 +38322,7 @@
         <v>5.25</v>
       </c>
       <c r="G1407" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -38342,7 +38348,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1408" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -38368,7 +38374,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1409" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -38394,7 +38400,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1410" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -38420,7 +38426,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1411" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38446,7 +38452,7 @@
         <v>5.25</v>
       </c>
       <c r="G1412" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -38472,7 +38478,7 @@
         <v>5.25</v>
       </c>
       <c r="G1413" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -38498,7 +38504,7 @@
         <v>5.25</v>
       </c>
       <c r="G1414" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -38524,7 +38530,7 @@
         <v>5.25</v>
       </c>
       <c r="G1415" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -38550,7 +38556,7 @@
         <v>5.25</v>
       </c>
       <c r="G1416" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -38576,7 +38582,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1417" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -38602,7 +38608,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1418" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -38628,7 +38634,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1419" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -38654,7 +38660,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1420" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -38680,7 +38686,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1421" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -38706,7 +38712,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1422" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -38732,7 +38738,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1423" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -38758,7 +38764,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1424" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -38784,7 +38790,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1425" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -38810,7 +38816,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1426" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -38836,7 +38842,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1427" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -38862,7 +38868,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1428" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -38888,7 +38894,7 @@
         <v>5.25</v>
       </c>
       <c r="G1429" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -38914,7 +38920,7 @@
         <v>5.25</v>
       </c>
       <c r="G1430" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -38940,7 +38946,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1431" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -38966,7 +38972,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1432" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -38992,7 +38998,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1433" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39018,7 +39024,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1434" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39044,7 +39050,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1435" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -39070,7 +39076,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1436" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -39096,7 +39102,7 @@
         <v>5</v>
       </c>
       <c r="G1437" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39122,7 +39128,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1438" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39148,7 +39154,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1439" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39174,7 +39180,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1440" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -39200,7 +39206,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1441" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -39226,7 +39232,7 @@
         <v>5</v>
       </c>
       <c r="G1442" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39252,7 +39258,7 @@
         <v>5</v>
       </c>
       <c r="G1443" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -39278,7 +39284,7 @@
         <v>5</v>
       </c>
       <c r="G1444" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -39304,7 +39310,7 @@
         <v>5</v>
       </c>
       <c r="G1445" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -39330,7 +39336,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1446" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -39356,7 +39362,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1447" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -39382,7 +39388,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1448" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -39408,7 +39414,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1449" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39434,7 +39440,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1450" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39460,7 +39466,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1451" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39486,7 +39492,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1452" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39512,7 +39518,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1453" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39538,7 +39544,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1454" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39564,7 +39570,7 @@
         <v>5</v>
       </c>
       <c r="G1455" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39590,7 +39596,7 @@
         <v>5</v>
       </c>
       <c r="G1456" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39616,7 +39622,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1457" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39642,7 +39648,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1458" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39668,7 +39674,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1459" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39694,7 +39700,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1460" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -39720,7 +39726,7 @@
         <v>5</v>
       </c>
       <c r="G1461" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -39746,7 +39752,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1462" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -39772,7 +39778,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1463" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -39798,7 +39804,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1464" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -39824,7 +39830,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1465" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -39850,7 +39856,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1466" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -39876,7 +39882,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1467" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -39902,7 +39908,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1468" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -39928,7 +39934,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1469" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -39954,7 +39960,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1470" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -39980,7 +39986,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1471" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40006,7 +40012,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1472" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40032,7 +40038,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1473" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40058,7 +40064,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1474" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40084,7 +40090,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1475" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -40110,7 +40116,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1476" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -40136,7 +40142,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1477" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -40162,7 +40168,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1478" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -40188,7 +40194,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1479" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -40214,7 +40220,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1480" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -40240,7 +40246,7 @@
         <v>4.5</v>
       </c>
       <c r="G1481" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -40266,7 +40272,7 @@
         <v>4.5</v>
       </c>
       <c r="G1482" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -40292,7 +40298,7 @@
         <v>4.5</v>
       </c>
       <c r="G1483" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -40318,7 +40324,7 @@
         <v>4.5</v>
       </c>
       <c r="G1484" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -40344,7 +40350,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1485" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -40370,7 +40376,7 @@
         <v>4.5</v>
       </c>
       <c r="G1486" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -40396,7 +40402,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1487" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -40422,7 +40428,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1488" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40448,7 +40454,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1489" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40474,7 +40480,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1490" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40500,7 +40506,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1491" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40526,7 +40532,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1492" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -40552,7 +40558,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1493" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40578,7 +40584,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1494" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -40604,7 +40610,7 @@
         <v>4.5</v>
       </c>
       <c r="G1495" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -40630,7 +40636,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1496" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -40656,7 +40662,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1497" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -40682,7 +40688,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1498" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -40708,7 +40714,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1499" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -40734,7 +40740,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1500" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -40760,7 +40766,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1501" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -40786,7 +40792,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1502" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -40812,7 +40818,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1503" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -40838,7 +40844,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1504" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -40864,7 +40870,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1505" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -40890,7 +40896,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1506" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -40916,7 +40922,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1507" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -40942,7 +40948,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1508" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -40968,7 +40974,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1509" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -40994,7 +41000,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1510" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41020,7 +41026,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1511" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41046,7 +41052,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1512" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41072,7 +41078,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1513" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41098,7 +41104,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1514" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41124,7 +41130,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1515" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41150,7 +41156,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1516" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41176,7 +41182,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1517" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -41202,7 +41208,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1518" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -41228,7 +41234,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1519" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41254,7 +41260,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1520" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -41280,7 +41286,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1521" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -41306,7 +41312,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1522" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -41332,7 +41338,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1523" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -41358,7 +41364,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1524" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -41384,7 +41390,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1525" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -41410,7 +41416,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1526" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41436,7 +41442,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1527" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41462,7 +41468,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1528" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41488,7 +41494,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1529" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41514,7 +41520,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1530" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41540,7 +41546,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1531" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41566,7 +41572,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1532" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41592,7 +41598,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1533" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41618,7 +41624,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1534" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41644,7 +41650,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1535" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41670,7 +41676,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1536" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41696,7 +41702,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1537" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -41722,7 +41728,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1538" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -41748,7 +41754,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1539" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -41774,7 +41780,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1540" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -41800,7 +41806,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1541" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -41826,7 +41832,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1542" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -41852,7 +41858,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1543" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -41878,7 +41884,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1544" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -41904,7 +41910,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1545" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -41930,7 +41936,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1546" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -41956,7 +41962,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1547" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -41982,7 +41988,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1548" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42008,7 +42014,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1549" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42034,7 +42040,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1550" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42060,7 +42066,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1551" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42086,7 +42092,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1552" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42112,7 +42118,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1553" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42138,7 +42144,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1554" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42164,7 +42170,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1555" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42190,7 +42196,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1556" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42216,7 +42222,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1557" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -42242,7 +42248,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1558" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -42268,7 +42274,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1559" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -42294,7 +42300,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1560" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -42320,7 +42326,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1561" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -42346,7 +42352,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1562" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -42372,7 +42378,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1563" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -42398,7 +42404,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1564" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -42424,7 +42430,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1565" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42450,7 +42456,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1566" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42476,7 +42482,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1567" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42502,7 +42508,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1568" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42528,7 +42534,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1569" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42554,7 +42560,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1570" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42580,7 +42586,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1571" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42606,7 +42612,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1572" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42632,7 +42638,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1573" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42658,7 +42664,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1574" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42684,7 +42690,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1575" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -42710,7 +42716,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1576" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -42736,7 +42742,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1577" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -42762,7 +42768,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1578" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -42788,7 +42794,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1579" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -42814,7 +42820,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1580" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -42840,7 +42846,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1581" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -42866,7 +42872,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1582" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -42892,7 +42898,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1583" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -42918,7 +42924,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1584" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -42944,7 +42950,7 @@
         <v>4.5</v>
       </c>
       <c r="G1585" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -42970,7 +42976,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -42996,7 +43002,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1587" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43022,7 +43028,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1588" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43048,7 +43054,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1589" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43074,7 +43080,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1590" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43100,7 +43106,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1591" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43126,7 +43132,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1592" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43152,7 +43158,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1593" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43178,7 +43184,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1594" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43204,7 +43210,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1595" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -43230,7 +43236,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1596" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43256,7 +43262,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1597" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -43282,7 +43288,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1598" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -43308,7 +43314,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1599" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -43334,7 +43340,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1600" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -43360,7 +43366,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1601" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -43386,7 +43392,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1602" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -43412,7 +43418,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1603" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43438,7 +43444,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1604" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43464,7 +43470,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1605" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43490,7 +43496,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1606" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43516,7 +43522,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1607" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43542,7 +43548,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1608" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43568,7 +43574,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1609" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43594,7 +43600,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1610" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43620,7 +43626,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1611" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43646,7 +43652,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1612" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43672,7 +43678,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1613" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43698,7 +43704,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1614" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43724,7 +43730,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1615" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -43750,7 +43756,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1616" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43776,7 +43782,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1617" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43802,7 +43808,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1618" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43828,7 +43834,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1619" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43854,7 +43860,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1620" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -43880,7 +43886,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1621" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -43906,7 +43912,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1622" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -43932,7 +43938,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1623" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -43958,7 +43964,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1624" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -43984,7 +43990,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1625" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44010,7 +44016,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1626" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44036,7 +44042,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1627" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44062,7 +44068,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1628" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44088,7 +44094,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1629" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44114,7 +44120,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1630" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44140,7 +44146,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1631" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44166,7 +44172,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1632" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44192,7 +44198,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1633" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44218,7 +44224,7 @@
         <v>5.75</v>
       </c>
       <c r="G1634" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44244,7 +44250,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1635" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44270,7 +44276,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1636" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44296,7 +44302,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1637" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44322,7 +44328,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1638" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44348,7 +44354,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1639" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44374,7 +44380,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1640" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44400,7 +44406,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1641" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44426,7 +44432,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1642" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44452,7 +44458,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1643" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44478,7 +44484,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1644" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44504,7 +44510,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1645" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44530,7 +44536,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1646" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44556,7 +44562,7 @@
         <v>5.75</v>
       </c>
       <c r="G1647" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44582,7 +44588,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1648" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44608,7 +44614,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1649" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44634,7 +44640,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1650" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44660,7 +44666,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1651" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44686,7 +44692,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1652" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44712,7 +44718,7 @@
         <v>5.25</v>
       </c>
       <c r="G1653" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44738,7 +44744,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1654" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44764,7 +44770,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1655" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44790,7 +44796,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1656" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44816,7 +44822,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1657" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44842,7 +44848,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1658" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44868,7 +44874,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1659" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -44894,7 +44900,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1660" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44920,7 +44926,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1661" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44946,7 +44952,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1662" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44972,7 +44978,7 @@
         <v>5.5</v>
       </c>
       <c r="G1663" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44998,7 +45004,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1664" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45024,7 +45030,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1665" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45050,7 +45056,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1666" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45076,7 +45082,7 @@
         <v>5.5</v>
       </c>
       <c r="G1667" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45102,7 +45108,7 @@
         <v>5.5</v>
       </c>
       <c r="G1668" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45128,7 +45134,7 @@
         <v>5.5</v>
       </c>
       <c r="G1669" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45154,7 +45160,7 @@
         <v>5.5</v>
       </c>
       <c r="G1670" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45180,7 +45186,7 @@
         <v>5.5</v>
       </c>
       <c r="G1671" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45206,7 +45212,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1672" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45232,7 +45238,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1673" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45258,7 +45264,7 @@
         <v>5.75</v>
       </c>
       <c r="G1674" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45284,7 +45290,7 @@
         <v>5.75</v>
       </c>
       <c r="G1675" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45310,7 +45316,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1676" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45336,7 +45342,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1677" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45362,7 +45368,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1678" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45388,7 +45394,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1679" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45414,7 +45420,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1680" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45440,7 +45446,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1681" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45466,7 +45472,7 @@
         <v>5.75</v>
       </c>
       <c r="G1682" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45492,7 +45498,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1683" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45518,7 +45524,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1684" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45544,7 +45550,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1685" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45570,7 +45576,7 @@
         <v>5.5</v>
       </c>
       <c r="G1686" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45596,7 +45602,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1687" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45622,7 +45628,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1688" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45648,7 +45654,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1689" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45674,7 +45680,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1690" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45700,7 +45706,7 @@
         <v>5.75</v>
       </c>
       <c r="G1691" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45726,7 +45732,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1692" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45752,7 +45758,7 @@
         <v>5.75</v>
       </c>
       <c r="G1693" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45778,7 +45784,7 @@
         <v>5.75</v>
       </c>
       <c r="G1694" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45804,7 +45810,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1695" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45830,7 +45836,7 @@
         <v>6</v>
       </c>
       <c r="G1696" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45856,7 +45862,7 @@
         <v>6</v>
       </c>
       <c r="G1697" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -45882,7 +45888,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1698" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -45908,7 +45914,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1699" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -45934,7 +45940,7 @@
         <v>5.75</v>
       </c>
       <c r="G1700" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -45960,7 +45966,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1701" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -45986,7 +45992,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1702" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46012,7 +46018,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1703" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46038,7 +46044,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1704" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46064,7 +46070,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1705" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46090,7 +46096,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1706" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46116,7 +46122,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1707" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46142,7 +46148,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1708" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46168,7 +46174,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1709" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46194,7 +46200,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1710" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46220,7 +46226,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1711" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46246,7 +46252,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1712" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46272,7 +46278,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1713" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46298,7 +46304,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1714" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46306,7 +46312,7 @@
     </row>
     <row r="1715">
       <c r="A1715" s="1" t="n">
-        <v>45972.4699884259</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B1715" t="n">
         <v>39600</v>
@@ -46324,7 +46330,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1715" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>

--- a/data/ILP.MI.xlsx
+++ b/data/ILP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="465">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95026278495789</t>
+    <t xml:space="preserve">1.9502626657486</t>
   </si>
   <si>
     <t xml:space="preserve">ILP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97638201713562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91543650627136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94112062454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00685524940491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97986459732056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93284940719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9585337638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92109572887421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94199132919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95418035984039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93067276477814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88931703567505</t>
+    <t xml:space="preserve">1.97638237476349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91543638706207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94112086296082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00685501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97986507415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93284964561462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95853364467621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92109596729279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94199120998383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95418047904968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93067300319672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88931655883789</t>
   </si>
   <si>
     <t xml:space="preserve">1.8679860830307</t>
@@ -86,151 +86,151 @@
     <t xml:space="preserve">1.8906227350235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9197895526886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94155621528625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93807339668274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91717755794525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97551143169403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93459069728851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9676753282547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02775073051453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01556181907654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00250172615051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01991438865662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89802348613739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98508870601654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88061046600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84578430652618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86319744586945</t>
+    <t xml:space="preserve">1.91978967189789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9415557384491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93807351589203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91717791557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9755117893219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93459057807922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96767568588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02775096893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01556134223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00250196456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01991510391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89802360534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98508882522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88061082363129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84578418731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86319708824158</t>
   </si>
   <si>
     <t xml:space="preserve">1.88994169235229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90777158737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87211191654205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9256010055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94343078136444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9612603187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97908973693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83645296096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81862318515778</t>
+    <t xml:space="preserve">1.90777122974396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87211203575134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92560148239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94343090057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96126019954681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97909009456635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83645272254944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81862330436707</t>
   </si>
   <si>
     <t xml:space="preserve">1.76513421535492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85428237915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80079352855682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78296387195587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93451583385468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95234549045563</t>
+    <t xml:space="preserve">1.8542822599411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80079340934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78296411037445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93451547622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95234525203705</t>
   </si>
   <si>
     <t xml:space="preserve">1.88102674484253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89885675907135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82753789424896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84536755084991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86319708824158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72947514057159</t>
+    <t xml:space="preserve">1.89885652065277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82753813266754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8453676700592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86319732666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72947490215302</t>
   </si>
   <si>
     <t xml:space="preserve">1.77404916286469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76959180831909</t>
+    <t xml:space="preserve">1.7695916891098</t>
   </si>
   <si>
     <t xml:space="preserve">1.79187870025635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8097083568573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77850663661957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70718812942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72501754760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74730455875397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73838973045349</t>
+    <t xml:space="preserve">1.80970859527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77850651741028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70718777179718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72501766681671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74730467796326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73838996887207</t>
   </si>
   <si>
     <t xml:space="preserve">1.75621962547302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71164524555206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72056019306183</t>
+    <t xml:space="preserve">1.71164560317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72056007385254</t>
   </si>
   <si>
     <t xml:space="preserve">1.6938157081604</t>
@@ -239,37 +239,37 @@
     <t xml:space="preserve">1.64032685756683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64924156665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67598605155945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56900835037231</t>
+    <t xml:space="preserve">1.6492418050766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67598617076874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56900823116302</t>
   </si>
   <si>
     <t xml:space="preserve">1.66707134246826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63141214847565</t>
+    <t xml:space="preserve">1.63141202926636</t>
   </si>
   <si>
     <t xml:space="preserve">1.65815651416779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68490076065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7027302980423</t>
+    <t xml:space="preserve">1.68490087985992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70273053646088</t>
   </si>
   <si>
     <t xml:space="preserve">1.61358225345612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03257870674133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19304585456848</t>
+    <t xml:space="preserve">2.03257894515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19304537773132</t>
   </si>
   <si>
     <t xml:space="preserve">2.13955688476562</t>
@@ -284,25 +284,25 @@
     <t xml:space="preserve">2.54963803291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58529782295227</t>
+    <t xml:space="preserve">2.58529758453369</t>
   </si>
   <si>
     <t xml:space="preserve">3.03103876113892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42329049110413</t>
+    <t xml:space="preserve">3.42329120635986</t>
   </si>
   <si>
     <t xml:space="preserve">3.22716450691223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19150495529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13801670074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01320934295654</t>
+    <t xml:space="preserve">3.19150519371033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13801646232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01320910453796</t>
   </si>
   <si>
     <t xml:space="preserve">2.99537920951843</t>
@@ -311,22 +311,22 @@
     <t xml:space="preserve">2.97754955291748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08452796936035</t>
+    <t xml:space="preserve">3.08452749252319</t>
   </si>
   <si>
     <t xml:space="preserve">2.88840174674988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71010541915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6922755241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67444562911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79925322532654</t>
+    <t xml:space="preserve">2.71010494232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69227528572083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67444586753845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79925346374512</t>
   </si>
   <si>
     <t xml:space="preserve">2.83491277694702</t>
@@ -341,64 +341,64 @@
     <t xml:space="preserve">2.87057185173035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00555157661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07754111289978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98755431175232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05954384803772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14953017234802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20352172851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32950329780579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38349533081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36549806594849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34750080108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27551174163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3115062713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29350900650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41948986053467</t>
+    <t xml:space="preserve">3.0055513381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0775408744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9875545501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05954360961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14952993392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2035219669342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32950377464294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38349509239197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36549782752991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34750056266785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2755115032196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31150603294373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29350876808167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41949009895325</t>
   </si>
   <si>
     <t xml:space="preserve">3.25751399993896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23951649665833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22151899337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40149235725403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43748688697815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65345501899719</t>
+    <t xml:space="preserve">3.2395167350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22151947021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40149259567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43748712539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65345525741577</t>
   </si>
   <si>
     <t xml:space="preserve">3.56346845626831</t>
@@ -407,55 +407,55 @@
     <t xml:space="preserve">3.63545775413513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8694224357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9954035282135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01340198516846</t>
+    <t xml:space="preserve">3.86942338943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99540424346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01340103149414</t>
   </si>
   <si>
     <t xml:space="preserve">3.94141221046448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76143860816956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92341494560242</t>
+    <t xml:space="preserve">3.76143932342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.923415184021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97740697860718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88742017745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85142588615417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90541744232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17537641525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15738105773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2473669052124</t>
+    <t xml:space="preserve">3.8874204158783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85142517089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90541696548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.175377368927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15737962722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24736642837524</t>
   </si>
   <si>
     <t xml:space="preserve">4.35535097122192</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39134502410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31935596466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30135869979858</t>
+    <t xml:space="preserve">4.39134550094604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31935548782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30135917663574</t>
   </si>
   <si>
     <t xml:space="preserve">4.32852506637573</t>
@@ -470,10 +470,10 @@
     <t xml:space="preserve">4.20174741744995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21985864639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12930393218994</t>
+    <t xml:space="preserve">4.21985912322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1293044090271</t>
   </si>
   <si>
     <t xml:space="preserve">4.05686044692993</t>
@@ -482,13 +482,13 @@
     <t xml:space="preserve">4.16552591323853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0930814743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43719053268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29230308532715</t>
+    <t xml:space="preserve">4.09308195114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43719100952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29230260848999</t>
   </si>
   <si>
     <t xml:space="preserve">4.11119270324707</t>
@@ -497,70 +497,70 @@
     <t xml:space="preserve">4.25608062744141</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41907978057861</t>
+    <t xml:space="preserve">4.41908025741577</t>
   </si>
   <si>
     <t xml:space="preserve">4.14741468429565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0749716758728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02063751220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9481942653656</t>
+    <t xml:space="preserve">4.07497119903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02063846588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94819450378418</t>
   </si>
   <si>
     <t xml:space="preserve">3.93008327484131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89386081695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98441624641418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03874969482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91197228431702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87575054168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74897313117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82141709327698</t>
+    <t xml:space="preserve">3.89386177062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98441576957703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03874921798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9119725227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87575006484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74897336959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8214168548584</t>
   </si>
   <si>
     <t xml:space="preserve">3.83952832221985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62219643592834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73086261749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65841841697693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78519511222839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00252723693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18363761901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31041383743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96630525588989</t>
+    <t xml:space="preserve">3.62219667434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73086285591125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65841817855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78519535064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00252628326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18363666534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31041431427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96630549430847</t>
   </si>
   <si>
     <t xml:space="preserve">3.80330610275269</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">3.71275115013123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.441086769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53164148330688</t>
+    <t xml:space="preserve">3.44108653068542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53164196014404</t>
   </si>
   <si>
     <t xml:space="preserve">3.4954195022583</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">3.15131092071533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73475813865662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80720233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69853639602661</t>
+    <t xml:space="preserve">2.7347583770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80720210075378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69853663444519</t>
   </si>
   <si>
     <t xml:space="preserve">2.58987021446228</t>
@@ -599,139 +599,139 @@
     <t xml:space="preserve">2.77098035812378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89775729179382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09697818756104</t>
+    <t xml:space="preserve">2.8977575302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09697794914246</t>
   </si>
   <si>
     <t xml:space="preserve">3.13320016860962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33242106437683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36864280700684</t>
+    <t xml:space="preserve">3.33242082595825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36864256858826</t>
   </si>
   <si>
     <t xml:space="preserve">3.40486478805542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31431007385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1875331401825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22375440597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56786394119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54975247383118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55880808830261</t>
+    <t xml:space="preserve">3.31430959701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18753337860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22375464439392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56786346435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5497522354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55880784988403</t>
   </si>
   <si>
     <t xml:space="preserve">3.51353073120117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45014214515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42297554016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35053157806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4139199256897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34147644042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25092148780823</t>
+    <t xml:space="preserve">3.45014190673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42297577857971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35053181648254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41392040252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34147596359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25092124938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3233654499054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33267426490784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35129261016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41645693778992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49092984199524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36991095542908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5374755859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63056755065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59333038330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74227714538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84467768669128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8539867401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79813170433044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7795135974884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75158619880676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67711281776428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66780376434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65849447250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37922024726868</t>
   </si>
   <si>
     <t xml:space="preserve">3.32336521148682</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33267426490784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35129261016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41645669937134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49092984199524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36991119384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5374755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63056707382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59333038330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74227690696716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84467744827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85398650169373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79813170433044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77951335906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75158619880676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67711281776428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66780400276184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65849471092224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37922024726868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3233654499054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44438409805298</t>
+    <t xml:space="preserve">3.44438433647156</t>
   </si>
   <si>
     <t xml:space="preserve">3.21165537834167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11856412887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18372845649719</t>
+    <t xml:space="preserve">3.11856389045715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18372797966003</t>
   </si>
   <si>
     <t xml:space="preserve">3.34198355674744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43507528305054</t>
+    <t xml:space="preserve">3.43507480621338</t>
   </si>
   <si>
     <t xml:space="preserve">3.4630024433136</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">3.60263967514038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47231149673462</t>
+    <t xml:space="preserve">3.4723117351532</t>
   </si>
   <si>
     <t xml:space="preserve">3.62125825881958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52816677093506</t>
+    <t xml:space="preserve">3.5281662940979</t>
   </si>
   <si>
     <t xml:space="preserve">3.48162078857422</t>
@@ -758,43 +758,43 @@
     <t xml:space="preserve">3.64918518066406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72365856170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5188570022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77020478248596</t>
+    <t xml:space="preserve">3.72365880012512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51885747909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7702043056488</t>
   </si>
   <si>
     <t xml:space="preserve">3.58402132987976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7050404548645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68642210960388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80744075775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29543805122375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5654034614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00293254852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92845964431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.788822889328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98431515693665</t>
+    <t xml:space="preserve">3.70504021644592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68642234802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8074414730072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29543781280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56540322303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00293350219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92845940589905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78882265090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98431444168091</t>
   </si>
   <si>
     <t xml:space="preserve">3.86329579353333</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">3.81674981117249</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671522140503</t>
+    <t xml:space="preserve">4.08671569824219</t>
   </si>
   <si>
     <t xml:space="preserve">4.16118812561035</t>
@@ -812,43 +812,43 @@
     <t xml:space="preserve">4.22635221481323</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38460779190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48700904846191</t>
+    <t xml:space="preserve">4.38460731506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48700952529907</t>
   </si>
   <si>
     <t xml:space="preserve">4.35667991638184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50562763214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63595390319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49631786346436</t>
+    <t xml:space="preserve">4.5056266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63595485687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49631834030151</t>
   </si>
   <si>
     <t xml:space="preserve">4.46839046478271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28220701217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20773363113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43115377426147</t>
+    <t xml:space="preserve">4.28220748901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20773410797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43115425109863</t>
   </si>
   <si>
     <t xml:space="preserve">4.56148195266724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57079124450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45908117294312</t>
+    <t xml:space="preserve">4.57079076766968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45908164978027</t>
   </si>
   <si>
     <t xml:space="preserve">4.524245262146</t>
@@ -860,58 +860,58 @@
     <t xml:space="preserve">4.59871816635132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44046258926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37529897689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41253566741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29151678085327</t>
+    <t xml:space="preserve">4.44046306610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37529850006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41253519058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29151630401611</t>
   </si>
   <si>
     <t xml:space="preserve">4.32875299453735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23566198348999</t>
+    <t xml:space="preserve">4.23566150665283</t>
   </si>
   <si>
     <t xml:space="preserve">4.33806228637695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15187978744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13326072692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18911647796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34737157821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19842529296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3194432258606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27289867401123</t>
+    <t xml:space="preserve">4.15187931060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13326120376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18911600112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34737110137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19842576980591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31944370269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27289772033691</t>
   </si>
   <si>
     <t xml:space="preserve">4.5149359703064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39391756057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42184448242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87799263000488</t>
+    <t xml:space="preserve">4.39391708374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42184495925903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87799310684204</t>
   </si>
   <si>
     <t xml:space="preserve">4.71042823791504</t>
@@ -920,13 +920,13 @@
     <t xml:space="preserve">4.60802793502808</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61733722686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26358938217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11464309692383</t>
+    <t xml:space="preserve">4.61733675003052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26358890533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11464214324951</t>
   </si>
   <si>
     <t xml:space="preserve">4.10533332824707</t>
@@ -947,25 +947,25 @@
     <t xml:space="preserve">4.04016971588135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25428009033203</t>
+    <t xml:space="preserve">4.25428056716919</t>
   </si>
   <si>
     <t xml:space="preserve">4.65457344055176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70111894607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54286336898804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30082654953003</t>
+    <t xml:space="preserve">4.7011194229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5428638458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30082559585571</t>
   </si>
   <si>
     <t xml:space="preserve">4.44977235794067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58010053634644</t>
+    <t xml:space="preserve">4.58010005950928</t>
   </si>
   <si>
     <t xml:space="preserve">4.79421043395996</t>
@@ -974,13 +974,13 @@
     <t xml:space="preserve">4.88730192184448</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61688423156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59804010391235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52266263961792</t>
+    <t xml:space="preserve">4.61688470840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59804058074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52266216278076</t>
   </si>
   <si>
     <t xml:space="preserve">4.57919597625732</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">4.56035137176514</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44728469848633</t>
+    <t xml:space="preserve">4.44728422164917</t>
   </si>
   <si>
     <t xml:space="preserve">4.67341804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69226169586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80532932281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8995509147644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85243988037109</t>
+    <t xml:space="preserve">4.69226217269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80532884597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89955043792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85244035720825</t>
   </si>
   <si>
     <t xml:space="preserve">4.99377346038818</t>
@@ -1013,19 +1013,19 @@
     <t xml:space="preserve">4.94666194915771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04088401794434</t>
+    <t xml:space="preserve">5.04088449478149</t>
   </si>
   <si>
     <t xml:space="preserve">5.22932863235474</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60621643066406</t>
+    <t xml:space="preserve">5.60621690750122</t>
   </si>
   <si>
     <t xml:space="preserve">5.5119948387146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.700439453125</t>
+    <t xml:space="preserve">5.70043897628784</t>
   </si>
   <si>
     <t xml:space="preserve">5.65332841873169</t>
@@ -1034,19 +1034,19 @@
     <t xml:space="preserve">5.32355070114136</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37066125869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18221759796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13510608673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0879955291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75821733474731</t>
+    <t xml:space="preserve">5.37066173553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18221664428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1351056098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08799505233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75821781158447</t>
   </si>
   <si>
     <t xml:space="preserve">4.71110677719116</t>
@@ -1055,10 +1055,10 @@
     <t xml:space="preserve">4.7671914100647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69091653823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70998477935791</t>
+    <t xml:space="preserve">4.69091606140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70998525619507</t>
   </si>
   <si>
     <t xml:space="preserve">4.81486320495605</t>
@@ -1067,16 +1067,16 @@
     <t xml:space="preserve">4.748122215271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67184734344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53836679458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65277862548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57650423049927</t>
+    <t xml:space="preserve">4.67184782028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53836631774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65277910232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57650327682495</t>
   </si>
   <si>
     <t xml:space="preserve">4.72905397415161</t>
@@ -1091,28 +1091,25 @@
     <t xml:space="preserve">4.95787858963013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63370990753174</t>
+    <t xml:space="preserve">4.6337103843689</t>
   </si>
   <si>
     <t xml:space="preserve">4.6146411895752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59557247161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55743503570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69091606140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74882888793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71022033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78743743896484</t>
+    <t xml:space="preserve">4.59557294845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55743551254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74882841110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71022081375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78743696212769</t>
   </si>
   <si>
     <t xml:space="preserve">5.01908683776855</t>
@@ -1130,7 +1127,7 @@
     <t xml:space="preserve">5.30865001678467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40517091751099</t>
+    <t xml:space="preserve">5.40517044067383</t>
   </si>
   <si>
     <t xml:space="preserve">5.26038932800293</t>
@@ -1148,22 +1145,22 @@
     <t xml:space="preserve">5.64647340774536</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54995250701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21212959289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06734800338745</t>
+    <t xml:space="preserve">5.54995203018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21212911605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06734752655029</t>
   </si>
   <si>
     <t xml:space="preserve">4.92256641387939</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11560869216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87430572509766</t>
+    <t xml:space="preserve">5.11560821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87430620193481</t>
   </si>
   <si>
     <t xml:space="preserve">4.82604551315308</t>
@@ -1172,7 +1169,7 @@
     <t xml:space="preserve">4.97082662582397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86340236663818</t>
+    <t xml:space="preserve">4.86340188980103</t>
   </si>
   <si>
     <t xml:space="preserve">4.93176364898682</t>
@@ -1196,19 +1193,19 @@
     <t xml:space="preserve">4.62902116775513</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58995771408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60948991775513</t>
+    <t xml:space="preserve">4.58995819091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60948944091797</t>
   </si>
   <si>
     <t xml:space="preserve">4.55089426040649</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51183128356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53136253356934</t>
+    <t xml:space="preserve">4.51183080673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53136301040649</t>
   </si>
   <si>
     <t xml:space="preserve">4.49229907989502</t>
@@ -1250,7 +1247,7 @@
     <t xml:space="preserve">3.76962494850159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6719663143158</t>
+    <t xml:space="preserve">3.67196655273438</t>
   </si>
   <si>
     <t xml:space="preserve">3.71102976799011</t>
@@ -1262,22 +1259,22 @@
     <t xml:space="preserve">3.92587900161743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1016640663147</t>
+    <t xml:space="preserve">4.10166454315186</t>
   </si>
   <si>
     <t xml:space="preserve">4.04306936264038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12119626998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17979192733765</t>
+    <t xml:space="preserve">4.12119579315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17979145050049</t>
   </si>
   <si>
     <t xml:space="preserve">4.0821328163147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19932317733765</t>
+    <t xml:space="preserve">4.1993236541748</t>
   </si>
   <si>
     <t xml:space="preserve">4.16026020050049</t>
@@ -1292,16 +1289,16 @@
     <t xml:space="preserve">4.33604526519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25791835784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86728382110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94541049003601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43370389938354</t>
+    <t xml:space="preserve">4.25791883468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86728358268738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94541072845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4337043762207</t>
   </si>
   <si>
     <t xml:space="preserve">4.59072542190552</t>
@@ -36554,7 +36551,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1339" t="s">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -36580,7 +36577,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1340" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -36606,7 +36603,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1341" t="s">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -36632,7 +36629,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1342" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -36658,7 +36655,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1343" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -36684,7 +36681,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1344" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -36710,7 +36707,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1345" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -36736,7 +36733,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1346" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -36762,7 +36759,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1347" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -36788,7 +36785,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1348" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -36814,7 +36811,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1349" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -36840,7 +36837,7 @@
         <v>5.5</v>
       </c>
       <c r="G1350" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -36866,7 +36863,7 @@
         <v>5.5</v>
       </c>
       <c r="G1351" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -36892,7 +36889,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1352" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -36918,7 +36915,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1353" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -36944,7 +36941,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1354" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -36970,7 +36967,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1355" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -36996,7 +36993,7 @@
         <v>5.5</v>
       </c>
       <c r="G1356" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37022,7 +37019,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1357" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37048,7 +37045,7 @@
         <v>5.5</v>
       </c>
       <c r="G1358" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -37074,7 +37071,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1359" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37100,7 +37097,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1360" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37126,7 +37123,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1361" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -37152,7 +37149,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1362" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37178,7 +37175,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1363" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -37204,7 +37201,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1364" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -37230,7 +37227,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1365" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -37256,7 +37253,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1366" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -37282,7 +37279,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1367" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -37308,7 +37305,7 @@
         <v>5.75</v>
       </c>
       <c r="G1368" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -37334,7 +37331,7 @@
         <v>5.75</v>
       </c>
       <c r="G1369" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -37360,7 +37357,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1370" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -37386,7 +37383,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1371" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -37412,7 +37409,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1372" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -37438,7 +37435,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1373" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -37464,7 +37461,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1374" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -37490,7 +37487,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1375" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -37516,7 +37513,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1376" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -37542,7 +37539,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1377" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -37568,7 +37565,7 @@
         <v>5.5</v>
       </c>
       <c r="G1378" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -37594,7 +37591,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1379" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -37620,7 +37617,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1380" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -37646,7 +37643,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1381" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -37672,7 +37669,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1382" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -37698,7 +37695,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1383" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -37724,7 +37721,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1384" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -37750,7 +37747,7 @@
         <v>5.5</v>
       </c>
       <c r="G1385" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -37776,7 +37773,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1386" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -37802,7 +37799,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1387" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -37828,7 +37825,7 @@
         <v>5.25</v>
       </c>
       <c r="G1388" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -37854,7 +37851,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1389" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -37880,7 +37877,7 @@
         <v>5.25</v>
       </c>
       <c r="G1390" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -37906,7 +37903,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1391" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -37932,7 +37929,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1392" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -37958,7 +37955,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1393" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -37984,7 +37981,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1394" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38010,7 +38007,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1395" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38036,7 +38033,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1396" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38062,7 +38059,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1397" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38088,7 +38085,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1398" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -38114,7 +38111,7 @@
         <v>5</v>
       </c>
       <c r="G1399" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -38140,7 +38137,7 @@
         <v>5</v>
       </c>
       <c r="G1400" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -38166,7 +38163,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1401" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -38192,7 +38189,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1402" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -38218,7 +38215,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1403" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -38244,7 +38241,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1404" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -38270,7 +38267,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1405" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -38296,7 +38293,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1406" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -38322,7 +38319,7 @@
         <v>5.25</v>
       </c>
       <c r="G1407" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -38348,7 +38345,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1408" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -38374,7 +38371,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1409" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -38400,7 +38397,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1410" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -38426,7 +38423,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1411" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38452,7 +38449,7 @@
         <v>5.25</v>
       </c>
       <c r="G1412" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -38478,7 +38475,7 @@
         <v>5.25</v>
       </c>
       <c r="G1413" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -38504,7 +38501,7 @@
         <v>5.25</v>
       </c>
       <c r="G1414" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -38530,7 +38527,7 @@
         <v>5.25</v>
       </c>
       <c r="G1415" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -38556,7 +38553,7 @@
         <v>5.25</v>
       </c>
       <c r="G1416" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -38582,7 +38579,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1417" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -38608,7 +38605,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1418" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -38634,7 +38631,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1419" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -38660,7 +38657,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1420" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -38686,7 +38683,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1421" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -38712,7 +38709,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1422" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -38738,7 +38735,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1423" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -38764,7 +38761,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1424" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -38790,7 +38787,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1425" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -38816,7 +38813,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1426" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -38842,7 +38839,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1427" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -38868,7 +38865,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1428" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -38894,7 +38891,7 @@
         <v>5.25</v>
       </c>
       <c r="G1429" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -38920,7 +38917,7 @@
         <v>5.25</v>
       </c>
       <c r="G1430" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -38946,7 +38943,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1431" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -38972,7 +38969,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1432" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -38998,7 +38995,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1433" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39024,7 +39021,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1434" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39050,7 +39047,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1435" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -39076,7 +39073,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1436" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -39102,7 +39099,7 @@
         <v>5</v>
       </c>
       <c r="G1437" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39128,7 +39125,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1438" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39154,7 +39151,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1439" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39180,7 +39177,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1440" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -39206,7 +39203,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1441" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -39232,7 +39229,7 @@
         <v>5</v>
       </c>
       <c r="G1442" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39258,7 +39255,7 @@
         <v>5</v>
       </c>
       <c r="G1443" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -39284,7 +39281,7 @@
         <v>5</v>
       </c>
       <c r="G1444" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -39310,7 +39307,7 @@
         <v>5</v>
       </c>
       <c r="G1445" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -39336,7 +39333,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1446" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -39362,7 +39359,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1447" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -39388,7 +39385,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1448" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -39414,7 +39411,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1449" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39440,7 +39437,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1450" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39466,7 +39463,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1451" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39492,7 +39489,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1452" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39518,7 +39515,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1453" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39544,7 +39541,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1454" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39570,7 +39567,7 @@
         <v>5</v>
       </c>
       <c r="G1455" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39596,7 +39593,7 @@
         <v>5</v>
       </c>
       <c r="G1456" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39622,7 +39619,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1457" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39648,7 +39645,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1458" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39674,7 +39671,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1459" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39700,7 +39697,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1460" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -39726,7 +39723,7 @@
         <v>5</v>
       </c>
       <c r="G1461" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -39752,7 +39749,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1462" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -39778,7 +39775,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1463" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -39804,7 +39801,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1464" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -39830,7 +39827,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1465" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -39856,7 +39853,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1466" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -39882,7 +39879,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1467" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -39908,7 +39905,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1468" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -39934,7 +39931,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1469" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -39960,7 +39957,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1470" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -39986,7 +39983,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1471" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40012,7 +40009,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1472" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40038,7 +40035,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1473" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40064,7 +40061,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1474" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40090,7 +40087,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1475" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -40116,7 +40113,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1476" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -40142,7 +40139,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1477" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -40168,7 +40165,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1478" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -40194,7 +40191,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1479" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -40220,7 +40217,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1480" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -40246,7 +40243,7 @@
         <v>4.5</v>
       </c>
       <c r="G1481" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -40272,7 +40269,7 @@
         <v>4.5</v>
       </c>
       <c r="G1482" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -40298,7 +40295,7 @@
         <v>4.5</v>
       </c>
       <c r="G1483" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -40324,7 +40321,7 @@
         <v>4.5</v>
       </c>
       <c r="G1484" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -40350,7 +40347,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1485" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -40376,7 +40373,7 @@
         <v>4.5</v>
       </c>
       <c r="G1486" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -40402,7 +40399,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1487" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -40428,7 +40425,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1488" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40454,7 +40451,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1489" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40480,7 +40477,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1490" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40506,7 +40503,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1491" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40532,7 +40529,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1492" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -40558,7 +40555,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1493" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40584,7 +40581,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1494" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -40610,7 +40607,7 @@
         <v>4.5</v>
       </c>
       <c r="G1495" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -40636,7 +40633,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1496" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -40662,7 +40659,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1497" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -40688,7 +40685,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1498" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -40714,7 +40711,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1499" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -40740,7 +40737,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1500" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -40766,7 +40763,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1501" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -40792,7 +40789,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1502" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -40818,7 +40815,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1503" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -40844,7 +40841,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1504" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -40870,7 +40867,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1505" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -40896,7 +40893,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1506" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -40922,7 +40919,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1507" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -40948,7 +40945,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1508" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -40974,7 +40971,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1509" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41000,7 +40997,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1510" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41026,7 +41023,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1511" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41052,7 +41049,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1512" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41078,7 +41075,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1513" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41104,7 +41101,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1514" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41130,7 +41127,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1515" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41156,7 +41153,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1516" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41182,7 +41179,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1517" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -41208,7 +41205,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1518" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -41234,7 +41231,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1519" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41260,7 +41257,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1520" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -41286,7 +41283,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1521" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -41312,7 +41309,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1522" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -41338,7 +41335,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1523" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -41364,7 +41361,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1524" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -41390,7 +41387,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1525" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -41416,7 +41413,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1526" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41442,7 +41439,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1527" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41468,7 +41465,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1528" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41494,7 +41491,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1529" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41520,7 +41517,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1530" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41546,7 +41543,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1531" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41572,7 +41569,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1532" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41598,7 +41595,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1533" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41624,7 +41621,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1534" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41650,7 +41647,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1535" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41676,7 +41673,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1536" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41702,7 +41699,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1537" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -41728,7 +41725,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1538" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -41754,7 +41751,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1539" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -41780,7 +41777,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1540" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -41806,7 +41803,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1541" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -41832,7 +41829,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1542" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -41858,7 +41855,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1543" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -41884,7 +41881,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1544" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -41910,7 +41907,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1545" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -41936,7 +41933,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1546" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -41962,7 +41959,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1547" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -41988,7 +41985,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1548" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42014,7 +42011,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1549" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42040,7 +42037,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1550" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42066,7 +42063,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1551" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42092,7 +42089,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1552" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42118,7 +42115,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1553" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42144,7 +42141,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1554" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42170,7 +42167,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1555" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42196,7 +42193,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1556" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42222,7 +42219,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1557" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -42248,7 +42245,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1558" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -42274,7 +42271,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1559" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -42300,7 +42297,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1560" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -42326,7 +42323,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1561" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -42352,7 +42349,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1562" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -42378,7 +42375,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1563" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -42404,7 +42401,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1564" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -42430,7 +42427,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1565" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42456,7 +42453,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1566" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42482,7 +42479,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1567" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42508,7 +42505,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1568" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42534,7 +42531,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1569" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42560,7 +42557,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1570" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42586,7 +42583,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1571" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42612,7 +42609,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1572" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42638,7 +42635,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1573" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42664,7 +42661,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1574" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42690,7 +42687,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1575" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -42716,7 +42713,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1576" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -42742,7 +42739,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1577" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -42768,7 +42765,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1578" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -42794,7 +42791,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1579" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -42820,7 +42817,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1580" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -42846,7 +42843,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1581" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -42872,7 +42869,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1582" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -42898,7 +42895,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1583" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -42924,7 +42921,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1584" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -42950,7 +42947,7 @@
         <v>4.5</v>
       </c>
       <c r="G1585" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -42976,7 +42973,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43002,7 +42999,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1587" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43028,7 +43025,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1588" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43054,7 +43051,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1589" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43080,7 +43077,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1590" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43106,7 +43103,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1591" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43132,7 +43129,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1592" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43158,7 +43155,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1593" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43184,7 +43181,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1594" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43210,7 +43207,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1595" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -43236,7 +43233,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1596" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43262,7 +43259,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1597" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -43288,7 +43285,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1598" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -43314,7 +43311,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1599" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -43340,7 +43337,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1600" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -43366,7 +43363,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1601" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -43392,7 +43389,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1602" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -43418,7 +43415,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1603" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43444,7 +43441,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1604" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43470,7 +43467,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1605" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43496,7 +43493,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1606" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43522,7 +43519,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1607" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43548,7 +43545,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1608" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43574,7 +43571,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1609" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43600,7 +43597,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1610" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43626,7 +43623,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1611" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43652,7 +43649,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1612" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43678,7 +43675,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1613" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43704,7 +43701,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1614" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43730,7 +43727,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1615" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -43756,7 +43753,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1616" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43782,7 +43779,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1617" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43808,7 +43805,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1618" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43834,7 +43831,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1619" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43860,7 +43857,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1620" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -43886,7 +43883,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1621" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -43912,7 +43909,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1622" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -43938,7 +43935,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1623" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -43964,7 +43961,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1624" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -43990,7 +43987,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1625" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44016,7 +44013,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1626" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44042,7 +44039,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1627" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44068,7 +44065,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1628" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44094,7 +44091,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1629" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44120,7 +44117,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1630" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44146,7 +44143,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1631" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44172,7 +44169,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1632" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44198,7 +44195,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1633" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44224,7 +44221,7 @@
         <v>5.75</v>
       </c>
       <c r="G1634" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44250,7 +44247,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1635" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44276,7 +44273,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1636" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44302,7 +44299,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1637" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44328,7 +44325,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1638" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44354,7 +44351,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1639" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44380,7 +44377,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1640" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44406,7 +44403,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1641" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44432,7 +44429,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1642" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44458,7 +44455,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1643" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44484,7 +44481,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1644" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44510,7 +44507,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1645" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44536,7 +44533,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1646" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44562,7 +44559,7 @@
         <v>5.75</v>
       </c>
       <c r="G1647" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44588,7 +44585,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1648" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44614,7 +44611,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1649" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44640,7 +44637,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1650" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44666,7 +44663,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1651" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44692,7 +44689,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1652" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44718,7 +44715,7 @@
         <v>5.25</v>
       </c>
       <c r="G1653" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44744,7 +44741,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1654" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44770,7 +44767,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1655" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44796,7 +44793,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1656" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44822,7 +44819,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1657" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44848,7 +44845,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1658" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44874,7 +44871,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1659" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -44900,7 +44897,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1660" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44926,7 +44923,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1661" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44952,7 +44949,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1662" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44978,7 +44975,7 @@
         <v>5.5</v>
       </c>
       <c r="G1663" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45004,7 +45001,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1664" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45030,7 +45027,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1665" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45056,7 +45053,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1666" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45082,7 +45079,7 @@
         <v>5.5</v>
       </c>
       <c r="G1667" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45108,7 +45105,7 @@
         <v>5.5</v>
       </c>
       <c r="G1668" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45134,7 +45131,7 @@
         <v>5.5</v>
       </c>
       <c r="G1669" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45160,7 +45157,7 @@
         <v>5.5</v>
       </c>
       <c r="G1670" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45186,7 +45183,7 @@
         <v>5.5</v>
       </c>
       <c r="G1671" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45212,7 +45209,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1672" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45238,7 +45235,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1673" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45264,7 +45261,7 @@
         <v>5.75</v>
       </c>
       <c r="G1674" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45290,7 +45287,7 @@
         <v>5.75</v>
       </c>
       <c r="G1675" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45316,7 +45313,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1676" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45342,7 +45339,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1677" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45368,7 +45365,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1678" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45394,7 +45391,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1679" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45420,7 +45417,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1680" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45446,7 +45443,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1681" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45472,7 +45469,7 @@
         <v>5.75</v>
       </c>
       <c r="G1682" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45498,7 +45495,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1683" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45524,7 +45521,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1684" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45550,7 +45547,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1685" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45576,7 +45573,7 @@
         <v>5.5</v>
       </c>
       <c r="G1686" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45602,7 +45599,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1687" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45628,7 +45625,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1688" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45654,7 +45651,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1689" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45680,7 +45677,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1690" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45706,7 +45703,7 @@
         <v>5.75</v>
       </c>
       <c r="G1691" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45732,7 +45729,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1692" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45758,7 +45755,7 @@
         <v>5.75</v>
       </c>
       <c r="G1693" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45784,7 +45781,7 @@
         <v>5.75</v>
       </c>
       <c r="G1694" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45810,7 +45807,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1695" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45836,7 +45833,7 @@
         <v>6</v>
       </c>
       <c r="G1696" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45862,7 +45859,7 @@
         <v>6</v>
       </c>
       <c r="G1697" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -45888,7 +45885,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1698" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -45914,7 +45911,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1699" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -45940,7 +45937,7 @@
         <v>5.75</v>
       </c>
       <c r="G1700" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -45966,7 +45963,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1701" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -45992,7 +45989,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1702" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46018,7 +46015,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1703" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46044,7 +46041,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1704" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46070,7 +46067,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1705" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46096,7 +46093,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1706" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46122,7 +46119,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1707" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46148,7 +46145,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1708" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46174,7 +46171,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1709" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46200,7 +46197,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1710" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46226,7 +46223,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1711" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46252,7 +46249,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1712" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46278,7 +46275,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1713" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46304,7 +46301,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1714" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46330,9 +46327,61 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1715" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1715" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" s="1" t="n">
+        <v>45973.3333333333</v>
+      </c>
+      <c r="B1716" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1716" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="D1716" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="E1716" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="F1716" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="G1716" t="s">
+        <v>463</v>
+      </c>
+      <c r="H1716" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" s="1" t="n">
+        <v>45974.3669328704</v>
+      </c>
+      <c r="B1717" t="n">
+        <v>600</v>
+      </c>
+      <c r="C1717" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="D1717" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="E1717" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="F1717" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="G1717" t="s">
+        <v>459</v>
+      </c>
+      <c r="H1717" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ILP.MI.xlsx
+++ b/data/ILP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="464">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,166 +38,166 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9502626657486</t>
+    <t xml:space="preserve">1.95026290416718</t>
   </si>
   <si>
     <t xml:space="preserve">ILP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97638237476349</t>
+    <t xml:space="preserve">1.97638213634491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91543638706207</t>
+    <t xml:space="preserve">1.91543650627136</t>
   </si>
   <si>
     <t xml:space="preserve">1.94112086296082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00685501098633</t>
+    <t xml:space="preserve">2.00685524940491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97986507415771</t>
+    <t xml:space="preserve">1.97986459732056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93284964561462</t>
+    <t xml:space="preserve">1.93284928798676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95853364467621</t>
+    <t xml:space="preserve">1.95853388309479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92109596729279</t>
+    <t xml:space="preserve">1.9210958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94199120998383</t>
+    <t xml:space="preserve">1.9419914484024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95418047904968</t>
+    <t xml:space="preserve">1.95418012142181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93067300319672</t>
+    <t xml:space="preserve">1.93067276477814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88931655883789</t>
+    <t xml:space="preserve">1.88931691646576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8679860830307</t>
+    <t xml:space="preserve">1.86798584461212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8906227350235</t>
+    <t xml:space="preserve">1.89062285423279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91978967189789</t>
+    <t xml:space="preserve">1.91978991031647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9415557384491</t>
+    <t xml:space="preserve">1.94155621528625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93807351589203</t>
+    <t xml:space="preserve">1.93807339668274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91717791557312</t>
+    <t xml:space="preserve">1.91717755794525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9755117893219</t>
+    <t xml:space="preserve">1.97551155090332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93459057807922</t>
+    <t xml:space="preserve">1.93459069728851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96767568588257</t>
+    <t xml:space="preserve">1.96767544746399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02775096893311</t>
+    <t xml:space="preserve">2.02775073051453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01556134223938</t>
+    <t xml:space="preserve">2.01556158065796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00250196456909</t>
+    <t xml:space="preserve">2.00250172615051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01991510391235</t>
+    <t xml:space="preserve">2.01991486549377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89802360534668</t>
+    <t xml:space="preserve">1.89802324771881</t>
   </si>
   <si>
     <t xml:space="preserve">1.98508882522583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88061082363129</t>
+    <t xml:space="preserve">1.88061046600342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84578418731689</t>
+    <t xml:space="preserve">1.8457840681076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86319708824158</t>
+    <t xml:space="preserve">1.86319756507874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88994169235229</t>
+    <t xml:space="preserve">1.88994157314301</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90777122974396</t>
+    <t xml:space="preserve">1.90777170658112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87211203575134</t>
+    <t xml:space="preserve">1.87211215496063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92560148239136</t>
+    <t xml:space="preserve">1.92560112476349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94343090057373</t>
+    <t xml:space="preserve">1.94343054294586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96126019954681</t>
+    <t xml:space="preserve">1.9612603187561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97909009456635</t>
+    <t xml:space="preserve">1.97908973693848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83645272254944</t>
+    <t xml:space="preserve">1.83645296096802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81862330436707</t>
+    <t xml:space="preserve">1.81862306594849</t>
   </si>
   <si>
     <t xml:space="preserve">1.76513421535492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8542822599411</t>
+    <t xml:space="preserve">1.85428237915039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80079340934753</t>
+    <t xml:space="preserve">1.80079352855682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78296411037445</t>
+    <t xml:space="preserve">1.78296387195587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93451547622681</t>
+    <t xml:space="preserve">1.93451583385468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95234525203705</t>
+    <t xml:space="preserve">1.95234572887421</t>
   </si>
   <si>
     <t xml:space="preserve">1.88102674484253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89885652065277</t>
+    <t xml:space="preserve">1.89885663986206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82753813266754</t>
+    <t xml:space="preserve">1.82753801345825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8453676700592</t>
+    <t xml:space="preserve">1.84536755084991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86319732666016</t>
+    <t xml:space="preserve">1.86319720745087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72947490215302</t>
+    <t xml:space="preserve">1.7294750213623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77404916286469</t>
+    <t xml:space="preserve">1.77404928207397</t>
   </si>
   <si>
     <t xml:space="preserve">1.7695916891098</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">1.79187870025635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80970859527588</t>
+    <t xml:space="preserve">1.8097083568573</t>
   </si>
   <si>
     <t xml:space="preserve">1.77850651741028</t>
@@ -215,19 +215,19 @@
     <t xml:space="preserve">1.70718777179718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72501766681671</t>
+    <t xml:space="preserve">1.72501754760742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74730467796326</t>
+    <t xml:space="preserve">1.74730455875397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73838996887207</t>
+    <t xml:space="preserve">1.73838984966278</t>
   </si>
   <si>
     <t xml:space="preserve">1.75621962547302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71164560317993</t>
+    <t xml:space="preserve">1.71164524555206</t>
   </si>
   <si>
     <t xml:space="preserve">1.72056007385254</t>
@@ -239,67 +239,67 @@
     <t xml:space="preserve">1.64032685756683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6492418050766</t>
+    <t xml:space="preserve">1.64924156665802</t>
   </si>
   <si>
     <t xml:space="preserve">1.67598617076874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56900823116302</t>
+    <t xml:space="preserve">1.56900811195374</t>
   </si>
   <si>
     <t xml:space="preserve">1.66707134246826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63141202926636</t>
+    <t xml:space="preserve">1.63141191005707</t>
   </si>
   <si>
     <t xml:space="preserve">1.65815651416779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68490087985992</t>
+    <t xml:space="preserve">1.6849011182785</t>
   </si>
   <si>
     <t xml:space="preserve">1.70273053646088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61358225345612</t>
+    <t xml:space="preserve">1.61358213424683</t>
   </si>
   <si>
     <t xml:space="preserve">2.03257894515991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19304537773132</t>
+    <t xml:space="preserve">2.19304609298706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13955688476562</t>
+    <t xml:space="preserve">2.13955664634705</t>
   </si>
   <si>
     <t xml:space="preserve">2.38917183876038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33568286895752</t>
+    <t xml:space="preserve">2.33568263053894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54963803291321</t>
+    <t xml:space="preserve">2.54963827133179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58529758453369</t>
+    <t xml:space="preserve">2.58529782295227</t>
   </si>
   <si>
     <t xml:space="preserve">3.03103876113892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42329120635986</t>
+    <t xml:space="preserve">3.42329049110413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22716450691223</t>
+    <t xml:space="preserve">3.22716426849365</t>
   </si>
   <si>
     <t xml:space="preserve">3.19150519371033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13801646232605</t>
+    <t xml:space="preserve">3.13801622390747</t>
   </si>
   <si>
     <t xml:space="preserve">3.01320910453796</t>
@@ -311,16 +311,16 @@
     <t xml:space="preserve">2.97754955291748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08452749252319</t>
+    <t xml:space="preserve">3.08452796936035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88840174674988</t>
+    <t xml:space="preserve">2.8884015083313</t>
   </si>
   <si>
     <t xml:space="preserve">2.71010494232178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69227528572083</t>
+    <t xml:space="preserve">2.6922755241394</t>
   </si>
   <si>
     <t xml:space="preserve">2.67444586753845</t>
@@ -329,37 +329,37 @@
     <t xml:space="preserve">2.79925346374512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83491277694702</t>
+    <t xml:space="preserve">2.83491253852844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90623116493225</t>
+    <t xml:space="preserve">2.90623092651367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78142333030701</t>
+    <t xml:space="preserve">2.78142404556274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87057185173035</t>
+    <t xml:space="preserve">2.87057161331177</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0055513381958</t>
+    <t xml:space="preserve">3.00555157661438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0775408744812</t>
+    <t xml:space="preserve">3.07754111289978</t>
   </si>
   <si>
     <t xml:space="preserve">2.9875545501709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05954360961914</t>
+    <t xml:space="preserve">3.05954337120056</t>
   </si>
   <si>
     <t xml:space="preserve">3.14952993392944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2035219669342</t>
+    <t xml:space="preserve">3.20352220535278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32950377464294</t>
+    <t xml:space="preserve">3.32950329780579</t>
   </si>
   <si>
     <t xml:space="preserve">3.38349509239197</t>
@@ -368,25 +368,25 @@
     <t xml:space="preserve">3.36549782752991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34750056266785</t>
+    <t xml:space="preserve">3.34750080108643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2755115032196</t>
+    <t xml:space="preserve">3.27551126480103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31150603294373</t>
+    <t xml:space="preserve">3.31150650978088</t>
   </si>
   <si>
     <t xml:space="preserve">3.29350876808167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41949009895325</t>
+    <t xml:space="preserve">3.41948962211609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25751399993896</t>
+    <t xml:space="preserve">3.25751376152039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2395167350769</t>
+    <t xml:space="preserve">3.23951649665833</t>
   </si>
   <si>
     <t xml:space="preserve">3.22151947021484</t>
@@ -395,52 +395,52 @@
     <t xml:space="preserve">3.40149259567261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43748712539673</t>
+    <t xml:space="preserve">3.43748736381531</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65345525741577</t>
+    <t xml:space="preserve">3.65345501899719</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56346845626831</t>
+    <t xml:space="preserve">3.56346821784973</t>
   </si>
   <si>
     <t xml:space="preserve">3.63545775413513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86942338943481</t>
+    <t xml:space="preserve">3.86942362785339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99540424346924</t>
+    <t xml:space="preserve">3.99540519714355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01340103149414</t>
+    <t xml:space="preserve">4.01340198516846</t>
   </si>
   <si>
     <t xml:space="preserve">3.94141221046448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76143932342529</t>
+    <t xml:space="preserve">3.76143908500671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.923415184021</t>
+    <t xml:space="preserve">3.92341494560242</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97740697860718</t>
+    <t xml:space="preserve">3.97740721702576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8874204158783</t>
+    <t xml:space="preserve">3.88742065429688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85142517089844</t>
+    <t xml:space="preserve">3.85142540931702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90541696548462</t>
+    <t xml:space="preserve">3.90541768074036</t>
   </si>
   <si>
     <t xml:space="preserve">4.175377368927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15737962722778</t>
+    <t xml:space="preserve">4.15738010406494</t>
   </si>
   <si>
     <t xml:space="preserve">4.24736642837524</t>
@@ -455,31 +455,31 @@
     <t xml:space="preserve">4.31935548782349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30135917663574</t>
+    <t xml:space="preserve">4.30135869979858</t>
   </si>
   <si>
     <t xml:space="preserve">4.32852506637573</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34663581848145</t>
+    <t xml:space="preserve">4.3466362953186</t>
   </si>
   <si>
     <t xml:space="preserve">4.23796939849854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20174741744995</t>
+    <t xml:space="preserve">4.20174789428711</t>
   </si>
   <si>
     <t xml:space="preserve">4.21985912322998</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1293044090271</t>
+    <t xml:space="preserve">4.12930393218994</t>
   </si>
   <si>
     <t xml:space="preserve">4.05686044692993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16552591323853</t>
+    <t xml:space="preserve">4.16552639007568</t>
   </si>
   <si>
     <t xml:space="preserve">4.09308195114136</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">4.29230260848999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11119270324707</t>
+    <t xml:space="preserve">4.11119318008423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25608062744141</t>
+    <t xml:space="preserve">4.25608110427856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41908025741577</t>
+    <t xml:space="preserve">4.41907978057861</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14741468429565</t>
+    <t xml:space="preserve">4.14741516113281</t>
   </si>
   <si>
     <t xml:space="preserve">4.07497119903564</t>
@@ -509,61 +509,61 @@
     <t xml:space="preserve">4.02063846588135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94819450378418</t>
+    <t xml:space="preserve">3.94819474220276</t>
   </si>
   <si>
     <t xml:space="preserve">3.93008327484131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89386177062988</t>
+    <t xml:space="preserve">3.89386200904846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98441576957703</t>
+    <t xml:space="preserve">3.98441648483276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03874921798706</t>
+    <t xml:space="preserve">4.03874969482422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9119725227356</t>
+    <t xml:space="preserve">3.91197299957275</t>
   </si>
   <si>
     <t xml:space="preserve">3.87575006484985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74897336959839</t>
+    <t xml:space="preserve">3.74897313117981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8214168548584</t>
+    <t xml:space="preserve">3.82141733169556</t>
   </si>
   <si>
     <t xml:space="preserve">3.83952832221985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62219667434692</t>
+    <t xml:space="preserve">3.62219643592834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73086285591125</t>
+    <t xml:space="preserve">3.73086190223694</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65841817855835</t>
+    <t xml:space="preserve">3.65841865539551</t>
   </si>
   <si>
     <t xml:space="preserve">3.78519535064697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00252628326416</t>
+    <t xml:space="preserve">4.00252676010132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18363666534424</t>
+    <t xml:space="preserve">4.1836371421814</t>
   </si>
   <si>
     <t xml:space="preserve">4.31041431427002</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96630549430847</t>
+    <t xml:space="preserve">3.96630573272705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80330610275269</t>
+    <t xml:space="preserve">3.80330657958984</t>
   </si>
   <si>
     <t xml:space="preserve">3.71275115013123</t>
@@ -572,34 +572,34 @@
     <t xml:space="preserve">3.44108653068542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53164196014404</t>
+    <t xml:space="preserve">3.53164148330688</t>
   </si>
   <si>
     <t xml:space="preserve">3.4954195022583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38675379753113</t>
+    <t xml:space="preserve">3.38675355911255</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15131092071533</t>
+    <t xml:space="preserve">3.15131115913391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7347583770752</t>
+    <t xml:space="preserve">2.73475813865662</t>
   </si>
   <si>
     <t xml:space="preserve">2.80720210075378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69853663444519</t>
+    <t xml:space="preserve">2.69853615760803</t>
   </si>
   <si>
     <t xml:space="preserve">2.58987021446228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77098035812378</t>
+    <t xml:space="preserve">2.7709801197052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8977575302124</t>
+    <t xml:space="preserve">2.89775705337524</t>
   </si>
   <si>
     <t xml:space="preserve">3.09697794914246</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">3.33242082595825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36864256858826</t>
+    <t xml:space="preserve">3.36864280700684</t>
   </si>
   <si>
     <t xml:space="preserve">3.40486478805542</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">3.31430959701538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18753337860107</t>
+    <t xml:space="preserve">3.18753266334534</t>
   </si>
   <si>
     <t xml:space="preserve">3.22375464439392</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">3.56786346435547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5497522354126</t>
+    <t xml:space="preserve">3.54975271224976</t>
   </si>
   <si>
     <t xml:space="preserve">3.55880784988403</t>
@@ -638,19 +638,19 @@
     <t xml:space="preserve">3.51353073120117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45014190673828</t>
+    <t xml:space="preserve">3.45014214515686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42297577857971</t>
+    <t xml:space="preserve">3.42297554016113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35053181648254</t>
+    <t xml:space="preserve">3.35053157806396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41392040252686</t>
+    <t xml:space="preserve">3.4139199256897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34147596359253</t>
+    <t xml:space="preserve">3.34147620201111</t>
   </si>
   <si>
     <t xml:space="preserve">3.25092124938965</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">3.49092984199524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36991095542908</t>
+    <t xml:space="preserve">3.3699107170105</t>
   </si>
   <si>
     <t xml:space="preserve">3.5374755859375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63056755065918</t>
+    <t xml:space="preserve">3.6305673122406</t>
   </si>
   <si>
     <t xml:space="preserve">3.59333038330078</t>
@@ -686,64 +686,61 @@
     <t xml:space="preserve">3.74227714538574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84467768669128</t>
+    <t xml:space="preserve">3.84467720985413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8539867401123</t>
+    <t xml:space="preserve">3.85398650169373</t>
   </si>
   <si>
     <t xml:space="preserve">3.79813170433044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7795135974884</t>
+    <t xml:space="preserve">3.77951335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75158619880676</t>
+    <t xml:space="preserve">3.75158643722534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67711281776428</t>
+    <t xml:space="preserve">3.67711305618286</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66780376434326</t>
+    <t xml:space="preserve">3.66780400276184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65849447250366</t>
+    <t xml:space="preserve">3.65849471092224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37922024726868</t>
+    <t xml:space="preserve">3.37922048568726</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32336521148682</t>
+    <t xml:space="preserve">3.44438409805298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44438433647156</t>
+    <t xml:space="preserve">3.21165585517883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21165537834167</t>
+    <t xml:space="preserve">3.11856412887573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11856389045715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18372797966003</t>
+    <t xml:space="preserve">3.18372821807861</t>
   </si>
   <si>
     <t xml:space="preserve">3.34198355674744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43507480621338</t>
+    <t xml:space="preserve">3.43507528305054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4630024433136</t>
+    <t xml:space="preserve">3.46300268173218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60263967514038</t>
+    <t xml:space="preserve">3.6026394367218</t>
   </si>
   <si>
     <t xml:space="preserve">3.4723117351532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62125825881958</t>
+    <t xml:space="preserve">3.621258020401</t>
   </si>
   <si>
     <t xml:space="preserve">3.5281662940979</t>
@@ -755,7 +752,7 @@
     <t xml:space="preserve">3.42576599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64918518066406</t>
+    <t xml:space="preserve">3.64918565750122</t>
   </si>
   <si>
     <t xml:space="preserve">3.72365880012512</t>
@@ -773,10 +770,10 @@
     <t xml:space="preserve">3.70504021644592</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68642234802246</t>
+    <t xml:space="preserve">3.6864218711853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8074414730072</t>
+    <t xml:space="preserve">3.80744075775146</t>
   </si>
   <si>
     <t xml:space="preserve">3.29543781280518</t>
@@ -785,22 +782,22 @@
     <t xml:space="preserve">3.56540322303772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00293350219727</t>
+    <t xml:space="preserve">4.00293302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92845940589905</t>
+    <t xml:space="preserve">3.92845964431763</t>
   </si>
   <si>
     <t xml:space="preserve">3.78882265090942</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98431444168091</t>
+    <t xml:space="preserve">3.98431468009949</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86329579353333</t>
+    <t xml:space="preserve">3.86329555511475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81674981117249</t>
+    <t xml:space="preserve">3.81675004959106</t>
   </si>
   <si>
     <t xml:space="preserve">4.08671569824219</t>
@@ -809,28 +806,28 @@
     <t xml:space="preserve">4.16118812561035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22635221481323</t>
+    <t xml:space="preserve">4.22635269165039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38460731506348</t>
+    <t xml:space="preserve">4.38460779190063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48700952529907</t>
+    <t xml:space="preserve">4.48700857162476</t>
   </si>
   <si>
     <t xml:space="preserve">4.35667991638184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5056266784668</t>
+    <t xml:space="preserve">4.50562715530396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63595485687256</t>
+    <t xml:space="preserve">4.63595533370972</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49631834030151</t>
+    <t xml:space="preserve">4.4963173866272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46839046478271</t>
+    <t xml:space="preserve">4.46839094161987</t>
   </si>
   <si>
     <t xml:space="preserve">4.28220748901367</t>
@@ -839,25 +836,25 @@
     <t xml:space="preserve">4.20773410797119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43115425109863</t>
+    <t xml:space="preserve">4.43115377426147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56148195266724</t>
+    <t xml:space="preserve">4.56148099899292</t>
   </si>
   <si>
     <t xml:space="preserve">4.57079076766968</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45908164978027</t>
+    <t xml:space="preserve">4.45908069610596</t>
   </si>
   <si>
     <t xml:space="preserve">4.524245262146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58940887451172</t>
+    <t xml:space="preserve">4.58940935134888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59871816635132</t>
+    <t xml:space="preserve">4.59871912002563</t>
   </si>
   <si>
     <t xml:space="preserve">4.44046306610107</t>
@@ -866,7 +863,7 @@
     <t xml:space="preserve">4.37529850006104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41253519058228</t>
+    <t xml:space="preserve">4.41253566741943</t>
   </si>
   <si>
     <t xml:space="preserve">4.29151630401611</t>
@@ -875,13 +872,13 @@
     <t xml:space="preserve">4.32875299453735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23566150665283</t>
+    <t xml:space="preserve">4.23566198348999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33806228637695</t>
+    <t xml:space="preserve">4.33806180953979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15187931060791</t>
+    <t xml:space="preserve">4.15187883377075</t>
   </si>
   <si>
     <t xml:space="preserve">4.13326120376587</t>
@@ -890,52 +887,52 @@
     <t xml:space="preserve">4.18911600112915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34737110137939</t>
+    <t xml:space="preserve">4.34737157821655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19842576980591</t>
+    <t xml:space="preserve">4.19842529296875</t>
   </si>
   <si>
     <t xml:space="preserve">4.31944370269775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27289772033691</t>
+    <t xml:space="preserve">4.27289819717407</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5149359703064</t>
+    <t xml:space="preserve">4.51493644714355</t>
   </si>
   <si>
     <t xml:space="preserve">4.39391708374023</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42184495925903</t>
+    <t xml:space="preserve">4.42184448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87799310684204</t>
+    <t xml:space="preserve">4.87799263000488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71042823791504</t>
+    <t xml:space="preserve">4.71042776107788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60802793502808</t>
+    <t xml:space="preserve">4.60802745819092</t>
   </si>
   <si>
     <t xml:space="preserve">4.61733675003052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26358890533447</t>
+    <t xml:space="preserve">4.26358938217163</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11464214324951</t>
+    <t xml:space="preserve">4.11464309692383</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10533332824707</t>
+    <t xml:space="preserve">4.10533380508423</t>
   </si>
   <si>
     <t xml:space="preserve">4.17980670928955</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07740640640259</t>
+    <t xml:space="preserve">4.07740592956543</t>
   </si>
   <si>
     <t xml:space="preserve">3.95638728141785</t>
@@ -944,19 +941,19 @@
     <t xml:space="preserve">3.90984129905701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04016971588135</t>
+    <t xml:space="preserve">4.04017019271851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25428056716919</t>
+    <t xml:space="preserve">4.25428009033203</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65457344055176</t>
+    <t xml:space="preserve">4.6545729637146</t>
   </si>
   <si>
     <t xml:space="preserve">4.7011194229126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5428638458252</t>
+    <t xml:space="preserve">4.54286336898804</t>
   </si>
   <si>
     <t xml:space="preserve">4.30082559585571</t>
@@ -974,40 +971,40 @@
     <t xml:space="preserve">4.88730192184448</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61688470840454</t>
+    <t xml:space="preserve">4.61688375473022</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59804058074951</t>
+    <t xml:space="preserve">4.59804010391235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52266216278076</t>
+    <t xml:space="preserve">4.52266311645508</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57919597625732</t>
+    <t xml:space="preserve">4.57919549942017</t>
   </si>
   <si>
     <t xml:space="preserve">4.56035137176514</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44728422164917</t>
+    <t xml:space="preserve">4.44728469848633</t>
   </si>
   <si>
     <t xml:space="preserve">4.67341804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69226217269897</t>
+    <t xml:space="preserve">4.69226264953613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80532884597778</t>
+    <t xml:space="preserve">4.80532836914062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89955043792725</t>
+    <t xml:space="preserve">4.8995509147644</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85244035720825</t>
+    <t xml:space="preserve">4.85243988037109</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99377346038818</t>
+    <t xml:space="preserve">4.99377298355103</t>
   </si>
   <si>
     <t xml:space="preserve">4.94666194915771</t>
@@ -1022,34 +1019,34 @@
     <t xml:space="preserve">5.60621690750122</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5119948387146</t>
+    <t xml:space="preserve">5.51199436187744</t>
   </si>
   <si>
     <t xml:space="preserve">5.70043897628784</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65332841873169</t>
+    <t xml:space="preserve">5.65332746505737</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32355070114136</t>
+    <t xml:space="preserve">5.3235502243042</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37066173553467</t>
+    <t xml:space="preserve">5.37066125869751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18221664428711</t>
+    <t xml:space="preserve">5.18221759796143</t>
   </si>
   <si>
     <t xml:space="preserve">5.1351056098938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08799505233765</t>
+    <t xml:space="preserve">5.0879955291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75821781158447</t>
+    <t xml:space="preserve">4.75821828842163</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71110677719116</t>
+    <t xml:space="preserve">4.711106300354</t>
   </si>
   <si>
     <t xml:space="preserve">4.7671914100647</t>
@@ -1061,13 +1058,13 @@
     <t xml:space="preserve">4.70998525619507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81486320495605</t>
+    <t xml:space="preserve">4.81486368179321</t>
   </si>
   <si>
-    <t xml:space="preserve">4.748122215271</t>
+    <t xml:space="preserve">4.74812269210815</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67184782028198</t>
+    <t xml:space="preserve">4.67184734344482</t>
   </si>
   <si>
     <t xml:space="preserve">4.53836631774902</t>
@@ -1076,31 +1073,31 @@
     <t xml:space="preserve">4.65277910232544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57650327682495</t>
+    <t xml:space="preserve">4.57650375366211</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72905397415161</t>
+    <t xml:space="preserve">4.72905349731445</t>
   </si>
   <si>
     <t xml:space="preserve">4.86253499984741</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91020727157593</t>
+    <t xml:space="preserve">4.91020679473877</t>
   </si>
   <si>
     <t xml:space="preserve">4.95787858963013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6337103843689</t>
+    <t xml:space="preserve">4.63370990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6146411895752</t>
+    <t xml:space="preserve">4.61464166641235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59557294845581</t>
+    <t xml:space="preserve">4.59557247161865</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55743551254272</t>
+    <t xml:space="preserve">4.55743503570557</t>
   </si>
   <si>
     <t xml:space="preserve">4.74882841110229</t>
@@ -23759,7 +23756,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G847" t="s">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -23785,7 +23782,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G848" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -23811,7 +23808,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G849" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -23863,7 +23860,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G851" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -23889,7 +23886,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G852" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -23915,7 +23912,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G853" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -23941,7 +23938,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G854" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -23967,7 +23964,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G855" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -23993,7 +23990,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G856" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24019,7 +24016,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G857" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -24045,7 +24042,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G858" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -24071,7 +24068,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G859" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -24097,7 +24094,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G860" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -24123,7 +24120,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G861" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -24175,7 +24172,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G863" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -24227,7 +24224,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G865" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -24253,7 +24250,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G866" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -24305,7 +24302,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G868" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -24331,7 +24328,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G869" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -24357,7 +24354,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G870" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -24383,7 +24380,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G871" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -24409,7 +24406,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G872" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -24435,7 +24432,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G873" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -24487,7 +24484,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G875" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -24591,7 +24588,7 @@
         <v>4</v>
       </c>
       <c r="G879" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -24617,7 +24614,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G880" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -24695,7 +24692,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G883" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -24799,7 +24796,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G887" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -24825,7 +24822,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G888" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -24929,7 +24926,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G892" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -24981,7 +24978,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G894" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -25007,7 +25004,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G895" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -25033,7 +25030,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G896" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -25059,7 +25056,7 @@
         <v>4</v>
       </c>
       <c r="G897" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -25137,7 +25134,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G900" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -25163,7 +25160,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G901" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -25189,7 +25186,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G902" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -25241,7 +25238,7 @@
         <v>4</v>
       </c>
       <c r="G904" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -25267,7 +25264,7 @@
         <v>4</v>
       </c>
       <c r="G905" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -25319,7 +25316,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G907" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -25345,7 +25342,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G908" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -25371,7 +25368,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G909" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -25397,7 +25394,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G910" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -25423,7 +25420,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G911" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -25475,7 +25472,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G913" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -25501,7 +25498,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G914" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -25631,7 +25628,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G919" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -25709,7 +25706,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G922" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -25735,7 +25732,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G923" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -25761,7 +25758,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G924" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -25787,7 +25784,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G925" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -25813,7 +25810,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G926" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -25839,7 +25836,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G927" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -25865,7 +25862,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G928" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -25891,7 +25888,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G929" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -25917,7 +25914,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G930" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -25943,7 +25940,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G931" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -25969,7 +25966,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G932" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -25995,7 +25992,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G933" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26021,7 +26018,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G934" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26047,7 +26044,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G935" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26073,7 +26070,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G936" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26099,7 +26096,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G937" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -26151,7 +26148,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G939" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26177,7 +26174,7 @@
         <v>4</v>
       </c>
       <c r="G940" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -26203,7 +26200,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G941" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -26229,7 +26226,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G942" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -26255,7 +26252,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G943" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -26281,7 +26278,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G944" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -26307,7 +26304,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G945" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -26333,7 +26330,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G946" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -26359,7 +26356,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G947" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -26437,7 +26434,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G950" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26489,7 +26486,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G952" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26515,7 +26512,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G953" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26541,7 +26538,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G954" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26567,7 +26564,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G955" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26593,7 +26590,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G956" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26619,7 +26616,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G957" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26645,7 +26642,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G958" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -26671,7 +26668,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G959" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -26697,7 +26694,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G960" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -26723,7 +26720,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G961" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -26749,7 +26746,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G962" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -26775,7 +26772,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G963" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -26801,7 +26798,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G964" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -26827,7 +26824,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G965" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -26853,7 +26850,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G966" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -26879,7 +26876,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G967" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -26905,7 +26902,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G968" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -26931,7 +26928,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G969" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -26957,7 +26954,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G970" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -26983,7 +26980,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G971" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27009,7 +27006,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G972" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27035,7 +27032,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G973" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27061,7 +27058,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G974" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27087,7 +27084,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G975" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -27113,7 +27110,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G976" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27139,7 +27136,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G977" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27165,7 +27162,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G978" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -27191,7 +27188,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G979" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27217,7 +27214,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G980" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27243,7 +27240,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G981" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27269,7 +27266,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G982" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -27295,7 +27292,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G983" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -27321,7 +27318,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G984" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27347,7 +27344,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G985" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -27373,7 +27370,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G986" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -27399,7 +27396,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G987" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -27425,7 +27422,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G988" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -27451,7 +27448,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G989" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -27477,7 +27474,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G990" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -27503,7 +27500,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G991" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -27529,7 +27526,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G992" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -27555,7 +27552,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G993" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -27581,7 +27578,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G994" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -27607,7 +27604,7 @@
         <v>4.5</v>
       </c>
       <c r="G995" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -27633,7 +27630,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G996" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -27659,7 +27656,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G997" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -27685,7 +27682,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G998" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -27711,7 +27708,7 @@
         <v>4.5</v>
       </c>
       <c r="G999" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -27737,7 +27734,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1000" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -27763,7 +27760,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1001" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -27789,7 +27786,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1002" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -27815,7 +27812,7 @@
         <v>4.5</v>
       </c>
       <c r="G1003" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -27841,7 +27838,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1004" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -27867,7 +27864,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1005" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -27893,7 +27890,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1006" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -27919,7 +27916,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1007" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -27945,7 +27942,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1008" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -27971,7 +27968,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1009" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -27997,7 +27994,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1010" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -28023,7 +28020,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1011" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28049,7 +28046,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1012" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28075,7 +28072,7 @@
         <v>4.75</v>
       </c>
       <c r="G1013" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28101,7 +28098,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1014" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28127,7 +28124,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1015" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -28153,7 +28150,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1016" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -28179,7 +28176,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1017" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -28205,7 +28202,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1018" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -28231,7 +28228,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1019" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -28257,7 +28254,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1020" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28283,7 +28280,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1021" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28309,7 +28306,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1022" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -28335,7 +28332,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1023" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -28361,7 +28358,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1024" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28387,7 +28384,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1025" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28413,7 +28410,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1026" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28439,7 +28436,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1027" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28465,7 +28462,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1028" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28491,7 +28488,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1029" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28517,7 +28514,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1030" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28543,7 +28540,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1031" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28569,7 +28566,7 @@
         <v>4.5</v>
       </c>
       <c r="G1032" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28595,7 +28592,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1033" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28621,7 +28618,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1034" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28647,7 +28644,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1035" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -28673,7 +28670,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1036" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -28699,7 +28696,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1037" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -28725,7 +28722,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1038" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -28751,7 +28748,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1039" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -28777,7 +28774,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1040" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -28803,7 +28800,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1041" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -28829,7 +28826,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1042" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -28855,7 +28852,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1043" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -28881,7 +28878,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1044" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -28907,7 +28904,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1045" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -28933,7 +28930,7 @@
         <v>4.25</v>
       </c>
       <c r="G1046" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -28959,7 +28956,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1047" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -28985,7 +28982,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1048" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29011,7 +29008,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1049" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29037,7 +29034,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1050" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29063,7 +29060,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1051" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29089,7 +29086,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1052" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -29115,7 +29112,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1053" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29141,7 +29138,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1054" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29167,7 +29164,7 @@
         <v>5</v>
       </c>
       <c r="G1055" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29193,7 +29190,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1056" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29219,7 +29216,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29245,7 +29242,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1058" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29271,7 +29268,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1059" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29297,7 +29294,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1060" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29323,7 +29320,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1061" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29349,7 +29346,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1062" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29375,7 +29372,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1063" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29401,7 +29398,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1064" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29427,7 +29424,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1065" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29453,7 +29450,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1066" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29479,7 +29476,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1067" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29505,7 +29502,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1068" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29531,7 +29528,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1069" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29557,7 +29554,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1070" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29583,7 +29580,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1071" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -29609,7 +29606,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1072" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -29635,7 +29632,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1073" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -29661,7 +29658,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1074" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -29687,7 +29684,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1075" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -29713,7 +29710,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1076" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -29739,7 +29736,7 @@
         <v>5.25</v>
       </c>
       <c r="G1077" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -29765,7 +29762,7 @@
         <v>5.25</v>
       </c>
       <c r="G1078" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -29791,7 +29788,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1079" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -29817,7 +29814,7 @@
         <v>5</v>
       </c>
       <c r="G1080" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -29843,7 +29840,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1081" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -29869,7 +29866,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1082" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -29895,7 +29892,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1083" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -29921,7 +29918,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1084" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -29947,7 +29944,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1085" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -29973,7 +29970,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1086" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -29999,7 +29996,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1087" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30025,7 +30022,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1088" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30051,7 +30048,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1089" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -30077,7 +30074,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1090" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30103,7 +30100,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1091" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30129,7 +30126,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1092" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30155,7 +30152,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1093" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30181,7 +30178,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1094" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -30207,7 +30204,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1095" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -30233,7 +30230,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1096" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -30259,7 +30256,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1097" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -30285,7 +30282,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1098" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -30311,7 +30308,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1099" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -30337,7 +30334,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1100" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -30363,7 +30360,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1101" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -30389,7 +30386,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1102" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -30415,7 +30412,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1103" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -30441,7 +30438,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1104" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -30467,7 +30464,7 @@
         <v>5.25</v>
       </c>
       <c r="G1105" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -30493,7 +30490,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1106" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30519,7 +30516,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1107" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30545,7 +30542,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1108" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -30571,7 +30568,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1109" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -30597,7 +30594,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1110" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -30623,7 +30620,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1111" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -30649,7 +30646,7 @@
         <v>6</v>
       </c>
       <c r="G1112" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -30675,7 +30672,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1113" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -30701,7 +30698,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1114" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -30727,7 +30724,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -30753,7 +30750,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1116" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -30779,7 +30776,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1117" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -30805,7 +30802,7 @@
         <v>5.5</v>
       </c>
       <c r="G1118" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -30831,7 +30828,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1119" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -30857,7 +30854,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1120" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -30883,7 +30880,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1121" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -30909,7 +30906,7 @@
         <v>5.5</v>
       </c>
       <c r="G1122" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -30935,7 +30932,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1123" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -30961,7 +30958,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1124" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -30987,7 +30984,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1125" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31013,7 +31010,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1126" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31039,7 +31036,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1127" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31065,7 +31062,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1128" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31091,7 +31088,7 @@
         <v>5.5</v>
       </c>
       <c r="G1129" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31117,7 +31114,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1130" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31143,7 +31140,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1131" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31169,7 +31166,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1132" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31195,7 +31192,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1133" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31221,7 +31218,7 @@
         <v>5.5</v>
       </c>
       <c r="G1134" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31247,7 +31244,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1135" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31273,7 +31270,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1136" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31299,7 +31296,7 @@
         <v>5.5</v>
       </c>
       <c r="G1137" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31325,7 +31322,7 @@
         <v>5.5</v>
       </c>
       <c r="G1138" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31351,7 +31348,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1139" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31377,7 +31374,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1140" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31403,7 +31400,7 @@
         <v>5.25</v>
       </c>
       <c r="G1141" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31429,7 +31426,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1142" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31455,7 +31452,7 @@
         <v>5.25</v>
       </c>
       <c r="G1143" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31481,7 +31478,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1144" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31507,7 +31504,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1145" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31533,7 +31530,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1146" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31559,7 +31556,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1147" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31585,7 +31582,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1148" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31611,7 +31608,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1149" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -31637,7 +31634,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1150" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -31663,7 +31660,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1151" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -31689,7 +31686,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1152" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -31715,7 +31712,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1153" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -31741,7 +31738,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1154" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -31767,7 +31764,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1155" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -31793,7 +31790,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1156" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -31819,7 +31816,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1157" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -31845,7 +31842,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1158" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -31871,7 +31868,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1159" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -31897,7 +31894,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1160" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -31923,7 +31920,7 @@
         <v>5.25</v>
       </c>
       <c r="G1161" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -31949,7 +31946,7 @@
         <v>5.25</v>
       </c>
       <c r="G1162" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -31975,7 +31972,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1163" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32001,7 +31998,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1164" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32027,7 +32024,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1165" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32053,7 +32050,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1166" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -32079,7 +32076,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1167" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -32105,7 +32102,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1168" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -32131,7 +32128,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1169" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -32157,7 +32154,7 @@
         <v>5</v>
       </c>
       <c r="G1170" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -32183,7 +32180,7 @@
         <v>5</v>
       </c>
       <c r="G1171" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -32209,7 +32206,7 @@
         <v>5</v>
       </c>
       <c r="G1172" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -32235,7 +32232,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1173" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -32261,7 +32258,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1174" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -32287,7 +32284,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1175" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -32313,7 +32310,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1176" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -32339,7 +32336,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1177" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -32365,7 +32362,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1178" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -32391,7 +32388,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1179" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -32417,7 +32414,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1180" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -32443,7 +32440,7 @@
         <v>5.25</v>
       </c>
       <c r="G1181" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -32469,7 +32466,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1182" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -32495,7 +32492,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1183" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -32521,7 +32518,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1184" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -32547,7 +32544,7 @@
         <v>5.25</v>
       </c>
       <c r="G1185" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -32573,7 +32570,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1186" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -32599,7 +32596,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1187" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -32625,7 +32622,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1188" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -32651,7 +32648,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1189" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -32677,7 +32674,7 @@
         <v>5</v>
       </c>
       <c r="G1190" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -32703,7 +32700,7 @@
         <v>5</v>
       </c>
       <c r="G1191" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -32729,7 +32726,7 @@
         <v>5</v>
       </c>
       <c r="G1192" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -32755,7 +32752,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1193" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -32781,7 +32778,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1194" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -32807,7 +32804,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1195" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -32833,7 +32830,7 @@
         <v>5</v>
       </c>
       <c r="G1196" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -32859,7 +32856,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1197" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -32885,7 +32882,7 @@
         <v>5</v>
       </c>
       <c r="G1198" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -32911,7 +32908,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1199" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -32937,7 +32934,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1200" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -32963,7 +32960,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1201" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -32989,7 +32986,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1202" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33015,7 +33012,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1203" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33041,7 +33038,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1204" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -33067,7 +33064,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1205" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -33093,7 +33090,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1206" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -33119,7 +33116,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1207" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -33145,7 +33142,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1208" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -33171,7 +33168,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1209" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -33197,7 +33194,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1210" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -33223,7 +33220,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1211" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -33249,7 +33246,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1212" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -33275,7 +33272,7 @@
         <v>5</v>
       </c>
       <c r="G1213" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -33301,7 +33298,7 @@
         <v>5</v>
       </c>
       <c r="G1214" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -33327,7 +33324,7 @@
         <v>5</v>
       </c>
       <c r="G1215" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -33353,7 +33350,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1216" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -33379,7 +33376,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1217" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -33405,7 +33402,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1218" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -33431,7 +33428,7 @@
         <v>5</v>
       </c>
       <c r="G1219" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -33457,7 +33454,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1220" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -33483,7 +33480,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1221" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -33509,7 +33506,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1222" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -33535,7 +33532,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1223" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -33561,7 +33558,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1224" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -33587,7 +33584,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1225" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -33613,7 +33610,7 @@
         <v>5</v>
       </c>
       <c r="G1226" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -33639,7 +33636,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1227" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -33665,7 +33662,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1228" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -33691,7 +33688,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1229" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -33717,7 +33714,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1230" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -33743,7 +33740,7 @@
         <v>5</v>
       </c>
       <c r="G1231" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -33769,7 +33766,7 @@
         <v>5</v>
       </c>
       <c r="G1232" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -33795,7 +33792,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1233" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -33821,7 +33818,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1234" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -33847,7 +33844,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1235" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -33873,7 +33870,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1236" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -33899,7 +33896,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1237" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -33925,7 +33922,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1238" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -33951,7 +33948,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1239" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -33977,7 +33974,7 @@
         <v>5</v>
       </c>
       <c r="G1240" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -34003,7 +34000,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1241" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34029,7 +34026,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1242" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -34055,7 +34052,7 @@
         <v>5</v>
       </c>
       <c r="G1243" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -34081,7 +34078,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1244" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -34107,7 +34104,7 @@
         <v>5</v>
       </c>
       <c r="G1245" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34133,7 +34130,7 @@
         <v>5</v>
       </c>
       <c r="G1246" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34159,7 +34156,7 @@
         <v>5</v>
       </c>
       <c r="G1247" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -34185,7 +34182,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1248" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -34211,7 +34208,7 @@
         <v>5</v>
       </c>
       <c r="G1249" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -34237,7 +34234,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1250" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -34263,7 +34260,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1251" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -34289,7 +34286,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1252" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -34315,7 +34312,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1253" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -34341,7 +34338,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1254" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -34367,7 +34364,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1255" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -34393,7 +34390,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1256" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -34419,7 +34416,7 @@
         <v>5</v>
       </c>
       <c r="G1257" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -34445,7 +34442,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1258" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -34471,7 +34468,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1259" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -34497,7 +34494,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1260" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -34523,7 +34520,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1261" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -34549,7 +34546,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1262" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -34575,7 +34572,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1263" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -34601,7 +34598,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1264" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -34627,7 +34624,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1265" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -34653,7 +34650,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1266" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -34679,7 +34676,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1267" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -34705,7 +34702,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1268" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -34731,7 +34728,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1269" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -34757,7 +34754,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1270" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -34783,7 +34780,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1271" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -34809,7 +34806,7 @@
         <v>5</v>
       </c>
       <c r="G1272" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -34835,7 +34832,7 @@
         <v>5</v>
       </c>
       <c r="G1273" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -34861,7 +34858,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1274" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -34887,7 +34884,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1275" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -34913,7 +34910,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1276" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -34939,7 +34936,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1277" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -34965,7 +34962,7 @@
         <v>5</v>
       </c>
       <c r="G1278" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -34991,7 +34988,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1279" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35017,7 +35014,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1280" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -35043,7 +35040,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1281" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -35069,7 +35066,7 @@
         <v>5</v>
       </c>
       <c r="G1282" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -35095,7 +35092,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1283" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -35121,7 +35118,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1284" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -35147,7 +35144,7 @@
         <v>5</v>
       </c>
       <c r="G1285" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -35173,7 +35170,7 @@
         <v>5</v>
       </c>
       <c r="G1286" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -35199,7 +35196,7 @@
         <v>5</v>
       </c>
       <c r="G1287" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -35225,7 +35222,7 @@
         <v>5</v>
       </c>
       <c r="G1288" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -35251,7 +35248,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1289" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -35277,7 +35274,7 @@
         <v>5</v>
       </c>
       <c r="G1290" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35303,7 +35300,7 @@
         <v>5</v>
       </c>
       <c r="G1291" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35329,7 +35326,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1292" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35355,7 +35352,7 @@
         <v>5</v>
       </c>
       <c r="G1293" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35381,7 +35378,7 @@
         <v>5</v>
       </c>
       <c r="G1294" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35407,7 +35404,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1295" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35433,7 +35430,7 @@
         <v>5</v>
       </c>
       <c r="G1296" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35459,7 +35456,7 @@
         <v>5</v>
       </c>
       <c r="G1297" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -35485,7 +35482,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1298" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35511,7 +35508,7 @@
         <v>5</v>
       </c>
       <c r="G1299" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35537,7 +35534,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1300" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35563,7 +35560,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1301" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -35589,7 +35586,7 @@
         <v>5</v>
       </c>
       <c r="G1302" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35615,7 +35612,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1303" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35641,7 +35638,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1304" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -35667,7 +35664,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1305" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -35693,7 +35690,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1306" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -35719,7 +35716,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1307" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -35745,7 +35742,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1308" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -35771,7 +35768,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1309" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -35797,7 +35794,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1310" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -35823,7 +35820,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1311" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -35849,7 +35846,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1312" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -35875,7 +35872,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1313" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -35901,7 +35898,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1314" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -35927,7 +35924,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1315" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -35953,7 +35950,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1316" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -35979